--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1347" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B1B6B24-7863-45DB-A56C-623DD9BC3C25}"/>
+  <xr:revisionPtr revIDLastSave="1379" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58D2120B-7E06-43A0-ACD2-C4B78EC94ABB}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="2" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
+    <workbookView xWindow="5420" yWindow="5420" windowWidth="28800" windowHeight="15290" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Assessments" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </externalReferences>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId6"/>
+    <pivotCache cacheId="2" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1292,7 +1292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1421,38 +1421,11 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="118">
+  <dxfs count="105">
     <dxf>
       <fill>
         <patternFill>
@@ -1516,220 +1489,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
       <font>
@@ -2956,6 +2715,31 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
           <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
@@ -3343,6 +3127,74 @@
         <name val="Calibri (Body)"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -3827,9 +3679,9 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -9222,7 +9074,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B70" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="34">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -9671,58 +9523,58 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}" name="Table1" displayName="Table1" ref="A1:AL177" totalsRowShown="0" headerRowDxfId="98" dataDxfId="96" headerRowBorderDxfId="97" tableBorderDxfId="95" totalsRowBorderDxfId="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}" name="Table1" displayName="Table1" ref="A1:AL177" totalsRowShown="0" headerRowDxfId="85" dataDxfId="83" headerRowBorderDxfId="84" tableBorderDxfId="82" totalsRowBorderDxfId="81">
   <autoFilter ref="A1:AL177" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AI148">
     <sortCondition ref="A1:A148"/>
   </sortState>
   <tableColumns count="38">
-    <tableColumn id="1" xr3:uid="{7078548A-F011-4851-AB36-1F04238FA2FE}" name="Module Code" dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{D2290F36-B8B3-427A-AEFE-45FD22901411}" name="Module Title" dataDxfId="92"/>
-    <tableColumn id="3" xr3:uid="{31165455-2AA3-4532-A0A0-C942837C0F79}" name="CA type" dataDxfId="91"/>
-    <tableColumn id="33" xr3:uid="{B83E0E3E-2B28-42F1-BC64-5D7177EC4229}" name="CA Weight" dataDxfId="23">
+    <tableColumn id="1" xr3:uid="{7078548A-F011-4851-AB36-1F04238FA2FE}" name="Module Code" dataDxfId="80"/>
+    <tableColumn id="2" xr3:uid="{D2290F36-B8B3-427A-AEFE-45FD22901411}" name="Module Title" dataDxfId="79"/>
+    <tableColumn id="3" xr3:uid="{31165455-2AA3-4532-A0A0-C942837C0F79}" name="CA type" dataDxfId="78"/>
+    <tableColumn id="33" xr3:uid="{B83E0E3E-2B28-42F1-BC64-5D7177EC4229}" name="CA Weight" dataDxfId="77">
       <calculatedColumnFormula>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{AEA2048C-138D-450A-BE52-3FCBDE03C67D}" name="Credits" dataDxfId="22">
+    <tableColumn id="34" xr3:uid="{AEA2048C-138D-450A-BE52-3FCBDE03C67D}" name="Credits" dataDxfId="76">
       <calculatedColumnFormula>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{82DD5B5B-C808-4E6E-849C-7A03DC6D0B69}" name="Description" dataDxfId="90"/>
-    <tableColumn id="36" xr3:uid="{A7BF30F6-C808-4B8F-B3FF-9FAF20E2145A}" name="Summative" dataDxfId="89"/>
-    <tableColumn id="37" xr3:uid="{68E504F9-116C-43AB-BCC6-3BB48B0860D2}" name="Day of Week" dataDxfId="21"/>
-    <tableColumn id="16" xr3:uid="{E6637FEB-7F23-45F0-99D2-96D20DD2DAEF}" name="Duration" dataDxfId="88"/>
-    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="87">
+    <tableColumn id="30" xr3:uid="{82DD5B5B-C808-4E6E-849C-7A03DC6D0B69}" name="Description" dataDxfId="75"/>
+    <tableColumn id="36" xr3:uid="{A7BF30F6-C808-4B8F-B3FF-9FAF20E2145A}" name="Summative" dataDxfId="74"/>
+    <tableColumn id="37" xr3:uid="{68E504F9-116C-43AB-BCC6-3BB48B0860D2}" name="Day of Week" dataDxfId="73"/>
+    <tableColumn id="16" xr3:uid="{E6637FEB-7F23-45F0-99D2-96D20DD2DAEF}" name="Duration" dataDxfId="72"/>
+    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="71">
       <calculatedColumnFormula>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="86"/>
-    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="85"/>
-    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="84"/>
-    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="83"/>
-    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="82"/>
-    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="81"/>
-    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="80"/>
-    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="79"/>
-    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="78"/>
-    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="77"/>
-    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="76"/>
-    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="75"/>
-    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="74"/>
-    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="73"/>
-    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="72"/>
-    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="71"/>
-    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="70"/>
-    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="69"/>
-    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="68"/>
-    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="67"/>
-    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="66"/>
-    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="65"/>
-    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="64"/>
-    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="63"/>
-    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="62"/>
-    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="20"/>
-    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="61">
+    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="70"/>
+    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="69"/>
+    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="68"/>
+    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="67"/>
+    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="66"/>
+    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="65"/>
+    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="64"/>
+    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="63"/>
+    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="62"/>
+    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="61"/>
+    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="60"/>
+    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="59"/>
+    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="58"/>
+    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="57"/>
+    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="56"/>
+    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="55"/>
+    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="54"/>
+    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="53"/>
+    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="52"/>
+    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="51"/>
+    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="50"/>
+    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="49"/>
+    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="48"/>
+    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="47"/>
+    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="46"/>
+    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="45"/>
+    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="44">
       <calculatedColumnFormula>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="60">
+    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="43">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9731,49 +9583,49 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41" tableBorderDxfId="39" totalsRowBorderDxfId="38">
   <autoFilter ref="A1:AE64" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD64">
     <sortCondition ref="A1:A132"/>
   </sortState>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="52"/>
-    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="51">
+    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="35"/>
+    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="34">
       <calculatedColumnFormula>INDEX(Table2[Credits],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="50">
+    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="33">
       <calculatedColumnFormula>INDEX(Table2[Semester],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="49">
+    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="32">
       <calculatedColumnFormula>INDEX(Table2[Contact Time],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="43"/>
-    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="42"/>
-    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="41"/>
-    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="40"/>
-    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="39"/>
-    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="38"/>
-    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="37"/>
-    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="36"/>
-    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="35"/>
-    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="34"/>
-    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="33"/>
-    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="32"/>
-    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="31"/>
-    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="30"/>
-    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="29"/>
-    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="28"/>
-    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="27"/>
-    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="26"/>
-    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="25"/>
-    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="24">
+    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="25"/>
+    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="24"/>
+    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="22"/>
+    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="20"/>
+    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="19"/>
+    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="18"/>
+    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="17"/>
+    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="16"/>
+    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="15"/>
+    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="14"/>
+    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="13"/>
+    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="12"/>
+    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="11"/>
+    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="10"/>
+    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="9"/>
+    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="8"/>
+    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="7">
       <calculatedColumnFormula>SUM(Table14[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9782,34 +9634,34 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}" name="Table2" displayName="Table2" ref="A1:T93" totalsRowShown="0" headerRowDxfId="117" dataDxfId="115" headerRowBorderDxfId="116">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}" name="Table2" displayName="Table2" ref="A1:T93" totalsRowShown="0" headerRowDxfId="104" dataDxfId="102" headerRowBorderDxfId="103">
   <autoFilter ref="A1:T93" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B61">
     <sortCondition ref="A1:A61"/>
   </sortState>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{A36A2B86-0F30-4188-9ECD-AE5BC71A59F4}" name="Module Code" dataDxfId="114"/>
-    <tableColumn id="2" xr3:uid="{D3F20037-EF35-4207-A530-484E1EB45719}" name="Module Title" dataDxfId="113"/>
-    <tableColumn id="9" xr3:uid="{40C22022-10B9-411F-9B76-B89140ABFFB2}" name="Alternative Module Code" dataDxfId="112"/>
-    <tableColumn id="13" xr3:uid="{CB12E405-1802-457C-AF17-F1B9CB3BBF13}" name="Source" dataDxfId="111"/>
-    <tableColumn id="8" xr3:uid="{EA737976-1AA7-49B6-8752-A388621554F4}" name="Semester" dataDxfId="110"/>
-    <tableColumn id="6" xr3:uid="{16DFC84F-5858-467D-B447-49992D721E4B}" name="Level" dataDxfId="109"/>
-    <tableColumn id="5" xr3:uid="{A17BC4BA-A3CB-442D-9BDC-D3B41B98B389}" name="Credits" dataDxfId="108"/>
-    <tableColumn id="19" xr3:uid="{98846C13-E462-4CFF-858E-AF75931B6712}" name="AllUG" dataDxfId="107"/>
-    <tableColumn id="3" xr3:uid="{7E25B4F4-1A7D-48D9-AAA2-AF5C97240797}" name="Physics" dataDxfId="106"/>
+    <tableColumn id="1" xr3:uid="{A36A2B86-0F30-4188-9ECD-AE5BC71A59F4}" name="Module Code" dataDxfId="101"/>
+    <tableColumn id="2" xr3:uid="{D3F20037-EF35-4207-A530-484E1EB45719}" name="Module Title" dataDxfId="100"/>
+    <tableColumn id="9" xr3:uid="{40C22022-10B9-411F-9B76-B89140ABFFB2}" name="Alternative Module Code" dataDxfId="99"/>
+    <tableColumn id="13" xr3:uid="{CB12E405-1802-457C-AF17-F1B9CB3BBF13}" name="Source" dataDxfId="98"/>
+    <tableColumn id="8" xr3:uid="{EA737976-1AA7-49B6-8752-A388621554F4}" name="Semester" dataDxfId="97"/>
+    <tableColumn id="6" xr3:uid="{16DFC84F-5858-467D-B447-49992D721E4B}" name="Level" dataDxfId="96"/>
+    <tableColumn id="5" xr3:uid="{A17BC4BA-A3CB-442D-9BDC-D3B41B98B389}" name="Credits" dataDxfId="95"/>
+    <tableColumn id="19" xr3:uid="{98846C13-E462-4CFF-858E-AF75931B6712}" name="AllUG" dataDxfId="94"/>
+    <tableColumn id="3" xr3:uid="{7E25B4F4-1A7D-48D9-AAA2-AF5C97240797}" name="Physics" dataDxfId="93"/>
     <tableColumn id="17" xr3:uid="{AA3AE96F-2651-49D7-89AD-BA94806438AE}" name="PhysAstro"/>
-    <tableColumn id="4" xr3:uid="{9C7DD469-E550-411F-8467-246A1543FB38}" name="Astro" dataDxfId="105"/>
-    <tableColumn id="7" xr3:uid="{3C5D3AEB-487E-4678-A42F-BE4BA4D0E9AA}" name="MedPhys" dataDxfId="104"/>
+    <tableColumn id="4" xr3:uid="{9C7DD469-E550-411F-8467-246A1543FB38}" name="Astro" dataDxfId="92"/>
+    <tableColumn id="7" xr3:uid="{3C5D3AEB-487E-4678-A42F-BE4BA4D0E9AA}" name="MedPhys" dataDxfId="91"/>
     <tableColumn id="20" xr3:uid="{C3673B06-C0A2-44F6-8978-F392282CECF8}" name="AllPG"/>
-    <tableColumn id="14" xr3:uid="{AE552873-9B31-41A6-B73C-D052477CA74C}" name="MScPhysics" dataDxfId="103"/>
-    <tableColumn id="15" xr3:uid="{8F51CE76-3A29-487A-A13C-FB63C79CF3E6}" name="MScAstro" dataDxfId="102"/>
+    <tableColumn id="14" xr3:uid="{AE552873-9B31-41A6-B73C-D052477CA74C}" name="MScPhysics" dataDxfId="90"/>
+    <tableColumn id="15" xr3:uid="{8F51CE76-3A29-487A-A13C-FB63C79CF3E6}" name="MScAstro" dataDxfId="89"/>
     <tableColumn id="18" xr3:uid="{10668F71-1EDF-482E-86A5-46E1F3C15120}" name="MScCSPhysics"/>
     <tableColumn id="16" xr3:uid="{DB790F5F-BEF0-41CE-A68A-1AA9DF83D66B}" name="Contact Time"/>
-    <tableColumn id="10" xr3:uid="{60774AFA-B365-4EB5-AAFF-6235868F8C97}" name="Exam Weight (%)" dataDxfId="101"/>
-    <tableColumn id="12" xr3:uid="{537B7C75-E9C0-42F2-9F3C-6E960AB2D257}" name="CA weight" dataDxfId="100">
+    <tableColumn id="10" xr3:uid="{60774AFA-B365-4EB5-AAFF-6235868F8C97}" name="Exam Weight (%)" dataDxfId="88"/>
+    <tableColumn id="12" xr3:uid="{537B7C75-E9C0-42F2-9F3C-6E960AB2D257}" name="CA weight" dataDxfId="87">
       <calculatedColumnFormula>100-Table2[[#This Row],[Exam Weight (%)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{75DA2527-5A08-4ECE-B4E4-752A8F8BF059}" name="CA Check" dataDxfId="99">
+    <tableColumn id="11" xr3:uid="{75DA2527-5A08-4ECE-B4E4-752A8F8BF059}" name="CA Check" dataDxfId="86">
       <calculatedColumnFormula>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10497,14 +10349,14 @@
       <c r="B5" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C5" s="48" t="s">
+      <c r="C5" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D5" s="49">
+      <c r="D5" s="29">
         <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>40</v>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="29">
         <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>20</v>
       </c>
@@ -10517,14 +10369,14 @@
       <c r="H5" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="11">
         <v>1</v>
       </c>
-      <c r="J5" s="50">
+      <c r="J5" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>2</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="11">
         <v>0.5</v>
       </c>
       <c r="L5" s="18"/>
@@ -10554,11 +10406,11 @@
       <c r="AH5" s="20"/>
       <c r="AI5" s="20"/>
       <c r="AJ5" s="20"/>
-      <c r="AK5" s="51">
+      <c r="AK5" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="AL5" s="51">
+      <c r="AL5" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>0.5</v>
       </c>
@@ -11091,11 +10943,11 @@
       <c r="C12" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="49">
+      <c r="D12" s="29">
         <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E12" s="49">
+      <c r="E12" s="29">
         <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>20</v>
       </c>
@@ -11108,10 +10960,10 @@
       <c r="H12" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="I12" s="48">
+      <c r="I12" s="11">
         <v>3</v>
       </c>
-      <c r="J12" s="50">
+      <c r="J12" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>14.8</v>
       </c>
@@ -11145,11 +10997,11 @@
       </c>
       <c r="AI12" s="20"/>
       <c r="AJ12" s="20"/>
-      <c r="AK12" s="51">
+      <c r="AK12" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.37</v>
       </c>
-      <c r="AL12" s="51">
+      <c r="AL12" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>29.6</v>
       </c>
@@ -11346,15 +11198,15 @@
       <c r="C15" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="49">
+      <c r="D15" s="29">
         <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="29">
         <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F15" s="48" t="s">
+      <c r="F15" s="11" t="s">
         <v>355</v>
       </c>
       <c r="G15" s="11" t="s">
@@ -11363,14 +11215,14 @@
       <c r="H15" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="I15" s="48">
+      <c r="I15" s="11">
         <v>3</v>
       </c>
-      <c r="J15" s="50">
+      <c r="J15" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>8</v>
-      </c>
-      <c r="K15" s="48">
+        <v>0</v>
+      </c>
+      <c r="K15" s="11">
         <v>5</v>
       </c>
       <c r="L15" s="18"/>
@@ -11391,20 +11243,22 @@
       <c r="AA15" s="20"/>
       <c r="AB15" s="20"/>
       <c r="AC15" s="20"/>
-      <c r="AD15" s="20"/>
+      <c r="AD15" s="20">
+        <v>0.2</v>
+      </c>
       <c r="AE15" s="20">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="AF15" s="20"/>
       <c r="AG15" s="20"/>
       <c r="AH15" s="20"/>
       <c r="AI15" s="20"/>
       <c r="AJ15" s="20"/>
-      <c r="AK15" s="51">
+      <c r="AK15" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
-      </c>
-      <c r="AL15" s="51">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>5</v>
       </c>
@@ -11595,7 +11449,7 @@
       </c>
       <c r="J18" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K18" s="11"/>
       <c r="L18" s="18"/>
@@ -11615,9 +11469,11 @@
       <c r="Z18" s="20"/>
       <c r="AA18" s="20"/>
       <c r="AB18" s="20">
+        <v>-0.1</v>
+      </c>
+      <c r="AC18" s="20">
         <v>0.1</v>
       </c>
-      <c r="AC18" s="20"/>
       <c r="AD18" s="20"/>
       <c r="AE18" s="20"/>
       <c r="AF18" s="20"/>
@@ -11627,11 +11483,11 @@
       <c r="AJ18" s="20"/>
       <c r="AK18" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AL18" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -11644,15 +11500,15 @@
       <c r="C19" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="49">
+      <c r="D19" s="29">
         <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>30</v>
       </c>
-      <c r="E19" s="49">
+      <c r="E19" s="29">
         <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F19" s="54" t="s">
+      <c r="F19" s="12" t="s">
         <v>357</v>
       </c>
       <c r="G19" s="11" t="s">
@@ -11661,14 +11517,14 @@
       <c r="H19" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="I19" s="48">
+      <c r="I19" s="11">
         <v>4</v>
       </c>
-      <c r="J19" s="50">
+      <c r="J19" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>4</v>
       </c>
-      <c r="K19" s="48"/>
+      <c r="K19" s="11"/>
       <c r="L19" s="18"/>
       <c r="M19" s="18"/>
       <c r="N19" s="18"/>
@@ -11696,11 +11552,11 @@
       <c r="AH19" s="20"/>
       <c r="AI19" s="20"/>
       <c r="AJ19" s="20"/>
-      <c r="AK19" s="51">
+      <c r="AK19" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
-      <c r="AL19" s="51">
+      <c r="AL19" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>4</v>
       </c>
@@ -12049,7 +11905,7 @@
       </c>
       <c r="J24" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>12</v>
+        <v>3.9999999999999996</v>
       </c>
       <c r="K24" s="11">
         <v>15</v>
@@ -12058,9 +11914,11 @@
       <c r="M24" s="18"/>
       <c r="N24" s="18"/>
       <c r="O24" s="19">
+        <v>-0.15</v>
+      </c>
+      <c r="P24" s="18">
         <v>0.15</v>
       </c>
-      <c r="P24" s="18"/>
       <c r="Q24" s="18"/>
       <c r="R24" s="18"/>
       <c r="S24" s="19"/>
@@ -12085,7 +11943,7 @@
       <c r="AJ24" s="20"/>
       <c r="AK24" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="AL24" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -12207,7 +12065,7 @@
       </c>
       <c r="J26" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K26" s="11">
         <v>0.5</v>
@@ -12219,9 +12077,11 @@
       <c r="P26" s="18"/>
       <c r="Q26" s="18"/>
       <c r="R26" s="18"/>
-      <c r="S26" s="19"/>
+      <c r="S26" s="19">
+        <v>0.2</v>
+      </c>
       <c r="T26" s="18">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="U26" s="18"/>
       <c r="V26" s="18"/>
@@ -12241,7 +12101,7 @@
       <c r="AJ26" s="20"/>
       <c r="AK26" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AL26" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -12715,14 +12575,14 @@
       <c r="B33" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C33" s="48" t="s">
+      <c r="C33" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D33" s="49">
+      <c r="D33" s="29">
         <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E33" s="49">
+      <c r="E33" s="29">
         <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>10</v>
       </c>
@@ -12735,14 +12595,14 @@
       <c r="H33" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="I33" s="48">
+      <c r="I33" s="11">
         <v>1</v>
       </c>
-      <c r="J33" s="50">
+      <c r="J33" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>20</v>
       </c>
-      <c r="K33" s="48">
+      <c r="K33" s="11">
         <v>0.5</v>
       </c>
       <c r="L33" s="18"/>
@@ -12772,11 +12632,11 @@
       <c r="AH33" s="20"/>
       <c r="AI33" s="20"/>
       <c r="AJ33" s="20"/>
-      <c r="AK33" s="51">
+      <c r="AK33" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.5</v>
       </c>
-      <c r="AL33" s="51">
+      <c r="AL33" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>0.5</v>
       </c>
@@ -12813,7 +12673,7 @@
       </c>
       <c r="J34" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>8</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="K34" s="11">
         <v>6</v>
@@ -12829,9 +12689,11 @@
       <c r="R34" s="18"/>
       <c r="S34" s="19"/>
       <c r="T34" s="18">
+        <v>-0.2</v>
+      </c>
+      <c r="U34" s="18">
         <v>0.2</v>
       </c>
-      <c r="U34" s="18"/>
       <c r="V34" s="18"/>
       <c r="W34" s="19"/>
       <c r="X34" s="20"/>
@@ -12849,7 +12711,7 @@
       <c r="AJ34" s="20"/>
       <c r="AK34" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AL34" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -13256,18 +13118,18 @@
       <c r="B40" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C40" s="48" t="s">
+      <c r="C40" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="D40" s="49">
+      <c r="D40" s="29">
         <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>50</v>
       </c>
-      <c r="E40" s="49">
+      <c r="E40" s="29">
         <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F40" s="48" t="s">
+      <c r="F40" s="11" t="s">
         <v>372</v>
       </c>
       <c r="G40" s="11" t="s">
@@ -13276,14 +13138,14 @@
       <c r="H40" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="I40" s="48">
+      <c r="I40" s="11">
         <v>1</v>
       </c>
-      <c r="J40" s="50">
+      <c r="J40" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>6</v>
       </c>
-      <c r="K40" s="48">
+      <c r="K40" s="11">
         <v>3</v>
       </c>
       <c r="L40" s="18"/>
@@ -13313,11 +13175,11 @@
       <c r="AH40" s="20"/>
       <c r="AI40" s="20"/>
       <c r="AJ40" s="20"/>
-      <c r="AK40" s="51">
+      <c r="AK40" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.15</v>
       </c>
-      <c r="AL40" s="51">
+      <c r="AL40" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>3</v>
       </c>
@@ -14075,11 +13937,11 @@
       <c r="C50" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D50" s="49">
+      <c r="D50" s="29">
         <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E50" s="49">
+      <c r="E50" s="29">
         <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>20</v>
       </c>
@@ -14095,7 +13957,7 @@
       <c r="I50" s="11">
         <v>2</v>
       </c>
-      <c r="J50" s="50">
+      <c r="J50" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>8</v>
       </c>
@@ -14127,11 +13989,11 @@
       <c r="AH50" s="20"/>
       <c r="AI50" s="20"/>
       <c r="AJ50" s="20"/>
-      <c r="AK50" s="51">
+      <c r="AK50" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
-      <c r="AL50" s="51">
+      <c r="AL50" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>8</v>
       </c>
@@ -14146,11 +14008,11 @@
       <c r="C51" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D51" s="49">
+      <c r="D51" s="29">
         <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E51" s="49">
+      <c r="E51" s="29">
         <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>20</v>
       </c>
@@ -14166,7 +14028,7 @@
       <c r="I51" s="11">
         <v>3</v>
       </c>
-      <c r="J51" s="50">
+      <c r="J51" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>16</v>
       </c>
@@ -14200,11 +14062,11 @@
       <c r="AH51" s="20"/>
       <c r="AI51" s="20"/>
       <c r="AJ51" s="20"/>
-      <c r="AK51" s="51">
+      <c r="AK51" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
-      <c r="AL51" s="51">
+      <c r="AL51" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>10</v>
       </c>
@@ -14219,11 +14081,11 @@
       <c r="C52" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D52" s="49">
+      <c r="D52" s="29">
         <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E52" s="49">
+      <c r="E52" s="29">
         <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>20</v>
       </c>
@@ -14239,7 +14101,7 @@
       <c r="I52" s="11">
         <v>6</v>
       </c>
-      <c r="J52" s="50">
+      <c r="J52" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>24</v>
       </c>
@@ -14271,11 +14133,11 @@
       </c>
       <c r="AI52" s="20"/>
       <c r="AJ52" s="20"/>
-      <c r="AK52" s="51">
+      <c r="AK52" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
-      <c r="AL52" s="51">
+      <c r="AL52" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>24</v>
       </c>
@@ -14468,7 +14330,7 @@
       </c>
       <c r="J55" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>4.0000000000000009</v>
+        <v>2</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="18"/>
@@ -14491,9 +14353,11 @@
       </c>
       <c r="AB55" s="20"/>
       <c r="AC55" s="20">
+        <v>-0.1</v>
+      </c>
+      <c r="AD55" s="20">
         <v>0.1</v>
       </c>
-      <c r="AD55" s="20"/>
       <c r="AE55" s="20"/>
       <c r="AF55" s="20"/>
       <c r="AG55" s="20">
@@ -14504,11 +14368,11 @@
       <c r="AJ55" s="20"/>
       <c r="AK55" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.30000000000000004</v>
+        <v>0.2</v>
       </c>
       <c r="AL55" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>12.000000000000004</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:38" ht="28">
@@ -16082,25 +15946,29 @@
       </c>
       <c r="J76" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K76" s="11">
         <v>9</v>
       </c>
       <c r="L76" s="18"/>
       <c r="M76" s="18"/>
-      <c r="N76" s="18"/>
+      <c r="N76" s="18">
+        <v>0.25</v>
+      </c>
       <c r="O76" s="18">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="P76" s="18">
         <v>0.25</v>
       </c>
       <c r="Q76" s="18"/>
       <c r="R76" s="18">
+        <v>-0.25</v>
+      </c>
+      <c r="S76" s="18">
         <v>0.25</v>
       </c>
-      <c r="S76" s="18"/>
       <c r="T76" s="24"/>
       <c r="U76" s="19"/>
       <c r="V76" s="19"/>
@@ -16120,7 +15988,7 @@
       <c r="AJ76" s="20"/>
       <c r="AK76" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="AL76" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -16631,7 +16499,7 @@
       </c>
       <c r="J83" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K83" s="13"/>
       <c r="L83" s="25"/>
@@ -16641,9 +16509,11 @@
       <c r="P83" s="26"/>
       <c r="Q83" s="26"/>
       <c r="R83" s="26">
+        <v>-0.2</v>
+      </c>
+      <c r="S83" s="26">
         <v>0.2</v>
       </c>
-      <c r="S83" s="26"/>
       <c r="T83" s="26"/>
       <c r="U83" s="26"/>
       <c r="V83" s="26"/>
@@ -16663,11 +16533,11 @@
       <c r="AJ83" s="20"/>
       <c r="AK83" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AL83" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:38" ht="28">
@@ -17194,12 +17064,12 @@
       <c r="B91" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C91" s="48"/>
-      <c r="D91" s="49">
+      <c r="C91" s="11"/>
+      <c r="D91" s="29">
         <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E91" s="49">
+      <c r="E91" s="29">
         <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>10</v>
       </c>
@@ -17212,14 +17082,14 @@
       <c r="H91" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="I91" s="48">
+      <c r="I91" s="11">
         <v>4</v>
       </c>
-      <c r="J91" s="50">
+      <c r="J91" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>4</v>
       </c>
-      <c r="K91" s="48"/>
+      <c r="K91" s="11"/>
       <c r="L91" s="18"/>
       <c r="M91" s="18"/>
       <c r="N91" s="18"/>
@@ -17247,11 +17117,11 @@
       <c r="AH91" s="20"/>
       <c r="AI91" s="20"/>
       <c r="AJ91" s="20"/>
-      <c r="AK91" s="51">
+      <c r="AK91" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
-      <c r="AL91" s="51">
+      <c r="AL91" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>4</v>
       </c>
@@ -17565,7 +17435,7 @@
       </c>
     </row>
     <row r="96" spans="1:38">
-      <c r="A96" s="52" t="s">
+      <c r="A96" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B96" s="3" t="s">
@@ -17574,11 +17444,11 @@
       <c r="C96" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D96" s="49">
+      <c r="D96" s="29">
         <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>30</v>
       </c>
-      <c r="E96" s="49">
+      <c r="E96" s="29">
         <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>20</v>
       </c>
@@ -17591,14 +17461,14 @@
       <c r="H96" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="I96" s="48">
+      <c r="I96" s="11">
         <v>3</v>
       </c>
-      <c r="J96" s="50">
+      <c r="J96" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>3.2</v>
       </c>
-      <c r="K96" s="48"/>
+      <c r="K96" s="11"/>
       <c r="L96" s="18"/>
       <c r="M96" s="18"/>
       <c r="N96" s="18"/>
@@ -17626,17 +17496,17 @@
       <c r="AH96" s="20"/>
       <c r="AI96" s="20"/>
       <c r="AJ96" s="20"/>
-      <c r="AK96" s="51">
+      <c r="AK96" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.04</v>
       </c>
-      <c r="AL96" s="51">
+      <c r="AL96" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>3.2</v>
       </c>
     </row>
     <row r="97" spans="1:38" ht="28">
-      <c r="A97" s="52" t="s">
+      <c r="A97" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B97" s="3" t="s">
@@ -17645,11 +17515,11 @@
       <c r="C97" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="D97" s="49">
+      <c r="D97" s="29">
         <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="E97" s="49">
+      <c r="E97" s="29">
         <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>10</v>
       </c>
@@ -17662,14 +17532,14 @@
       <c r="H97" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="I97" s="48">
+      <c r="I97" s="11">
         <v>6</v>
       </c>
-      <c r="J97" s="50">
+      <c r="J97" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>6.4</v>
       </c>
-      <c r="K97" s="48"/>
+      <c r="K97" s="11"/>
       <c r="L97" s="18"/>
       <c r="M97" s="18"/>
       <c r="N97" s="18"/>
@@ -17697,11 +17567,11 @@
       <c r="AH97" s="20"/>
       <c r="AI97" s="20"/>
       <c r="AJ97" s="20"/>
-      <c r="AK97" s="51">
+      <c r="AK97" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.16</v>
       </c>
-      <c r="AL97" s="51">
+      <c r="AL97" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>6.4</v>
       </c>
@@ -18639,11 +18509,11 @@
       <c r="C110" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D110" s="49">
+      <c r="D110" s="29">
         <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E110" s="49">
+      <c r="E110" s="29">
         <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>30</v>
       </c>
@@ -18659,7 +18529,7 @@
       <c r="I110" s="11">
         <v>11</v>
       </c>
-      <c r="J110" s="50">
+      <c r="J110" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>48</v>
       </c>
@@ -18693,11 +18563,11 @@
       </c>
       <c r="AI110" s="20"/>
       <c r="AJ110" s="20"/>
-      <c r="AK110" s="51">
+      <c r="AK110" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.4</v>
       </c>
-      <c r="AL110" s="51">
+      <c r="AL110" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>10</v>
       </c>
@@ -18712,11 +18582,11 @@
       <c r="C111" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D111" s="49">
+      <c r="D111" s="29">
         <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E111" s="49">
+      <c r="E111" s="29">
         <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>30</v>
       </c>
@@ -18732,7 +18602,7 @@
       <c r="I111" s="11">
         <v>6</v>
       </c>
-      <c r="J111" s="50">
+      <c r="J111" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>24</v>
       </c>
@@ -18766,11 +18636,11 @@
       <c r="AH111" s="20"/>
       <c r="AI111" s="20"/>
       <c r="AJ111" s="20"/>
-      <c r="AK111" s="51">
+      <c r="AK111" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
-      <c r="AL111" s="51">
+      <c r="AL111" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>15</v>
       </c>
@@ -18908,7 +18778,7 @@
       </c>
       <c r="J113" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K113" s="11"/>
       <c r="L113" s="18"/>
@@ -18918,9 +18788,11 @@
       <c r="P113" s="18"/>
       <c r="Q113" s="18"/>
       <c r="R113" s="18">
+        <v>-0.2</v>
+      </c>
+      <c r="S113" s="19">
         <v>0.2</v>
       </c>
-      <c r="S113" s="19"/>
       <c r="T113" s="18"/>
       <c r="U113" s="18"/>
       <c r="V113" s="18"/>
@@ -18940,11 +18812,11 @@
       <c r="AJ113" s="20"/>
       <c r="AK113" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AL113" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:38">
@@ -19256,18 +19128,18 @@
       <c r="B118" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C118" s="48" t="s">
+      <c r="C118" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D118" s="49">
+      <c r="D118" s="29">
         <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>25</v>
       </c>
-      <c r="E118" s="49">
+      <c r="E118" s="29">
         <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F118" s="48" t="s">
+      <c r="F118" s="11" t="s">
         <v>206</v>
       </c>
       <c r="G118" s="11" t="s">
@@ -19276,14 +19148,14 @@
       <c r="H118" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="I118" s="48">
+      <c r="I118" s="11">
         <v>6</v>
       </c>
-      <c r="J118" s="50">
+      <c r="J118" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>4.4000000000000004</v>
       </c>
-      <c r="K118" s="48"/>
+      <c r="K118" s="11"/>
       <c r="L118" s="18"/>
       <c r="M118" s="18"/>
       <c r="N118" s="18"/>
@@ -19313,11 +19185,11 @@
       <c r="AH118" s="20"/>
       <c r="AI118" s="20"/>
       <c r="AJ118" s="20"/>
-      <c r="AK118" s="51">
+      <c r="AK118" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.22</v>
       </c>
-      <c r="AL118" s="51">
+      <c r="AL118" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>8.8000000000000007</v>
       </c>
@@ -19414,16 +19286,16 @@
       <c r="B120" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C120" s="48"/>
-      <c r="D120" s="49">
+      <c r="C120" s="11"/>
+      <c r="D120" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E120" s="49">
+      <c r="E120" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F120" s="48" t="s">
+      <c r="F120" s="11" t="s">
         <v>302</v>
       </c>
       <c r="G120" s="11" t="s">
@@ -19432,14 +19304,14 @@
       <c r="H120" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="I120" s="48">
+      <c r="I120" s="11">
         <v>1</v>
       </c>
-      <c r="J120" s="50">
+      <c r="J120" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>4</v>
       </c>
-      <c r="K120" s="48">
+      <c r="K120" s="11">
         <v>0.5</v>
       </c>
       <c r="L120" s="18"/>
@@ -19469,11 +19341,11 @@
       <c r="AH120" s="20"/>
       <c r="AI120" s="20"/>
       <c r="AJ120" s="20"/>
-      <c r="AK120" s="51">
+      <c r="AK120" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
-      <c r="AL120" s="51">
+      <c r="AL120" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>0.5</v>
       </c>
@@ -19510,16 +19382,18 @@
       </c>
       <c r="J121" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K121" s="11"/>
       <c r="L121" s="18"/>
       <c r="M121" s="18"/>
       <c r="N121" s="18"/>
       <c r="O121" s="19"/>
-      <c r="P121" s="18"/>
+      <c r="P121" s="18">
+        <v>0.35</v>
+      </c>
       <c r="Q121" s="18">
-        <v>0.35</v>
+        <v>-0.35</v>
       </c>
       <c r="R121" s="18"/>
       <c r="S121" s="19"/>
@@ -19542,11 +19416,11 @@
       <c r="AJ121" s="20"/>
       <c r="AK121" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="AL121" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:38">
@@ -19914,11 +19788,11 @@
       <c r="AA126" s="20"/>
       <c r="AB126" s="20"/>
       <c r="AC126" s="20"/>
-      <c r="AD126" s="20">
+      <c r="AD126" s="20"/>
+      <c r="AE126" s="20"/>
+      <c r="AF126" s="20">
         <v>0.3</v>
       </c>
-      <c r="AE126" s="20"/>
-      <c r="AF126" s="20"/>
       <c r="AG126" s="20"/>
       <c r="AH126" s="20"/>
       <c r="AI126" s="20"/>
@@ -20680,7 +20554,7 @@
       </c>
       <c r="J136" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>8</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="K136" s="11"/>
       <c r="L136" s="18"/>
@@ -20700,9 +20574,11 @@
       <c r="Z136" s="20"/>
       <c r="AA136" s="20"/>
       <c r="AB136" s="20"/>
-      <c r="AC136" s="20"/>
+      <c r="AC136" s="20">
+        <v>0.2</v>
+      </c>
       <c r="AD136" s="20">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="AE136" s="20"/>
       <c r="AF136" s="20"/>
@@ -20714,11 +20590,11 @@
       <c r="AJ136" s="20"/>
       <c r="AK136" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AL136" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>16</v>
+        <v>5.333333333333333</v>
       </c>
     </row>
     <row r="137" spans="1:38" ht="28">
@@ -21055,7 +20931,7 @@
       </c>
       <c r="J141" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K141" s="11"/>
       <c r="L141" s="18"/>
@@ -21075,10 +20951,12 @@
       <c r="Z141" s="20"/>
       <c r="AA141" s="20"/>
       <c r="AB141" s="20"/>
-      <c r="AC141" s="20"/>
+      <c r="AC141" s="20">
+        <v>0.2</v>
+      </c>
       <c r="AD141" s="20"/>
       <c r="AE141" s="20">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="AF141" s="20"/>
       <c r="AG141" s="20"/>
@@ -21087,11 +20965,11 @@
       <c r="AJ141" s="20"/>
       <c r="AK141" s="27">
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AL141" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:38">
@@ -21660,11 +21538,11 @@
       <c r="C149" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D149" s="49">
+      <c r="D149" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>75</v>
       </c>
-      <c r="E149" s="49">
+      <c r="E149" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>60</v>
       </c>
@@ -21680,7 +21558,7 @@
       <c r="I149" s="11">
         <v>11</v>
       </c>
-      <c r="J149" s="50">
+      <c r="J149" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>48</v>
       </c>
@@ -21718,7 +21596,7 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
-      <c r="AL149" s="51">
+      <c r="AL149" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>10</v>
       </c>
@@ -21733,11 +21611,11 @@
       <c r="C150" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D150" s="49">
+      <c r="D150" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>75</v>
       </c>
-      <c r="E150" s="49">
+      <c r="E150" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>60</v>
       </c>
@@ -21753,7 +21631,7 @@
       <c r="I150" s="11">
         <v>11</v>
       </c>
-      <c r="J150" s="50">
+      <c r="J150" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>96</v>
       </c>
@@ -21791,7 +21669,7 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.4</v>
       </c>
-      <c r="AL150" s="51">
+      <c r="AL150" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>10</v>
       </c>
@@ -21806,11 +21684,11 @@
       <c r="C151" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D151" s="49">
+      <c r="D151" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>75</v>
       </c>
-      <c r="E151" s="49">
+      <c r="E151" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>60</v>
       </c>
@@ -21826,7 +21704,7 @@
       <c r="I151" s="11">
         <v>1</v>
       </c>
-      <c r="J151" s="50" t="e">
+      <c r="J151" s="11" t="e">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>#DIV/0!</v>
       </c>
@@ -21864,7 +21742,7 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0</v>
       </c>
-      <c r="AL151" s="51">
+      <c r="AL151" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>0</v>
       </c>
@@ -21879,11 +21757,11 @@
       <c r="C152" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="D152" s="49">
+      <c r="D152" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>75</v>
       </c>
-      <c r="E152" s="49">
+      <c r="E152" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>60</v>
       </c>
@@ -21899,7 +21777,7 @@
       <c r="I152" s="11">
         <v>1</v>
       </c>
-      <c r="J152" s="50" t="e">
+      <c r="J152" s="11" t="e">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>#DIV/0!</v>
       </c>
@@ -21937,7 +21815,7 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0</v>
       </c>
-      <c r="AL152" s="51">
+      <c r="AL152" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>0</v>
       </c>
@@ -22229,24 +22107,24 @@
       </c>
     </row>
     <row r="157" spans="1:38">
-      <c r="A157" s="46" t="s">
+      <c r="A157" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="B157" s="53" t="s">
+      <c r="B157" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="C157" s="48" t="s">
+      <c r="C157" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D157" s="49">
+      <c r="D157" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E157" s="49">
+      <c r="E157" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F157" s="48" t="s">
+      <c r="F157" s="11" t="s">
         <v>304</v>
       </c>
       <c r="G157" s="11" t="s">
@@ -22258,7 +22136,7 @@
       <c r="I157" s="11">
         <v>1</v>
       </c>
-      <c r="J157" s="50">
+      <c r="J157" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>1.9999999999999998</v>
       </c>
@@ -22312,30 +22190,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.49999999999999994</v>
       </c>
-      <c r="AL157" s="51">
+      <c r="AL157" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>19.999999999999996</v>
       </c>
     </row>
     <row r="158" spans="1:38">
-      <c r="A158" s="46" t="s">
+      <c r="A158" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="B158" s="53" t="s">
+      <c r="B158" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="C158" s="48" t="s">
+      <c r="C158" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D158" s="49">
+      <c r="D158" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E158" s="49">
+      <c r="E158" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F158" s="48" t="s">
+      <c r="F158" s="11" t="s">
         <v>306</v>
       </c>
       <c r="G158" s="11" t="s">
@@ -22347,7 +22225,7 @@
       <c r="I158" s="11">
         <v>1</v>
       </c>
-      <c r="J158" s="50">
+      <c r="J158" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>0.79999999999999982</v>
       </c>
@@ -22401,30 +22279,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.19999999999999998</v>
       </c>
-      <c r="AL158" s="51">
+      <c r="AL158" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>7.9999999999999982</v>
       </c>
     </row>
     <row r="159" spans="1:38">
-      <c r="A159" s="46" t="s">
+      <c r="A159" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="B159" s="53" t="s">
+      <c r="B159" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="C159" s="48" t="s">
+      <c r="C159" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D159" s="49">
+      <c r="D159" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E159" s="49">
+      <c r="E159" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F159" s="48" t="s">
+      <c r="F159" s="11" t="s">
         <v>307</v>
       </c>
       <c r="G159" s="11" t="s">
@@ -22436,7 +22314,7 @@
       <c r="I159" s="11">
         <v>11</v>
       </c>
-      <c r="J159" s="50">
+      <c r="J159" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>12</v>
       </c>
@@ -22472,30 +22350,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
-      <c r="AL159" s="51">
+      <c r="AL159" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>12</v>
       </c>
     </row>
     <row r="160" spans="1:38">
-      <c r="A160" s="46" t="s">
+      <c r="A160" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B160" s="47" t="s">
+      <c r="B160" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C160" s="48" t="s">
+      <c r="C160" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D160" s="49">
+      <c r="D160" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E160" s="49">
+      <c r="E160" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="F160" s="48" t="s">
+      <c r="F160" s="11" t="s">
         <v>308</v>
       </c>
       <c r="G160" s="11" t="s">
@@ -22507,7 +22385,7 @@
       <c r="I160" s="11">
         <v>2</v>
       </c>
-      <c r="J160" s="50">
+      <c r="J160" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>4</v>
       </c>
@@ -22543,30 +22421,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.05</v>
       </c>
-      <c r="AL160" s="51">
+      <c r="AL160" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>4</v>
       </c>
     </row>
     <row r="161" spans="1:38">
-      <c r="A161" s="46" t="s">
+      <c r="A161" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B161" s="47" t="s">
+      <c r="B161" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C161" s="48" t="s">
+      <c r="C161" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D161" s="49">
+      <c r="D161" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E161" s="49">
+      <c r="E161" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="F161" s="48" t="s">
+      <c r="F161" s="11" t="s">
         <v>309</v>
       </c>
       <c r="G161" s="11" t="s">
@@ -22578,7 +22456,7 @@
       <c r="I161" s="11">
         <v>2</v>
       </c>
-      <c r="J161" s="50">
+      <c r="J161" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>4</v>
       </c>
@@ -22614,30 +22492,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.05</v>
       </c>
-      <c r="AL161" s="51">
+      <c r="AL161" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>4</v>
       </c>
     </row>
     <row r="162" spans="1:38">
-      <c r="A162" s="46" t="s">
+      <c r="A162" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B162" s="47" t="s">
+      <c r="B162" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C162" s="48" t="s">
+      <c r="C162" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D162" s="49">
+      <c r="D162" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E162" s="49">
+      <c r="E162" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="F162" s="48" t="s">
+      <c r="F162" s="11" t="s">
         <v>310</v>
       </c>
       <c r="G162" s="11" t="s">
@@ -22649,7 +22527,7 @@
       <c r="I162" s="11">
         <v>3</v>
       </c>
-      <c r="J162" s="50">
+      <c r="J162" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>24</v>
       </c>
@@ -22685,30 +22563,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
-      <c r="AL162" s="51">
+      <c r="AL162" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>24</v>
       </c>
     </row>
     <row r="163" spans="1:38">
-      <c r="A163" s="46" t="s">
+      <c r="A163" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B163" s="47" t="s">
+      <c r="B163" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C163" s="48" t="s">
+      <c r="C163" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D163" s="49">
+      <c r="D163" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E163" s="49">
+      <c r="E163" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="F163" s="48" t="s">
+      <c r="F163" s="11" t="s">
         <v>265</v>
       </c>
       <c r="G163" s="11" t="s">
@@ -22720,7 +22598,7 @@
       <c r="I163" s="11">
         <v>6</v>
       </c>
-      <c r="J163" s="50">
+      <c r="J163" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>8</v>
       </c>
@@ -22758,30 +22636,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
-      <c r="AL163" s="51">
+      <c r="AL163" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>4</v>
       </c>
     </row>
     <row r="164" spans="1:38">
-      <c r="A164" s="46" t="s">
+      <c r="A164" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B164" s="47" t="s">
+      <c r="B164" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C164" s="48" t="s">
+      <c r="C164" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="D164" s="49">
+      <c r="D164" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E164" s="49">
+      <c r="E164" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="F164" s="48" t="s">
+      <c r="F164" s="11" t="s">
         <v>312</v>
       </c>
       <c r="G164" s="11" t="s">
@@ -22793,7 +22671,7 @@
       <c r="I164" s="11">
         <v>6</v>
       </c>
-      <c r="J164" s="50">
+      <c r="J164" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>24</v>
       </c>
@@ -22831,30 +22709,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
-      <c r="AL164" s="51">
+      <c r="AL164" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="165" spans="1:38">
-      <c r="A165" s="46" t="s">
+      <c r="A165" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B165" s="47" t="s">
+      <c r="B165" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C165" s="48" t="s">
+      <c r="C165" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="D165" s="49">
+      <c r="D165" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E165" s="49">
+      <c r="E165" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="F165" s="48" t="s">
+      <c r="F165" s="11" t="s">
         <v>314</v>
       </c>
       <c r="G165" s="11" t="s">
@@ -22866,7 +22744,7 @@
       <c r="I165" s="11">
         <v>1</v>
       </c>
-      <c r="J165" s="50">
+      <c r="J165" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>16</v>
       </c>
@@ -22904,30 +22782,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
-      <c r="AL165" s="51">
+      <c r="AL165" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:38">
-      <c r="A166" s="46" t="s">
+      <c r="A166" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="B166" s="47" t="s">
+      <c r="B166" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C166" s="48" t="s">
+      <c r="C166" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D166" s="49">
+      <c r="D166" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E166" s="49">
+      <c r="E166" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="F166" s="48" t="s">
+      <c r="F166" s="11" t="s">
         <v>316</v>
       </c>
       <c r="G166" s="11" t="s">
@@ -22939,7 +22817,7 @@
       <c r="I166" s="11">
         <v>3</v>
       </c>
-      <c r="J166" s="50">
+      <c r="J166" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>4</v>
       </c>
@@ -22975,30 +22853,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.05</v>
       </c>
-      <c r="AL166" s="51">
+      <c r="AL166" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>4</v>
       </c>
     </row>
     <row r="167" spans="1:38">
-      <c r="A167" s="46" t="s">
+      <c r="A167" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="B167" s="47" t="s">
+      <c r="B167" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C167" s="48" t="s">
+      <c r="C167" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D167" s="49">
+      <c r="D167" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E167" s="49">
+      <c r="E167" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="F167" s="48" t="s">
+      <c r="F167" s="11" t="s">
         <v>312</v>
       </c>
       <c r="G167" s="11" t="s">
@@ -23010,7 +22888,7 @@
       <c r="I167" s="11">
         <v>7</v>
       </c>
-      <c r="J167" s="50">
+      <c r="J167" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>16</v>
       </c>
@@ -23048,30 +22926,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
-      <c r="AL167" s="51">
+      <c r="AL167" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="168" spans="1:38">
-      <c r="A168" s="46" t="s">
+      <c r="A168" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="B168" s="47" t="s">
+      <c r="B168" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C168" s="48" t="s">
+      <c r="C168" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="D168" s="49">
+      <c r="D168" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E168" s="49">
+      <c r="E168" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="F168" s="48" t="s">
+      <c r="F168" s="11" t="s">
         <v>317</v>
       </c>
       <c r="G168" s="11" t="s">
@@ -23083,7 +22961,7 @@
       <c r="I168" s="11">
         <v>6</v>
       </c>
-      <c r="J168" s="50">
+      <c r="J168" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>24</v>
       </c>
@@ -23119,30 +22997,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
-      <c r="AL168" s="51">
+      <c r="AL168" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>24</v>
       </c>
     </row>
     <row r="169" spans="1:38">
-      <c r="A169" s="46" t="s">
+      <c r="A169" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="B169" s="47" t="s">
+      <c r="B169" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C169" s="48" t="s">
+      <c r="C169" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D169" s="49">
+      <c r="D169" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
-      <c r="E169" s="49">
+      <c r="E169" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
-      <c r="F169" s="48" t="s">
+      <c r="F169" s="11" t="s">
         <v>318</v>
       </c>
       <c r="G169" s="11" t="s">
@@ -23154,7 +23032,7 @@
       <c r="I169" s="11">
         <v>6</v>
       </c>
-      <c r="J169" s="50">
+      <c r="J169" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>36</v>
       </c>
@@ -23190,30 +23068,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.45</v>
       </c>
-      <c r="AL169" s="51">
+      <c r="AL169" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>36</v>
       </c>
     </row>
     <row r="170" spans="1:38">
-      <c r="A170" s="52" t="s">
+      <c r="A170" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="B170" s="53" t="s">
+      <c r="B170" s="28" t="s">
         <v>320</v>
       </c>
-      <c r="C170" s="48" t="s">
+      <c r="C170" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D170" s="49" t="e">
+      <c r="D170" s="29" t="e">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="E170" s="49" t="e">
+      <c r="E170" s="29" t="e">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="F170" s="48" t="s">
+      <c r="F170" s="11" t="s">
         <v>321</v>
       </c>
       <c r="G170" s="11" t="s">
@@ -23225,7 +23103,7 @@
       <c r="I170" s="11">
         <v>4</v>
       </c>
-      <c r="J170" s="50" t="e">
+      <c r="J170" s="11" t="e">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>#N/A</v>
       </c>
@@ -23261,30 +23139,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
-      <c r="AL170" s="51" t="e">
+      <c r="AL170" s="27" t="e">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="171" spans="1:38">
-      <c r="A171" s="52" t="s">
+      <c r="A171" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="B171" s="53" t="s">
+      <c r="B171" s="28" t="s">
         <v>320</v>
       </c>
-      <c r="C171" s="48" t="s">
+      <c r="C171" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D171" s="49" t="e">
+      <c r="D171" s="29" t="e">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="E171" s="49" t="e">
+      <c r="E171" s="29" t="e">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="F171" s="48" t="s">
+      <c r="F171" s="11" t="s">
         <v>323</v>
       </c>
       <c r="G171" s="11" t="s">
@@ -23296,7 +23174,7 @@
       <c r="I171" s="11">
         <v>6</v>
       </c>
-      <c r="J171" s="50" t="e">
+      <c r="J171" s="11" t="e">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>#N/A</v>
       </c>
@@ -23332,30 +23210,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
-      <c r="AL171" s="51" t="e">
+      <c r="AL171" s="27" t="e">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="172" spans="1:38">
-      <c r="A172" s="52" t="s">
+      <c r="A172" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B172" s="53" t="s">
+      <c r="B172" s="28" t="s">
         <v>325</v>
       </c>
-      <c r="C172" s="48" t="s">
+      <c r="C172" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D172" s="49" t="e">
+      <c r="D172" s="29" t="e">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="E172" s="49" t="e">
+      <c r="E172" s="29" t="e">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="F172" s="48" t="s">
+      <c r="F172" s="11" t="s">
         <v>326</v>
       </c>
       <c r="G172" s="11" t="s">
@@ -23367,7 +23245,7 @@
       <c r="I172" s="11">
         <v>3</v>
       </c>
-      <c r="J172" s="50" t="e">
+      <c r="J172" s="11" t="e">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>#N/A</v>
       </c>
@@ -23403,30 +23281,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
-      <c r="AL172" s="51" t="e">
+      <c r="AL172" s="27" t="e">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="173" spans="1:38">
-      <c r="A173" s="52" t="s">
+      <c r="A173" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B173" s="53" t="s">
+      <c r="B173" s="28" t="s">
         <v>325</v>
       </c>
-      <c r="C173" s="48" t="s">
+      <c r="C173" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D173" s="49" t="e">
+      <c r="D173" s="29" t="e">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="E173" s="49" t="e">
+      <c r="E173" s="29" t="e">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="F173" s="48" t="s">
+      <c r="F173" s="11" t="s">
         <v>328</v>
       </c>
       <c r="G173" s="11" t="s">
@@ -23438,7 +23316,7 @@
       <c r="I173" s="11">
         <v>8</v>
       </c>
-      <c r="J173" s="50" t="e">
+      <c r="J173" s="11" t="e">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>#N/A</v>
       </c>
@@ -23474,30 +23352,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.5</v>
       </c>
-      <c r="AL173" s="51" t="e">
+      <c r="AL173" s="27" t="e">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="174" spans="1:38">
-      <c r="A174" s="52" t="s">
+      <c r="A174" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B174" s="53" t="s">
+      <c r="B174" s="28" t="s">
         <v>325</v>
       </c>
-      <c r="C174" s="48" t="s">
+      <c r="C174" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D174" s="49" t="e">
+      <c r="D174" s="29" t="e">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="E174" s="49" t="e">
+      <c r="E174" s="29" t="e">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="F174" s="48" t="s">
+      <c r="F174" s="11" t="s">
         <v>329</v>
       </c>
       <c r="G174" s="11" t="s">
@@ -23509,7 +23387,7 @@
       <c r="I174" s="11">
         <v>3</v>
       </c>
-      <c r="J174" s="50" t="e">
+      <c r="J174" s="11" t="e">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>#N/A</v>
       </c>
@@ -23545,30 +23423,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
-      <c r="AL174" s="51" t="e">
+      <c r="AL174" s="27" t="e">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="175" spans="1:38">
-      <c r="A175" s="52" t="s">
+      <c r="A175" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B175" s="53" t="s">
+      <c r="B175" s="28" t="s">
         <v>331</v>
       </c>
-      <c r="C175" s="48" t="s">
+      <c r="C175" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D175" s="49" t="e">
+      <c r="D175" s="29" t="e">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="E175" s="49" t="e">
+      <c r="E175" s="29" t="e">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="F175" s="48" t="s">
+      <c r="F175" s="11" t="s">
         <v>332</v>
       </c>
       <c r="G175" s="11" t="s">
@@ -23580,7 +23458,7 @@
       <c r="I175" s="11">
         <v>4</v>
       </c>
-      <c r="J175" s="50" t="e">
+      <c r="J175" s="11" t="e">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>#N/A</v>
       </c>
@@ -23618,30 +23496,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.5</v>
       </c>
-      <c r="AL175" s="51">
+      <c r="AL175" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>20</v>
       </c>
     </row>
     <row r="176" spans="1:38">
-      <c r="A176" s="52" t="s">
+      <c r="A176" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B176" s="53" t="s">
+      <c r="B176" s="28" t="s">
         <v>331</v>
       </c>
-      <c r="C176" s="48" t="s">
+      <c r="C176" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D176" s="49" t="e">
+      <c r="D176" s="29" t="e">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="E176" s="49" t="e">
+      <c r="E176" s="29" t="e">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="F176" s="48" t="s">
+      <c r="F176" s="11" t="s">
         <v>333</v>
       </c>
       <c r="G176" s="11" t="s">
@@ -23653,7 +23531,7 @@
       <c r="I176" s="11">
         <v>1</v>
       </c>
-      <c r="J176" s="50" t="e">
+      <c r="J176" s="11" t="e">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>#N/A</v>
       </c>
@@ -23691,30 +23569,30 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.5</v>
       </c>
-      <c r="AL176" s="51">
+      <c r="AL176" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:38">
-      <c r="A177" s="52" t="s">
+      <c r="A177" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B177" s="53" t="s">
+      <c r="B177" s="28" t="s">
         <v>335</v>
       </c>
-      <c r="C177" s="48" t="s">
+      <c r="C177" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D177" s="49" t="e">
+      <c r="D177" s="29" t="e">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="E177" s="49" t="e">
+      <c r="E177" s="29" t="e">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>#N/A</v>
       </c>
-      <c r="F177" s="48" t="s">
+      <c r="F177" s="11" t="s">
         <v>336</v>
       </c>
       <c r="G177" s="11" t="s">
@@ -23726,7 +23604,7 @@
       <c r="I177" s="11">
         <v>2</v>
       </c>
-      <c r="J177" s="50" t="e">
+      <c r="J177" s="11" t="e">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>#N/A</v>
       </c>
@@ -23764,7 +23642,7 @@
         <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.5</v>
       </c>
-      <c r="AL177" s="51">
+      <c r="AL177" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>8</v>
       </c>
@@ -30307,7 +30185,7 @@
       </c>
       <c r="T7">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -30359,7 +30237,7 @@
       </c>
       <c r="T8">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30.000000000000004</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -30555,7 +30433,7 @@
       </c>
       <c r="T12">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -30605,7 +30483,7 @@
       </c>
       <c r="T13">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -30749,7 +30627,7 @@
       </c>
       <c r="T16">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:20">
@@ -31045,7 +30923,7 @@
       </c>
       <c r="T22">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30.000000000000004</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:20">
@@ -31495,7 +31373,7 @@
       </c>
       <c r="T31">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:20">
@@ -31601,7 +31479,7 @@
       </c>
       <c r="T33">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -32229,7 +32107,7 @@
       </c>
       <c r="T45">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:20">
@@ -32441,7 +32319,7 @@
       </c>
       <c r="T49">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="50" spans="1:20">
@@ -32917,7 +32795,7 @@
       </c>
       <c r="T58">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:20">
@@ -33025,7 +32903,7 @@
       </c>
       <c r="T60">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>50</v>
+        <v>30.000000000000004</v>
       </c>
     </row>
     <row r="61" spans="1:20">
@@ -33263,7 +33141,7 @@
       </c>
       <c r="T65">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:20">
@@ -33353,7 +33231,7 @@
       </c>
       <c r="T67">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:20">
@@ -33638,7 +33516,7 @@
       </c>
       <c r="T73">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:20">
@@ -33833,7 +33711,7 @@
       </c>
       <c r="T77">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="78" spans="1:20">
@@ -34259,7 +34137,7 @@
       </c>
       <c r="T86">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:20">
@@ -34355,7 +34233,7 @@
       </c>
       <c r="T88">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>50</v>
+        <v>30.000000000000004</v>
       </c>
     </row>
     <row r="89" spans="1:20">
@@ -34782,13 +34660,13 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E2:E93">
-    <cfRule type="containsText" dxfId="13" priority="4" operator="containsText" text="SEMD">
+    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="SEMD">
       <formula>NOT(ISERROR(SEARCH("SEMD",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="SEM2">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="SEM2">
       <formula>NOT(ISERROR(SEARCH("SEM2",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="6" operator="containsText" text="SEM1">
+    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="SEM1">
       <formula>NOT(ISERROR(SEARCH("SEM1",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34815,15 +34693,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:Q93">
-    <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="O">
+    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="O">
       <formula>NOT(ISERROR(SEARCH("O",H2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="9" operator="containsText" text="C">
+    <cfRule type="containsText" dxfId="2" priority="9" operator="containsText" text="C">
       <formula>NOT(ISERROR(SEARCH("C",H2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T93">
-    <cfRule type="expression" dxfId="7" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>T2&lt;&gt;S2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35038,7 +34916,7 @@
       </c>
       <c r="C10">
         <f>SUMIF(Table1[Module Code],Sheet2!A10,Table1[Total Hours])</f>
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
       <c r="D10">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A10,Table14[Module Code],0))</f>
@@ -35046,11 +34924,11 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>28.5</v>
       </c>
       <c r="F10">
         <f t="shared" si="1"/>
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -35350,7 +35228,7 @@
       </c>
       <c r="C23">
         <f>SUMIF(Table1[Module Code],Sheet2!A23,Table1[Total Hours])</f>
-        <v>12.000000000000004</v>
+        <v>6</v>
       </c>
       <c r="D23">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A23,Table14[Module Code],0))</f>
@@ -35358,11 +35236,11 @@
       </c>
       <c r="E23">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -35638,7 +35516,7 @@
       </c>
       <c r="C35">
         <f>SUMIF(Table1[Module Code],Sheet2!A35,Table1[Total Hours])</f>
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D35">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A35,Table14[Module Code],0))</f>
@@ -35646,11 +35524,11 @@
       </c>
       <c r="E35">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F35">
         <f t="shared" si="1"/>
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -35998,7 +35876,7 @@
       </c>
       <c r="C50">
         <f>SUMIF(Table1[Module Code],Sheet2!A50,Table1[Total Hours])</f>
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D50">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A50,Table14[Module Code],0))</f>
@@ -36006,11 +35884,11 @@
       </c>
       <c r="E50">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F50">
         <f t="shared" si="1"/>
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -36118,7 +35996,7 @@
       </c>
       <c r="C55">
         <f>SUMIF(Table1[Module Code],Sheet2!A55,Table1[Total Hours])</f>
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D55">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A55,Table14[Module Code],0))</f>
@@ -36126,11 +36004,11 @@
       </c>
       <c r="E55">
         <f t="shared" si="0"/>
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="F55">
         <f t="shared" si="1"/>
-        <v>6.5</v>
+        <v>5.0999999999999996</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -36334,7 +36212,7 @@
       </c>
       <c r="C64">
         <f>SUMIF(Table1[Module Code],Sheet2!A64,Table1[Total Hours])</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D64">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A64,Table14[Module Code],0))</f>
@@ -36342,11 +36220,11 @@
       </c>
       <c r="E64">
         <f t="shared" si="0"/>
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F64">
         <f t="shared" si="1"/>
-        <v>4.4000000000000004</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="65" spans="1:6">

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1379" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58D2120B-7E06-43A0-ACD2-C4B78EC94ABB}"/>
+  <xr:revisionPtr revIDLastSave="1512" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96133C9B-F3E8-486A-BB54-652495E5D8D5}"/>
   <bookViews>
-    <workbookView xWindow="5420" yWindow="5420" windowWidth="28800" windowHeight="15290" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="2" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Assessments" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2772" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2876" uniqueCount="388">
   <si>
     <t>Module Code</t>
   </si>
@@ -1198,6 +1198,33 @@
   </si>
   <si>
     <t>Portfolio (P)</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>na/</t>
+  </si>
+  <si>
+    <t>PXT143</t>
+  </si>
+  <si>
+    <t>SEM3</t>
+  </si>
+  <si>
+    <t>ENT795</t>
+  </si>
+  <si>
+    <t>Optoelectronics</t>
+  </si>
+  <si>
+    <t>CDTCSPhysics</t>
+  </si>
+  <si>
+    <t>MScDataPhys</t>
+  </si>
+  <si>
+    <t>MScDataAstro</t>
   </si>
 </sst>
 </file>
@@ -1292,7 +1319,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1421,11 +1448,82 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="105">
+  <dxfs count="120">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1489,6 +1587,111 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
       <font>
@@ -2344,31 +2547,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="0.000"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
       <font>
@@ -3679,9 +3857,9 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="3"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -9523,58 +9701,58 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}" name="Table1" displayName="Table1" ref="A1:AL177" totalsRowShown="0" headerRowDxfId="85" dataDxfId="83" headerRowBorderDxfId="84" tableBorderDxfId="82" totalsRowBorderDxfId="81">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}" name="Table1" displayName="Table1" ref="A1:AL177" totalsRowShown="0" headerRowDxfId="100" dataDxfId="98" headerRowBorderDxfId="99" tableBorderDxfId="97" totalsRowBorderDxfId="96">
   <autoFilter ref="A1:AL177" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AI148">
     <sortCondition ref="A1:A148"/>
   </sortState>
   <tableColumns count="38">
-    <tableColumn id="1" xr3:uid="{7078548A-F011-4851-AB36-1F04238FA2FE}" name="Module Code" dataDxfId="80"/>
-    <tableColumn id="2" xr3:uid="{D2290F36-B8B3-427A-AEFE-45FD22901411}" name="Module Title" dataDxfId="79"/>
-    <tableColumn id="3" xr3:uid="{31165455-2AA3-4532-A0A0-C942837C0F79}" name="CA type" dataDxfId="78"/>
-    <tableColumn id="33" xr3:uid="{B83E0E3E-2B28-42F1-BC64-5D7177EC4229}" name="CA Weight" dataDxfId="77">
+    <tableColumn id="1" xr3:uid="{7078548A-F011-4851-AB36-1F04238FA2FE}" name="Module Code" dataDxfId="95"/>
+    <tableColumn id="2" xr3:uid="{D2290F36-B8B3-427A-AEFE-45FD22901411}" name="Module Title" dataDxfId="94"/>
+    <tableColumn id="3" xr3:uid="{31165455-2AA3-4532-A0A0-C942837C0F79}" name="CA type" dataDxfId="93"/>
+    <tableColumn id="33" xr3:uid="{B83E0E3E-2B28-42F1-BC64-5D7177EC4229}" name="CA Weight" dataDxfId="92">
       <calculatedColumnFormula>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{AEA2048C-138D-450A-BE52-3FCBDE03C67D}" name="Credits" dataDxfId="76">
+    <tableColumn id="34" xr3:uid="{AEA2048C-138D-450A-BE52-3FCBDE03C67D}" name="Credits" dataDxfId="91">
       <calculatedColumnFormula>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{82DD5B5B-C808-4E6E-849C-7A03DC6D0B69}" name="Description" dataDxfId="75"/>
-    <tableColumn id="36" xr3:uid="{A7BF30F6-C808-4B8F-B3FF-9FAF20E2145A}" name="Summative" dataDxfId="74"/>
-    <tableColumn id="37" xr3:uid="{68E504F9-116C-43AB-BCC6-3BB48B0860D2}" name="Day of Week" dataDxfId="73"/>
-    <tableColumn id="16" xr3:uid="{E6637FEB-7F23-45F0-99D2-96D20DD2DAEF}" name="Duration" dataDxfId="72"/>
-    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="71">
+    <tableColumn id="30" xr3:uid="{82DD5B5B-C808-4E6E-849C-7A03DC6D0B69}" name="Description" dataDxfId="90"/>
+    <tableColumn id="36" xr3:uid="{A7BF30F6-C808-4B8F-B3FF-9FAF20E2145A}" name="Summative" dataDxfId="89"/>
+    <tableColumn id="37" xr3:uid="{68E504F9-116C-43AB-BCC6-3BB48B0860D2}" name="Day of Week" dataDxfId="88"/>
+    <tableColumn id="16" xr3:uid="{E6637FEB-7F23-45F0-99D2-96D20DD2DAEF}" name="Duration" dataDxfId="87"/>
+    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="86">
       <calculatedColumnFormula>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="70"/>
-    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="69"/>
-    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="68"/>
-    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="67"/>
-    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="66"/>
-    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="65"/>
-    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="64"/>
-    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="63"/>
-    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="62"/>
-    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="61"/>
-    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="60"/>
-    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="59"/>
-    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="58"/>
-    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="57"/>
-    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="56"/>
-    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="55"/>
-    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="54"/>
-    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="53"/>
-    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="52"/>
-    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="51"/>
-    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="50"/>
-    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="49"/>
-    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="48"/>
-    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="47"/>
-    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="46"/>
-    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="45"/>
-    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="44">
-      <calculatedColumnFormula>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
+    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="85"/>
+    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="84"/>
+    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="83"/>
+    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="82"/>
+    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="81"/>
+    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="80"/>
+    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="79"/>
+    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="78"/>
+    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="77"/>
+    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="76"/>
+    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="75"/>
+    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="74"/>
+    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="73"/>
+    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="72"/>
+    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="71"/>
+    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="70"/>
+    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="69"/>
+    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="68"/>
+    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="67"/>
+    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="66"/>
+    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="65"/>
+    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="64"/>
+    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="63"/>
+    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="62"/>
+    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="61"/>
+    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="60"/>
+    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="22">
+      <calculatedColumnFormula>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="43">
+    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="59">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9583,49 +9761,49 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41" tableBorderDxfId="39" totalsRowBorderDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="58" dataDxfId="56" headerRowBorderDxfId="57" tableBorderDxfId="55" totalsRowBorderDxfId="54">
   <autoFilter ref="A1:AE64" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD64">
     <sortCondition ref="A1:A132"/>
   </sortState>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="35"/>
-    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="34">
+    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="53"/>
+    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="51"/>
+    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="50">
       <calculatedColumnFormula>INDEX(Table2[Credits],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="33">
+    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="49">
       <calculatedColumnFormula>INDEX(Table2[Semester],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="32">
+    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="48">
       <calculatedColumnFormula>INDEX(Table2[Contact Time],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="22"/>
-    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="21"/>
-    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="20"/>
-    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="19"/>
-    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="18"/>
-    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="17"/>
-    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="16"/>
-    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="15"/>
-    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="14"/>
-    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="13"/>
-    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="12"/>
-    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="11"/>
-    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="10"/>
-    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="9"/>
-    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="8"/>
-    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="7">
+    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="45"/>
+    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="43"/>
+    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="42"/>
+    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="41"/>
+    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="40"/>
+    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="39"/>
+    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="38"/>
+    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="37"/>
+    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="36"/>
+    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="35"/>
+    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="34"/>
+    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="33"/>
+    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="32"/>
+    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="31"/>
+    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="30"/>
+    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="29"/>
+    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="28"/>
+    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="27"/>
+    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="26"/>
+    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="25"/>
+    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="24"/>
+    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="23">
       <calculatedColumnFormula>SUM(Table14[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9634,34 +9812,37 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}" name="Table2" displayName="Table2" ref="A1:T93" totalsRowShown="0" headerRowDxfId="104" dataDxfId="102" headerRowBorderDxfId="103">
-  <autoFilter ref="A1:T93" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B61">
-    <sortCondition ref="A1:A61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}" name="Table2" displayName="Table2" ref="A1:W100" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118">
+  <autoFilter ref="A1:W100" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B62">
+    <sortCondition ref="A1:A62"/>
   </sortState>
-  <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{A36A2B86-0F30-4188-9ECD-AE5BC71A59F4}" name="Module Code" dataDxfId="101"/>
-    <tableColumn id="2" xr3:uid="{D3F20037-EF35-4207-A530-484E1EB45719}" name="Module Title" dataDxfId="100"/>
-    <tableColumn id="9" xr3:uid="{40C22022-10B9-411F-9B76-B89140ABFFB2}" name="Alternative Module Code" dataDxfId="99"/>
-    <tableColumn id="13" xr3:uid="{CB12E405-1802-457C-AF17-F1B9CB3BBF13}" name="Source" dataDxfId="98"/>
-    <tableColumn id="8" xr3:uid="{EA737976-1AA7-49B6-8752-A388621554F4}" name="Semester" dataDxfId="97"/>
-    <tableColumn id="6" xr3:uid="{16DFC84F-5858-467D-B447-49992D721E4B}" name="Level" dataDxfId="96"/>
-    <tableColumn id="5" xr3:uid="{A17BC4BA-A3CB-442D-9BDC-D3B41B98B389}" name="Credits" dataDxfId="95"/>
-    <tableColumn id="19" xr3:uid="{98846C13-E462-4CFF-858E-AF75931B6712}" name="AllUG" dataDxfId="94"/>
-    <tableColumn id="3" xr3:uid="{7E25B4F4-1A7D-48D9-AAA2-AF5C97240797}" name="Physics" dataDxfId="93"/>
+  <tableColumns count="23">
+    <tableColumn id="1" xr3:uid="{A36A2B86-0F30-4188-9ECD-AE5BC71A59F4}" name="Module Code" dataDxfId="116"/>
+    <tableColumn id="2" xr3:uid="{D3F20037-EF35-4207-A530-484E1EB45719}" name="Module Title" dataDxfId="115"/>
+    <tableColumn id="9" xr3:uid="{40C22022-10B9-411F-9B76-B89140ABFFB2}" name="Alternative Module Code" dataDxfId="114"/>
+    <tableColumn id="13" xr3:uid="{CB12E405-1802-457C-AF17-F1B9CB3BBF13}" name="Source" dataDxfId="113"/>
+    <tableColumn id="8" xr3:uid="{EA737976-1AA7-49B6-8752-A388621554F4}" name="Semester" dataDxfId="112"/>
+    <tableColumn id="6" xr3:uid="{16DFC84F-5858-467D-B447-49992D721E4B}" name="Level" dataDxfId="111"/>
+    <tableColumn id="5" xr3:uid="{A17BC4BA-A3CB-442D-9BDC-D3B41B98B389}" name="Credits" dataDxfId="110"/>
+    <tableColumn id="19" xr3:uid="{98846C13-E462-4CFF-858E-AF75931B6712}" name="AllUG" dataDxfId="109"/>
+    <tableColumn id="3" xr3:uid="{7E25B4F4-1A7D-48D9-AAA2-AF5C97240797}" name="Physics" dataDxfId="108"/>
     <tableColumn id="17" xr3:uid="{AA3AE96F-2651-49D7-89AD-BA94806438AE}" name="PhysAstro"/>
-    <tableColumn id="4" xr3:uid="{9C7DD469-E550-411F-8467-246A1543FB38}" name="Astro" dataDxfId="92"/>
-    <tableColumn id="7" xr3:uid="{3C5D3AEB-487E-4678-A42F-BE4BA4D0E9AA}" name="MedPhys" dataDxfId="91"/>
+    <tableColumn id="4" xr3:uid="{9C7DD469-E550-411F-8467-246A1543FB38}" name="Astro" dataDxfId="107"/>
+    <tableColumn id="7" xr3:uid="{3C5D3AEB-487E-4678-A42F-BE4BA4D0E9AA}" name="MedPhys" dataDxfId="106"/>
     <tableColumn id="20" xr3:uid="{C3673B06-C0A2-44F6-8978-F392282CECF8}" name="AllPG"/>
-    <tableColumn id="14" xr3:uid="{AE552873-9B31-41A6-B73C-D052477CA74C}" name="MScPhysics" dataDxfId="90"/>
-    <tableColumn id="15" xr3:uid="{8F51CE76-3A29-487A-A13C-FB63C79CF3E6}" name="MScAstro" dataDxfId="89"/>
+    <tableColumn id="14" xr3:uid="{AE552873-9B31-41A6-B73C-D052477CA74C}" name="MScPhysics" dataDxfId="105"/>
+    <tableColumn id="15" xr3:uid="{8F51CE76-3A29-487A-A13C-FB63C79CF3E6}" name="MScAstro" dataDxfId="104"/>
+    <tableColumn id="21" xr3:uid="{FC74E264-78AB-4682-A1B8-D8964ED1C3F3}" name="MScDataPhys" dataDxfId="14"/>
+    <tableColumn id="22" xr3:uid="{2D5776F7-D7F7-4D20-A7CB-DB57997AD074}" name="MScDataAstro" dataDxfId="13"/>
     <tableColumn id="18" xr3:uid="{10668F71-1EDF-482E-86A5-46E1F3C15120}" name="MScCSPhysics"/>
+    <tableColumn id="23" xr3:uid="{E837FCBC-49C7-45CE-AFAA-4F01143EF2A8}" name="CDTCSPhysics"/>
     <tableColumn id="16" xr3:uid="{DB790F5F-BEF0-41CE-A68A-1AA9DF83D66B}" name="Contact Time"/>
-    <tableColumn id="10" xr3:uid="{60774AFA-B365-4EB5-AAFF-6235868F8C97}" name="Exam Weight (%)" dataDxfId="88"/>
-    <tableColumn id="12" xr3:uid="{537B7C75-E9C0-42F2-9F3C-6E960AB2D257}" name="CA weight" dataDxfId="87">
+    <tableColumn id="10" xr3:uid="{60774AFA-B365-4EB5-AAFF-6235868F8C97}" name="Exam Weight (%)" dataDxfId="103"/>
+    <tableColumn id="12" xr3:uid="{537B7C75-E9C0-42F2-9F3C-6E960AB2D257}" name="CA weight" dataDxfId="102">
       <calculatedColumnFormula>100-Table2[[#This Row],[Exam Weight (%)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{75DA2527-5A08-4ECE-B4E4-752A8F8BF059}" name="CA Check" dataDxfId="86">
+    <tableColumn id="11" xr3:uid="{75DA2527-5A08-4ECE-B4E4-752A8F8BF059}" name="CA Check" dataDxfId="101">
       <calculatedColumnFormula>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10188,7 +10369,7 @@
       <c r="AI2" s="20"/>
       <c r="AJ2" s="20"/>
       <c r="AK2" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL2" s="27">
@@ -10261,7 +10442,7 @@
       <c r="AI3" s="20"/>
       <c r="AJ3" s="20"/>
       <c r="AK3" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL3" s="27">
@@ -10334,7 +10515,7 @@
       <c r="AI4" s="20"/>
       <c r="AJ4" s="20"/>
       <c r="AK4" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL4" s="27">
@@ -10407,7 +10588,7 @@
       <c r="AI5" s="20"/>
       <c r="AJ5" s="20"/>
       <c r="AK5" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="AL5" s="27">
@@ -10505,7 +10686,7 @@
       <c r="AI6" s="20"/>
       <c r="AJ6" s="20"/>
       <c r="AK6" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL6" s="27">
@@ -10585,7 +10766,7 @@
       <c r="AI7" s="20"/>
       <c r="AJ7" s="20"/>
       <c r="AK7" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL7" s="27">
@@ -10658,7 +10839,7 @@
       <c r="AI8" s="20"/>
       <c r="AJ8" s="20"/>
       <c r="AK8" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
       <c r="AL8" s="27">
@@ -10769,7 +10950,7 @@
       <c r="AI9" s="20"/>
       <c r="AJ9" s="20"/>
       <c r="AK9" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>1.0000000000000002</v>
       </c>
       <c r="AL9" s="27">
@@ -10852,7 +11033,7 @@
       <c r="AI10" s="20"/>
       <c r="AJ10" s="20"/>
       <c r="AK10" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.53999999999999992</v>
       </c>
       <c r="AL10" s="27">
@@ -10925,7 +11106,7 @@
       <c r="AI11" s="20"/>
       <c r="AJ11" s="20"/>
       <c r="AK11" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.09</v>
       </c>
       <c r="AL11" s="27">
@@ -10998,7 +11179,7 @@
       <c r="AI12" s="20"/>
       <c r="AJ12" s="20"/>
       <c r="AK12" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.37</v>
       </c>
       <c r="AL12" s="27">
@@ -11089,7 +11270,7 @@
       <c r="AI13" s="20"/>
       <c r="AJ13" s="20"/>
       <c r="AK13" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="AL13" s="27">
@@ -11180,7 +11361,7 @@
       <c r="AI14" s="20"/>
       <c r="AJ14" s="20"/>
       <c r="AK14" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.49999999999999994</v>
       </c>
       <c r="AL14" s="27">
@@ -11255,8 +11436,8 @@
       <c r="AI15" s="20"/>
       <c r="AJ15" s="20"/>
       <c r="AK15" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.2</v>
       </c>
       <c r="AL15" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -11328,7 +11509,7 @@
       </c>
       <c r="AJ16" s="20"/>
       <c r="AK16" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
       <c r="AL16" s="27">
@@ -11368,7 +11549,7 @@
       </c>
       <c r="J17" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0.8</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="K17" s="11">
         <v>0.5</v>
@@ -11391,9 +11572,11 @@
       <c r="AA17" s="20">
         <v>0.02</v>
       </c>
-      <c r="AB17" s="20"/>
+      <c r="AB17" s="20">
+        <v>0.02</v>
+      </c>
       <c r="AC17" s="20">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="AD17" s="20"/>
       <c r="AE17" s="20">
@@ -11409,7 +11592,7 @@
       <c r="AI17" s="20"/>
       <c r="AJ17" s="20"/>
       <c r="AK17" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL17" s="27">
@@ -11482,8 +11665,8 @@
       <c r="AI18" s="20"/>
       <c r="AJ18" s="20"/>
       <c r="AK18" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.1</v>
       </c>
       <c r="AL18" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -11553,7 +11736,7 @@
       <c r="AI19" s="20"/>
       <c r="AJ19" s="20"/>
       <c r="AK19" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL19" s="27">
@@ -11632,7 +11815,7 @@
       <c r="AI20" s="20"/>
       <c r="AJ20" s="20"/>
       <c r="AK20" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.4</v>
       </c>
       <c r="AL20" s="27">
@@ -11703,7 +11886,7 @@
       <c r="AI21" s="20"/>
       <c r="AJ21" s="20"/>
       <c r="AK21" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.05</v>
       </c>
       <c r="AL21" s="27">
@@ -11774,7 +11957,7 @@
       <c r="AI22" s="20"/>
       <c r="AJ22" s="20"/>
       <c r="AK22" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.15</v>
       </c>
       <c r="AL22" s="27">
@@ -11865,7 +12048,7 @@
       <c r="AI23" s="20"/>
       <c r="AJ23" s="20"/>
       <c r="AK23" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="AL23" s="27">
@@ -11905,7 +12088,7 @@
       </c>
       <c r="J24" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>3.9999999999999996</v>
+        <v>0</v>
       </c>
       <c r="K24" s="11">
         <v>15</v>
@@ -11921,9 +12104,11 @@
       </c>
       <c r="Q24" s="18"/>
       <c r="R24" s="18"/>
-      <c r="S24" s="19"/>
+      <c r="S24" s="19">
+        <v>0.15</v>
+      </c>
       <c r="T24" s="18">
-        <v>0.15</v>
+        <v>-0.15</v>
       </c>
       <c r="U24" s="18"/>
       <c r="V24" s="18"/>
@@ -11942,8 +12127,8 @@
       <c r="AI24" s="20"/>
       <c r="AJ24" s="20"/>
       <c r="AK24" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.15</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.3</v>
       </c>
       <c r="AL24" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -12025,7 +12210,7 @@
       <c r="AI25" s="20"/>
       <c r="AJ25" s="20"/>
       <c r="AK25" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL25" s="27">
@@ -12065,7 +12250,7 @@
       </c>
       <c r="J26" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K26" s="11">
         <v>0.5</v>
@@ -12077,11 +12262,9 @@
       <c r="P26" s="18"/>
       <c r="Q26" s="18"/>
       <c r="R26" s="18"/>
-      <c r="S26" s="19">
+      <c r="S26" s="19"/>
+      <c r="T26" s="18">
         <v>0.2</v>
-      </c>
-      <c r="T26" s="18">
-        <v>-0.2</v>
       </c>
       <c r="U26" s="18"/>
       <c r="V26" s="18"/>
@@ -12100,23 +12283,23 @@
       <c r="AI26" s="20"/>
       <c r="AJ26" s="20"/>
       <c r="AK26" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.2</v>
       </c>
       <c r="AL26" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>0.5</v>
       </c>
     </row>
-    <row r="27" spans="1:38" ht="28">
+    <row r="27" spans="1:38">
       <c r="A27" s="4" t="s">
-        <v>49</v>
+        <v>234</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>48</v>
+        <v>235</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
       <c r="D27" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -12126,40 +12309,54 @@
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F27" s="37" t="s">
-        <v>293</v>
+      <c r="F27" s="11" t="s">
+        <v>358</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="I27" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J27" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>7.2000000000000011</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="K27" s="11">
-        <v>6</v>
-      </c>
-      <c r="L27" s="18"/>
-      <c r="M27" s="18"/>
-      <c r="N27" s="18"/>
+        <v>1</v>
+      </c>
+      <c r="L27" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="M27" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="N27" s="18">
+        <v>0.01</v>
+      </c>
       <c r="O27" s="18">
-        <v>0.18</v>
-      </c>
-      <c r="P27" s="18"/>
-      <c r="Q27" s="18"/>
+        <v>0.01</v>
+      </c>
+      <c r="P27" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="Q27" s="18">
+        <v>0.01</v>
+      </c>
       <c r="R27" s="18">
-        <v>0.18</v>
-      </c>
-      <c r="S27" s="19"/>
-      <c r="T27" s="18"/>
+        <v>0.01</v>
+      </c>
+      <c r="S27" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="T27" s="18">
+        <v>0.01</v>
+      </c>
       <c r="U27" s="18">
-        <v>0.18</v>
+        <v>0.01</v>
       </c>
       <c r="V27" s="18"/>
       <c r="W27" s="19"/>
@@ -12177,20 +12374,20 @@
       <c r="AI27" s="20"/>
       <c r="AJ27" s="20"/>
       <c r="AK27" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.54</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="AL27" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:38">
       <c r="A28" s="4" t="s">
-        <v>49</v>
+        <v>234</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>48</v>
+        <v>235</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>5</v>
@@ -12204,37 +12401,39 @@
         <v>10</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>204</v>
+        <v>350</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>360</v>
+        <v>305</v>
       </c>
       <c r="I28" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J28" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K28" s="11">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L28" s="18"/>
-      <c r="M28" s="18">
-        <v>0.1</v>
-      </c>
+      <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="19"/>
       <c r="P28" s="18"/>
       <c r="Q28" s="18"/>
-      <c r="R28" s="18"/>
+      <c r="R28" s="18">
+        <v>0.2</v>
+      </c>
       <c r="S28" s="19"/>
       <c r="T28" s="18"/>
       <c r="U28" s="18"/>
-      <c r="V28" s="18"/>
+      <c r="V28" s="18">
+        <v>0.2</v>
+      </c>
       <c r="W28" s="19"/>
       <c r="X28" s="20"/>
       <c r="Y28" s="20"/>
@@ -12250,50 +12449,50 @@
       <c r="AI28" s="20"/>
       <c r="AJ28" s="20"/>
       <c r="AK28" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.1</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.4</v>
       </c>
       <c r="AL28" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:38">
       <c r="A29" s="4" t="s">
-        <v>49</v>
+        <v>234</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>48</v>
+        <v>235</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29" s="29">
-        <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
+        <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>100</v>
       </c>
       <c r="E29" s="29">
-        <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
+        <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>205</v>
+        <v>267</v>
       </c>
       <c r="G29" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="I29" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J29" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K29" s="11">
-        <v>15</v>
+        <v>0.5</v>
       </c>
       <c r="L29" s="18"/>
       <c r="M29" s="18"/>
@@ -12305,10 +12504,10 @@
       <c r="S29" s="19"/>
       <c r="T29" s="18"/>
       <c r="U29" s="18"/>
-      <c r="V29" s="18">
-        <v>0.3</v>
-      </c>
-      <c r="W29" s="19"/>
+      <c r="V29" s="18"/>
+      <c r="W29" s="19">
+        <v>0.5</v>
+      </c>
       <c r="X29" s="20"/>
       <c r="Y29" s="20"/>
       <c r="Z29" s="20"/>
@@ -12323,62 +12522,68 @@
       <c r="AI29" s="20"/>
       <c r="AJ29" s="20"/>
       <c r="AK29" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.3</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.5</v>
       </c>
       <c r="AL29" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>15</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30" spans="1:38">
       <c r="A30" s="4" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="E30" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="I30" s="11">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J30" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>2.4</v>
-      </c>
-      <c r="K30" s="11"/>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="K30" s="11">
+        <v>6</v>
+      </c>
       <c r="L30" s="18"/>
       <c r="M30" s="18"/>
       <c r="N30" s="18"/>
       <c r="O30" s="19"/>
       <c r="P30" s="18"/>
-      <c r="Q30" s="18"/>
+      <c r="Q30" s="18">
+        <v>0.2</v>
+      </c>
       <c r="R30" s="18"/>
       <c r="S30" s="19"/>
-      <c r="T30" s="18"/>
-      <c r="U30" s="18"/>
-      <c r="V30" s="18">
-        <v>0.06</v>
-      </c>
+      <c r="T30" s="18">
+        <v>-0.2</v>
+      </c>
+      <c r="U30" s="18">
+        <v>0.2</v>
+      </c>
+      <c r="V30" s="18"/>
       <c r="W30" s="19"/>
       <c r="X30" s="20"/>
       <c r="Y30" s="20"/>
@@ -12394,23 +12599,23 @@
       <c r="AI30" s="20"/>
       <c r="AJ30" s="20"/>
       <c r="AK30" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.06</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.4</v>
       </c>
       <c r="AL30" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>2.4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:38">
       <c r="A31" s="4" t="s">
-        <v>234</v>
+        <v>44</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>235</v>
+        <v>42</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="D31" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -12421,56 +12626,56 @@
         <v>10</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>358</v>
+        <v>297</v>
       </c>
       <c r="G31" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>311</v>
+        <v>351</v>
       </c>
       <c r="I31" s="11">
         <v>1</v>
       </c>
       <c r="J31" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0.39999999999999991</v>
-      </c>
-      <c r="K31" s="11">
-        <v>1</v>
-      </c>
+        <v>0.18181818181818185</v>
+      </c>
+      <c r="K31" s="11"/>
       <c r="L31" s="18">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="M31" s="18">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="N31" s="18">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="O31" s="18">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="P31" s="18">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="Q31" s="18">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="R31" s="18">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="S31" s="18">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="T31" s="18">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="U31" s="18">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="V31" s="18"/>
-      <c r="W31" s="19"/>
+      <c r="W31" s="19">
+        <v>0.04</v>
+      </c>
       <c r="X31" s="20"/>
       <c r="Y31" s="20"/>
       <c r="Z31" s="20"/>
@@ -12485,20 +12690,20 @@
       <c r="AI31" s="20"/>
       <c r="AJ31" s="20"/>
       <c r="AK31" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>9.9999999999999992E-2</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.05</v>
       </c>
       <c r="AL31" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>10</v>
+        <v>2.0000000000000004</v>
       </c>
     </row>
     <row r="32" spans="1:38">
       <c r="A32" s="4" t="s">
-        <v>234</v>
+        <v>44</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>235</v>
+        <v>42</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>5</v>
@@ -12512,7 +12717,7 @@
         <v>10</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>350</v>
+        <v>298</v>
       </c>
       <c r="G32" s="11" t="s">
         <v>229</v>
@@ -12521,30 +12726,30 @@
         <v>305</v>
       </c>
       <c r="I32" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K32" s="11">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L32" s="18"/>
       <c r="M32" s="18"/>
       <c r="N32" s="18"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="18"/>
+      <c r="O32" s="19">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="P32" s="19"/>
       <c r="Q32" s="18"/>
-      <c r="R32" s="18">
-        <v>0.2</v>
-      </c>
-      <c r="S32" s="19"/>
+      <c r="R32" s="18"/>
+      <c r="S32" s="18">
+        <v>7.4999999999999997E-2</v>
+      </c>
       <c r="T32" s="18"/>
       <c r="U32" s="18"/>
-      <c r="V32" s="18">
-        <v>0.2</v>
-      </c>
+      <c r="V32" s="18"/>
       <c r="W32" s="19"/>
       <c r="X32" s="20"/>
       <c r="Y32" s="20"/>
@@ -12560,50 +12765,50 @@
       <c r="AI32" s="20"/>
       <c r="AJ32" s="20"/>
       <c r="AK32" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.4</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.15</v>
       </c>
       <c r="AL32" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:38">
       <c r="A33" s="4" t="s">
-        <v>234</v>
+        <v>44</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>235</v>
+        <v>42</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c r="D33" s="29">
-        <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
+        <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
       <c r="E33" s="29">
-        <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
+        <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>267</v>
+        <v>208</v>
       </c>
       <c r="G33" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="I33" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J33" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K33" s="11">
-        <v>0.5</v>
+        <v>15</v>
       </c>
       <c r="L33" s="18"/>
       <c r="M33" s="18"/>
@@ -12611,14 +12816,14 @@
       <c r="O33" s="19"/>
       <c r="P33" s="18"/>
       <c r="Q33" s="18"/>
-      <c r="R33" s="18"/>
+      <c r="R33" s="18">
+        <v>0.2</v>
+      </c>
       <c r="S33" s="19"/>
       <c r="T33" s="18"/>
       <c r="U33" s="18"/>
       <c r="V33" s="18"/>
-      <c r="W33" s="19">
-        <v>0.5</v>
-      </c>
+      <c r="W33" s="19"/>
       <c r="X33" s="20"/>
       <c r="Y33" s="20"/>
       <c r="Z33" s="20"/>
@@ -12633,69 +12838,65 @@
       <c r="AI33" s="20"/>
       <c r="AJ33" s="20"/>
       <c r="AK33" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.5</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.2</v>
       </c>
       <c r="AL33" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>0.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" spans="1:38">
       <c r="A34" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="D34" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E34" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>206</v>
+        <v>299</v>
       </c>
       <c r="G34" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="I34" s="11">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J34" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>2.6666666666666665</v>
+        <v>24</v>
       </c>
       <c r="K34" s="11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L34" s="18"/>
       <c r="M34" s="18"/>
       <c r="N34" s="18"/>
       <c r="O34" s="19"/>
       <c r="P34" s="18"/>
-      <c r="Q34" s="18">
-        <v>0.2</v>
-      </c>
+      <c r="Q34" s="18"/>
       <c r="R34" s="18"/>
       <c r="S34" s="19"/>
-      <c r="T34" s="18">
-        <v>-0.2</v>
-      </c>
-      <c r="U34" s="18">
-        <v>0.2</v>
-      </c>
+      <c r="T34" s="18"/>
+      <c r="U34" s="18"/>
       <c r="V34" s="18"/>
-      <c r="W34" s="19"/>
+      <c r="W34" s="19">
+        <v>0.6</v>
+      </c>
       <c r="X34" s="20"/>
       <c r="Y34" s="20"/>
       <c r="Z34" s="20"/>
@@ -12710,37 +12911,37 @@
       <c r="AI34" s="20"/>
       <c r="AJ34" s="20"/>
       <c r="AK34" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.6</v>
       </c>
       <c r="AL34" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:38">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:38" ht="14.65" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D35" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E35" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>297</v>
+        <v>373</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="H35" s="11" t="s">
         <v>351</v>
@@ -12750,43 +12951,33 @@
       </c>
       <c r="J35" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0.18181818181818185</v>
-      </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="18">
-        <v>1E-3</v>
-      </c>
-      <c r="M35" s="18">
-        <v>1E-3</v>
-      </c>
-      <c r="N35" s="18">
-        <v>1E-3</v>
-      </c>
-      <c r="O35" s="18">
-        <v>1E-3</v>
-      </c>
-      <c r="P35" s="18">
-        <v>1E-3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="K35" s="11">
+        <v>3</v>
+      </c>
+      <c r="L35" s="18"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="19"/>
+      <c r="P35" s="18"/>
       <c r="Q35" s="18">
-        <v>1E-3</v>
+        <v>0.05</v>
       </c>
       <c r="R35" s="18">
-        <v>1E-3</v>
+        <v>0.05</v>
       </c>
       <c r="S35" s="18">
-        <v>1E-3</v>
+        <v>0.05</v>
       </c>
       <c r="T35" s="18">
-        <v>1E-3</v>
+        <v>0.05</v>
       </c>
       <c r="U35" s="18">
-        <v>1E-3</v>
+        <v>0.05</v>
       </c>
       <c r="V35" s="18"/>
-      <c r="W35" s="19">
-        <v>0.04</v>
-      </c>
+      <c r="W35" s="19"/>
       <c r="X35" s="20"/>
       <c r="Y35" s="20"/>
       <c r="Z35" s="20"/>
@@ -12801,34 +12992,34 @@
       <c r="AI35" s="20"/>
       <c r="AJ35" s="20"/>
       <c r="AK35" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.05</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.25</v>
       </c>
       <c r="AL35" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>2.0000000000000004</v>
-      </c>
-    </row>
-    <row r="36" spans="1:38">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:38" ht="14.65" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>5</v>
+        <v>371</v>
       </c>
       <c r="D36" s="29">
-        <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
+        <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>100</v>
       </c>
       <c r="E36" s="29">
-        <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
+        <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>298</v>
+        <v>372</v>
       </c>
       <c r="G36" s="11" t="s">
         <v>229</v>
@@ -12837,31 +13028,29 @@
         <v>305</v>
       </c>
       <c r="I36" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
+        <v>6</v>
+      </c>
+      <c r="K36" s="11">
         <v>3</v>
-      </c>
-      <c r="K36" s="11">
-        <v>2</v>
       </c>
       <c r="L36" s="18"/>
       <c r="M36" s="18"/>
       <c r="N36" s="18"/>
-      <c r="O36" s="19">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="P36" s="19"/>
+      <c r="O36" s="19"/>
+      <c r="P36" s="18"/>
       <c r="Q36" s="18"/>
       <c r="R36" s="18"/>
-      <c r="S36" s="18">
-        <v>7.4999999999999997E-2</v>
-      </c>
+      <c r="S36" s="19"/>
       <c r="T36" s="18"/>
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
-      <c r="W36" s="19"/>
+      <c r="W36" s="19">
+        <v>0.15</v>
+      </c>
       <c r="X36" s="20"/>
       <c r="Y36" s="20"/>
       <c r="Z36" s="20"/>
@@ -12876,65 +13065,63 @@
       <c r="AI36" s="20"/>
       <c r="AJ36" s="20"/>
       <c r="AK36" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.15</v>
       </c>
       <c r="AL36" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:38">
       <c r="A37" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="D37" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E37" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G37" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="I37" s="11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J37" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
         <v>8</v>
       </c>
-      <c r="K37" s="11">
-        <v>15</v>
-      </c>
+      <c r="K37" s="11"/>
       <c r="L37" s="18"/>
       <c r="M37" s="18"/>
       <c r="N37" s="18"/>
       <c r="O37" s="19"/>
       <c r="P37" s="18"/>
       <c r="Q37" s="18"/>
-      <c r="R37" s="18">
-        <v>0.2</v>
-      </c>
+      <c r="R37" s="18"/>
       <c r="S37" s="19"/>
       <c r="T37" s="18"/>
       <c r="U37" s="18"/>
       <c r="V37" s="18"/>
-      <c r="W37" s="19"/>
+      <c r="W37" s="19">
+        <v>0.2</v>
+      </c>
       <c r="X37" s="20"/>
       <c r="Y37" s="20"/>
       <c r="Z37" s="20"/>
@@ -12949,23 +13136,23 @@
       <c r="AI37" s="20"/>
       <c r="AJ37" s="20"/>
       <c r="AK37" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL37" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:38" ht="28">
       <c r="A38" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D38" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -12975,39 +13162,43 @@
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F38" s="11" t="s">
-        <v>299</v>
+      <c r="F38" s="37" t="s">
+        <v>293</v>
       </c>
       <c r="G38" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>305</v>
+        <v>360</v>
       </c>
       <c r="I38" s="11">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J38" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>24</v>
+        <v>7.2000000000000011</v>
       </c>
       <c r="K38" s="11">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L38" s="18"/>
       <c r="M38" s="18"/>
       <c r="N38" s="18"/>
-      <c r="O38" s="19"/>
+      <c r="O38" s="18">
+        <v>0.18</v>
+      </c>
       <c r="P38" s="18"/>
       <c r="Q38" s="18"/>
-      <c r="R38" s="18"/>
+      <c r="R38" s="18">
+        <v>0.18</v>
+      </c>
       <c r="S38" s="19"/>
       <c r="T38" s="18"/>
-      <c r="U38" s="18"/>
+      <c r="U38" s="18">
+        <v>0.18</v>
+      </c>
       <c r="V38" s="18"/>
-      <c r="W38" s="19">
-        <v>0.6</v>
-      </c>
+      <c r="W38" s="19"/>
       <c r="X38" s="20"/>
       <c r="Y38" s="20"/>
       <c r="Z38" s="20"/>
@@ -13022,71 +13213,63 @@
       <c r="AI38" s="20"/>
       <c r="AJ38" s="20"/>
       <c r="AK38" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.6</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.54</v>
       </c>
       <c r="AL38" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:38" ht="14.65" customHeight="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="1:38">
       <c r="A39" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
       <c r="D39" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="E39" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>373</v>
+        <v>204</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="I39" s="11">
         <v>1</v>
       </c>
       <c r="J39" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K39" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L39" s="18"/>
-      <c r="M39" s="18"/>
+      <c r="M39" s="18">
+        <v>0.1</v>
+      </c>
       <c r="N39" s="18"/>
       <c r="O39" s="19"/>
       <c r="P39" s="18"/>
-      <c r="Q39" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="R39" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="S39" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="T39" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="U39" s="18">
-        <v>0.05</v>
-      </c>
+      <c r="Q39" s="18"/>
+      <c r="R39" s="18"/>
+      <c r="S39" s="19"/>
+      <c r="T39" s="18"/>
+      <c r="U39" s="18"/>
       <c r="V39" s="18"/>
       <c r="W39" s="19"/>
       <c r="X39" s="20"/>
@@ -13103,34 +13286,34 @@
       <c r="AI39" s="20"/>
       <c r="AJ39" s="20"/>
       <c r="AK39" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.25</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.1</v>
       </c>
       <c r="AL39" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:38" ht="14.65" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:38">
       <c r="A40" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>371</v>
+        <v>5</v>
       </c>
       <c r="D40" s="29">
-        <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
-        <v>50</v>
+        <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
+        <v>100</v>
       </c>
       <c r="E40" s="29">
-        <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
+        <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>372</v>
+        <v>205</v>
       </c>
       <c r="G40" s="11" t="s">
         <v>229</v>
@@ -13139,14 +13322,14 @@
         <v>305</v>
       </c>
       <c r="I40" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J40" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K40" s="11">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L40" s="18"/>
       <c r="M40" s="18"/>
@@ -13158,10 +13341,10 @@
       <c r="S40" s="19"/>
       <c r="T40" s="18"/>
       <c r="U40" s="18"/>
-      <c r="V40" s="18"/>
-      <c r="W40" s="19">
-        <v>0.15</v>
-      </c>
+      <c r="V40" s="18">
+        <v>0.3</v>
+      </c>
+      <c r="W40" s="19"/>
       <c r="X40" s="20"/>
       <c r="Y40" s="20"/>
       <c r="Z40" s="20"/>
@@ -13176,47 +13359,47 @@
       <c r="AI40" s="20"/>
       <c r="AJ40" s="20"/>
       <c r="AK40" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.15</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.3</v>
       </c>
       <c r="AL40" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:38">
       <c r="A41" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C41" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D41" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="E41" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>205</v>
+        <v>260</v>
       </c>
       <c r="G41" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="I41" s="11">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J41" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>8</v>
+        <v>2.4</v>
       </c>
       <c r="K41" s="11"/>
       <c r="L41" s="18"/>
@@ -13229,10 +13412,10 @@
       <c r="S41" s="19"/>
       <c r="T41" s="18"/>
       <c r="U41" s="18"/>
-      <c r="V41" s="18"/>
-      <c r="W41" s="19">
-        <v>0.2</v>
-      </c>
+      <c r="V41" s="18">
+        <v>0.06</v>
+      </c>
+      <c r="W41" s="19"/>
       <c r="X41" s="20"/>
       <c r="Y41" s="20"/>
       <c r="Z41" s="20"/>
@@ -13247,12 +13430,12 @@
       <c r="AI41" s="20"/>
       <c r="AJ41" s="20"/>
       <c r="AK41" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.06</v>
       </c>
       <c r="AL41" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="42" spans="1:38">
@@ -13356,7 +13539,7 @@
       <c r="AI42" s="20"/>
       <c r="AJ42" s="20"/>
       <c r="AK42" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.95000000000000029</v>
       </c>
       <c r="AL42" s="27">
@@ -13429,7 +13612,7 @@
       <c r="AI43" s="20"/>
       <c r="AJ43" s="20"/>
       <c r="AK43" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.05</v>
       </c>
       <c r="AL43" s="27">
@@ -13506,7 +13689,7 @@
       <c r="AI44" s="20"/>
       <c r="AJ44" s="20"/>
       <c r="AK44" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="AL44" s="27">
@@ -13583,7 +13766,7 @@
       <c r="AI45" s="20"/>
       <c r="AJ45" s="20"/>
       <c r="AK45" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="AL45" s="27">
@@ -13656,7 +13839,7 @@
       <c r="AI46" s="22"/>
       <c r="AJ46" s="22"/>
       <c r="AK46" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.05</v>
       </c>
       <c r="AL46" s="27">
@@ -13729,7 +13912,7 @@
       <c r="AI47" s="20"/>
       <c r="AJ47" s="20"/>
       <c r="AK47" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
       <c r="AL47" s="27">
@@ -13840,7 +14023,7 @@
       <c r="AI48" s="20"/>
       <c r="AJ48" s="20"/>
       <c r="AK48" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>1.0000000000000002</v>
       </c>
       <c r="AL48" s="27">
@@ -13919,7 +14102,7 @@
       <c r="AI49" s="20"/>
       <c r="AJ49" s="20"/>
       <c r="AK49" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.4</v>
       </c>
       <c r="AL49" s="27">
@@ -13990,7 +14173,7 @@
       <c r="AI50" s="20"/>
       <c r="AJ50" s="20"/>
       <c r="AK50" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL50" s="27">
@@ -14063,7 +14246,7 @@
       <c r="AI51" s="20"/>
       <c r="AJ51" s="20"/>
       <c r="AK51" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL51" s="27">
@@ -14134,7 +14317,7 @@
       <c r="AI52" s="20"/>
       <c r="AJ52" s="20"/>
       <c r="AK52" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
       <c r="AL52" s="27">
@@ -14215,7 +14398,7 @@
       <c r="AI53" s="20"/>
       <c r="AJ53" s="20"/>
       <c r="AK53" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL53" s="27">
@@ -14290,7 +14473,7 @@
       <c r="AI54" s="20"/>
       <c r="AJ54" s="20"/>
       <c r="AK54" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL54" s="27">
@@ -14367,8 +14550,8 @@
       <c r="AI55" s="20"/>
       <c r="AJ55" s="20"/>
       <c r="AK55" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AL55" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -14446,7 +14629,7 @@
       <c r="AI56" s="20"/>
       <c r="AJ56" s="20"/>
       <c r="AK56" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.15</v>
       </c>
       <c r="AL56" s="27">
@@ -14525,7 +14708,7 @@
       <c r="AI57" s="20"/>
       <c r="AJ57" s="20"/>
       <c r="AK57" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.15</v>
       </c>
       <c r="AL57" s="27">
@@ -14596,7 +14779,7 @@
       <c r="AI58" s="20"/>
       <c r="AJ58" s="20"/>
       <c r="AK58" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL58" s="27">
@@ -14667,7 +14850,7 @@
       </c>
       <c r="AJ59" s="20"/>
       <c r="AK59" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL59" s="27">
@@ -14754,7 +14937,7 @@
       <c r="AI60" s="20"/>
       <c r="AJ60" s="20"/>
       <c r="AK60" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.71999999999999986</v>
       </c>
       <c r="AL60" s="27">
@@ -14825,7 +15008,7 @@
       <c r="AI61" s="20"/>
       <c r="AJ61" s="20"/>
       <c r="AK61" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.13</v>
       </c>
       <c r="AL61" s="27">
@@ -14898,7 +15081,7 @@
       <c r="AI62" s="20"/>
       <c r="AJ62" s="20"/>
       <c r="AK62" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.05</v>
       </c>
       <c r="AL62" s="27">
@@ -14969,7 +15152,7 @@
       <c r="AI63" s="20"/>
       <c r="AJ63" s="20"/>
       <c r="AK63" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL63" s="27">
@@ -15056,7 +15239,7 @@
       <c r="AI64" s="20"/>
       <c r="AJ64" s="20"/>
       <c r="AK64" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.71999999999999986</v>
       </c>
       <c r="AL64" s="27">
@@ -15127,7 +15310,7 @@
       <c r="AI65" s="20"/>
       <c r="AJ65" s="20"/>
       <c r="AK65" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.13</v>
       </c>
       <c r="AL65" s="27">
@@ -15200,7 +15383,7 @@
       <c r="AI66" s="20"/>
       <c r="AJ66" s="20"/>
       <c r="AK66" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.05</v>
       </c>
       <c r="AL66" s="27">
@@ -15271,7 +15454,7 @@
       <c r="AI67" s="20"/>
       <c r="AJ67" s="20"/>
       <c r="AK67" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL67" s="27">
@@ -15358,7 +15541,7 @@
       <c r="AI68" s="20"/>
       <c r="AJ68" s="20"/>
       <c r="AK68" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.09</v>
       </c>
       <c r="AL68" s="27">
@@ -15431,7 +15614,7 @@
       <c r="AI69" s="20"/>
       <c r="AJ69" s="20"/>
       <c r="AK69" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL69" s="27">
@@ -15502,7 +15685,7 @@
       <c r="AI70" s="20"/>
       <c r="AJ70" s="20"/>
       <c r="AK70" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL70" s="27">
@@ -15598,7 +15781,7 @@
       <c r="AI71" s="20"/>
       <c r="AJ71" s="20"/>
       <c r="AK71" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
       <c r="AL71" s="27">
@@ -15683,7 +15866,7 @@
       <c r="AI72" s="20"/>
       <c r="AJ72" s="20"/>
       <c r="AK72" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.5</v>
       </c>
       <c r="AL72" s="27">
@@ -15758,7 +15941,7 @@
       <c r="AI73" s="20"/>
       <c r="AJ73" s="20"/>
       <c r="AK73" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL73" s="27">
@@ -15833,7 +16016,7 @@
       <c r="AI74" s="20"/>
       <c r="AJ74" s="20"/>
       <c r="AK74" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.8</v>
       </c>
       <c r="AL74" s="27">
@@ -15873,7 +16056,7 @@
       </c>
       <c r="J75" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>4</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="K75" s="11"/>
       <c r="L75" s="18"/>
@@ -15887,9 +16070,11 @@
       <c r="R75" s="23"/>
       <c r="S75" s="23"/>
       <c r="T75" s="23">
+        <v>-0.1</v>
+      </c>
+      <c r="U75" s="23">
         <v>0.1</v>
       </c>
-      <c r="U75" s="23"/>
       <c r="V75" s="23"/>
       <c r="W75" s="23"/>
       <c r="X75" s="20"/>
@@ -15906,12 +16091,12 @@
       <c r="AI75" s="20"/>
       <c r="AJ75" s="20"/>
       <c r="AK75" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL75" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>8</v>
+        <v>2.6666666666666665</v>
       </c>
     </row>
     <row r="76" spans="1:38">
@@ -15946,29 +16131,25 @@
       </c>
       <c r="J76" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K76" s="11">
         <v>9</v>
       </c>
       <c r="L76" s="18"/>
       <c r="M76" s="18"/>
-      <c r="N76" s="18">
+      <c r="N76" s="18"/>
+      <c r="O76" s="18">
         <v>0.25</v>
-      </c>
-      <c r="O76" s="18">
-        <v>-0.25</v>
       </c>
       <c r="P76" s="18">
         <v>0.25</v>
       </c>
       <c r="Q76" s="18"/>
       <c r="R76" s="18">
-        <v>-0.25</v>
-      </c>
-      <c r="S76" s="18">
         <v>0.25</v>
       </c>
+      <c r="S76" s="18"/>
       <c r="T76" s="24"/>
       <c r="U76" s="19"/>
       <c r="V76" s="19"/>
@@ -15987,8 +16168,8 @@
       <c r="AI76" s="20"/>
       <c r="AJ76" s="20"/>
       <c r="AK76" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.25</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.75</v>
       </c>
       <c r="AL76" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -16060,7 +16241,7 @@
       <c r="AI77" s="20"/>
       <c r="AJ77" s="20"/>
       <c r="AK77" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL77" s="27">
@@ -16133,7 +16314,7 @@
       <c r="AI78" s="20"/>
       <c r="AJ78" s="20"/>
       <c r="AK78" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.15</v>
       </c>
       <c r="AL78" s="27">
@@ -16165,7 +16346,9 @@
       <c r="G79" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H79" s="11"/>
+      <c r="H79" s="11" t="s">
+        <v>379</v>
+      </c>
       <c r="I79" s="11">
         <v>1</v>
       </c>
@@ -16218,7 +16401,7 @@
       <c r="AI79" s="20"/>
       <c r="AJ79" s="20"/>
       <c r="AK79" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.42500000000000004</v>
       </c>
       <c r="AL79" s="27">
@@ -16293,7 +16476,7 @@
       <c r="AI80" s="20"/>
       <c r="AJ80" s="20"/>
       <c r="AK80" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL80" s="27">
@@ -16368,7 +16551,7 @@
       <c r="AI81" s="20"/>
       <c r="AJ81" s="20"/>
       <c r="AK81" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.8</v>
       </c>
       <c r="AL81" s="27">
@@ -16459,7 +16642,7 @@
       <c r="AI82" s="20"/>
       <c r="AJ82" s="20"/>
       <c r="AK82" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="AL82" s="27">
@@ -16511,10 +16694,10 @@
       <c r="R83" s="26">
         <v>-0.2</v>
       </c>
-      <c r="S83" s="26">
+      <c r="S83" s="26"/>
+      <c r="T83" s="26">
         <v>0.2</v>
       </c>
-      <c r="T83" s="26"/>
       <c r="U83" s="26"/>
       <c r="V83" s="26"/>
       <c r="W83" s="23"/>
@@ -16532,8 +16715,8 @@
       <c r="AI83" s="20"/>
       <c r="AJ83" s="20"/>
       <c r="AK83" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.2</v>
       </c>
       <c r="AL83" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -16613,7 +16796,7 @@
       <c r="AI84" s="20"/>
       <c r="AJ84" s="20"/>
       <c r="AK84" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.15</v>
       </c>
       <c r="AL84" s="27">
@@ -16694,7 +16877,7 @@
       <c r="AI85" s="20"/>
       <c r="AJ85" s="20"/>
       <c r="AK85" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.15</v>
       </c>
       <c r="AL85" s="27">
@@ -16765,7 +16948,7 @@
       <c r="AI86" s="20"/>
       <c r="AJ86" s="20"/>
       <c r="AK86" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL86" s="27">
@@ -16836,7 +17019,7 @@
       <c r="AI87" s="20"/>
       <c r="AJ87" s="20"/>
       <c r="AK87" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL87" s="27">
@@ -16907,7 +17090,7 @@
       <c r="AI88" s="20"/>
       <c r="AJ88" s="20"/>
       <c r="AK88" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL88" s="27">
@@ -16978,7 +17161,7 @@
       <c r="AI89" s="20"/>
       <c r="AJ89" s="20"/>
       <c r="AK89" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.4</v>
       </c>
       <c r="AL89" s="27">
@@ -17049,7 +17232,7 @@
       <c r="AI90" s="20"/>
       <c r="AJ90" s="20"/>
       <c r="AK90" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL90" s="27">
@@ -17066,11 +17249,11 @@
       </c>
       <c r="C91" s="11"/>
       <c r="D91" s="29">
-        <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
-        <v>100</v>
+        <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
+        <v>20</v>
       </c>
       <c r="E91" s="29">
-        <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
+        <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F91" s="11" t="s">
@@ -17118,7 +17301,7 @@
       <c r="AI91" s="20"/>
       <c r="AJ91" s="20"/>
       <c r="AK91" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL91" s="27">
@@ -17150,7 +17333,9 @@
       <c r="G92" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H92" s="11"/>
+      <c r="H92" s="11" t="s">
+        <v>380</v>
+      </c>
       <c r="I92" s="11">
         <v>1</v>
       </c>
@@ -17207,7 +17392,7 @@
       <c r="AI92" s="20"/>
       <c r="AJ92" s="20"/>
       <c r="AK92" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AL92" s="27">
@@ -17280,7 +17465,7 @@
       <c r="AI93" s="20"/>
       <c r="AJ93" s="20"/>
       <c r="AK93" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="AL93" s="27">
@@ -17355,7 +17540,7 @@
       <c r="AI94" s="20"/>
       <c r="AJ94" s="20"/>
       <c r="AK94" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.23</v>
       </c>
       <c r="AL94" s="27">
@@ -17426,7 +17611,7 @@
       <c r="AI95" s="20"/>
       <c r="AJ95" s="20"/>
       <c r="AK95" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL95" s="27">
@@ -17445,12 +17630,12 @@
         <v>5</v>
       </c>
       <c r="D96" s="29">
-        <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
-        <v>30</v>
+        <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
+        <v>20</v>
       </c>
       <c r="E96" s="29">
-        <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
-        <v>20</v>
+        <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
+        <v>10</v>
       </c>
       <c r="F96" s="12" t="s">
         <v>363</v>
@@ -17466,7 +17651,7 @@
       </c>
       <c r="J96" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="K96" s="11"/>
       <c r="L96" s="18"/>
@@ -17497,12 +17682,12 @@
       <c r="AI96" s="20"/>
       <c r="AJ96" s="20"/>
       <c r="AK96" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.04</v>
       </c>
       <c r="AL96" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="97" spans="1:38" ht="28">
@@ -17516,11 +17701,11 @@
         <v>121</v>
       </c>
       <c r="D97" s="29">
-        <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
+        <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
       <c r="E97" s="29">
-        <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
+        <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F97" s="45" t="s">
@@ -17568,7 +17753,7 @@
       <c r="AI97" s="20"/>
       <c r="AJ97" s="20"/>
       <c r="AK97" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.16</v>
       </c>
       <c r="AL97" s="27">
@@ -17641,7 +17826,7 @@
       <c r="AI98" s="20"/>
       <c r="AJ98" s="20"/>
       <c r="AK98" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL98" s="27">
@@ -17714,7 +17899,7 @@
       <c r="AI99" s="20"/>
       <c r="AJ99" s="20"/>
       <c r="AK99" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL99" s="27">
@@ -17787,7 +17972,7 @@
       </c>
       <c r="AJ100" s="20"/>
       <c r="AK100" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.7</v>
       </c>
       <c r="AL100" s="27">
@@ -17860,7 +18045,7 @@
       </c>
       <c r="AJ101" s="20"/>
       <c r="AK101" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL101" s="27">
@@ -17933,7 +18118,7 @@
       </c>
       <c r="AJ102" s="20"/>
       <c r="AK102" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL102" s="27">
@@ -18004,7 +18189,7 @@
       <c r="AI103" s="20"/>
       <c r="AJ103" s="20"/>
       <c r="AK103" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL103" s="27">
@@ -18075,7 +18260,7 @@
       <c r="AI104" s="20"/>
       <c r="AJ104" s="20"/>
       <c r="AK104" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL104" s="27">
@@ -18148,7 +18333,7 @@
       <c r="AI105" s="20"/>
       <c r="AJ105" s="20"/>
       <c r="AK105" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL105" s="27">
@@ -18268,7 +18453,7 @@
       </c>
       <c r="AJ106" s="20"/>
       <c r="AK106" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.99999999999999956</v>
       </c>
       <c r="AL106" s="27">
@@ -18345,7 +18530,7 @@
       <c r="AI107" s="20"/>
       <c r="AJ107" s="20"/>
       <c r="AK107" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL107" s="27">
@@ -18418,7 +18603,7 @@
       <c r="AI108" s="20"/>
       <c r="AJ108" s="20"/>
       <c r="AK108" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.4</v>
       </c>
       <c r="AL108" s="27">
@@ -18491,7 +18676,7 @@
       <c r="AI109" s="20"/>
       <c r="AJ109" s="20"/>
       <c r="AK109" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL109" s="27">
@@ -18510,11 +18695,11 @@
         <v>123</v>
       </c>
       <c r="D110" s="29">
-        <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
+        <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
       <c r="E110" s="29">
-        <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
+        <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>30</v>
       </c>
       <c r="F110" s="11" t="s">
@@ -18564,7 +18749,7 @@
       <c r="AI110" s="20"/>
       <c r="AJ110" s="20"/>
       <c r="AK110" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.4</v>
       </c>
       <c r="AL110" s="27">
@@ -18583,11 +18768,11 @@
         <v>121</v>
       </c>
       <c r="D111" s="29">
-        <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
+        <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
       </c>
       <c r="E111" s="29">
-        <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
+        <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>30</v>
       </c>
       <c r="F111" s="11" t="s">
@@ -18637,7 +18822,7 @@
       <c r="AI111" s="20"/>
       <c r="AJ111" s="20"/>
       <c r="AK111" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL111" s="27">
@@ -18738,7 +18923,7 @@
       <c r="AI112" s="20"/>
       <c r="AJ112" s="20"/>
       <c r="AK112" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="AL112" s="27">
@@ -18811,8 +18996,8 @@
       <c r="AI113" s="20"/>
       <c r="AJ113" s="20"/>
       <c r="AK113" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.2</v>
       </c>
       <c r="AL113" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -18882,7 +19067,7 @@
       <c r="AI114" s="20"/>
       <c r="AJ114" s="20"/>
       <c r="AK114" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.15</v>
       </c>
       <c r="AL114" s="27">
@@ -18953,7 +19138,7 @@
       <c r="AI115" s="20"/>
       <c r="AJ115" s="20"/>
       <c r="AK115" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.15</v>
       </c>
       <c r="AL115" s="27">
@@ -19026,7 +19211,7 @@
       <c r="AI116" s="20"/>
       <c r="AJ116" s="20"/>
       <c r="AK116" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.25</v>
       </c>
       <c r="AL116" s="27">
@@ -19113,7 +19298,7 @@
       <c r="AI117" s="20"/>
       <c r="AJ117" s="20"/>
       <c r="AK117" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.08</v>
       </c>
       <c r="AL117" s="27">
@@ -19132,11 +19317,11 @@
         <v>5</v>
       </c>
       <c r="D118" s="29">
-        <f>INDEX([1]!Table2[CA weight],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
-        <v>25</v>
+        <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
+        <v>30</v>
       </c>
       <c r="E118" s="29">
-        <f>INDEX([1]!Table2[Credits],MATCH([1]!Table1[[#This Row],[Module Code]],[1]!Table2[Module Code],0))</f>
+        <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F118" s="11" t="s">
@@ -19186,7 +19371,7 @@
       <c r="AI118" s="20"/>
       <c r="AJ118" s="20"/>
       <c r="AK118" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.22</v>
       </c>
       <c r="AL118" s="27">
@@ -19271,7 +19456,7 @@
       <c r="AI119" s="20"/>
       <c r="AJ119" s="20"/>
       <c r="AK119" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>8.7499999999999994E-2</v>
       </c>
       <c r="AL119" s="27">
@@ -19342,7 +19527,7 @@
       <c r="AI120" s="20"/>
       <c r="AJ120" s="20"/>
       <c r="AK120" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL120" s="27">
@@ -19415,8 +19600,8 @@
       <c r="AI121" s="20"/>
       <c r="AJ121" s="20"/>
       <c r="AK121" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.35</v>
       </c>
       <c r="AL121" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -19488,7 +19673,7 @@
       <c r="AI122" s="20"/>
       <c r="AJ122" s="20"/>
       <c r="AK122" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="AL122" s="27">
@@ -19579,7 +19764,7 @@
       <c r="AI123" s="20"/>
       <c r="AJ123" s="20"/>
       <c r="AK123" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="AL123" s="27">
@@ -19656,7 +19841,7 @@
       <c r="AI124" s="20"/>
       <c r="AJ124" s="20"/>
       <c r="AK124" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.4</v>
       </c>
       <c r="AL124" s="27">
@@ -19727,7 +19912,7 @@
       <c r="AI125" s="20"/>
       <c r="AJ125" s="20"/>
       <c r="AK125" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL125" s="27">
@@ -19798,7 +19983,7 @@
       <c r="AI126" s="20"/>
       <c r="AJ126" s="20"/>
       <c r="AK126" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
       <c r="AL126" s="27">
@@ -19889,7 +20074,7 @@
       <c r="AI127" s="20"/>
       <c r="AJ127" s="20"/>
       <c r="AK127" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.19999999999999998</v>
       </c>
       <c r="AL127" s="27">
@@ -19960,7 +20145,7 @@
       <c r="AI128" s="20"/>
       <c r="AJ128" s="20"/>
       <c r="AK128" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL128" s="27">
@@ -20033,7 +20218,7 @@
       <c r="AI129" s="20"/>
       <c r="AJ129" s="20"/>
       <c r="AK129" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
       <c r="AL129" s="27">
@@ -20114,7 +20299,7 @@
       <c r="AI130" s="20"/>
       <c r="AJ130" s="20"/>
       <c r="AK130" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL130" s="27">
@@ -20195,7 +20380,7 @@
       <c r="AI131" s="20"/>
       <c r="AJ131" s="20"/>
       <c r="AK131" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL131" s="27">
@@ -20266,7 +20451,7 @@
       <c r="AI132" s="20"/>
       <c r="AJ132" s="20"/>
       <c r="AK132" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.4</v>
       </c>
       <c r="AL132" s="27">
@@ -20337,7 +20522,7 @@
       <c r="AI133" s="20"/>
       <c r="AJ133" s="20"/>
       <c r="AK133" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="AL133" s="27">
@@ -20410,7 +20595,7 @@
       <c r="AI134" s="20"/>
       <c r="AJ134" s="20"/>
       <c r="AK134" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.05</v>
       </c>
       <c r="AL134" s="27">
@@ -20514,7 +20699,7 @@
       <c r="AI135" s="20"/>
       <c r="AJ135" s="20"/>
       <c r="AK135" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.10000000000000002</v>
       </c>
       <c r="AL135" s="27">
@@ -20589,8 +20774,8 @@
       <c r="AI136" s="20"/>
       <c r="AJ136" s="20"/>
       <c r="AK136" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.4</v>
       </c>
       <c r="AL136" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -20668,7 +20853,7 @@
       <c r="AI137" s="20"/>
       <c r="AJ137" s="20"/>
       <c r="AK137" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.15</v>
       </c>
       <c r="AL137" s="27">
@@ -20747,7 +20932,7 @@
       <c r="AI138" s="20"/>
       <c r="AJ138" s="20"/>
       <c r="AK138" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.15</v>
       </c>
       <c r="AL138" s="27">
@@ -20818,7 +21003,7 @@
       </c>
       <c r="AJ139" s="20"/>
       <c r="AK139" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.5</v>
       </c>
       <c r="AL139" s="27">
@@ -20891,7 +21076,7 @@
       <c r="AI140" s="20"/>
       <c r="AJ140" s="20"/>
       <c r="AK140" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL140" s="27">
@@ -20964,8 +21149,8 @@
       <c r="AI141" s="20"/>
       <c r="AJ141" s="20"/>
       <c r="AK141" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0</v>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.2</v>
       </c>
       <c r="AL141" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -21035,7 +21220,7 @@
       <c r="AI142" s="20"/>
       <c r="AJ142" s="20"/>
       <c r="AK142" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL142" s="27">
@@ -21106,7 +21291,7 @@
       <c r="AI143" s="20"/>
       <c r="AJ143" s="20"/>
       <c r="AK143" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.4</v>
       </c>
       <c r="AL143" s="27">
@@ -21177,7 +21362,7 @@
       <c r="AI144" s="20"/>
       <c r="AJ144" s="20"/>
       <c r="AK144" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.4</v>
       </c>
       <c r="AL144" s="27">
@@ -21297,7 +21482,7 @@
       </c>
       <c r="AJ145" s="20"/>
       <c r="AK145" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.99999999999999956</v>
       </c>
       <c r="AL145" s="27">
@@ -21374,7 +21559,7 @@
       <c r="AI146" s="20"/>
       <c r="AJ146" s="20"/>
       <c r="AK146" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.125</v>
       </c>
       <c r="AL146" s="27">
@@ -21447,7 +21632,7 @@
       </c>
       <c r="AJ147" s="20"/>
       <c r="AK147" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.25</v>
       </c>
       <c r="AL147" s="27">
@@ -21520,7 +21705,7 @@
       <c r="AI148" s="20"/>
       <c r="AJ148" s="20"/>
       <c r="AK148" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL148" s="27">
@@ -21593,7 +21778,7 @@
       <c r="AI149" s="20"/>
       <c r="AJ149" s="20"/>
       <c r="AK149" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL149" s="27">
@@ -21666,7 +21851,7 @@
       </c>
       <c r="AJ150" s="20"/>
       <c r="AK150" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.4</v>
       </c>
       <c r="AL150" s="27">
@@ -21739,7 +21924,7 @@
         <v>0.15</v>
       </c>
       <c r="AK151" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0</v>
       </c>
       <c r="AL151" s="27">
@@ -21812,7 +21997,7 @@
         <v>0.15</v>
       </c>
       <c r="AK152" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0</v>
       </c>
       <c r="AL152" s="27">
@@ -21883,7 +22068,7 @@
       <c r="AI153" s="20"/>
       <c r="AJ153" s="20"/>
       <c r="AK153" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.4</v>
       </c>
       <c r="AL153" s="27">
@@ -21954,7 +22139,7 @@
       <c r="AI154" s="20"/>
       <c r="AJ154" s="20"/>
       <c r="AK154" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.4</v>
       </c>
       <c r="AL154" s="27">
@@ -22025,7 +22210,7 @@
       <c r="AI155" s="20"/>
       <c r="AJ155" s="20"/>
       <c r="AK155" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL155" s="27">
@@ -22098,7 +22283,7 @@
       <c r="AI156" s="20"/>
       <c r="AJ156" s="20"/>
       <c r="AK156" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>1</v>
       </c>
       <c r="AL156" s="27">
@@ -22187,7 +22372,7 @@
       <c r="AI157" s="20"/>
       <c r="AJ157" s="20"/>
       <c r="AK157" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.49999999999999994</v>
       </c>
       <c r="AL157" s="27">
@@ -22276,7 +22461,7 @@
       <c r="AI158" s="20"/>
       <c r="AJ158" s="20"/>
       <c r="AK158" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.19999999999999998</v>
       </c>
       <c r="AL158" s="27">
@@ -22347,7 +22532,7 @@
       <c r="AI159" s="20"/>
       <c r="AJ159" s="20"/>
       <c r="AK159" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
       <c r="AL159" s="27">
@@ -22418,7 +22603,7 @@
       <c r="AI160" s="20"/>
       <c r="AJ160" s="20"/>
       <c r="AK160" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.05</v>
       </c>
       <c r="AL160" s="27">
@@ -22489,7 +22674,7 @@
       <c r="AI161" s="20"/>
       <c r="AJ161" s="20"/>
       <c r="AK161" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.05</v>
       </c>
       <c r="AL161" s="27">
@@ -22560,7 +22745,7 @@
       <c r="AI162" s="20"/>
       <c r="AJ162" s="20"/>
       <c r="AK162" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
       <c r="AL162" s="27">
@@ -22633,7 +22818,7 @@
       <c r="AI163" s="20"/>
       <c r="AJ163" s="20"/>
       <c r="AK163" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
       <c r="AL163" s="27">
@@ -22706,7 +22891,7 @@
       <c r="AI164" s="20"/>
       <c r="AJ164" s="20"/>
       <c r="AK164" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
       <c r="AL164" s="27">
@@ -22779,7 +22964,7 @@
       <c r="AI165" s="20"/>
       <c r="AJ165" s="20"/>
       <c r="AK165" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL165" s="27">
@@ -22850,7 +23035,7 @@
       <c r="AI166" s="20"/>
       <c r="AJ166" s="20"/>
       <c r="AK166" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.05</v>
       </c>
       <c r="AL166" s="27">
@@ -22923,7 +23108,7 @@
       <c r="AI167" s="20"/>
       <c r="AJ167" s="20"/>
       <c r="AK167" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
       <c r="AL167" s="27">
@@ -22994,7 +23179,7 @@
       <c r="AI168" s="20"/>
       <c r="AJ168" s="20"/>
       <c r="AK168" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
       <c r="AL168" s="27">
@@ -23065,7 +23250,7 @@
       </c>
       <c r="AJ169" s="20"/>
       <c r="AK169" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.45</v>
       </c>
       <c r="AL169" s="27">
@@ -23083,13 +23268,13 @@
       <c r="C170" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D170" s="29" t="e">
+      <c r="D170" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E170" s="29" t="e">
+        <v>30</v>
+      </c>
+      <c r="E170" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>#N/A</v>
+        <v>10</v>
       </c>
       <c r="F170" s="11" t="s">
         <v>321</v>
@@ -23103,9 +23288,9 @@
       <c r="I170" s="11">
         <v>4</v>
       </c>
-      <c r="J170" s="11" t="e">
+      <c r="J170" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>#N/A</v>
+        <v>4</v>
       </c>
       <c r="K170" s="11"/>
       <c r="L170" s="18"/>
@@ -23136,12 +23321,12 @@
       <c r="AI170" s="20"/>
       <c r="AJ170" s="20"/>
       <c r="AK170" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.1</v>
       </c>
-      <c r="AL170" s="27" t="e">
+      <c r="AL170" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>#N/A</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171" spans="1:38">
@@ -23154,13 +23339,13 @@
       <c r="C171" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D171" s="29" t="e">
+      <c r="D171" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E171" s="29" t="e">
+        <v>30</v>
+      </c>
+      <c r="E171" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>#N/A</v>
+        <v>10</v>
       </c>
       <c r="F171" s="11" t="s">
         <v>323</v>
@@ -23174,9 +23359,9 @@
       <c r="I171" s="11">
         <v>6</v>
       </c>
-      <c r="J171" s="11" t="e">
+      <c r="J171" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>#N/A</v>
+        <v>8</v>
       </c>
       <c r="K171" s="11"/>
       <c r="L171" s="18"/>
@@ -23207,12 +23392,12 @@
       <c r="AI171" s="20"/>
       <c r="AJ171" s="20"/>
       <c r="AK171" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
-      <c r="AL171" s="27" t="e">
+      <c r="AL171" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>#N/A</v>
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:38">
@@ -23225,13 +23410,13 @@
       <c r="C172" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D172" s="29" t="e">
+      <c r="D172" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E172" s="29" t="e">
+        <v>100</v>
+      </c>
+      <c r="E172" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>#N/A</v>
+        <v>10</v>
       </c>
       <c r="F172" s="11" t="s">
         <v>326</v>
@@ -23245,9 +23430,9 @@
       <c r="I172" s="11">
         <v>3</v>
       </c>
-      <c r="J172" s="11" t="e">
+      <c r="J172" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>#N/A</v>
+        <v>8</v>
       </c>
       <c r="K172" s="11"/>
       <c r="L172" s="18"/>
@@ -23278,12 +23463,12 @@
       <c r="AI172" s="20"/>
       <c r="AJ172" s="20"/>
       <c r="AK172" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.2</v>
       </c>
-      <c r="AL172" s="27" t="e">
+      <c r="AL172" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>#N/A</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:38">
@@ -23296,13 +23481,13 @@
       <c r="C173" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D173" s="29" t="e">
+      <c r="D173" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E173" s="29" t="e">
+        <v>100</v>
+      </c>
+      <c r="E173" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>#N/A</v>
+        <v>10</v>
       </c>
       <c r="F173" s="11" t="s">
         <v>328</v>
@@ -23316,9 +23501,9 @@
       <c r="I173" s="11">
         <v>8</v>
       </c>
-      <c r="J173" s="11" t="e">
+      <c r="J173" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>#N/A</v>
+        <v>20</v>
       </c>
       <c r="K173" s="11"/>
       <c r="L173" s="18"/>
@@ -23349,12 +23534,12 @@
       </c>
       <c r="AJ173" s="20"/>
       <c r="AK173" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.5</v>
       </c>
-      <c r="AL173" s="27" t="e">
+      <c r="AL173" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>#N/A</v>
+        <v>20</v>
       </c>
     </row>
     <row r="174" spans="1:38">
@@ -23367,13 +23552,13 @@
       <c r="C174" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D174" s="29" t="e">
+      <c r="D174" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E174" s="29" t="e">
+        <v>100</v>
+      </c>
+      <c r="E174" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>#N/A</v>
+        <v>10</v>
       </c>
       <c r="F174" s="11" t="s">
         <v>329</v>
@@ -23387,9 +23572,9 @@
       <c r="I174" s="11">
         <v>3</v>
       </c>
-      <c r="J174" s="11" t="e">
+      <c r="J174" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>#N/A</v>
+        <v>12</v>
       </c>
       <c r="K174" s="11"/>
       <c r="L174" s="18"/>
@@ -23420,12 +23605,12 @@
       </c>
       <c r="AJ174" s="20"/>
       <c r="AK174" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
-      <c r="AL174" s="27" t="e">
+      <c r="AL174" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>#N/A</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175" spans="1:38">
@@ -23438,13 +23623,13 @@
       <c r="C175" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D175" s="29" t="e">
+      <c r="D175" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E175" s="29" t="e">
+        <v>100</v>
+      </c>
+      <c r="E175" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>#N/A</v>
+        <v>20</v>
       </c>
       <c r="F175" s="11" t="s">
         <v>332</v>
@@ -23458,9 +23643,9 @@
       <c r="I175" s="11">
         <v>4</v>
       </c>
-      <c r="J175" s="11" t="e">
+      <c r="J175" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>#N/A</v>
+        <v>40</v>
       </c>
       <c r="K175" s="11">
         <v>20</v>
@@ -23493,7 +23678,7 @@
       </c>
       <c r="AJ175" s="20"/>
       <c r="AK175" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.5</v>
       </c>
       <c r="AL175" s="27">
@@ -23511,13 +23696,13 @@
       <c r="C176" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D176" s="29" t="e">
+      <c r="D176" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E176" s="29" t="e">
+        <v>100</v>
+      </c>
+      <c r="E176" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>#N/A</v>
+        <v>20</v>
       </c>
       <c r="F176" s="11" t="s">
         <v>333</v>
@@ -23531,9 +23716,9 @@
       <c r="I176" s="11">
         <v>1</v>
       </c>
-      <c r="J176" s="11" t="e">
+      <c r="J176" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>#N/A</v>
+        <v>40</v>
       </c>
       <c r="K176" s="11">
         <v>1</v>
@@ -23566,7 +23751,7 @@
       <c r="AI176" s="20"/>
       <c r="AJ176" s="20"/>
       <c r="AK176" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.5</v>
       </c>
       <c r="AL176" s="27">
@@ -23584,13 +23769,13 @@
       <c r="C177" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D177" s="29" t="e">
+      <c r="D177" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E177" s="29" t="e">
+        <v>50</v>
+      </c>
+      <c r="E177" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>#N/A</v>
+        <v>20</v>
       </c>
       <c r="F177" s="11" t="s">
         <v>336</v>
@@ -23604,9 +23789,9 @@
       <c r="I177" s="11">
         <v>2</v>
       </c>
-      <c r="J177" s="11" t="e">
+      <c r="J177" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>#N/A</v>
+        <v>40</v>
       </c>
       <c r="K177" s="11">
         <v>8</v>
@@ -23639,7 +23824,7 @@
       <c r="AI177" s="20"/>
       <c r="AJ177" s="20"/>
       <c r="AK177" s="27">
-        <f>SUM(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.5</v>
       </c>
       <c r="AL177" s="27">
@@ -29813,7 +29998,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D548CE7-BEAC-43FA-847F-FDE82E3A5926}">
-  <dimension ref="A1:T127"/>
+  <dimension ref="A1:W129"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
@@ -29826,7 +30011,7 @@
     <col min="8" max="8" width="9" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:23">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -29873,22 +30058,31 @@
         <v>197</v>
       </c>
       <c r="P1" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="R1" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="S1" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="T1" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:23">
       <c r="A2" s="4" t="s">
         <v>55</v>
       </c>
@@ -29923,22 +30117,22 @@
       <c r="L2" t="s">
         <v>143</v>
       </c>
-      <c r="Q2">
+      <c r="T2">
         <v>4</v>
       </c>
-      <c r="R2">
+      <c r="U2">
         <v>60</v>
       </c>
-      <c r="S2">
+      <c r="V2">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="T2">
+      <c r="W2">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:23">
       <c r="A3" s="4" t="s">
         <v>252</v>
       </c>
@@ -29973,22 +30167,22 @@
       <c r="L3" t="s">
         <v>143</v>
       </c>
-      <c r="Q3">
+      <c r="T3">
         <v>4</v>
       </c>
-      <c r="R3">
+      <c r="U3">
         <v>60</v>
       </c>
-      <c r="S3">
+      <c r="V3">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="T3">
+      <c r="W3">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:23">
       <c r="A4" s="4" t="s">
         <v>255</v>
       </c>
@@ -30023,22 +30217,22 @@
       <c r="L4" t="s">
         <v>143</v>
       </c>
-      <c r="Q4">
-        <v>2</v>
-      </c>
-      <c r="R4">
+      <c r="T4">
+        <v>2</v>
+      </c>
+      <c r="U4">
         <v>50</v>
       </c>
-      <c r="S4">
+      <c r="V4">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>50</v>
       </c>
-      <c r="T4">
+      <c r="W4">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:23">
       <c r="A5" s="4" t="s">
         <v>59</v>
       </c>
@@ -30073,22 +30267,22 @@
       <c r="L5" t="s">
         <v>143</v>
       </c>
-      <c r="Q5">
+      <c r="T5">
         <v>4</v>
       </c>
-      <c r="R5">
+      <c r="U5">
         <v>0</v>
       </c>
-      <c r="S5">
+      <c r="V5">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T5">
+      <c r="W5">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:23">
       <c r="A6" s="3" t="s">
         <v>81</v>
       </c>
@@ -30123,22 +30317,22 @@
       <c r="L6" t="s">
         <v>143</v>
       </c>
-      <c r="Q6">
+      <c r="T6">
         <v>4</v>
       </c>
-      <c r="R6">
+      <c r="U6">
         <v>70</v>
       </c>
-      <c r="S6">
+      <c r="V6">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="T6">
+      <c r="W6">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30.000000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:23">
       <c r="A7" s="3" t="s">
         <v>187</v>
       </c>
@@ -30173,22 +30367,22 @@
       <c r="L7" t="s">
         <v>143</v>
       </c>
-      <c r="Q7">
+      <c r="T7">
         <v>3</v>
       </c>
-      <c r="R7">
+      <c r="U7">
         <v>0</v>
       </c>
-      <c r="S7">
+      <c r="V7">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T7">
+      <c r="W7">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
       <c r="A8" s="3" t="s">
         <v>83</v>
       </c>
@@ -30225,22 +30419,25 @@
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
       <c r="P8" s="6"/>
-      <c r="Q8" s="6">
-        <v>2</v>
-      </c>
-      <c r="R8">
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6">
+        <v>2</v>
+      </c>
+      <c r="U8">
         <v>70</v>
       </c>
-      <c r="S8">
+      <c r="V8">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="T8">
+      <c r="W8">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
+        <v>30.000000000000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
       <c r="A9" s="3" t="s">
         <v>84</v>
       </c>
@@ -30275,22 +30472,22 @@
       <c r="L9" t="s">
         <v>143</v>
       </c>
-      <c r="Q9">
-        <v>2</v>
-      </c>
-      <c r="R9">
+      <c r="T9">
+        <v>2</v>
+      </c>
+      <c r="U9">
         <v>60</v>
       </c>
-      <c r="S9">
+      <c r="V9">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="T9">
+      <c r="W9">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:23">
       <c r="A10" s="7" t="s">
         <v>82</v>
       </c>
@@ -30321,22 +30518,22 @@
       <c r="L10" t="s">
         <v>143</v>
       </c>
-      <c r="Q10">
-        <v>2</v>
-      </c>
-      <c r="R10">
+      <c r="T10">
+        <v>2</v>
+      </c>
+      <c r="U10">
         <v>80</v>
       </c>
-      <c r="S10">
+      <c r="V10">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="T10">
+      <c r="W10">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:23">
       <c r="A11" s="3" t="s">
         <v>215</v>
       </c>
@@ -30371,22 +30568,22 @@
       <c r="L11" t="s">
         <v>143</v>
       </c>
-      <c r="Q11">
+      <c r="T11">
         <v>1</v>
       </c>
-      <c r="R11">
+      <c r="U11">
         <v>0</v>
       </c>
-      <c r="S11">
+      <c r="V11">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T11">
+      <c r="W11">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:23">
       <c r="A12" s="4" t="s">
         <v>37</v>
       </c>
@@ -30421,22 +30618,22 @@
       <c r="L12" t="s">
         <v>143</v>
       </c>
-      <c r="Q12">
+      <c r="T12">
         <v>4</v>
       </c>
-      <c r="R12">
+      <c r="U12">
         <v>60</v>
       </c>
-      <c r="S12">
+      <c r="V12">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="T12">
+      <c r="W12">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
       <c r="A13" s="4" t="s">
         <v>258</v>
       </c>
@@ -30471,22 +30668,22 @@
       <c r="L13" t="s">
         <v>143</v>
       </c>
-      <c r="Q13">
+      <c r="T13">
         <v>3</v>
       </c>
-      <c r="R13">
+      <c r="U13">
         <v>60</v>
       </c>
-      <c r="S13">
+      <c r="V13">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="T13">
+      <c r="W13">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
       <c r="A14" s="4" t="s">
         <v>49</v>
       </c>
@@ -30513,22 +30710,22 @@
       <c r="L14" t="s">
         <v>143</v>
       </c>
-      <c r="Q14">
+      <c r="T14">
         <v>4</v>
       </c>
-      <c r="R14">
+      <c r="U14">
         <v>0</v>
       </c>
-      <c r="S14">
+      <c r="V14">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T14">
+      <c r="W14">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:23">
       <c r="A15" s="4" t="s">
         <v>234</v>
       </c>
@@ -30563,22 +30760,22 @@
       <c r="L15" t="s">
         <v>143</v>
       </c>
-      <c r="Q15">
+      <c r="T15">
         <v>3</v>
       </c>
-      <c r="R15">
+      <c r="U15">
         <v>0</v>
       </c>
-      <c r="S15">
+      <c r="V15">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T15">
+      <c r="W15">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:23">
       <c r="A16" s="4" t="s">
         <v>40</v>
       </c>
@@ -30615,22 +30812,25 @@
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
-      <c r="Q16" s="6">
-        <v>2</v>
-      </c>
-      <c r="R16">
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="6">
+        <v>2</v>
+      </c>
+      <c r="U16">
         <v>60</v>
       </c>
-      <c r="S16">
+      <c r="V16">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="T16">
+      <c r="W16">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
       <c r="A17" s="4" t="s">
         <v>44</v>
       </c>
@@ -30665,22 +30865,25 @@
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
-      <c r="Q17" s="6">
-        <v>2</v>
-      </c>
-      <c r="R17">
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6">
+        <v>2</v>
+      </c>
+      <c r="U17">
         <v>0</v>
       </c>
-      <c r="S17">
+      <c r="V17">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T17">
+      <c r="W17">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:23">
       <c r="A18" s="4" t="s">
         <v>45</v>
       </c>
@@ -30713,22 +30916,22 @@
       <c r="L18" t="s">
         <v>143</v>
       </c>
-      <c r="Q18">
-        <v>2</v>
-      </c>
-      <c r="R18">
+      <c r="T18">
+        <v>2</v>
+      </c>
+      <c r="U18">
         <v>65</v>
       </c>
-      <c r="S18">
+      <c r="V18">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>35</v>
       </c>
-      <c r="T18">
+      <c r="W18">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:23">
       <c r="A19" s="4" t="s">
         <v>51</v>
       </c>
@@ -30761,22 +30964,25 @@
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
-      <c r="Q19" s="6">
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="6"/>
+      <c r="T19" s="6">
         <v>4</v>
       </c>
-      <c r="R19">
+      <c r="U19">
         <v>0</v>
       </c>
-      <c r="S19">
+      <c r="V19">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T19">
+      <c r="W19">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100.00000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:23">
       <c r="A20" s="4" t="s">
         <v>53</v>
       </c>
@@ -30811,22 +31017,25 @@
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
-      <c r="Q20" s="6">
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="6">
         <v>3</v>
       </c>
-      <c r="R20">
+      <c r="U20">
         <v>0</v>
       </c>
-      <c r="S20">
+      <c r="V20">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T20">
+      <c r="W20">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:23">
       <c r="A21" s="3" t="s">
         <v>93</v>
       </c>
@@ -30861,22 +31070,22 @@
       <c r="L21" t="s">
         <v>143</v>
       </c>
-      <c r="Q21">
+      <c r="T21">
         <v>4</v>
       </c>
-      <c r="R21">
+      <c r="U21">
         <v>70</v>
       </c>
-      <c r="S21">
+      <c r="V21">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="T21">
+      <c r="W21">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30.000000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:23">
       <c r="A22" s="3" t="s">
         <v>94</v>
       </c>
@@ -30911,22 +31120,22 @@
       <c r="L22" t="s">
         <v>143</v>
       </c>
-      <c r="Q22">
-        <v>2</v>
-      </c>
-      <c r="R22">
+      <c r="T22">
+        <v>2</v>
+      </c>
+      <c r="U22">
         <v>70</v>
       </c>
-      <c r="S22">
+      <c r="V22">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="T22">
+      <c r="W22">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20">
+        <v>30.000000000000004</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23">
       <c r="A23" s="3" t="s">
         <v>186</v>
       </c>
@@ -30961,22 +31170,22 @@
       <c r="L23" t="s">
         <v>143</v>
       </c>
-      <c r="Q23">
+      <c r="T23">
         <v>3</v>
       </c>
-      <c r="R23">
+      <c r="U23">
         <v>70</v>
       </c>
-      <c r="S23">
+      <c r="V23">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="T23">
+      <c r="W23">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:23">
       <c r="A24" s="3" t="s">
         <v>89</v>
       </c>
@@ -31005,22 +31214,22 @@
       <c r="L24" t="s">
         <v>143</v>
       </c>
-      <c r="Q24">
-        <v>2</v>
-      </c>
-      <c r="R24">
+      <c r="T24">
+        <v>2</v>
+      </c>
+      <c r="U24">
         <v>80</v>
       </c>
-      <c r="S24">
+      <c r="V24">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="T24">
+      <c r="W24">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:23">
       <c r="A25" s="3" t="s">
         <v>91</v>
       </c>
@@ -31053,22 +31262,22 @@
       <c r="L25" t="s">
         <v>143</v>
       </c>
-      <c r="Q25">
+      <c r="T25">
         <v>3</v>
       </c>
-      <c r="R25">
+      <c r="U25">
         <v>0</v>
       </c>
-      <c r="S25">
+      <c r="V25">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T25">
+      <c r="W25">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:23">
       <c r="A26" s="3" t="s">
         <v>95</v>
       </c>
@@ -31103,22 +31312,25 @@
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
-      <c r="Q26" s="6">
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="6"/>
+      <c r="T26" s="6">
         <v>3</v>
       </c>
-      <c r="R26">
+      <c r="U26">
         <v>0</v>
       </c>
-      <c r="S26">
+      <c r="V26">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T26">
+      <c r="W26">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:23">
       <c r="A27" s="4" t="s">
         <v>1</v>
       </c>
@@ -31153,22 +31365,22 @@
       <c r="L27" t="s">
         <v>143</v>
       </c>
-      <c r="Q27">
+      <c r="T27">
         <v>4</v>
       </c>
-      <c r="R27">
+      <c r="U27">
         <v>80</v>
       </c>
-      <c r="S27">
+      <c r="V27">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="T27">
+      <c r="W27">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:23">
       <c r="A28" s="4" t="s">
         <v>248</v>
       </c>
@@ -31205,22 +31417,22 @@
       <c r="L28" t="s">
         <v>144</v>
       </c>
-      <c r="Q28">
+      <c r="T28">
         <v>3</v>
       </c>
-      <c r="R28">
+      <c r="U28">
         <v>70</v>
       </c>
-      <c r="S28">
+      <c r="V28">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="T28">
+      <c r="W28">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:23">
       <c r="A29" s="4" t="s">
         <v>8</v>
       </c>
@@ -31257,22 +31469,22 @@
       <c r="L29" t="s">
         <v>144</v>
       </c>
-      <c r="Q29">
-        <v>2</v>
-      </c>
-      <c r="R29">
+      <c r="T29">
+        <v>2</v>
+      </c>
+      <c r="U29">
         <v>0</v>
       </c>
-      <c r="S29">
+      <c r="V29">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T29">
+      <c r="W29">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:23">
       <c r="A30" s="4" t="s">
         <v>10</v>
       </c>
@@ -31309,22 +31521,22 @@
       <c r="L30" t="s">
         <v>144</v>
       </c>
-      <c r="Q30">
-        <v>2</v>
-      </c>
-      <c r="R30">
+      <c r="T30">
+        <v>2</v>
+      </c>
+      <c r="U30">
         <v>80</v>
       </c>
-      <c r="S30">
+      <c r="V30">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="T30">
+      <c r="W30">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:23">
       <c r="A31" s="4" t="s">
         <v>14</v>
       </c>
@@ -31361,22 +31573,22 @@
       <c r="L31" t="s">
         <v>144</v>
       </c>
-      <c r="Q31">
-        <v>2</v>
-      </c>
-      <c r="R31">
+      <c r="T31">
+        <v>2</v>
+      </c>
+      <c r="U31">
         <v>0</v>
       </c>
-      <c r="S31">
+      <c r="V31">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T31">
+      <c r="W31">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23">
       <c r="A32" s="4" t="s">
         <v>15</v>
       </c>
@@ -31415,22 +31627,25 @@
       <c r="N32" s="6"/>
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
-      <c r="Q32" s="6">
-        <v>2</v>
-      </c>
-      <c r="R32">
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="6"/>
+      <c r="T32" s="6">
+        <v>2</v>
+      </c>
+      <c r="U32">
         <v>0</v>
       </c>
-      <c r="S32">
+      <c r="V32">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T32">
+      <c r="W32">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" spans="1:23">
       <c r="A33" s="4" t="s">
         <v>16</v>
       </c>
@@ -31467,22 +31682,25 @@
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
       <c r="P33" s="6"/>
-      <c r="Q33" s="6">
-        <v>2</v>
-      </c>
-      <c r="R33">
+      <c r="Q33" s="6"/>
+      <c r="R33" s="6"/>
+      <c r="S33" s="6"/>
+      <c r="T33" s="6">
+        <v>2</v>
+      </c>
+      <c r="U33">
         <v>70</v>
       </c>
-      <c r="S33">
+      <c r="V33">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="T33">
+      <c r="W33">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23">
       <c r="A34" s="4" t="s">
         <v>18</v>
       </c>
@@ -31523,22 +31741,25 @@
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
-      <c r="Q34" s="6">
-        <v>2</v>
-      </c>
-      <c r="R34">
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6">
+        <v>2</v>
+      </c>
+      <c r="U34">
         <v>70</v>
       </c>
-      <c r="S34">
+      <c r="V34">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="T34">
+      <c r="W34">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:23">
       <c r="A35" s="4" t="s">
         <v>24</v>
       </c>
@@ -31579,22 +31800,25 @@
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
       <c r="P35" s="6"/>
-      <c r="Q35" s="6">
+      <c r="Q35" s="6"/>
+      <c r="R35" s="6"/>
+      <c r="S35" s="6"/>
+      <c r="T35" s="6">
         <v>3</v>
       </c>
-      <c r="R35">
+      <c r="U35">
         <v>0</v>
       </c>
-      <c r="S35">
+      <c r="V35">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T35">
+      <c r="W35">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:20">
+    <row r="36" spans="1:23">
       <c r="A36" s="8" t="s">
         <v>21</v>
       </c>
@@ -31629,22 +31853,25 @@
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
       <c r="P36" s="6"/>
-      <c r="Q36" s="6">
-        <v>2</v>
-      </c>
-      <c r="R36">
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
+      <c r="S36" s="6"/>
+      <c r="T36" s="6">
+        <v>2</v>
+      </c>
+      <c r="U36">
         <v>80</v>
       </c>
-      <c r="S36">
+      <c r="V36">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="T36">
+      <c r="W36">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:20">
+    <row r="37" spans="1:23">
       <c r="A37" s="3" t="s">
         <v>106</v>
       </c>
@@ -31679,22 +31906,22 @@
       <c r="L37" t="s">
         <v>143</v>
       </c>
-      <c r="Q37">
+      <c r="T37">
         <v>4</v>
       </c>
-      <c r="R37">
+      <c r="U37">
         <v>70</v>
       </c>
-      <c r="S37">
+      <c r="V37">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="T37">
+      <c r="W37">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30.000000000000004</v>
       </c>
     </row>
-    <row r="38" spans="1:20">
+    <row r="38" spans="1:23">
       <c r="A38" s="3" t="s">
         <v>188</v>
       </c>
@@ -31729,187 +31956,194 @@
       <c r="L38" t="s">
         <v>144</v>
       </c>
-      <c r="Q38">
-        <v>2</v>
-      </c>
-      <c r="R38">
+      <c r="T38">
+        <v>2</v>
+      </c>
+      <c r="U38">
         <v>80</v>
       </c>
-      <c r="S38">
+      <c r="V38">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="T38">
+      <c r="W38">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:20">
-      <c r="A39" s="3" t="s">
+    <row r="39" spans="1:23">
+      <c r="A39" s="46" t="s">
+        <v>108</v>
+      </c>
+      <c r="B39" s="46" t="s">
+        <v>362</v>
+      </c>
+      <c r="C39" s="46" t="s">
+        <v>381</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="E39" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="F39" s="47">
+        <v>6</v>
+      </c>
+      <c r="G39" s="51">
+        <v>10</v>
+      </c>
+      <c r="H39" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="I39" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="J39" t="s">
+        <v>144</v>
+      </c>
+      <c r="K39" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="L39" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="N39" s="49"/>
+      <c r="O39" s="49"/>
+      <c r="P39" s="49"/>
+      <c r="Q39" s="49"/>
+      <c r="T39">
+        <v>2</v>
+      </c>
+      <c r="U39" s="49">
+        <v>80</v>
+      </c>
+      <c r="V39" s="50">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>20</v>
+      </c>
+      <c r="W39" s="50">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23">
+      <c r="A40" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B40" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F40" s="2">
         <v>6</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G40" s="2">
         <v>10</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="H40" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6" t="s">
+      <c r="I40" s="6"/>
+      <c r="J40" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K39" s="6" t="s">
+      <c r="K40" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6">
-        <v>2</v>
-      </c>
-      <c r="R39">
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="6">
+        <v>2</v>
+      </c>
+      <c r="U40">
         <v>60</v>
       </c>
-      <c r="S39">
+      <c r="V40">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="T39">
+      <c r="W40">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:20">
-      <c r="A40" s="3" t="s">
+    <row r="41" spans="1:23">
+      <c r="A41" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B41" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E40" s="3" t="s">
+      <c r="E41" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F41" s="2">
         <v>6</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G41" s="2">
         <v>10</v>
       </c>
-      <c r="H40" s="2" t="s">
+      <c r="H41" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I41" t="s">
         <v>144</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J41" t="s">
         <v>144</v>
       </c>
-      <c r="K40" t="s">
+      <c r="K41" t="s">
         <v>144</v>
       </c>
-      <c r="L40" t="s">
+      <c r="L41" t="s">
         <v>144</v>
       </c>
-      <c r="Q40">
-        <v>2</v>
-      </c>
-      <c r="R40">
+      <c r="T41">
+        <v>2</v>
+      </c>
+      <c r="U41">
         <v>0</v>
       </c>
-      <c r="S40">
+      <c r="V41">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T40">
+      <c r="W41">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="41" spans="1:20">
-      <c r="A41" s="3" t="s">
+    <row r="42" spans="1:23">
+      <c r="A42" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B42" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F41" s="2">
-        <v>6</v>
-      </c>
-      <c r="G41" s="2">
-        <v>10</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I41" t="s">
-        <v>144</v>
-      </c>
-      <c r="J41" t="s">
-        <v>144</v>
-      </c>
-      <c r="K41" t="s">
-        <v>143</v>
-      </c>
-      <c r="L41" s="6"/>
-      <c r="M41" s="6"/>
-      <c r="N41" s="6"/>
-      <c r="O41" s="6"/>
-      <c r="P41" s="6"/>
-      <c r="Q41" s="6">
-        <v>2</v>
-      </c>
-      <c r="R41">
-        <v>80</v>
-      </c>
-      <c r="S41">
-        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>20</v>
-      </c>
-      <c r="T41">
-        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20">
-      <c r="A42" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C42" s="3"/>
       <c r="D42" s="2" t="s">
         <v>180</v>
       </c>
@@ -31928,38 +32162,41 @@
       <c r="I42" t="s">
         <v>144</v>
       </c>
-      <c r="J42" s="6" t="s">
+      <c r="J42" t="s">
         <v>144</v>
       </c>
-      <c r="K42" s="6"/>
-      <c r="L42" s="6" t="s">
+      <c r="K42" t="s">
         <v>143</v>
       </c>
+      <c r="L42" s="6"/>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
       <c r="O42" s="6"/>
       <c r="P42" s="6"/>
-      <c r="Q42" s="6">
-        <v>2</v>
-      </c>
-      <c r="R42">
+      <c r="Q42" s="6"/>
+      <c r="R42" s="6"/>
+      <c r="S42" s="6"/>
+      <c r="T42" s="6">
+        <v>2</v>
+      </c>
+      <c r="U42">
         <v>80</v>
       </c>
-      <c r="S42">
+      <c r="V42">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="T42">
+      <c r="W42">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:20">
+    <row r="43" spans="1:23">
       <c r="A43" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="2" t="s">
@@ -31991,134 +32228,138 @@
       <c r="N43" s="6"/>
       <c r="O43" s="6"/>
       <c r="P43" s="6"/>
-      <c r="Q43" s="6">
-        <v>2</v>
-      </c>
-      <c r="R43">
+      <c r="Q43" s="6"/>
+      <c r="R43" s="6"/>
+      <c r="S43" s="6"/>
+      <c r="T43" s="6">
+        <v>2</v>
+      </c>
+      <c r="U43">
         <v>80</v>
       </c>
-      <c r="S43">
+      <c r="V43">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="T43">
+      <c r="W43">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:20">
-      <c r="A44" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C44" s="2"/>
+    <row r="44" spans="1:23">
+      <c r="A44" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="3"/>
       <c r="D44" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>149</v>
+      <c r="E44" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="F44" s="2">
         <v>6</v>
       </c>
       <c r="G44" s="2">
+        <v>10</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I44" t="s">
+        <v>144</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="6"/>
+      <c r="Q44" s="6"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="6"/>
+      <c r="T44" s="6">
+        <v>2</v>
+      </c>
+      <c r="U44">
+        <v>80</v>
+      </c>
+      <c r="V44">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>20</v>
+      </c>
+      <c r="W44">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23">
+      <c r="A45" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F45" s="2">
+        <v>6</v>
+      </c>
+      <c r="G45" s="2">
         <v>30</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="H45" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I45" t="s">
         <v>143</v>
       </c>
-      <c r="J44" t="s">
+      <c r="J45" t="s">
         <v>143</v>
       </c>
-      <c r="K44" t="s">
+      <c r="K45" t="s">
         <v>143</v>
       </c>
-      <c r="L44" t="s">
+      <c r="L45" t="s">
         <v>143</v>
       </c>
-      <c r="Q44">
+      <c r="T45">
         <v>0.5</v>
       </c>
-      <c r="R44">
+      <c r="U45">
         <v>0</v>
       </c>
-      <c r="S44">
+      <c r="V45">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T44">
+      <c r="W45">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:20">
-      <c r="A45" s="4" t="s">
+    <row r="46" spans="1:23">
+      <c r="A46" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B46" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C46" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F45" s="2">
-        <v>7</v>
-      </c>
-      <c r="G45" s="2">
-        <v>10</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I45" t="s">
-        <v>144</v>
-      </c>
-      <c r="J45" t="s">
-        <v>144</v>
-      </c>
-      <c r="K45" t="s">
-        <v>143</v>
-      </c>
-      <c r="L45" s="6"/>
-      <c r="M45" s="6"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="6"/>
-      <c r="P45" s="6"/>
-      <c r="Q45" s="6">
-        <v>2</v>
-      </c>
-      <c r="R45">
-        <v>70</v>
-      </c>
-      <c r="S45">
-        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="T45">
-        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20">
-      <c r="A46" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>251</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>180</v>
@@ -32142,37 +32383,40 @@
         <v>144</v>
       </c>
       <c r="K46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
       <c r="O46" s="6"/>
       <c r="P46" s="6"/>
-      <c r="Q46" s="6">
-        <v>2</v>
-      </c>
-      <c r="R46">
+      <c r="Q46" s="6"/>
+      <c r="R46" s="6"/>
+      <c r="S46" s="6"/>
+      <c r="T46" s="6">
+        <v>2</v>
+      </c>
+      <c r="U46">
         <v>70</v>
       </c>
-      <c r="S46">
+      <c r="V46">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="T46">
+      <c r="W46">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="47" spans="1:20">
+    <row r="47" spans="1:23">
       <c r="A47" s="4" t="s">
-        <v>63</v>
+        <v>238</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>296</v>
+        <v>237</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>134</v>
+        <v>251</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>180</v>
@@ -32192,37 +32436,44 @@
       <c r="I47" t="s">
         <v>144</v>
       </c>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
+      <c r="J47" t="s">
+        <v>144</v>
+      </c>
+      <c r="K47" t="s">
+        <v>144</v>
+      </c>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
       <c r="O47" s="6"/>
       <c r="P47" s="6"/>
-      <c r="Q47" s="6">
-        <v>2</v>
-      </c>
-      <c r="R47">
-        <v>75</v>
-      </c>
-      <c r="S47">
+      <c r="Q47" s="6"/>
+      <c r="R47" s="6"/>
+      <c r="S47" s="6"/>
+      <c r="T47" s="6">
+        <v>2</v>
+      </c>
+      <c r="U47">
+        <v>70</v>
+      </c>
+      <c r="V47">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>25</v>
-      </c>
-      <c r="T47">
+        <v>30</v>
+      </c>
+      <c r="W47">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:23">
       <c r="A48" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>67</v>
+        <v>296</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>180</v>
@@ -32242,41 +32493,40 @@
       <c r="I48" t="s">
         <v>144</v>
       </c>
-      <c r="J48" t="s">
-        <v>144</v>
-      </c>
-      <c r="K48" t="s">
-        <v>144</v>
-      </c>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
       <c r="O48" s="6"/>
       <c r="P48" s="6"/>
-      <c r="Q48" s="6">
-        <v>3</v>
-      </c>
-      <c r="R48">
-        <v>70</v>
-      </c>
-      <c r="S48">
+      <c r="Q48" s="6"/>
+      <c r="R48" s="6"/>
+      <c r="S48" s="6"/>
+      <c r="T48" s="6">
+        <v>2</v>
+      </c>
+      <c r="U48">
+        <v>75</v>
+      </c>
+      <c r="V48">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="T48">
+        <v>25</v>
+      </c>
+      <c r="W48">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23">
       <c r="A49" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>180</v>
@@ -32307,30 +32557,33 @@
       <c r="N49" s="6"/>
       <c r="O49" s="6"/>
       <c r="P49" s="6"/>
-      <c r="Q49" s="6">
-        <v>2</v>
-      </c>
-      <c r="R49">
-        <v>0</v>
-      </c>
-      <c r="S49">
+      <c r="Q49" s="6"/>
+      <c r="R49" s="6"/>
+      <c r="S49" s="6"/>
+      <c r="T49" s="6">
+        <v>3</v>
+      </c>
+      <c r="U49">
+        <v>70</v>
+      </c>
+      <c r="V49">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="T49">
+        <v>30</v>
+      </c>
+      <c r="W49">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23">
       <c r="A50" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>180</v>
@@ -32361,36 +32614,39 @@
       <c r="N50" s="6"/>
       <c r="O50" s="6"/>
       <c r="P50" s="6"/>
-      <c r="Q50" s="6">
-        <v>2</v>
-      </c>
-      <c r="R50">
-        <v>50</v>
-      </c>
-      <c r="S50">
+      <c r="Q50" s="6"/>
+      <c r="R50" s="6"/>
+      <c r="S50" s="6"/>
+      <c r="T50" s="6">
+        <v>2</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>50</v>
-      </c>
-      <c r="T50">
+        <v>100</v>
+      </c>
+      <c r="W50">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20">
-      <c r="A51" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>154</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23">
+      <c r="A51" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>148</v>
+      <c r="E51" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F51" s="2">
         <v>7</v>
@@ -32404,37 +32660,44 @@
       <c r="I51" t="s">
         <v>144</v>
       </c>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
+      <c r="J51" t="s">
+        <v>144</v>
+      </c>
+      <c r="K51" t="s">
+        <v>144</v>
+      </c>
       <c r="L51" s="6"/>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
       <c r="O51" s="6"/>
       <c r="P51" s="6"/>
-      <c r="Q51" s="6">
-        <v>2</v>
-      </c>
-      <c r="R51">
-        <v>80</v>
-      </c>
-      <c r="S51">
+      <c r="Q51" s="6"/>
+      <c r="R51" s="6"/>
+      <c r="S51" s="6"/>
+      <c r="T51" s="6">
+        <v>2</v>
+      </c>
+      <c r="U51">
+        <v>50</v>
+      </c>
+      <c r="V51">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>20</v>
-      </c>
-      <c r="T51">
+        <v>50</v>
+      </c>
+      <c r="W51">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23">
       <c r="A52" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>180</v>
@@ -32454,41 +32717,40 @@
       <c r="I52" t="s">
         <v>144</v>
       </c>
-      <c r="J52" t="s">
-        <v>144</v>
-      </c>
-      <c r="K52" t="s">
-        <v>144</v>
-      </c>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
       <c r="L52" s="6"/>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
       <c r="P52" s="6"/>
-      <c r="Q52" s="6">
-        <v>2</v>
-      </c>
-      <c r="R52">
-        <v>70</v>
-      </c>
-      <c r="S52">
+      <c r="Q52" s="6"/>
+      <c r="R52" s="6"/>
+      <c r="S52" s="6"/>
+      <c r="T52" s="6">
+        <v>2</v>
+      </c>
+      <c r="U52">
+        <v>80</v>
+      </c>
+      <c r="V52">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="T52">
+        <v>20</v>
+      </c>
+      <c r="W52">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:23">
       <c r="A53" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>180</v>
@@ -32519,30 +32781,33 @@
       <c r="N53" s="6"/>
       <c r="O53" s="6"/>
       <c r="P53" s="6"/>
-      <c r="Q53" s="6">
-        <v>2</v>
-      </c>
-      <c r="R53">
-        <v>40</v>
-      </c>
-      <c r="S53">
+      <c r="Q53" s="6"/>
+      <c r="R53" s="6"/>
+      <c r="S53" s="6"/>
+      <c r="T53" s="6">
+        <v>2</v>
+      </c>
+      <c r="U53">
+        <v>70</v>
+      </c>
+      <c r="V53">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>60</v>
-      </c>
-      <c r="T53">
+        <v>30</v>
+      </c>
+      <c r="W53">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23">
       <c r="A54" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>180</v>
@@ -32559,42 +32824,47 @@
       <c r="H54" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I54" s="6"/>
+      <c r="I54" t="s">
+        <v>144</v>
+      </c>
       <c r="J54" t="s">
         <v>144</v>
       </c>
       <c r="K54" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
       <c r="O54" s="6"/>
       <c r="P54" s="6"/>
-      <c r="Q54" s="6">
-        <v>2</v>
-      </c>
-      <c r="R54">
-        <v>80</v>
-      </c>
-      <c r="S54">
+      <c r="Q54" s="6"/>
+      <c r="R54" s="6"/>
+      <c r="S54" s="6"/>
+      <c r="T54" s="6">
+        <v>2</v>
+      </c>
+      <c r="U54">
+        <v>40</v>
+      </c>
+      <c r="V54">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>20</v>
-      </c>
-      <c r="T54">
+        <v>60</v>
+      </c>
+      <c r="W54">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23">
       <c r="A55" s="3" t="s">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>180</v>
@@ -32611,44 +32881,45 @@
       <c r="H55" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I55" t="s">
-        <v>144</v>
-      </c>
+      <c r="I55" s="6"/>
       <c r="J55" t="s">
         <v>144</v>
       </c>
       <c r="K55" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
       <c r="O55" s="6"/>
       <c r="P55" s="6"/>
-      <c r="Q55" s="6">
-        <v>3</v>
-      </c>
-      <c r="R55">
-        <v>0</v>
-      </c>
-      <c r="S55">
+      <c r="Q55" s="6"/>
+      <c r="R55" s="6"/>
+      <c r="S55" s="6"/>
+      <c r="T55" s="6">
+        <v>2</v>
+      </c>
+      <c r="U55">
+        <v>80</v>
+      </c>
+      <c r="V55">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="T55">
+        <v>20</v>
+      </c>
+      <c r="W55">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23">
       <c r="A56" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>180</v>
@@ -32679,30 +32950,33 @@
       <c r="N56" s="6"/>
       <c r="O56" s="6"/>
       <c r="P56" s="6"/>
-      <c r="Q56" s="6">
-        <v>2</v>
-      </c>
-      <c r="R56">
-        <v>70</v>
-      </c>
-      <c r="S56">
+      <c r="Q56" s="6"/>
+      <c r="R56" s="6"/>
+      <c r="S56" s="6"/>
+      <c r="T56" s="6">
+        <v>3</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="T56">
+        <v>100</v>
+      </c>
+      <c r="W56">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23">
       <c r="A57" s="3" t="s">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>180</v>
@@ -32722,37 +32996,44 @@
       <c r="I57" t="s">
         <v>144</v>
       </c>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
+      <c r="J57" t="s">
+        <v>144</v>
+      </c>
+      <c r="K57" t="s">
+        <v>144</v>
+      </c>
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
       <c r="O57" s="6"/>
       <c r="P57" s="6"/>
-      <c r="Q57" s="6">
-        <v>2</v>
-      </c>
-      <c r="R57">
-        <v>50</v>
-      </c>
-      <c r="S57">
+      <c r="Q57" s="6"/>
+      <c r="R57" s="6"/>
+      <c r="S57" s="6"/>
+      <c r="T57" s="6">
+        <v>2</v>
+      </c>
+      <c r="U57">
+        <v>70</v>
+      </c>
+      <c r="V57">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>50</v>
-      </c>
-      <c r="T57">
+        <v>30</v>
+      </c>
+      <c r="W57">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:23">
       <c r="A58" s="3" t="s">
-        <v>194</v>
+        <v>68</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>180</v>
@@ -32772,41 +33053,40 @@
       <c r="I58" t="s">
         <v>144</v>
       </c>
-      <c r="J58" t="s">
-        <v>144</v>
-      </c>
-      <c r="K58" t="s">
-        <v>144</v>
-      </c>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
       <c r="O58" s="6"/>
       <c r="P58" s="6"/>
-      <c r="Q58" s="6">
-        <v>3</v>
-      </c>
-      <c r="R58">
-        <v>60</v>
-      </c>
-      <c r="S58">
+      <c r="Q58" s="6"/>
+      <c r="R58" s="6"/>
+      <c r="S58" s="6"/>
+      <c r="T58" s="6">
+        <v>2</v>
+      </c>
+      <c r="U58">
+        <v>50</v>
+      </c>
+      <c r="V58">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>40</v>
-      </c>
-      <c r="T58">
+        <v>50</v>
+      </c>
+      <c r="W58">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23">
       <c r="A59" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>180</v>
@@ -32837,44 +33117,47 @@
       <c r="N59" s="6"/>
       <c r="O59" s="6"/>
       <c r="P59" s="6"/>
-      <c r="Q59" s="6">
-        <v>2</v>
-      </c>
-      <c r="R59">
-        <v>0</v>
-      </c>
-      <c r="S59">
+      <c r="Q59" s="6"/>
+      <c r="R59" s="6"/>
+      <c r="S59" s="6"/>
+      <c r="T59" s="6">
+        <v>3</v>
+      </c>
+      <c r="U59">
+        <v>60</v>
+      </c>
+      <c r="V59">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="T59">
+        <v>40</v>
+      </c>
+      <c r="W59">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23">
       <c r="A60" s="3" t="s">
-        <v>239</v>
+        <v>195</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>240</v>
+        <v>119</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D60" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>180</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F60" s="4">
+      <c r="F60" s="2">
         <v>7</v>
       </c>
-      <c r="G60" s="28">
+      <c r="G60" s="2">
         <v>10</v>
       </c>
-      <c r="H60" s="28" t="s">
+      <c r="H60" s="2" t="s">
         <v>144</v>
       </c>
       <c r="I60" t="s">
@@ -32891,127 +33174,145 @@
       <c r="N60" s="6"/>
       <c r="O60" s="6"/>
       <c r="P60" s="6"/>
-      <c r="Q60" s="6">
-        <v>2</v>
-      </c>
-      <c r="R60">
-        <v>50</v>
-      </c>
-      <c r="S60">
+      <c r="Q60" s="6"/>
+      <c r="R60" s="6"/>
+      <c r="S60" s="6"/>
+      <c r="T60" s="6">
+        <v>2</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>50</v>
-      </c>
-      <c r="T60">
+        <v>100</v>
+      </c>
+      <c r="W60">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30.000000000000004</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20">
-      <c r="A61" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23">
+      <c r="A61" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D61" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F61" s="2">
+      <c r="E61" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F61" s="4">
         <v>7</v>
       </c>
-      <c r="G61" s="2">
-        <v>60</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>143</v>
+      <c r="G61" s="28">
+        <v>10</v>
+      </c>
+      <c r="H61" s="28" t="s">
+        <v>144</v>
       </c>
       <c r="I61" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J61" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K61" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
       <c r="O61" s="6"/>
       <c r="P61" s="6"/>
-      <c r="Q61" s="6">
+      <c r="Q61" s="6"/>
+      <c r="R61" s="6"/>
+      <c r="S61" s="6"/>
+      <c r="T61" s="6">
+        <v>2</v>
+      </c>
+      <c r="U61">
+        <v>50</v>
+      </c>
+      <c r="V61">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>50</v>
+      </c>
+      <c r="W61">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23">
+      <c r="A62" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F62" s="2">
+        <v>7</v>
+      </c>
+      <c r="G62" s="2">
+        <v>60</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I62" t="s">
+        <v>143</v>
+      </c>
+      <c r="J62" t="s">
+        <v>143</v>
+      </c>
+      <c r="K62" t="s">
+        <v>143</v>
+      </c>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="6"/>
+      <c r="O62" s="6"/>
+      <c r="P62" s="6"/>
+      <c r="Q62" s="6"/>
+      <c r="R62" s="6"/>
+      <c r="S62" s="6"/>
+      <c r="T62" s="6">
         <v>0.5</v>
       </c>
-      <c r="R61">
+      <c r="U62">
         <v>25</v>
       </c>
-      <c r="S61">
+      <c r="V62">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>75</v>
       </c>
-      <c r="T61">
+      <c r="W62">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>75</v>
       </c>
     </row>
-    <row r="62" spans="1:20">
-      <c r="A62" s="3" t="s">
+    <row r="63" spans="1:23">
+      <c r="A63" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B63" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="D62" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F62" s="4">
-        <v>7</v>
-      </c>
-      <c r="G62" s="2">
-        <v>10</v>
-      </c>
-      <c r="H62" s="2"/>
-      <c r="M62" t="s">
-        <v>144</v>
-      </c>
-      <c r="N62" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q62">
-        <f>INDEX(Q2:Q61,MATCH(Table2[[#This Row],[Alternative Module Code]],A2:A61,0))</f>
-        <v>3</v>
-      </c>
-      <c r="R62">
-        <v>70</v>
-      </c>
-      <c r="S62">
-        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="T62">
-        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20">
-      <c r="A63" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="D63" s="28" t="s">
         <v>178</v>
@@ -33032,37 +33333,31 @@
       <c r="N63" t="s">
         <v>144</v>
       </c>
-      <c r="O63" t="s">
-        <v>144</v>
-      </c>
-      <c r="P63" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q63">
-        <f>INDEX(Q3:Q62,MATCH(Table2[[#This Row],[Alternative Module Code]],A3:A62,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R63">
-        <v>0</v>
-      </c>
-      <c r="S63">
+      <c r="T63">
+        <f>INDEX(T2:T62,MATCH(Table2[[#This Row],[Alternative Module Code]],A2:A62,0))</f>
+        <v>3</v>
+      </c>
+      <c r="U63">
+        <v>70</v>
+      </c>
+      <c r="V63">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="T63">
+        <v>30</v>
+      </c>
+      <c r="W63">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23">
       <c r="A64" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D64" s="28" t="s">
         <v>178</v>
@@ -33080,34 +33375,40 @@
       <c r="M64" t="s">
         <v>144</v>
       </c>
+      <c r="N64" t="s">
+        <v>144</v>
+      </c>
       <c r="O64" t="s">
         <v>144</v>
       </c>
-      <c r="Q64">
-        <f>INDEX(Q4:Q63,MATCH(Table2[[#This Row],[Alternative Module Code]],A4:A63,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R64">
-        <v>80</v>
-      </c>
-      <c r="S64">
+      <c r="R64" t="s">
+        <v>144</v>
+      </c>
+      <c r="T64">
+        <f>INDEX(T3:T63,MATCH(Table2[[#This Row],[Alternative Module Code]],A3:A63,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>20</v>
-      </c>
-      <c r="T64">
+        <v>100</v>
+      </c>
+      <c r="W64">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23">
       <c r="A65" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D65" s="28" t="s">
         <v>178</v>
@@ -33125,34 +33426,37 @@
       <c r="M65" t="s">
         <v>144</v>
       </c>
-      <c r="N65" t="s">
+      <c r="O65" t="s">
         <v>144</v>
       </c>
-      <c r="Q65">
-        <f>INDEX(Q5:Q64,MATCH(Table2[[#This Row],[Alternative Module Code]],A5:A64,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R65">
-        <v>0</v>
-      </c>
-      <c r="S65">
+      <c r="Q65" t="s">
+        <v>144</v>
+      </c>
+      <c r="T65">
+        <f>INDEX(T4:T64,MATCH(Table2[[#This Row],[Alternative Module Code]],A4:A64,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U65">
+        <v>80</v>
+      </c>
+      <c r="V65">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="T65">
+        <v>20</v>
+      </c>
+      <c r="W65">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23">
       <c r="A66" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D66" s="28" t="s">
         <v>178</v>
@@ -33173,31 +33477,31 @@
       <c r="N66" t="s">
         <v>144</v>
       </c>
-      <c r="Q66">
-        <f>INDEX(Q6:Q65,MATCH(Table2[[#This Row],[Alternative Module Code]],A6:A65,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R66">
+      <c r="T66">
+        <f>INDEX(T5:T65,MATCH(Table2[[#This Row],[Alternative Module Code]],A5:A65,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U66">
         <v>0</v>
       </c>
-      <c r="S66">
+      <c r="V66">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T66">
+      <c r="W66">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:20">
+    <row r="67" spans="1:23">
       <c r="A67" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>17</v>
+        <v>145</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D67" s="28" t="s">
         <v>178</v>
@@ -33215,34 +33519,34 @@
       <c r="M67" t="s">
         <v>144</v>
       </c>
-      <c r="O67" t="s">
+      <c r="N67" t="s">
         <v>144</v>
       </c>
-      <c r="Q67">
-        <f>INDEX(Q7:Q66,MATCH(Table2[[#This Row],[Alternative Module Code]],A7:A66,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R67">
-        <v>70</v>
-      </c>
-      <c r="S67">
+      <c r="T67">
+        <f>INDEX(T6:T66,MATCH(Table2[[#This Row],[Alternative Module Code]],A6:A66,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U67">
+        <v>0</v>
+      </c>
+      <c r="V67">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="T67">
+        <v>100</v>
+      </c>
+      <c r="W67">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23">
       <c r="A68" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D68" s="28" t="s">
         <v>178</v>
@@ -33260,37 +33564,37 @@
       <c r="M68" t="s">
         <v>144</v>
       </c>
-      <c r="N68" t="s">
-        <v>144</v>
-      </c>
       <c r="O68" t="s">
         <v>144</v>
       </c>
-      <c r="Q68">
-        <f>INDEX(Q8:Q67,MATCH(Table2[[#This Row],[Alternative Module Code]],A8:A67,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R68">
+      <c r="Q68" t="s">
+        <v>144</v>
+      </c>
+      <c r="T68">
+        <f>INDEX(T7:T67,MATCH(Table2[[#This Row],[Alternative Module Code]],A7:A67,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U68">
         <v>70</v>
       </c>
-      <c r="S68">
+      <c r="V68">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="T68">
+      <c r="W68">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:20">
+    <row r="69" spans="1:23">
       <c r="A69" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D69" s="28" t="s">
         <v>178</v>
@@ -33317,37 +33621,37 @@
       <c r="P69" t="s">
         <v>144</v>
       </c>
-      <c r="Q69">
-        <f>INDEX(Q9:Q68,MATCH(Table2[[#This Row],[Alternative Module Code]],A9:A68,0))</f>
-        <v>3</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
+      <c r="T69">
+        <f>INDEX(T8:T68,MATCH(Table2[[#This Row],[Alternative Module Code]],A8:A68,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U69">
+        <v>70</v>
+      </c>
+      <c r="V69">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="T69">
+        <v>30</v>
+      </c>
+      <c r="W69">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23">
       <c r="A70" s="3" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>189</v>
+        <v>24</v>
       </c>
       <c r="D70" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F70" s="4">
         <v>7</v>
@@ -33359,34 +33663,40 @@
       <c r="M70" t="s">
         <v>144</v>
       </c>
+      <c r="N70" t="s">
+        <v>144</v>
+      </c>
       <c r="O70" t="s">
         <v>144</v>
       </c>
-      <c r="Q70">
-        <f>INDEX(Q10:Q69,MATCH(Table2[[#This Row],[Alternative Module Code]],A10:A69,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R70">
-        <v>60</v>
-      </c>
-      <c r="S70">
+      <c r="R70" t="s">
+        <v>144</v>
+      </c>
+      <c r="T70">
+        <f>INDEX(T9:T69,MATCH(Table2[[#This Row],[Alternative Module Code]],A9:A69,0))</f>
+        <v>3</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>40</v>
-      </c>
-      <c r="T70">
+        <v>100</v>
+      </c>
+      <c r="W70">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23">
       <c r="A71" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>109</v>
+        <v>189</v>
       </c>
       <c r="D71" s="28" t="s">
         <v>178</v>
@@ -33404,37 +33714,37 @@
       <c r="M71" t="s">
         <v>144</v>
       </c>
-      <c r="N71" t="s">
+      <c r="O71" t="s">
         <v>144</v>
       </c>
-      <c r="P71" t="s">
+      <c r="Q71" t="s">
         <v>144</v>
       </c>
-      <c r="Q71">
-        <f>INDEX(Q13:Q70,MATCH(Table2[[#This Row],[Alternative Module Code]],A13:A70,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
-      <c r="S71">
+      <c r="T71">
+        <f>INDEX(T10:T70,MATCH(Table2[[#This Row],[Alternative Module Code]],A10:A70,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U71">
+        <v>60</v>
+      </c>
+      <c r="V71">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="T71">
+        <v>40</v>
+      </c>
+      <c r="W71">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>99.999999999999986</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23">
       <c r="A72" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D72" s="28" t="s">
         <v>178</v>
@@ -33452,40 +33762,46 @@
       <c r="M72" t="s">
         <v>144</v>
       </c>
-      <c r="O72" t="s">
+      <c r="N72" t="s">
         <v>144</v>
       </c>
-      <c r="Q72">
-        <f>INDEX(Q14:Q71,MATCH(Table2[[#This Row],[Alternative Module Code]],A14:A71,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R72">
-        <v>80</v>
-      </c>
-      <c r="S72">
+      <c r="R72" t="s">
+        <v>144</v>
+      </c>
+      <c r="S72" t="s">
+        <v>144</v>
+      </c>
+      <c r="T72">
+        <f>INDEX(T13:T71,MATCH(Table2[[#This Row],[Alternative Module Code]],A13:A71,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>20</v>
-      </c>
-      <c r="T72">
+        <v>100</v>
+      </c>
+      <c r="W72">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20">
+        <v>99.999999999999986</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23">
       <c r="A73" s="3" t="s">
-        <v>133</v>
+        <v>152</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="D73" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F73" s="4">
         <v>7</v>
@@ -33497,85 +33813,99 @@
       <c r="M73" t="s">
         <v>144</v>
       </c>
-      <c r="N73" t="s">
-        <v>144</v>
-      </c>
       <c r="O73" t="s">
         <v>144</v>
       </c>
-      <c r="Q73">
-        <f>INDEX(Q16:Q72,MATCH(Table2[[#This Row],[Alternative Module Code]],A16:A72,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R73">
-        <v>70</v>
-      </c>
-      <c r="S73">
+      <c r="Q73" t="s">
+        <v>144</v>
+      </c>
+      <c r="T73">
+        <f>INDEX(T14:T72,MATCH(Table2[[#This Row],[Alternative Module Code]],A14:A72,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U73">
+        <v>80</v>
+      </c>
+      <c r="V73">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="T73">
+        <v>20</v>
+      </c>
+      <c r="W73">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23">
       <c r="A74" s="3" t="s">
-        <v>251</v>
+        <v>381</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>237</v>
+        <v>362</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="D74" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E74" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F74" s="4">
+      <c r="E74" s="46" t="s">
+        <v>382</v>
+      </c>
+      <c r="F74" s="47">
         <v>7</v>
       </c>
-      <c r="G74" s="2">
+      <c r="G74" s="48">
         <v>10</v>
       </c>
-      <c r="H74" s="2"/>
+      <c r="H74" s="28"/>
+      <c r="I74" s="49"/>
+      <c r="K74" s="49"/>
+      <c r="L74" s="49"/>
       <c r="M74" t="s">
         <v>144</v>
       </c>
-      <c r="N74" t="s">
+      <c r="N74" s="49" t="s">
         <v>144</v>
       </c>
-      <c r="O74" t="s">
+      <c r="O74" s="49" t="s">
         <v>144</v>
       </c>
-      <c r="Q74">
-        <f>INDEX(Q17:Q73,MATCH(Table2[[#This Row],[Alternative Module Code]],A17:A73,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R74">
-        <v>70</v>
-      </c>
-      <c r="S74">
+      <c r="P74" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q74" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="R74" t="s">
+        <v>144</v>
+      </c>
+      <c r="S74" t="s">
+        <v>144</v>
+      </c>
+      <c r="T74">
+        <v>2</v>
+      </c>
+      <c r="U74" s="49">
+        <v>80</v>
+      </c>
+      <c r="V74" s="50">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="T74">
+        <v>20</v>
+      </c>
+      <c r="W74" s="50">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23">
       <c r="A75" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D75" s="28" t="s">
         <v>178</v>
@@ -33596,34 +33926,37 @@
       <c r="N75" t="s">
         <v>144</v>
       </c>
-      <c r="P75" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q75">
-        <f>INDEX(Q18:Q74,MATCH(Table2[[#This Row],[Alternative Module Code]],A18:A74,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R75">
-        <v>75</v>
-      </c>
-      <c r="S75">
+      <c r="O75" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>144</v>
+      </c>
+      <c r="T75">
+        <f>INDEX(T16:T73,MATCH(Table2[[#This Row],[Alternative Module Code]],A16:A73,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U75">
+        <v>70</v>
+      </c>
+      <c r="V75">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>25</v>
-      </c>
-      <c r="T75">
+        <v>30</v>
+      </c>
+      <c r="W75">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23">
       <c r="A76" s="3" t="s">
-        <v>135</v>
+        <v>251</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>67</v>
+        <v>237</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>66</v>
+        <v>238</v>
       </c>
       <c r="D76" s="28" t="s">
         <v>178</v>
@@ -33644,34 +33977,40 @@
       <c r="N76" t="s">
         <v>144</v>
       </c>
-      <c r="P76" t="s">
+      <c r="O76" t="s">
         <v>144</v>
       </c>
-      <c r="Q76">
-        <f>INDEX(Q20:Q75,MATCH(Table2[[#This Row],[Alternative Module Code]],A20:A75,0))</f>
-        <v>3</v>
-      </c>
-      <c r="R76">
+      <c r="R76" t="s">
+        <v>144</v>
+      </c>
+      <c r="S76" t="s">
+        <v>144</v>
+      </c>
+      <c r="T76">
+        <f>INDEX(T17:T75,MATCH(Table2[[#This Row],[Alternative Module Code]],A17:A75,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U76">
         <v>70</v>
       </c>
-      <c r="S76">
+      <c r="V76">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="T76">
+      <c r="W76">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="77" spans="1:20">
+    <row r="77" spans="1:23">
       <c r="A77" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D77" s="28" t="s">
         <v>178</v>
@@ -33692,37 +34031,37 @@
       <c r="N77" t="s">
         <v>144</v>
       </c>
-      <c r="O77" t="s">
-        <v>144</v>
-      </c>
-      <c r="P77" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q77">
-        <f>INDEX(Q21:Q76,MATCH(Table2[[#This Row],[Alternative Module Code]],A21:A76,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R77">
-        <v>0</v>
-      </c>
-      <c r="S77">
+      <c r="R77" t="s">
+        <v>143</v>
+      </c>
+      <c r="S77" t="s">
+        <v>143</v>
+      </c>
+      <c r="T77">
+        <f>INDEX(T18:T76,MATCH(Table2[[#This Row],[Alternative Module Code]],A18:A76,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U77">
+        <v>75</v>
+      </c>
+      <c r="V77">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="T77">
+        <v>25</v>
+      </c>
+      <c r="W77">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23">
       <c r="A78" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D78" s="28" t="s">
         <v>178</v>
@@ -33743,43 +34082,46 @@
       <c r="N78" t="s">
         <v>144</v>
       </c>
-      <c r="O78" t="s">
-        <v>144</v>
-      </c>
       <c r="P78" t="s">
         <v>144</v>
       </c>
-      <c r="Q78">
-        <f>INDEX(Q22:Q77,MATCH(Table2[[#This Row],[Alternative Module Code]],A22:A77,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R78">
-        <v>50</v>
-      </c>
-      <c r="S78">
+      <c r="R78" t="s">
+        <v>144</v>
+      </c>
+      <c r="S78" t="s">
+        <v>144</v>
+      </c>
+      <c r="T78">
+        <f>INDEX(T20:T77,MATCH(Table2[[#This Row],[Alternative Module Code]],A20:A77,0))</f>
+        <v>3</v>
+      </c>
+      <c r="U78">
+        <v>70</v>
+      </c>
+      <c r="V78">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>50</v>
-      </c>
-      <c r="T78">
+        <v>30</v>
+      </c>
+      <c r="W78">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23">
       <c r="A79" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>190</v>
+        <v>69</v>
       </c>
       <c r="D79" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F79" s="4">
         <v>7</v>
@@ -33794,40 +34136,52 @@
       <c r="N79" t="s">
         <v>144</v>
       </c>
+      <c r="O79" t="s">
+        <v>144</v>
+      </c>
       <c r="P79" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>143</v>
+      </c>
+      <c r="R79" t="s">
         <v>144</v>
       </c>
-      <c r="Q79">
-        <f>INDEX(Q23:Q78,MATCH(Table2[[#This Row],[Alternative Module Code]],A23:A78,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R79">
-        <v>80</v>
-      </c>
-      <c r="S79">
+      <c r="S79" t="s">
+        <v>144</v>
+      </c>
+      <c r="T79">
+        <f>INDEX(T21:T78,MATCH(Table2[[#This Row],[Alternative Module Code]],A21:A78,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U79">
+        <v>0</v>
+      </c>
+      <c r="V79">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>20</v>
-      </c>
-      <c r="T79">
+        <v>100</v>
+      </c>
+      <c r="W79">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23">
       <c r="A80" s="3" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>191</v>
+        <v>71</v>
       </c>
       <c r="D80" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F80" s="4">
         <v>7</v>
@@ -33845,31 +34199,37 @@
       <c r="O80" t="s">
         <v>144</v>
       </c>
-      <c r="Q80">
-        <f>INDEX(Q24:Q79,MATCH(Table2[[#This Row],[Alternative Module Code]],A24:A79,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R80">
-        <v>70</v>
-      </c>
-      <c r="S80">
+      <c r="R80" t="s">
+        <v>144</v>
+      </c>
+      <c r="S80" t="s">
+        <v>144</v>
+      </c>
+      <c r="T80">
+        <f>INDEX(T22:T79,MATCH(Table2[[#This Row],[Alternative Module Code]],A22:A79,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U80">
+        <v>50</v>
+      </c>
+      <c r="V80">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="T80">
+        <v>50</v>
+      </c>
+      <c r="W80">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23">
       <c r="A81" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D81" s="28" t="s">
         <v>178</v>
@@ -33890,37 +34250,40 @@
       <c r="N81" t="s">
         <v>144</v>
       </c>
-      <c r="O81" t="s">
-        <v>144</v>
-      </c>
       <c r="P81" t="s">
         <v>144</v>
       </c>
-      <c r="Q81">
-        <f>INDEX(Q25:Q80,MATCH(Table2[[#This Row],[Alternative Module Code]],A25:A80,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R81">
-        <v>40</v>
-      </c>
-      <c r="S81">
+      <c r="R81" t="s">
+        <v>144</v>
+      </c>
+      <c r="S81" t="s">
+        <v>144</v>
+      </c>
+      <c r="T81">
+        <f>INDEX(T23:T80,MATCH(Table2[[#This Row],[Alternative Module Code]],A23:A80,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U81">
+        <v>80</v>
+      </c>
+      <c r="V81">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>60</v>
-      </c>
-      <c r="T81">
+        <v>20</v>
+      </c>
+      <c r="W81">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" spans="1:23">
       <c r="A82" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D82" s="28" t="s">
         <v>178</v>
@@ -33938,34 +34301,43 @@
       <c r="M82" t="s">
         <v>144</v>
       </c>
+      <c r="N82" t="s">
+        <v>144</v>
+      </c>
       <c r="O82" t="s">
         <v>144</v>
       </c>
-      <c r="Q82">
-        <f>INDEX(Q26:Q81,MATCH(Table2[[#This Row],[Alternative Module Code]],A26:A81,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R82">
-        <v>80</v>
-      </c>
-      <c r="S82">
+      <c r="P82" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>144</v>
+      </c>
+      <c r="T82">
+        <f>INDEX(T24:T81,MATCH(Table2[[#This Row],[Alternative Module Code]],A24:A81,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U82">
+        <v>70</v>
+      </c>
+      <c r="V82">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>20</v>
-      </c>
-      <c r="T82">
+        <v>30</v>
+      </c>
+      <c r="W82">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23">
       <c r="A83" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="D83" s="28" t="s">
         <v>178</v>
@@ -33989,31 +34361,40 @@
       <c r="O83" t="s">
         <v>144</v>
       </c>
-      <c r="Q83">
-        <f>INDEX(Q27:Q82,MATCH(Table2[[#This Row],[Alternative Module Code]],A27:A82,0))</f>
-        <v>3</v>
-      </c>
-      <c r="R83">
-        <v>0</v>
-      </c>
-      <c r="S83">
+      <c r="P83" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>144</v>
+      </c>
+      <c r="R83" t="s">
+        <v>144</v>
+      </c>
+      <c r="T83">
+        <f>INDEX(T25:T82,MATCH(Table2[[#This Row],[Alternative Module Code]],A25:A82,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U83">
+        <v>40</v>
+      </c>
+      <c r="V83">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="T83">
+        <v>60</v>
+      </c>
+      <c r="W83">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23">
       <c r="A84" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>116</v>
+        <v>193</v>
       </c>
       <c r="D84" s="28" t="s">
         <v>178</v>
@@ -34031,37 +34412,37 @@
       <c r="M84" t="s">
         <v>144</v>
       </c>
-      <c r="N84" t="s">
-        <v>144</v>
-      </c>
       <c r="O84" t="s">
         <v>144</v>
       </c>
-      <c r="Q84">
-        <f>INDEX(Q28:Q83,MATCH(Table2[[#This Row],[Alternative Module Code]],A28:A83,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R84">
-        <v>70</v>
-      </c>
-      <c r="S84">
+      <c r="Q84" t="s">
+        <v>144</v>
+      </c>
+      <c r="T84">
+        <f>INDEX(T26:T83,MATCH(Table2[[#This Row],[Alternative Module Code]],A26:A83,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U84">
+        <v>80</v>
+      </c>
+      <c r="V84">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="T84">
+        <v>20</v>
+      </c>
+      <c r="W84">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23">
       <c r="A85" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="D85" s="28" t="s">
         <v>178</v>
@@ -34079,31 +34460,43 @@
       <c r="M85" t="s">
         <v>144</v>
       </c>
-      <c r="Q85">
-        <f>INDEX(Q29:Q84,MATCH(Table2[[#This Row],[Alternative Module Code]],A29:A84,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R85">
-        <v>50</v>
-      </c>
-      <c r="S85">
+      <c r="N85" t="s">
+        <v>144</v>
+      </c>
+      <c r="O85" t="s">
+        <v>144</v>
+      </c>
+      <c r="P85" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>144</v>
+      </c>
+      <c r="T85">
+        <f>INDEX(T27:T84,MATCH(Table2[[#This Row],[Alternative Module Code]],A27:A84,0))</f>
+        <v>3</v>
+      </c>
+      <c r="U85">
+        <v>0</v>
+      </c>
+      <c r="V85">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>50</v>
-      </c>
-      <c r="T85">
+        <v>100</v>
+      </c>
+      <c r="W85">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23">
       <c r="A86" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>194</v>
+        <v>116</v>
       </c>
       <c r="D86" s="28" t="s">
         <v>178</v>
@@ -34121,34 +34514,40 @@
       <c r="M86" t="s">
         <v>144</v>
       </c>
+      <c r="N86" t="s">
+        <v>144</v>
+      </c>
       <c r="O86" t="s">
         <v>144</v>
       </c>
-      <c r="Q86">
-        <f>INDEX(Q30:Q85,MATCH(Table2[[#This Row],[Alternative Module Code]],A30:A85,0))</f>
-        <v>3</v>
-      </c>
-      <c r="R86">
-        <v>60</v>
-      </c>
-      <c r="S86">
+      <c r="P86" t="s">
+        <v>144</v>
+      </c>
+      <c r="T86">
+        <f>INDEX(T28:T85,MATCH(Table2[[#This Row],[Alternative Module Code]],A28:A85,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U86">
+        <v>70</v>
+      </c>
+      <c r="V86">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>40</v>
-      </c>
-      <c r="T86">
+        <v>30</v>
+      </c>
+      <c r="W86">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23">
       <c r="A87" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>195</v>
+        <v>68</v>
       </c>
       <c r="D87" s="28" t="s">
         <v>178</v>
@@ -34166,131 +34565,145 @@
       <c r="M87" t="s">
         <v>144</v>
       </c>
-      <c r="N87" t="s">
+      <c r="R87" t="s">
+        <v>143</v>
+      </c>
+      <c r="S87" t="s">
+        <v>143</v>
+      </c>
+      <c r="T87">
+        <f>INDEX(T29:T86,MATCH(Table2[[#This Row],[Alternative Module Code]],A29:A86,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U87">
+        <v>50</v>
+      </c>
+      <c r="V87">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>50</v>
+      </c>
+      <c r="W87">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23">
+      <c r="A88" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D88" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F88" s="4">
+        <v>7</v>
+      </c>
+      <c r="G88" s="2">
+        <v>10</v>
+      </c>
+      <c r="H88" s="2"/>
+      <c r="M88" t="s">
         <v>144</v>
       </c>
-      <c r="O87" t="s">
+      <c r="O88" t="s">
         <v>144</v>
       </c>
-      <c r="Q87">
-        <f>INDEX(Q31:Q86,MATCH(Table2[[#This Row],[Alternative Module Code]],A31:A86,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R87">
+      <c r="Q88" t="s">
+        <v>144</v>
+      </c>
+      <c r="T88">
+        <f>INDEX(T30:T87,MATCH(Table2[[#This Row],[Alternative Module Code]],A30:A87,0))</f>
+        <v>3</v>
+      </c>
+      <c r="U88">
+        <v>60</v>
+      </c>
+      <c r="V88">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>40</v>
+      </c>
+      <c r="W88">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23">
+      <c r="A89" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D89" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F89" s="4">
+        <v>7</v>
+      </c>
+      <c r="G89" s="2">
+        <v>10</v>
+      </c>
+      <c r="H89" s="2"/>
+      <c r="M89" t="s">
+        <v>144</v>
+      </c>
+      <c r="N89" t="s">
+        <v>144</v>
+      </c>
+      <c r="O89" t="s">
+        <v>144</v>
+      </c>
+      <c r="P89" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>144</v>
+      </c>
+      <c r="T89">
+        <f>INDEX(T31:T88,MATCH(Table2[[#This Row],[Alternative Module Code]],A31:A88,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U89">
         <v>0</v>
       </c>
-      <c r="S87">
+      <c r="V89">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T87">
+      <c r="W89">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="88" spans="1:20">
-      <c r="A88" s="3" t="s">
+    <row r="90" spans="1:23">
+      <c r="A90" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B90" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C90" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D88" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F88" s="4">
-        <v>7</v>
-      </c>
-      <c r="G88" s="28">
-        <v>10</v>
-      </c>
-      <c r="H88" s="28"/>
-      <c r="M88" t="s">
-        <v>144</v>
-      </c>
-      <c r="N88" t="s">
-        <v>144</v>
-      </c>
-      <c r="O88" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q88">
-        <f>INDEX(Q32:Q87,MATCH(Table2[[#This Row],[Alternative Module Code]],A32:A87,0))</f>
-        <v>2</v>
-      </c>
-      <c r="R88">
-        <v>50</v>
-      </c>
-      <c r="S88">
-        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>50</v>
-      </c>
-      <c r="T88">
-        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30.000000000000004</v>
-      </c>
-    </row>
-    <row r="89" spans="1:20">
-      <c r="A89" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C89" s="3"/>
-      <c r="D89" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F89" s="4">
-        <v>7</v>
-      </c>
-      <c r="G89" s="28">
-        <v>10</v>
-      </c>
-      <c r="H89" s="28"/>
-      <c r="M89" t="s">
-        <v>144</v>
-      </c>
-      <c r="P89" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q89">
-        <v>2</v>
-      </c>
-      <c r="R89">
-        <v>0</v>
-      </c>
-      <c r="S89">
-        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="T89">
-        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="90" spans="1:20">
-      <c r="A90" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C90" s="3"/>
       <c r="D90" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F90" s="4">
         <v>7</v>
@@ -34305,37 +34718,44 @@
       <c r="N90" t="s">
         <v>144</v>
       </c>
+      <c r="O90" t="s">
+        <v>144</v>
+      </c>
       <c r="P90" t="s">
         <v>144</v>
       </c>
-      <c r="Q90">
-        <v>2</v>
-      </c>
-      <c r="R90">
-        <v>0</v>
-      </c>
-      <c r="S90">
+      <c r="Q90" t="s">
+        <v>144</v>
+      </c>
+      <c r="T90">
+        <f>INDEX(T32:T89,MATCH(Table2[[#This Row],[Alternative Module Code]],A32:A89,0))</f>
+        <v>2</v>
+      </c>
+      <c r="U90">
+        <v>50</v>
+      </c>
+      <c r="V90">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="T90">
+        <v>50</v>
+      </c>
+      <c r="W90">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="91" spans="1:20">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23">
       <c r="A91" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F91" s="4">
         <v>7</v>
@@ -34347,30 +34767,33 @@
       <c r="M91" t="s">
         <v>144</v>
       </c>
-      <c r="P91" t="s">
+      <c r="R91" t="s">
         <v>144</v>
       </c>
-      <c r="Q91">
-        <v>2</v>
-      </c>
-      <c r="R91">
+      <c r="S91" t="s">
+        <v>144</v>
+      </c>
+      <c r="T91">
+        <v>2</v>
+      </c>
+      <c r="U91">
         <v>0</v>
       </c>
-      <c r="S91">
+      <c r="V91">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T91">
+      <c r="W91">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="1:20">
+    <row r="92" spans="1:23">
       <c r="A92" s="3" t="s">
-        <v>181</v>
+        <v>244</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>184</v>
+        <v>245</v>
       </c>
       <c r="C92" s="3"/>
       <c r="D92" s="28" t="s">
@@ -34382,43 +34805,43 @@
       <c r="F92" s="4">
         <v>7</v>
       </c>
-      <c r="G92" s="2">
-        <v>20</v>
-      </c>
-      <c r="H92" s="2"/>
+      <c r="G92" s="28">
+        <v>10</v>
+      </c>
+      <c r="H92" s="28"/>
       <c r="M92" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N92" t="s">
-        <v>143</v>
-      </c>
-      <c r="O92" t="s">
-        <v>143</v>
-      </c>
-      <c r="P92" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q92">
-        <v>3</v>
-      </c>
-      <c r="R92">
+        <v>144</v>
+      </c>
+      <c r="R92" t="s">
+        <v>144</v>
+      </c>
+      <c r="S92" t="s">
+        <v>144</v>
+      </c>
+      <c r="T92">
+        <v>2</v>
+      </c>
+      <c r="U92">
         <v>0</v>
       </c>
-      <c r="S92">
+      <c r="V92">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T92">
+      <c r="W92">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="93" spans="1:20">
+    <row r="93" spans="1:23">
       <c r="A93" s="3" t="s">
-        <v>182</v>
+        <v>246</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>185</v>
+        <v>247</v>
       </c>
       <c r="C93" s="3"/>
       <c r="D93" s="28" t="s">
@@ -34430,248 +34853,565 @@
       <c r="F93" s="4">
         <v>7</v>
       </c>
-      <c r="G93" s="2">
-        <v>20</v>
-      </c>
-      <c r="H93" s="2"/>
+      <c r="G93" s="28">
+        <v>10</v>
+      </c>
+      <c r="H93" s="28"/>
       <c r="M93" t="s">
-        <v>143</v>
-      </c>
-      <c r="N93" t="s">
-        <v>143</v>
-      </c>
-      <c r="O93" t="s">
-        <v>143</v>
-      </c>
-      <c r="P93" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q93">
-        <v>4</v>
-      </c>
-      <c r="R93">
+        <v>144</v>
+      </c>
+      <c r="R93" t="s">
+        <v>144</v>
+      </c>
+      <c r="S93" t="s">
+        <v>144</v>
+      </c>
+      <c r="T93">
+        <v>2</v>
+      </c>
+      <c r="U93">
         <v>0</v>
       </c>
-      <c r="S93">
+      <c r="V93">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="T93">
+      <c r="W93">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="1:20">
-      <c r="A94"/>
-      <c r="B94"/>
-      <c r="C94"/>
-      <c r="D94"/>
-      <c r="E94"/>
-      <c r="F94"/>
-      <c r="G94"/>
-      <c r="H94"/>
-    </row>
-    <row r="95" spans="1:20">
-      <c r="A95"/>
-      <c r="B95"/>
-      <c r="C95"/>
-      <c r="D95"/>
-      <c r="E95"/>
-      <c r="F95"/>
-      <c r="G95"/>
-      <c r="H95"/>
-    </row>
-    <row r="96" spans="1:20">
-      <c r="A96"/>
-      <c r="B96"/>
-      <c r="C96"/>
-      <c r="D96"/>
-      <c r="E96"/>
-      <c r="F96"/>
-      <c r="G96"/>
-      <c r="H96"/>
-    </row>
-    <row r="97" customFormat="1"/>
-    <row r="98" customFormat="1"/>
-    <row r="99" customFormat="1"/>
-    <row r="100" customFormat="1"/>
-    <row r="101" customFormat="1"/>
-    <row r="102" customFormat="1"/>
-    <row r="103" customFormat="1"/>
-    <row r="104" customFormat="1"/>
-    <row r="105" customFormat="1"/>
-    <row r="106" customFormat="1"/>
-    <row r="107" customFormat="1"/>
-    <row r="108" customFormat="1"/>
-    <row r="109" customFormat="1"/>
-    <row r="110" customFormat="1"/>
-    <row r="111" customFormat="1"/>
-    <row r="112" customFormat="1"/>
-    <row r="113" spans="1:8">
-      <c r="A113"/>
-      <c r="B113"/>
-      <c r="C113"/>
-      <c r="D113"/>
-      <c r="E113"/>
-      <c r="F113"/>
-      <c r="G113"/>
-      <c r="H113"/>
-    </row>
-    <row r="114" spans="1:8">
-      <c r="A114"/>
-      <c r="B114"/>
-      <c r="C114"/>
-      <c r="D114"/>
-      <c r="E114"/>
-      <c r="F114"/>
-      <c r="G114"/>
-      <c r="H114"/>
-    </row>
-    <row r="115" spans="1:8">
-      <c r="A115"/>
-      <c r="B115"/>
-      <c r="C115"/>
-      <c r="D115"/>
-      <c r="E115"/>
-      <c r="F115"/>
-      <c r="G115"/>
-      <c r="H115"/>
-    </row>
-    <row r="116" spans="1:8">
-      <c r="A116"/>
-      <c r="B116"/>
-      <c r="C116"/>
-      <c r="D116"/>
-      <c r="E116"/>
-      <c r="F116"/>
-      <c r="G116"/>
-      <c r="H116"/>
-    </row>
-    <row r="117" spans="1:8">
-      <c r="A117"/>
-      <c r="B117"/>
-      <c r="C117"/>
-      <c r="D117"/>
-      <c r="E117"/>
-      <c r="F117"/>
-      <c r="G117"/>
-      <c r="H117"/>
-    </row>
-    <row r="118" spans="1:8">
-      <c r="A118"/>
-      <c r="B118"/>
-      <c r="C118"/>
-      <c r="D118"/>
-      <c r="E118"/>
-      <c r="F118"/>
-      <c r="G118"/>
-      <c r="H118"/>
-    </row>
-    <row r="119" spans="1:8">
-      <c r="A119"/>
-      <c r="B119"/>
-      <c r="C119"/>
-      <c r="D119"/>
-      <c r="E119"/>
-      <c r="F119"/>
-      <c r="G119"/>
-      <c r="H119"/>
-    </row>
-    <row r="120" spans="1:8">
-      <c r="A120"/>
-      <c r="B120"/>
-      <c r="C120"/>
-      <c r="D120"/>
-      <c r="E120"/>
-      <c r="F120"/>
-      <c r="G120"/>
-      <c r="H120"/>
-    </row>
-    <row r="121" spans="1:8">
-      <c r="A121"/>
-      <c r="B121"/>
-      <c r="C121"/>
-      <c r="D121"/>
-      <c r="E121"/>
-      <c r="F121"/>
-      <c r="G121"/>
-      <c r="H121"/>
-    </row>
-    <row r="122" spans="1:8">
-      <c r="A122"/>
-      <c r="B122"/>
-      <c r="C122"/>
-      <c r="D122"/>
-      <c r="E122"/>
-      <c r="F122"/>
-      <c r="G122"/>
-      <c r="H122"/>
-    </row>
-    <row r="123" spans="1:8">
-      <c r="A123"/>
-      <c r="B123"/>
-      <c r="C123"/>
-      <c r="D123"/>
-      <c r="E123"/>
-      <c r="F123"/>
-      <c r="G123"/>
-      <c r="H123"/>
-    </row>
-    <row r="124" spans="1:8">
-      <c r="A124"/>
-      <c r="B124"/>
-      <c r="C124"/>
-      <c r="D124"/>
-      <c r="E124"/>
-      <c r="F124"/>
-      <c r="G124"/>
-      <c r="H124"/>
-    </row>
-    <row r="125" spans="1:8">
-      <c r="A125"/>
-      <c r="B125"/>
-      <c r="C125"/>
-      <c r="D125"/>
-      <c r="E125"/>
-      <c r="F125"/>
-      <c r="G125"/>
-      <c r="H125"/>
-    </row>
-    <row r="126" spans="1:8">
-      <c r="A126"/>
-      <c r="B126"/>
-      <c r="C126"/>
-      <c r="D126"/>
-      <c r="E126"/>
-      <c r="F126"/>
-      <c r="G126"/>
-      <c r="H126"/>
-    </row>
-    <row r="127" spans="1:8">
-      <c r="A127" s="3"/>
-      <c r="B127" s="3"/>
-      <c r="C127" s="3"/>
-      <c r="D127" s="3"/>
-      <c r="E127" s="3"/>
-      <c r="F127" s="3"/>
-      <c r="G127" s="3"/>
-      <c r="H127" s="3"/>
+    <row r="94" spans="1:23">
+      <c r="A94" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C94" s="3"/>
+      <c r="D94" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F94" s="4">
+        <v>7</v>
+      </c>
+      <c r="G94" s="2">
+        <v>20</v>
+      </c>
+      <c r="H94" s="2"/>
+      <c r="M94" t="s">
+        <v>143</v>
+      </c>
+      <c r="N94" t="s">
+        <v>143</v>
+      </c>
+      <c r="O94" t="s">
+        <v>143</v>
+      </c>
+      <c r="P94" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>143</v>
+      </c>
+      <c r="R94" t="s">
+        <v>143</v>
+      </c>
+      <c r="S94" t="s">
+        <v>143</v>
+      </c>
+      <c r="T94">
+        <v>3</v>
+      </c>
+      <c r="U94">
+        <v>0</v>
+      </c>
+      <c r="V94">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="W94">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23">
+      <c r="A95" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C95" s="3"/>
+      <c r="D95" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F95" s="4">
+        <v>7</v>
+      </c>
+      <c r="G95" s="2">
+        <v>20</v>
+      </c>
+      <c r="H95" s="2"/>
+      <c r="M95" t="s">
+        <v>143</v>
+      </c>
+      <c r="N95" t="s">
+        <v>143</v>
+      </c>
+      <c r="O95" t="s">
+        <v>143</v>
+      </c>
+      <c r="P95" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>143</v>
+      </c>
+      <c r="R95" t="s">
+        <v>143</v>
+      </c>
+      <c r="S95" t="s">
+        <v>143</v>
+      </c>
+      <c r="T95">
+        <v>4</v>
+      </c>
+      <c r="U95">
+        <v>0</v>
+      </c>
+      <c r="V95">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="W95">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23">
+      <c r="A96" s="46" t="s">
+        <v>319</v>
+      </c>
+      <c r="B96" s="46" t="s">
+        <v>320</v>
+      </c>
+      <c r="C96" s="46"/>
+      <c r="D96" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E96" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="F96" s="47">
+        <v>7</v>
+      </c>
+      <c r="G96" s="48">
+        <v>10</v>
+      </c>
+      <c r="H96" s="28"/>
+      <c r="I96" s="49"/>
+      <c r="K96" s="49"/>
+      <c r="L96" s="49"/>
+      <c r="M96" t="s">
+        <v>144</v>
+      </c>
+      <c r="N96" s="49"/>
+      <c r="O96" s="49"/>
+      <c r="P96" s="49"/>
+      <c r="Q96" s="49"/>
+      <c r="R96" t="s">
+        <v>144</v>
+      </c>
+      <c r="S96" t="s">
+        <v>144</v>
+      </c>
+      <c r="T96">
+        <v>2</v>
+      </c>
+      <c r="U96">
+        <v>70</v>
+      </c>
+      <c r="V96" s="50">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>30</v>
+      </c>
+      <c r="W96" s="50">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>30.000000000000004</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23">
+      <c r="A97" s="46" t="s">
+        <v>383</v>
+      </c>
+      <c r="B97" s="46" t="s">
+        <v>384</v>
+      </c>
+      <c r="C97" s="46"/>
+      <c r="D97" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E97" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="F97" s="47">
+        <v>7</v>
+      </c>
+      <c r="G97" s="48">
+        <v>10</v>
+      </c>
+      <c r="H97" s="28"/>
+      <c r="I97" s="49"/>
+      <c r="K97" s="49"/>
+      <c r="L97" s="49"/>
+      <c r="M97" t="s">
+        <v>144</v>
+      </c>
+      <c r="N97" s="49"/>
+      <c r="O97" s="49"/>
+      <c r="P97" s="49"/>
+      <c r="Q97" s="49"/>
+      <c r="R97" t="s">
+        <v>144</v>
+      </c>
+      <c r="S97" t="s">
+        <v>144</v>
+      </c>
+      <c r="T97">
+        <v>2</v>
+      </c>
+      <c r="U97">
+        <v>100</v>
+      </c>
+      <c r="V97" s="50">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>0</v>
+      </c>
+      <c r="W97" s="50">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23">
+      <c r="A98" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="B98" s="46" t="s">
+        <v>325</v>
+      </c>
+      <c r="C98" s="46"/>
+      <c r="D98" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E98" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="F98" s="47">
+        <v>7</v>
+      </c>
+      <c r="G98" s="48">
+        <v>10</v>
+      </c>
+      <c r="H98" s="28"/>
+      <c r="I98" s="49"/>
+      <c r="K98" s="49"/>
+      <c r="L98" s="49"/>
+      <c r="M98" t="s">
+        <v>144</v>
+      </c>
+      <c r="N98" s="49"/>
+      <c r="O98" s="49"/>
+      <c r="P98" s="49"/>
+      <c r="Q98" s="49"/>
+      <c r="R98" t="s">
+        <v>144</v>
+      </c>
+      <c r="S98" t="s">
+        <v>144</v>
+      </c>
+      <c r="T98">
+        <v>2</v>
+      </c>
+      <c r="U98">
+        <v>0</v>
+      </c>
+      <c r="V98" s="50">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="W98" s="50">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23">
+      <c r="A99" s="46" t="s">
+        <v>330</v>
+      </c>
+      <c r="B99" s="46" t="s">
+        <v>331</v>
+      </c>
+      <c r="C99" s="46"/>
+      <c r="D99" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E99" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="F99" s="47">
+        <v>7</v>
+      </c>
+      <c r="G99" s="48">
+        <v>20</v>
+      </c>
+      <c r="H99" s="28"/>
+      <c r="I99" s="49"/>
+      <c r="K99" s="49"/>
+      <c r="L99" s="49"/>
+      <c r="M99" t="s">
+        <v>144</v>
+      </c>
+      <c r="N99" s="49"/>
+      <c r="O99" s="49"/>
+      <c r="P99" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q99" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="T99">
+        <v>4</v>
+      </c>
+      <c r="U99">
+        <v>0</v>
+      </c>
+      <c r="V99" s="50">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="W99" s="50">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23">
+      <c r="A100" s="46" t="s">
+        <v>334</v>
+      </c>
+      <c r="B100" s="46" t="s">
+        <v>335</v>
+      </c>
+      <c r="C100" s="46"/>
+      <c r="D100" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E100" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="F100" s="47">
+        <v>7</v>
+      </c>
+      <c r="G100" s="48">
+        <v>20</v>
+      </c>
+      <c r="H100" s="28"/>
+      <c r="I100" s="49"/>
+      <c r="K100" s="49"/>
+      <c r="L100" s="49"/>
+      <c r="M100" t="s">
+        <v>144</v>
+      </c>
+      <c r="N100" s="49"/>
+      <c r="O100" s="49"/>
+      <c r="P100" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q100" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="T100">
+        <v>4</v>
+      </c>
+      <c r="U100">
+        <v>50</v>
+      </c>
+      <c r="V100" s="50">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>50</v>
+      </c>
+      <c r="W100" s="50">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23">
+      <c r="A101"/>
+      <c r="B101"/>
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
+      <c r="H101"/>
+    </row>
+    <row r="102" spans="1:23">
+      <c r="A102"/>
+      <c r="B102"/>
+      <c r="C102"/>
+      <c r="D102"/>
+      <c r="E102"/>
+      <c r="F102"/>
+      <c r="G102"/>
+      <c r="H102"/>
+    </row>
+    <row r="103" spans="1:23">
+      <c r="A103"/>
+      <c r="B103"/>
+      <c r="C103"/>
+      <c r="D103"/>
+      <c r="E103"/>
+      <c r="F103"/>
+      <c r="G103"/>
+      <c r="H103"/>
+    </row>
+    <row r="104" spans="1:23">
+      <c r="A104"/>
+      <c r="B104"/>
+      <c r="C104"/>
+      <c r="D104"/>
+      <c r="E104"/>
+      <c r="F104"/>
+      <c r="G104"/>
+      <c r="H104"/>
+    </row>
+    <row r="105" spans="1:23">
+      <c r="A105"/>
+      <c r="B105"/>
+      <c r="C105"/>
+      <c r="D105"/>
+      <c r="E105"/>
+      <c r="F105"/>
+      <c r="G105"/>
+      <c r="H105"/>
+    </row>
+    <row r="106" spans="1:23">
+      <c r="A106"/>
+      <c r="B106"/>
+      <c r="C106"/>
+      <c r="D106"/>
+      <c r="E106"/>
+      <c r="F106"/>
+      <c r="G106"/>
+      <c r="H106"/>
+    </row>
+    <row r="107" spans="1:23">
+      <c r="A107"/>
+      <c r="B107"/>
+      <c r="C107"/>
+      <c r="D107"/>
+      <c r="E107"/>
+      <c r="F107"/>
+      <c r="G107"/>
+      <c r="H107"/>
+    </row>
+    <row r="108" spans="1:23">
+      <c r="A108"/>
+      <c r="B108"/>
+      <c r="C108"/>
+      <c r="D108"/>
+      <c r="E108"/>
+      <c r="F108"/>
+      <c r="G108"/>
+      <c r="H108"/>
+    </row>
+    <row r="109" spans="1:23">
+      <c r="A109"/>
+      <c r="B109"/>
+      <c r="C109"/>
+      <c r="D109"/>
+      <c r="E109"/>
+      <c r="F109"/>
+      <c r="G109"/>
+      <c r="H109"/>
+    </row>
+    <row r="110" spans="1:23">
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+      <c r="D110"/>
+      <c r="E110"/>
+      <c r="F110"/>
+      <c r="G110"/>
+      <c r="H110"/>
+    </row>
+    <row r="111" spans="1:23">
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+      <c r="D111"/>
+      <c r="E111"/>
+      <c r="F111"/>
+      <c r="G111"/>
+      <c r="H111"/>
+    </row>
+    <row r="112" spans="1:23">
+      <c r="A112"/>
+      <c r="B112"/>
+      <c r="C112"/>
+      <c r="D112"/>
+      <c r="E112"/>
+      <c r="F112"/>
+      <c r="G112"/>
+      <c r="H112"/>
+    </row>
+    <row r="113" customFormat="1"/>
+    <row r="114" customFormat="1"/>
+    <row r="115" customFormat="1"/>
+    <row r="116" customFormat="1"/>
+    <row r="117" customFormat="1"/>
+    <row r="118" customFormat="1"/>
+    <row r="119" customFormat="1"/>
+    <row r="120" customFormat="1"/>
+    <row r="121" customFormat="1"/>
+    <row r="122" customFormat="1"/>
+    <row r="123" customFormat="1"/>
+    <row r="124" customFormat="1"/>
+    <row r="125" customFormat="1"/>
+    <row r="126" customFormat="1"/>
+    <row r="127" customFormat="1"/>
+    <row r="128" customFormat="1"/>
+    <row r="129" spans="1:8">
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3"/>
+      <c r="H129" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="E2:E93">
-    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="SEMD">
+  <conditionalFormatting sqref="E2:E100">
+    <cfRule type="containsText" dxfId="12" priority="12" operator="containsText" text="SEMD">
       <formula>NOT(ISERROR(SEARCH("SEMD",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="SEM2">
+    <cfRule type="containsText" dxfId="11" priority="13" operator="containsText" text="SEM2">
       <formula>NOT(ISERROR(SEARCH("SEM2",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="6" operator="containsText" text="SEM1">
+    <cfRule type="containsText" dxfId="10" priority="14" operator="containsText" text="SEM1">
       <formula>NOT(ISERROR(SEARCH("SEM1",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F93">
-    <cfRule type="colorScale" priority="153">
+  <conditionalFormatting sqref="F2:F100">
+    <cfRule type="colorScale" priority="161">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -34680,8 +35420,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G93">
-    <cfRule type="colorScale" priority="155">
+  <conditionalFormatting sqref="G2:G100">
+    <cfRule type="colorScale" priority="163">
       <colorScale>
         <cfvo type="num" val="10"/>
         <cfvo type="percentile" val="50"/>
@@ -34692,17 +35432,58 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:Q93">
-    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="O">
+  <conditionalFormatting sqref="H2:T95 H96:S100">
+    <cfRule type="containsText" dxfId="9" priority="16" operator="containsText" text="O">
       <formula>NOT(ISERROR(SEARCH("O",H2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="9" operator="containsText" text="C">
+    <cfRule type="containsText" dxfId="8" priority="17" operator="containsText" text="C">
       <formula>NOT(ISERROR(SEARCH("C",H2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T93">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>T2&lt;&gt;S2</formula>
+  <conditionalFormatting sqref="W2:W100">
+    <cfRule type="expression" dxfId="6" priority="9">
+      <formula>W2&lt;&gt;V2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E96:E100">
+    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="SEMD">
+      <formula>NOT(ISERROR(SEARCH("SEMD",E96)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="SEM2">
+      <formula>NOT(ISERROR(SEARCH("SEM2",E96)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="SEM1">
+      <formula>NOT(ISERROR(SEARCH("SEM1",E96)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F96:F100">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G96:G100">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="10"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T96:T100">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="O">
+      <formula>NOT(ISERROR(SEARCH("O",T96)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="C">
+      <formula>NOT(ISERROR(SEARCH("C",T96)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34714,7 +35495,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{AB48118A-1CFE-488B-B12E-453EA0CADD16}">
+          <x14:cfRule type="containsText" priority="10" operator="containsText" id="{AB48118A-1CFE-488B-B12E-453EA0CADD16}">
             <xm:f>NOT(ISERROR(SEARCH("-",I2)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
@@ -34725,7 +35506,21 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>I2:Q93</xm:sqref>
+          <xm:sqref>I2:T95 I96:S100</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{631B2A6D-16EC-488F-9A76-B8FF0576AF03}">
+            <xm:f>NOT(ISERROR(SEARCH("-",T96)))</xm:f>
+            <xm:f>"-"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0" tint="-0.24994659260841701"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>T96:T100</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -35420,7 +36215,7 @@
       </c>
       <c r="C31">
         <f>SUMIF(Table1[Module Code],Sheet2!A31,Table1[Total Hours])</f>
-        <v>8</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="D31">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A31,Table14[Module Code],0))</f>
@@ -35428,11 +36223,11 @@
       </c>
       <c r="E31">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>24.666666666666668</v>
       </c>
       <c r="F31">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>2.4666666666666668</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -35660,7 +36455,7 @@
       </c>
       <c r="C41">
         <f>SUMIF(Table1[Module Code],Sheet2!A41,Table1[Total Hours])</f>
-        <v>9.6000000000000014</v>
+        <v>8</v>
       </c>
       <c r="D41" t="e">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A41,Table14[Module Code],0))</f>

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1512" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96133C9B-F3E8-486A-BB54-652495E5D8D5}"/>
+  <xr:revisionPtr revIDLastSave="1518" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{110D60BC-2481-4889-855B-EECDB33D830D}"/>
   <bookViews>
-    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="2" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
+    <workbookView xWindow="19110" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Assessments" sheetId="1" r:id="rId1"/>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="J17" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0.53333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="K17" s="11">
         <v>0.5</v>
@@ -11572,11 +11572,9 @@
       <c r="AA17" s="20">
         <v>0.02</v>
       </c>
-      <c r="AB17" s="20">
+      <c r="AB17" s="20"/>
+      <c r="AC17" s="20">
         <v>0.02</v>
-      </c>
-      <c r="AC17" s="20">
-        <v>-0.02</v>
       </c>
       <c r="AD17" s="20"/>
       <c r="AE17" s="20">
@@ -11632,7 +11630,7 @@
       </c>
       <c r="J18" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K18" s="11"/>
       <c r="L18" s="18"/>
@@ -11652,11 +11650,9 @@
       <c r="Z18" s="20"/>
       <c r="AA18" s="20"/>
       <c r="AB18" s="20">
-        <v>-0.1</v>
-      </c>
-      <c r="AC18" s="20">
         <v>0.1</v>
       </c>
+      <c r="AC18" s="20"/>
       <c r="AD18" s="20"/>
       <c r="AE18" s="20"/>
       <c r="AF18" s="20"/>
@@ -11670,7 +11666,7 @@
       </c>
       <c r="AL18" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -11776,7 +11772,7 @@
       </c>
       <c r="J20" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>4</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="K20" s="11">
         <v>4</v>
@@ -11800,9 +11796,11 @@
       </c>
       <c r="AA20" s="20"/>
       <c r="AB20" s="20">
+        <v>-0.1</v>
+      </c>
+      <c r="AC20" s="20">
         <v>0.1</v>
       </c>
-      <c r="AC20" s="20"/>
       <c r="AD20" s="20"/>
       <c r="AE20" s="20">
         <v>0.1</v>
@@ -35711,7 +35709,7 @@
       </c>
       <c r="C10">
         <f>SUMIF(Table1[Module Code],Sheet2!A10,Table1[Total Hours])</f>
-        <v>6.5</v>
+        <v>10.5</v>
       </c>
       <c r="D10">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A10,Table14[Module Code],0))</f>
@@ -35719,11 +35717,11 @@
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>28.5</v>
+        <v>32.5</v>
       </c>
       <c r="F10">
         <f t="shared" si="1"/>
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="11" spans="1:6">

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1636" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDF25096-6C25-4464-9382-E85C5EBCFE74}"/>
+  <xr:revisionPtr revIDLastSave="1667" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44791E17-0171-4A8F-AC83-9BF5FE1675C4}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
@@ -22,6 +22,7 @@
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -941,15 +942,6 @@
     <t>Semiconductor Fabrication</t>
   </si>
   <si>
-    <t>Weekly Tasks (P)</t>
-  </si>
-  <si>
-    <t>Peer assess. (P)</t>
-  </si>
-  <si>
-    <t>Synoptic Refl. (P)</t>
-  </si>
-  <si>
     <t>Quiz Portfolio (P)
 (best 5 of 8)</t>
   </si>
@@ -1230,6 +1222,16 @@
   <si>
     <t>Presentation (*)
 +/- 1 week</t>
+  </si>
+  <si>
+    <t>Reflective Report</t>
+  </si>
+  <si>
+    <t>Class Activities
+(beat 7 of 9)</t>
+  </si>
+  <si>
+    <t>Synoptic Reflection</t>
   </si>
 </sst>
 </file>
@@ -1324,7 +1326,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1455,15 +1457,6 @@
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10118,7 +10111,7 @@
         <v>228</v>
       </c>
       <c r="H1" s="40" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="I1" s="40" t="s">
         <v>75</v>
@@ -10202,7 +10195,7 @@
         <v>174</v>
       </c>
       <c r="AJ1" s="42" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AK1" s="43" t="s">
         <v>175</v>
@@ -10236,7 +10229,7 @@
         <v>229</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I2" s="11">
         <v>1</v>
@@ -10309,13 +10302,13 @@
         <v>20</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I3" s="11">
         <v>4</v>
@@ -10388,7 +10381,7 @@
         <v>229</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I4" s="11">
         <v>3</v>
@@ -10461,7 +10454,7 @@
         <v>220</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I5" s="11">
         <v>1</v>
@@ -10534,7 +10527,7 @@
         <v>229</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I6" s="11">
         <v>1</v>
@@ -10632,7 +10625,7 @@
         <v>229</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I7" s="11">
         <v>2</v>
@@ -10712,7 +10705,7 @@
         <v>229</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="I8" s="11">
         <v>3</v>
@@ -10779,13 +10772,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G9" s="11" t="s">
         <v>220</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="I9" s="11">
         <v>1</v>
@@ -10890,13 +10883,13 @@
         <v>20</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G10" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="I10" s="11">
         <v>2</v>
@@ -10973,13 +10966,13 @@
         <v>20</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="G11" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="I11" s="11">
         <v>1</v>
@@ -11052,7 +11045,7 @@
         <v>229</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I12" s="11">
         <v>3</v>
@@ -11125,7 +11118,7 @@
         <v>229</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I13" s="11">
         <v>2</v>
@@ -11216,7 +11209,7 @@
         <v>229</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="I14" s="11">
         <v>1</v>
@@ -11301,13 +11294,13 @@
         <v>10</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I15" s="11">
         <v>3</v>
@@ -11376,13 +11369,13 @@
         <v>10</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G16" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I16" s="11">
         <v>2</v>
@@ -11455,7 +11448,7 @@
         <v>229</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I17" s="11">
         <v>1</v>
@@ -11536,7 +11529,7 @@
         <v>229</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I18" s="11">
         <v>4</v>
@@ -11601,13 +11594,13 @@
         <v>10</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="G19" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I19" s="11">
         <v>4</v>
@@ -11678,7 +11671,7 @@
         <v>229</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I20" s="11">
         <v>2</v>
@@ -11759,7 +11752,7 @@
         <v>229</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I21" s="11">
         <v>6</v>
@@ -11830,7 +11823,7 @@
         <v>229</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I22" s="11">
         <v>6</v>
@@ -11895,13 +11888,13 @@
         <v>20</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I23" s="11">
         <v>1</v>
@@ -11986,13 +11979,13 @@
         <v>20</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I24" s="11">
         <v>3</v>
@@ -12067,7 +12060,7 @@
         <v>229</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I25" s="11">
         <v>2</v>
@@ -12148,7 +12141,7 @@
         <v>229</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I26" s="11">
         <v>1</v>
@@ -12231,7 +12224,7 @@
         <v>229</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I27" s="11">
         <v>3</v>
@@ -12298,13 +12291,13 @@
         <v>10</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I28" s="11">
         <v>1</v>
@@ -12389,13 +12382,13 @@
         <v>10</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G29" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I29" s="11">
         <v>3</v>
@@ -12472,7 +12465,7 @@
         <v>229</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I30" s="11">
         <v>1</v>
@@ -12545,7 +12538,7 @@
         <v>229</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I31" s="11">
         <v>3</v>
@@ -12597,7 +12590,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:38">
+    <row r="32" spans="1:38" ht="28">
       <c r="A32" s="4" t="s">
         <v>44</v>
       </c>
@@ -12615,57 +12608,53 @@
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>295</v>
+      <c r="F32" s="37" t="s">
+        <v>388</v>
       </c>
       <c r="G32" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I32" s="11">
         <v>1</v>
       </c>
       <c r="J32" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0.18181818181818185</v>
+        <v>0.4</v>
       </c>
       <c r="K32" s="11"/>
       <c r="L32" s="18">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="M32" s="18">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="N32" s="18">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="O32" s="18">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="P32" s="18">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="Q32" s="18">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="R32" s="18">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="S32" s="18">
-        <v>1E-3</v>
+        <v>0.01</v>
       </c>
       <c r="T32" s="18">
-        <v>1E-3</v>
-      </c>
-      <c r="U32" s="18">
-        <v>1E-3</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="U32" s="18"/>
       <c r="V32" s="18"/>
-      <c r="W32" s="19">
-        <v>0.04</v>
-      </c>
+      <c r="W32" s="19"/>
       <c r="X32" s="20"/>
       <c r="Y32" s="20"/>
       <c r="Z32" s="20"/>
@@ -12681,11 +12670,11 @@
       <c r="AJ32" s="20"/>
       <c r="AK32" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="AL32" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>2.0000000000000004</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="33" spans="1:38">
@@ -12707,20 +12696,20 @@
         <v>10</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>296</v>
+        <v>387</v>
       </c>
       <c r="G33" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I33" s="11">
         <v>2</v>
       </c>
       <c r="J33" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>3</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="K33" s="11">
         <v>2</v>
@@ -12729,15 +12718,17 @@
       <c r="M33" s="18"/>
       <c r="N33" s="18"/>
       <c r="O33" s="19">
-        <v>7.4999999999999997E-2</v>
+        <v>0.08</v>
       </c>
       <c r="P33" s="19"/>
       <c r="Q33" s="18"/>
       <c r="R33" s="18"/>
       <c r="S33" s="18">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="T33" s="18"/>
+        <v>-7.4999999999999997E-2</v>
+      </c>
+      <c r="T33" s="18">
+        <v>0.08</v>
+      </c>
       <c r="U33" s="18"/>
       <c r="V33" s="18"/>
       <c r="W33" s="19"/>
@@ -12756,7 +12747,7 @@
       <c r="AJ33" s="20"/>
       <c r="AK33" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="AL33" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -12788,14 +12779,14 @@
         <v>229</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I34" s="11">
         <v>3</v>
       </c>
       <c r="J34" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K34" s="11">
         <v>15</v>
@@ -12807,9 +12798,11 @@
       <c r="P34" s="18"/>
       <c r="Q34" s="18"/>
       <c r="R34" s="18">
+        <v>-0.2</v>
+      </c>
+      <c r="S34" s="19">
         <v>0.2</v>
       </c>
-      <c r="S34" s="19"/>
       <c r="T34" s="18"/>
       <c r="U34" s="18"/>
       <c r="V34" s="18"/>
@@ -12855,20 +12848,20 @@
         <v>10</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>297</v>
+        <v>389</v>
       </c>
       <c r="G35" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I35" s="11">
         <v>9</v>
       </c>
       <c r="J35" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K35" s="11">
         <v>9</v>
@@ -12885,7 +12878,7 @@
       <c r="U35" s="18"/>
       <c r="V35" s="18"/>
       <c r="W35" s="19">
-        <v>0.6</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="X35" s="20"/>
       <c r="Y35" s="20"/>
@@ -12902,7 +12895,7 @@
       <c r="AJ35" s="20"/>
       <c r="AK35" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.6</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AL35" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -12928,13 +12921,13 @@
         <v>10</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G36" s="11" t="s">
         <v>220</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I36" s="11">
         <v>1</v>
@@ -12998,7 +12991,7 @@
         <v>43</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D37" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -13009,13 +13002,13 @@
         <v>10</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G37" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I37" s="11">
         <v>1</v>
@@ -13088,7 +13081,7 @@
         <v>229</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I38" s="11">
         <v>5</v>
@@ -13159,7 +13152,7 @@
         <v>229</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I39" s="11">
         <v>3</v>
@@ -13236,7 +13229,7 @@
         <v>229</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I40" s="11">
         <v>1</v>
@@ -13309,7 +13302,7 @@
         <v>229</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I41" s="11">
         <v>3</v>
@@ -13382,7 +13375,7 @@
         <v>229</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I42" s="11">
         <v>9</v>
@@ -13447,13 +13440,13 @@
         <v>20</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G43" s="11" t="s">
         <v>220</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I43" s="11">
         <v>1</v>
@@ -13556,13 +13549,13 @@
         <v>20</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="G44" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I44" s="11">
         <v>1</v>
@@ -13629,13 +13622,13 @@
         <v>20</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G45" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I45" s="11">
         <v>3</v>
@@ -13706,13 +13699,13 @@
         <v>20</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="G46" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I46" s="11">
         <v>3</v>
@@ -13789,7 +13782,7 @@
         <v>229</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I47" s="11">
         <v>11</v>
@@ -13862,7 +13855,7 @@
         <v>229</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I48" s="11">
         <v>4</v>
@@ -13929,13 +13922,13 @@
         <v>20</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G49" s="11" t="s">
         <v>220</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I49" s="11">
         <v>1</v>
@@ -14046,7 +14039,7 @@
         <v>229</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I50" s="11">
         <v>2</v>
@@ -14125,7 +14118,7 @@
         <v>229</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="I51" s="11">
         <v>2</v>
@@ -14196,7 +14189,7 @@
         <v>229</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I52" s="11">
         <v>3</v>
@@ -14263,13 +14256,13 @@
         <v>20</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G53" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I53" s="11">
         <v>6</v>
@@ -14340,7 +14333,7 @@
         <v>229</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I54" s="11">
         <v>1</v>
@@ -14421,7 +14414,7 @@
         <v>229</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I55" s="11">
         <v>3</v>
@@ -14496,7 +14489,7 @@
         <v>229</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I56" s="11">
         <v>1</v>
@@ -14573,7 +14566,7 @@
         <v>229</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I57" s="11">
         <v>1</v>
@@ -14652,7 +14645,7 @@
         <v>229</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I58" s="11">
         <v>1</v>
@@ -14731,7 +14724,7 @@
         <v>229</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I59" s="11">
         <v>4</v>
@@ -14802,7 +14795,7 @@
         <v>229</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I60" s="11">
         <v>4</v>
@@ -14867,13 +14860,13 @@
         <v>10</v>
       </c>
       <c r="F61" s="37" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G61" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I61" s="11">
         <v>1</v>
@@ -14960,7 +14953,7 @@
         <v>229</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I62" s="11">
         <v>6</v>
@@ -15031,7 +15024,7 @@
         <v>229</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I63" s="11">
         <v>1</v>
@@ -15104,7 +15097,7 @@
         <v>229</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I64" s="11">
         <v>9</v>
@@ -15169,13 +15162,13 @@
         <v>10</v>
       </c>
       <c r="F65" s="37" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="G65" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I65" s="11">
         <v>1</v>
@@ -15262,7 +15255,7 @@
         <v>229</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I66" s="11">
         <v>6</v>
@@ -15333,7 +15326,7 @@
         <v>229</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I67" s="11">
         <v>1</v>
@@ -15406,7 +15399,7 @@
         <v>229</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I68" s="11">
         <v>1</v>
@@ -15558,13 +15551,13 @@
         <v>20</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G70" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I70" s="11">
         <v>1</v>
@@ -15637,7 +15630,7 @@
         <v>229</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I71" s="11">
         <v>4</v>
@@ -15702,13 +15695,13 @@
         <v>10</v>
       </c>
       <c r="F72" s="37" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="G72" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I72" s="13">
         <v>1</v>
@@ -15798,7 +15791,7 @@
         <v>10</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G73" s="11" t="s">
         <v>220</v>
@@ -15889,7 +15882,7 @@
         <v>229</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I74" s="11">
         <v>1</v>
@@ -15958,13 +15951,13 @@
         <v>10</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G75" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I75" s="11">
         <v>4</v>
@@ -16029,13 +16022,13 @@
         <v>10</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G76" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I76" s="11">
         <v>4</v>
@@ -16100,13 +16093,13 @@
         <v>10</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G77" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I77" s="11">
         <v>4</v>
@@ -16179,7 +16172,7 @@
         <v>229</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I78" s="11">
         <v>2</v>
@@ -16256,7 +16249,7 @@
         <v>229</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I79" s="11">
         <v>1</v>
@@ -16333,7 +16326,7 @@
         <v>229</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I80" s="11">
         <v>1</v>
@@ -16406,7 +16399,7 @@
         <v>229</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I81" s="11">
         <v>5</v>
@@ -16473,13 +16466,13 @@
         <v>10</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G82" s="11" t="s">
         <v>220</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I82" s="11">
         <v>1</v>
@@ -16566,7 +16559,7 @@
         <v>229</v>
       </c>
       <c r="H83" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I83" s="11">
         <v>1</v>
@@ -16635,13 +16628,13 @@
         <v>10</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G84" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I84" s="11">
         <v>4</v>
@@ -16706,13 +16699,13 @@
         <v>10</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G85" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I85" s="11">
         <v>4</v>
@@ -16783,7 +16776,7 @@
         <v>229</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I86" s="13">
         <v>1</v>
@@ -16874,7 +16867,7 @@
         <v>229</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I87" s="13">
         <v>4</v>
@@ -16947,7 +16940,7 @@
         <v>229</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I88" s="11">
         <v>1</v>
@@ -17028,7 +17021,7 @@
         <v>229</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I89" s="11">
         <v>1</v>
@@ -17103,13 +17096,13 @@
         <v>10</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="G90" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I90" s="11">
         <v>3</v>
@@ -17174,13 +17167,13 @@
         <v>10</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="G91" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H91" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I91" s="11">
         <v>2</v>
@@ -17245,13 +17238,13 @@
         <v>10</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="G92" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I92" s="11">
         <v>4</v>
@@ -17316,13 +17309,13 @@
         <v>10</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="G93" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I93" s="11">
         <v>11</v>
@@ -17393,7 +17386,7 @@
         <v>229</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I94" s="11">
         <v>4</v>
@@ -17462,7 +17455,7 @@
         <v>229</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I95" s="11">
         <v>4</v>
@@ -17527,13 +17520,13 @@
         <v>20</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G96" s="11" t="s">
         <v>220</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="I96" s="11">
         <v>1</v>
@@ -17624,7 +17617,7 @@
         <v>229</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I97" s="11">
         <v>1</v>
@@ -17697,7 +17690,7 @@
         <v>229</v>
       </c>
       <c r="H98" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I98" s="11">
         <v>3</v>
@@ -17772,7 +17765,7 @@
         <v>229</v>
       </c>
       <c r="H99" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I99" s="11">
         <v>6</v>
@@ -17823,7 +17816,7 @@
         <v>108</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C100" s="12" t="s">
         <v>5</v>
@@ -17837,13 +17830,13 @@
         <v>10</v>
       </c>
       <c r="F100" s="12" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="G100" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I100" s="11">
         <v>3</v>
@@ -17894,7 +17887,7 @@
         <v>108</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C101" s="12" t="s">
         <v>121</v>
@@ -17908,13 +17901,13 @@
         <v>10</v>
       </c>
       <c r="F101" s="45" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G101" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I101" s="11">
         <v>6</v>
@@ -17985,7 +17978,7 @@
         <v>229</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I102" s="11">
         <v>6</v>
@@ -18058,7 +18051,7 @@
         <v>229</v>
       </c>
       <c r="H103" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I103" s="11">
         <v>2</v>
@@ -18131,7 +18124,7 @@
         <v>229</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I104" s="11">
         <v>11</v>
@@ -18198,13 +18191,13 @@
         <v>10</v>
       </c>
       <c r="F105" s="12" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G105" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I105" s="11">
         <v>11</v>
@@ -18277,7 +18270,7 @@
         <v>229</v>
       </c>
       <c r="H106" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I106" s="11">
         <v>11</v>
@@ -18350,7 +18343,7 @@
         <v>229</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I107" s="11">
         <v>6</v>
@@ -18421,7 +18414,7 @@
         <v>229</v>
       </c>
       <c r="H108" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I108" s="11">
         <v>2</v>
@@ -18492,7 +18485,7 @@
         <v>229</v>
       </c>
       <c r="H109" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I109" s="11">
         <v>4</v>
@@ -18562,10 +18555,10 @@
         <v>230</v>
       </c>
       <c r="G110" s="11" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H110" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I110" s="11">
         <v>1</v>
@@ -18679,13 +18672,13 @@
         <v>30</v>
       </c>
       <c r="F111" s="12" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G111" s="11" t="s">
         <v>220</v>
       </c>
       <c r="H111" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I111" s="11">
         <v>1</v>
@@ -18756,13 +18749,13 @@
         <v>30</v>
       </c>
       <c r="F112" s="13" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G112" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H112" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I112" s="13">
         <v>1</v>
@@ -18829,13 +18822,13 @@
         <v>30</v>
       </c>
       <c r="F113" s="11" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G113" s="11" t="s">
         <v>220</v>
       </c>
       <c r="H113" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I113" s="11">
         <v>11</v>
@@ -18902,13 +18895,13 @@
         <v>30</v>
       </c>
       <c r="F114" s="11" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G114" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H114" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I114" s="11">
         <v>11</v>
@@ -18981,7 +18974,7 @@
         <v>229</v>
       </c>
       <c r="H115" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I115" s="11">
         <v>6</v>
@@ -19054,7 +19047,7 @@
         <v>229</v>
       </c>
       <c r="H116" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I116" s="11">
         <v>4</v>
@@ -19070,7 +19063,7 @@
       <c r="M116" s="18"/>
       <c r="N116" s="18"/>
       <c r="O116" s="18">
-        <f t="shared" ref="M116:V116" si="2">0.1/10</f>
+        <f t="shared" ref="O116:V116" si="2">0.1/10</f>
         <v>0.01</v>
       </c>
       <c r="P116" s="18">
@@ -19149,7 +19142,7 @@
         <v>229</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I117" s="11">
         <v>4</v>
@@ -19222,7 +19215,7 @@
         <v>229</v>
       </c>
       <c r="H118" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I118" s="11">
         <v>3</v>
@@ -19287,13 +19280,13 @@
         <v>10</v>
       </c>
       <c r="F119" s="11" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="G119" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H119" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I119" s="11">
         <v>3</v>
@@ -19358,13 +19351,13 @@
         <v>10</v>
       </c>
       <c r="F120" s="37" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G120" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H120" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I120" s="11">
         <v>2</v>
@@ -19437,7 +19430,7 @@
         <v>229</v>
       </c>
       <c r="H121" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I121" s="11">
         <v>1</v>
@@ -19524,7 +19517,7 @@
         <v>229</v>
       </c>
       <c r="H122" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I122" s="11">
         <v>6</v>
@@ -19591,13 +19584,13 @@
         <v>10</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="G123" s="11" t="s">
         <v>220</v>
       </c>
       <c r="H123" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I123" s="11">
         <v>1</v>
@@ -19674,13 +19667,13 @@
         <v>10</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G124" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H124" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I124" s="11">
         <v>1</v>
@@ -19747,13 +19740,13 @@
         <v>10</v>
       </c>
       <c r="F125" s="11" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G125" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H125" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I125" s="11">
         <v>4</v>
@@ -19826,7 +19819,7 @@
         <v>229</v>
       </c>
       <c r="H126" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I126" s="11">
         <v>4</v>
@@ -19891,13 +19884,13 @@
         <v>10</v>
       </c>
       <c r="F127" s="37" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="G127" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H127" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I127" s="11">
         <v>1</v>
@@ -19988,7 +19981,7 @@
         <v>229</v>
       </c>
       <c r="H128" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I128" s="11">
         <v>2</v>
@@ -20065,7 +20058,7 @@
         <v>229</v>
       </c>
       <c r="H129" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I129" s="11">
         <v>3</v>
@@ -20136,7 +20129,7 @@
         <v>229</v>
       </c>
       <c r="H130" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I130" s="11">
         <v>4</v>
@@ -20207,7 +20200,7 @@
         <v>229</v>
       </c>
       <c r="H131" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I131" s="11">
         <v>1</v>
@@ -20298,7 +20291,7 @@
         <v>229</v>
       </c>
       <c r="H132" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I132" s="11">
         <v>3</v>
@@ -20363,13 +20356,13 @@
         <v>10</v>
       </c>
       <c r="F133" s="12" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G133" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H133" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I133" s="11">
         <v>2</v>
@@ -20440,7 +20433,7 @@
         <v>229</v>
       </c>
       <c r="H134" s="11" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I134" s="11">
         <v>1</v>
@@ -20521,7 +20514,7 @@
         <v>229</v>
       </c>
       <c r="H135" s="11" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I135" s="11">
         <v>1</v>
@@ -20602,7 +20595,7 @@
         <v>229</v>
       </c>
       <c r="H136" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I136" s="11">
         <v>3</v>
@@ -20673,7 +20666,7 @@
         <v>229</v>
       </c>
       <c r="H137" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I137" s="11">
         <v>3</v>
@@ -20744,7 +20737,7 @@
         <v>229</v>
       </c>
       <c r="H138" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I138" s="11">
         <v>1</v>
@@ -20817,7 +20810,7 @@
         <v>229</v>
       </c>
       <c r="H139" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I139" s="11">
         <v>1</v>
@@ -20921,7 +20914,7 @@
         <v>229</v>
       </c>
       <c r="H140" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I140" s="11">
         <v>4</v>
@@ -20996,7 +20989,7 @@
         <v>229</v>
       </c>
       <c r="H141" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I141" s="11">
         <v>1</v>
@@ -21075,7 +21068,7 @@
         <v>229</v>
       </c>
       <c r="H142" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I142" s="11">
         <v>1</v>
@@ -21148,13 +21141,13 @@
         <v>10</v>
       </c>
       <c r="F143" s="12" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="G143" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H143" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I143" s="11">
         <v>3</v>
@@ -21225,7 +21218,7 @@
         <v>229</v>
       </c>
       <c r="H144" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I144" s="11">
         <v>3</v>
@@ -21298,7 +21291,7 @@
         <v>229</v>
       </c>
       <c r="H145" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I145" s="11">
         <v>3</v>
@@ -21365,22 +21358,22 @@
         <v>10</v>
       </c>
       <c r="F146" s="12" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G146" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H146" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I146" s="11">
         <v>3</v>
       </c>
-      <c r="J146" s="48">
+      <c r="J146" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
         <v>12</v>
       </c>
-      <c r="K146" s="47"/>
+      <c r="K146" s="11"/>
       <c r="L146" s="18"/>
       <c r="M146" s="18"/>
       <c r="N146" s="18"/>
@@ -21408,11 +21401,11 @@
       <c r="AH146" s="20"/>
       <c r="AI146" s="20"/>
       <c r="AJ146" s="20"/>
-      <c r="AK146" s="49">
+      <c r="AK146" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
         <v>0.3</v>
       </c>
-      <c r="AL146" s="49">
+      <c r="AL146" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>12</v>
       </c>
@@ -21436,13 +21429,13 @@
         <v>10</v>
       </c>
       <c r="F147" s="12" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="G147" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H147" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I147" s="11">
         <v>3</v>
@@ -21513,7 +21506,7 @@
         <v>229</v>
       </c>
       <c r="H148" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I148" s="11">
         <v>3</v>
@@ -21584,7 +21577,7 @@
         <v>229</v>
       </c>
       <c r="H149" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I149" s="11">
         <v>3</v>
@@ -21652,10 +21645,10 @@
         <v>231</v>
       </c>
       <c r="G150" s="11" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H150" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I150" s="11">
         <v>1</v>
@@ -21769,13 +21762,13 @@
         <v>60</v>
       </c>
       <c r="F151" s="11" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G151" s="11" t="s">
         <v>220</v>
       </c>
       <c r="H151" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I151" s="11">
         <v>1</v>
@@ -21846,13 +21839,13 @@
         <v>60</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G152" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H152" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I152" s="11">
         <v>1</v>
@@ -21919,13 +21912,13 @@
         <v>60</v>
       </c>
       <c r="F153" s="11" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="G153" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H153" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I153" s="11">
         <v>1</v>
@@ -21992,13 +21985,13 @@
         <v>60</v>
       </c>
       <c r="F154" s="11" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="G154" s="11" t="s">
         <v>220</v>
       </c>
       <c r="H154" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I154" s="11">
         <v>11</v>
@@ -22071,7 +22064,7 @@
         <v>229</v>
       </c>
       <c r="H155" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I155" s="11">
         <v>11</v>
@@ -22138,13 +22131,13 @@
         <v>60</v>
       </c>
       <c r="F156" s="11" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="G156" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H156" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I156" s="11">
         <v>1</v>
@@ -22200,7 +22193,7 @@
         <v>23</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D157" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -22211,13 +22204,13 @@
         <v>60</v>
       </c>
       <c r="F157" s="37" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G157" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H157" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I157" s="11">
         <v>1</v>
@@ -22290,7 +22283,7 @@
         <v>229</v>
       </c>
       <c r="H158" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I158" s="11">
         <v>2</v>
@@ -22361,7 +22354,7 @@
         <v>229</v>
       </c>
       <c r="H159" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I159" s="11">
         <v>4</v>
@@ -22432,7 +22425,7 @@
         <v>229</v>
       </c>
       <c r="H160" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I160" s="11">
         <v>3</v>
@@ -22503,7 +22496,7 @@
         <v>229</v>
       </c>
       <c r="H161" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I161" s="11">
         <v>5</v>
@@ -22570,13 +22563,13 @@
         <v>10</v>
       </c>
       <c r="F162" s="11" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G162" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H162" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I162" s="11">
         <v>1</v>
@@ -22659,13 +22652,13 @@
         <v>10</v>
       </c>
       <c r="F163" s="11" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G163" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H163" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I163" s="11">
         <v>1</v>
@@ -22748,13 +22741,13 @@
         <v>10</v>
       </c>
       <c r="F164" s="11" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="G164" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H164" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I164" s="11">
         <v>11</v>
@@ -22819,13 +22812,13 @@
         <v>20</v>
       </c>
       <c r="F165" s="11" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="G165" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H165" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I165" s="11">
         <v>2</v>
@@ -22890,13 +22883,13 @@
         <v>20</v>
       </c>
       <c r="F166" s="11" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G166" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H166" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I166" s="11">
         <v>2</v>
@@ -22961,13 +22954,13 @@
         <v>20</v>
       </c>
       <c r="F167" s="11" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="G167" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H167" s="11" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="I167" s="11">
         <v>3</v>
@@ -23038,7 +23031,7 @@
         <v>229</v>
       </c>
       <c r="H168" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I168" s="11">
         <v>6</v>
@@ -23105,13 +23098,13 @@
         <v>20</v>
       </c>
       <c r="F169" s="11" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G169" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H169" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I169" s="11">
         <v>6</v>
@@ -23167,7 +23160,7 @@
         <v>184</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D170" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -23178,13 +23171,13 @@
         <v>20</v>
       </c>
       <c r="F170" s="11" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G170" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H170" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I170" s="11">
         <v>1</v>
@@ -23251,13 +23244,13 @@
         <v>20</v>
       </c>
       <c r="F171" s="11" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G171" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H171" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I171" s="11">
         <v>3</v>
@@ -23322,13 +23315,13 @@
         <v>20</v>
       </c>
       <c r="F172" s="11" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G172" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H172" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I172" s="11">
         <v>7</v>
@@ -23395,13 +23388,13 @@
         <v>20</v>
       </c>
       <c r="F173" s="11" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="G173" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H173" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I173" s="11">
         <v>6</v>
@@ -23466,13 +23459,13 @@
         <v>20</v>
       </c>
       <c r="F174" s="11" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G174" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H174" s="11" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="I174" s="11">
         <v>6</v>
@@ -23520,10 +23513,10 @@
     </row>
     <row r="175" spans="1:38">
       <c r="A175" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B175" s="28" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C175" s="11" t="s">
         <v>5</v>
@@ -23537,13 +23530,13 @@
         <v>10</v>
       </c>
       <c r="F175" s="11" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="G175" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H175" s="11" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I175" s="11">
         <v>4</v>
@@ -23591,10 +23584,10 @@
     </row>
     <row r="176" spans="1:38">
       <c r="A176" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B176" s="28" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C176" s="11" t="s">
         <v>5</v>
@@ -23608,13 +23601,13 @@
         <v>10</v>
       </c>
       <c r="F176" s="11" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G176" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H176" s="11" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I176" s="11">
         <v>6</v>
@@ -23662,10 +23655,10 @@
     </row>
     <row r="177" spans="1:38">
       <c r="A177" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B177" s="28" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C177" s="11" t="s">
         <v>5</v>
@@ -23679,13 +23672,13 @@
         <v>10</v>
       </c>
       <c r="F177" s="11" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G177" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H177" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I177" s="11">
         <v>3</v>
@@ -23733,10 +23726,10 @@
     </row>
     <row r="178" spans="1:38">
       <c r="A178" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B178" s="28" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C178" s="11" t="s">
         <v>5</v>
@@ -23750,13 +23743,13 @@
         <v>10</v>
       </c>
       <c r="F178" s="11" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G178" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H178" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I178" s="11">
         <v>8</v>
@@ -23804,10 +23797,10 @@
     </row>
     <row r="179" spans="1:38">
       <c r="A179" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B179" s="28" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C179" s="11" t="s">
         <v>5</v>
@@ -23821,13 +23814,13 @@
         <v>10</v>
       </c>
       <c r="F179" s="11" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G179" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H179" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I179" s="11">
         <v>3</v>
@@ -23875,10 +23868,10 @@
     </row>
     <row r="180" spans="1:38">
       <c r="A180" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B180" s="28" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C180" s="11" t="s">
         <v>5</v>
@@ -23892,13 +23885,13 @@
         <v>20</v>
       </c>
       <c r="F180" s="11" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="G180" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H180" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I180" s="11">
         <v>4</v>
@@ -23948,10 +23941,10 @@
     </row>
     <row r="181" spans="1:38">
       <c r="A181" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B181" s="28" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C181" s="11" t="s">
         <v>4</v>
@@ -23965,13 +23958,13 @@
         <v>20</v>
       </c>
       <c r="F181" s="11" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G181" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H181" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="I181" s="11">
         <v>1</v>
@@ -24021,10 +24014,10 @@
     </row>
     <row r="182" spans="1:38">
       <c r="A182" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B182" s="28" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C182" s="11" t="s">
         <v>5</v>
@@ -24038,13 +24031,13 @@
         <v>20</v>
       </c>
       <c r="F182" s="11" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="G182" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H182" s="11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="I182" s="11">
         <v>2</v>
@@ -30318,16 +30311,16 @@
         <v>197</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="R1" s="5" t="s">
         <v>241</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="T1" s="5" t="s">
         <v>212</v>
@@ -32236,10 +32229,10 @@
         <v>108</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D39" s="28" t="s">
         <v>180</v>
@@ -34093,10 +34086,10 @@
     </row>
     <row r="74" spans="1:23">
       <c r="A74" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>108</v>
@@ -34105,7 +34098,7 @@
         <v>178</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F74" s="4">
         <v>7</v>
@@ -35250,10 +35243,10 @@
     </row>
     <row r="96" spans="1:23">
       <c r="A96" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C96" s="3"/>
       <c r="D96" s="28" t="s">
@@ -35295,10 +35288,10 @@
     </row>
     <row r="97" spans="1:23">
       <c r="A97" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="28" t="s">
@@ -35340,10 +35333,10 @@
     </row>
     <row r="98" spans="1:23">
       <c r="A98" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C98" s="3"/>
       <c r="D98" s="28" t="s">
@@ -35385,10 +35378,10 @@
     </row>
     <row r="99" spans="1:23">
       <c r="A99" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C99" s="3"/>
       <c r="D99" s="28" t="s">
@@ -35430,10 +35423,10 @@
     </row>
     <row r="100" spans="1:23">
       <c r="A100" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="28" t="s">
@@ -36125,7 +36118,7 @@
       </c>
       <c r="C18">
         <f>SUMIF(Table1[Module Code],Sheet2!A18,Table1[Total Hours])</f>
-        <v>30</v>
+        <v>31.6</v>
       </c>
       <c r="D18">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A18,Table14[Module Code],0))</f>
@@ -36133,11 +36126,11 @@
       </c>
       <c r="E18">
         <f t="shared" si="0"/>
-        <v>52</v>
+        <v>53.6</v>
       </c>
       <c r="F18">
         <f t="shared" si="1"/>
-        <v>5.2</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="19" spans="1:6">

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1667" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44791E17-0171-4A8F-AC83-9BF5FE1675C4}"/>
+  <xr:revisionPtr revIDLastSave="1694" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CE02383-8009-4323-9646-F3E5D1C75C09}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Assessments" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="2" r:id="rId5"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -9162,7 +9161,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B70" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="34">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -10388,7 +10387,7 @@
       </c>
       <c r="J4" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>8</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="18"/>
@@ -10399,9 +10398,11 @@
       <c r="O4" s="19"/>
       <c r="P4" s="18"/>
       <c r="Q4" s="18">
+        <v>-0.1</v>
+      </c>
+      <c r="R4" s="18">
         <v>0.1</v>
       </c>
-      <c r="R4" s="18"/>
       <c r="S4" s="19"/>
       <c r="T4" s="18"/>
       <c r="U4" s="18"/>
@@ -10426,7 +10427,7 @@
       </c>
       <c r="AL4" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>16</v>
+        <v>5.333333333333333</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -10534,47 +10535,36 @@
       </c>
       <c r="J6" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>1.7777777777777779</v>
+        <v>1.9999999999999998</v>
       </c>
       <c r="K6" s="11">
         <v>0.5</v>
       </c>
       <c r="L6" s="18"/>
-      <c r="M6" s="18">
-        <f t="shared" ref="M6:U6" si="0">0.2/9</f>
-        <v>2.2222222222222223E-2</v>
-      </c>
+      <c r="M6" s="18"/>
       <c r="N6" s="18">
-        <f t="shared" si="0"/>
-        <v>2.2222222222222223E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="O6" s="18">
-        <f t="shared" si="0"/>
-        <v>2.2222222222222223E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="P6" s="18">
-        <f t="shared" si="0"/>
-        <v>2.2222222222222223E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="Q6" s="18">
-        <f t="shared" si="0"/>
-        <v>2.2222222222222223E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="R6" s="18">
-        <f t="shared" si="0"/>
-        <v>2.2222222222222223E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="S6" s="18">
-        <f t="shared" si="0"/>
-        <v>2.2222222222222223E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="T6" s="18">
-        <f t="shared" si="0"/>
-        <v>2.2222222222222223E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="U6" s="18">
-        <f t="shared" si="0"/>
-        <v>2.2222222222222223E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="V6" s="18"/>
       <c r="W6" s="19"/>
@@ -10593,11 +10583,11 @@
       <c r="AJ6" s="20"/>
       <c r="AK6" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="AL6" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>4.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -10625,36 +10615,37 @@
         <v>229</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>300</v>
+        <v>346</v>
       </c>
       <c r="I7" s="11">
         <v>2</v>
       </c>
       <c r="J7" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>2.6666666666666665</v>
+        <v>1.6</v>
       </c>
       <c r="K7" s="11">
         <v>3</v>
       </c>
       <c r="L7" s="18"/>
-      <c r="M7" s="18"/>
+      <c r="M7" s="18">
+        <v>0.04</v>
+      </c>
       <c r="N7" s="19"/>
       <c r="O7" s="18">
-        <f>0.2/3</f>
-        <v>6.6666666666666666E-2</v>
+        <v>0.04</v>
       </c>
       <c r="P7" s="18"/>
-      <c r="Q7" s="18"/>
+      <c r="Q7" s="18">
+        <v>0.04</v>
+      </c>
       <c r="R7" s="19"/>
       <c r="S7" s="18">
-        <f>0.2/3</f>
-        <v>6.6666666666666666E-2</v>
+        <v>0.04</v>
       </c>
       <c r="T7" s="18"/>
       <c r="U7" s="18">
-        <f>0.2/3</f>
-        <v>6.6666666666666666E-2</v>
+        <v>0.04</v>
       </c>
       <c r="V7" s="18"/>
       <c r="W7" s="19"/>
@@ -10677,7 +10668,7 @@
       </c>
       <c r="AL7" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -15717,35 +15708,35 @@
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="N72" s="18">
-        <f t="shared" ref="N72:U72" si="1">0.3/9</f>
+        <f t="shared" ref="N72:U72" si="0">0.3/9</f>
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="O72" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="P72" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="Q72" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="R72" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="S72" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="T72" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="U72" s="18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="V72" s="18"/>
@@ -19054,7 +19045,7 @@
       </c>
       <c r="J116" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0.4</v>
+        <v>0.49999999999999994</v>
       </c>
       <c r="K116" s="11">
         <v>0.5</v>
@@ -19063,36 +19054,28 @@
       <c r="M116" s="18"/>
       <c r="N116" s="18"/>
       <c r="O116" s="18">
-        <f t="shared" ref="O116:V116" si="2">0.1/10</f>
-        <v>0.01</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="P116" s="18">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="Q116" s="18">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="R116" s="18">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="S116" s="18">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="T116" s="18">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="U116" s="18">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="V116" s="18">
-        <f t="shared" si="2"/>
-        <v>0.01</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="W116" s="19"/>
       <c r="X116" s="20"/>
@@ -19110,7 +19093,7 @@
       <c r="AJ116" s="20"/>
       <c r="AK116" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.08</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="AL116" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -20817,7 +20800,7 @@
       </c>
       <c r="J139" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0.3636363636363637</v>
+        <v>0.32727272727272722</v>
       </c>
       <c r="K139" s="11">
         <v>0.5</v>
@@ -20835,58 +20818,47 @@
       <c r="V139" s="18"/>
       <c r="W139" s="19"/>
       <c r="X139" s="20">
-        <f>0.1/11</f>
-        <v>9.0909090909090922E-3</v>
+        <v>-0.01</v>
       </c>
       <c r="Y139" s="20">
-        <f t="shared" ref="Y139:AH139" si="3">0.1/11</f>
-        <v>9.0909090909090922E-3</v>
+        <v>0.01</v>
       </c>
       <c r="Z139" s="20">
-        <f t="shared" si="3"/>
-        <v>9.0909090909090922E-3</v>
+        <v>0.01</v>
       </c>
       <c r="AA139" s="20">
-        <f t="shared" si="3"/>
-        <v>9.0909090909090922E-3</v>
+        <v>0.01</v>
       </c>
       <c r="AB139" s="20">
-        <f t="shared" si="3"/>
-        <v>9.0909090909090922E-3</v>
+        <v>0.01</v>
       </c>
       <c r="AC139" s="20">
-        <f t="shared" si="3"/>
-        <v>9.0909090909090922E-3</v>
+        <v>0.01</v>
       </c>
       <c r="AD139" s="20">
-        <f t="shared" si="3"/>
-        <v>9.0909090909090922E-3</v>
+        <v>0.01</v>
       </c>
       <c r="AE139" s="20">
-        <f t="shared" si="3"/>
-        <v>9.0909090909090922E-3</v>
+        <v>0.01</v>
       </c>
       <c r="AF139" s="20">
-        <f t="shared" si="3"/>
-        <v>9.0909090909090922E-3</v>
+        <v>0.01</v>
       </c>
       <c r="AG139" s="20">
-        <f t="shared" si="3"/>
-        <v>9.0909090909090922E-3</v>
+        <v>0.01</v>
       </c>
       <c r="AH139" s="20">
-        <f t="shared" si="3"/>
-        <v>9.0909090909090922E-3</v>
+        <v>0.01</v>
       </c>
       <c r="AI139" s="20"/>
       <c r="AJ139" s="20"/>
       <c r="AK139" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.10000000000000002</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="AL139" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:38">
@@ -32654,7 +32626,7 @@
       </c>
       <c r="W46">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>28.000000000000004</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:23">
@@ -34191,7 +34163,7 @@
       </c>
       <c r="W75">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>28.000000000000004</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76" spans="1:23">

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1694" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1CE02383-8009-4323-9646-F3E5D1C75C09}"/>
+  <xr:revisionPtr revIDLastSave="1695" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71427935-BE0E-4554-AAF3-C655B1382B39}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Assessments" sheetId="1" r:id="rId1"/>
@@ -10615,7 +10615,7 @@
         <v>229</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="I7" s="11">
         <v>2</v>

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1695" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71427935-BE0E-4554-AAF3-C655B1382B39}"/>
+  <xr:revisionPtr revIDLastSave="1717" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2302D11-700C-4396-8088-4D903DED3669}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -9161,7 +9161,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B70" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="34">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -10241,24 +10241,24 @@
         <v>0.5</v>
       </c>
       <c r="L2" s="18"/>
-      <c r="M2" s="18"/>
-      <c r="N2" s="18">
+      <c r="M2" s="18">
         <v>0.05</v>
       </c>
-      <c r="O2" s="19"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="19">
+        <v>0.05</v>
+      </c>
       <c r="P2" s="18"/>
-      <c r="Q2" s="18">
+      <c r="Q2" s="18"/>
+      <c r="R2" s="18">
         <v>0.05</v>
       </c>
-      <c r="R2" s="18"/>
-      <c r="S2" s="19">
+      <c r="S2" s="19"/>
+      <c r="T2" s="18"/>
+      <c r="U2" s="18"/>
+      <c r="V2" s="18">
         <v>0.05</v>
       </c>
-      <c r="T2" s="18"/>
-      <c r="U2" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="V2" s="18"/>
       <c r="W2" s="19"/>
       <c r="X2" s="20"/>
       <c r="Y2" s="20"/>
@@ -10387,7 +10387,7 @@
       </c>
       <c r="J4" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>2.6666666666666665</v>
+        <v>8</v>
       </c>
       <c r="K4" s="11"/>
       <c r="L4" s="18"/>
@@ -10398,11 +10398,9 @@
       <c r="O4" s="19"/>
       <c r="P4" s="18"/>
       <c r="Q4" s="18">
-        <v>-0.1</v>
-      </c>
-      <c r="R4" s="18">
         <v>0.1</v>
       </c>
+      <c r="R4" s="18"/>
       <c r="S4" s="19"/>
       <c r="T4" s="18"/>
       <c r="U4" s="18"/>
@@ -10427,7 +10425,7 @@
       </c>
       <c r="AL4" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>5.333333333333333</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -10615,7 +10613,7 @@
         <v>229</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>354</v>
+        <v>300</v>
       </c>
       <c r="I7" s="11">
         <v>2</v>
@@ -11439,7 +11437,7 @@
         <v>229</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="I17" s="11">
         <v>1</v>
@@ -18780,10 +18778,10 @@
       <c r="AE112" s="20"/>
       <c r="AF112" s="20"/>
       <c r="AG112" s="20"/>
-      <c r="AH112" s="20">
+      <c r="AH112" s="20"/>
+      <c r="AI112" s="20">
         <v>0.4</v>
       </c>
-      <c r="AI112" s="20"/>
       <c r="AJ112" s="20"/>
       <c r="AK112" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
@@ -18926,10 +18924,10 @@
       <c r="AE114" s="20"/>
       <c r="AF114" s="20"/>
       <c r="AG114" s="20"/>
-      <c r="AH114" s="20">
+      <c r="AH114" s="20"/>
+      <c r="AI114" s="20">
         <v>0.4</v>
       </c>
-      <c r="AI114" s="20"/>
       <c r="AJ114" s="20"/>
       <c r="AK114" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1717" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2302D11-700C-4396-8088-4D903DED3669}"/>
+  <xr:revisionPtr revIDLastSave="1719" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DF1D3AC-FAAA-4E2E-9CD9-F9F5868C7E94}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
@@ -10231,7 +10231,7 @@
         <v>346</v>
       </c>
       <c r="I2" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
@@ -10697,7 +10697,7 @@
         <v>347</v>
       </c>
       <c r="I8" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1719" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DF1D3AC-FAAA-4E2E-9CD9-F9F5868C7E94}"/>
+  <xr:revisionPtr revIDLastSave="1721" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1DA1401-9B91-4C37-8EF1-6A05E14248CB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
@@ -19043,14 +19043,18 @@
       </c>
       <c r="J116" s="11">
         <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0.49999999999999994</v>
+        <v>0.29599999999999999</v>
       </c>
       <c r="K116" s="11">
         <v>0.5</v>
       </c>
       <c r="L116" s="18"/>
-      <c r="M116" s="18"/>
-      <c r="N116" s="18"/>
+      <c r="M116" s="18">
+        <v>-1.2999999999999999E-2</v>
+      </c>
+      <c r="N116" s="18">
+        <v>-1.2999999999999999E-2</v>
+      </c>
       <c r="O116" s="18">
         <v>1.2500000000000001E-2</v>
       </c>

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1721" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1DA1401-9B91-4C37-8EF1-6A05E14248CB}"/>
+  <xr:revisionPtr revIDLastSave="1725" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC466023-8838-48DA-AF14-A3A1A7521268}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
@@ -1462,6 +1462,31 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="113">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3457,31 +3482,6 @@
         <name val="Calibri (Body)"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -9625,39 +9625,39 @@
     <tableColumn id="36" xr3:uid="{A7BF30F6-C808-4B8F-B3FF-9FAF20E2145A}" name="Summative" dataDxfId="101"/>
     <tableColumn id="37" xr3:uid="{68E504F9-116C-43AB-BCC6-3BB48B0860D2}" name="Day of Week" dataDxfId="100"/>
     <tableColumn id="16" xr3:uid="{E6637FEB-7F23-45F0-99D2-96D20DD2DAEF}" name="Duration" dataDxfId="99"/>
-    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="98">
-      <calculatedColumnFormula>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</calculatedColumnFormula>
+    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="0">
+      <calculatedColumnFormula>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="97"/>
-    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="96"/>
-    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="95"/>
-    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="94"/>
-    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="93"/>
-    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="92"/>
-    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="91"/>
-    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="90"/>
-    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="89"/>
-    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="88"/>
-    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="87"/>
-    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="86"/>
-    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="85"/>
-    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="84"/>
-    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="83"/>
-    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="82"/>
-    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="81"/>
-    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="80"/>
-    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="79"/>
-    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="78"/>
-    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="77"/>
-    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="76"/>
-    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="75"/>
-    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="74"/>
-    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="73"/>
-    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="72"/>
-    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="71">
+    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="96"/>
+    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="95"/>
+    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="94"/>
+    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="93"/>
+    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="92"/>
+    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="91"/>
+    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="90"/>
+    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="89"/>
+    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="88"/>
+    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="87"/>
+    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="86"/>
+    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="85"/>
+    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="84"/>
+    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="83"/>
+    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="82"/>
+    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="81"/>
+    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="80"/>
+    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="79"/>
+    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="78"/>
+    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="77"/>
+    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="76"/>
+    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="75"/>
+    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="74"/>
+    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="73"/>
+    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="72">
       <calculatedColumnFormula>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="70">
+    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="71">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9666,49 +9666,49 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68" tableBorderDxfId="66" totalsRowBorderDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69" tableBorderDxfId="67" totalsRowBorderDxfId="66">
   <autoFilter ref="A1:AE64" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD64">
     <sortCondition ref="A1:A132"/>
   </sortState>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="62"/>
-    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="61">
+    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="65"/>
+    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="63"/>
+    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="62">
       <calculatedColumnFormula>INDEX(Table2[Credits],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="60">
+    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="61">
       <calculatedColumnFormula>INDEX(Table2[Semester],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="59">
+    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="60">
       <calculatedColumnFormula>INDEX(Table2[Contact Time],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="56"/>
-    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="55"/>
-    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="54"/>
-    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="53"/>
-    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="52"/>
-    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="51"/>
-    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="50"/>
-    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="49"/>
-    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="48"/>
-    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="47"/>
-    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="46"/>
-    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="45"/>
-    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="44"/>
-    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="43"/>
-    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="42"/>
-    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="41"/>
-    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="40"/>
-    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="39"/>
-    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="38"/>
-    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="37"/>
-    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="36"/>
-    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="35"/>
-    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="34">
+    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="57"/>
+    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="55"/>
+    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="54"/>
+    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="52"/>
+    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="51"/>
+    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="50"/>
+    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="49"/>
+    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="48"/>
+    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="47"/>
+    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="46"/>
+    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="45"/>
+    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="44"/>
+    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="43"/>
+    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="42"/>
+    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="41"/>
+    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="40"/>
+    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="39"/>
+    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="38"/>
+    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="37"/>
+    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="36"/>
+    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="35">
       <calculatedColumnFormula>SUM(Table14[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9717,37 +9717,37 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}" name="Table2" displayName="Table2" ref="A1:W100" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}" name="Table2" displayName="Table2" ref="A1:W100" totalsRowShown="0" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33">
   <autoFilter ref="A1:W100" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B62">
     <sortCondition ref="A1:A62"/>
   </sortState>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{A36A2B86-0F30-4188-9ECD-AE5BC71A59F4}" name="Module Code" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{D3F20037-EF35-4207-A530-484E1EB45719}" name="Module Title" dataDxfId="29"/>
-    <tableColumn id="9" xr3:uid="{40C22022-10B9-411F-9B76-B89140ABFFB2}" name="Alternative Module Code" dataDxfId="28"/>
-    <tableColumn id="13" xr3:uid="{CB12E405-1802-457C-AF17-F1B9CB3BBF13}" name="Source" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{EA737976-1AA7-49B6-8752-A388621554F4}" name="Semester" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{16DFC84F-5858-467D-B447-49992D721E4B}" name="Level" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{A17BC4BA-A3CB-442D-9BDC-D3B41B98B389}" name="Credits" dataDxfId="24"/>
-    <tableColumn id="19" xr3:uid="{98846C13-E462-4CFF-858E-AF75931B6712}" name="AllUG" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{7E25B4F4-1A7D-48D9-AAA2-AF5C97240797}" name="Physics" dataDxfId="22"/>
+    <tableColumn id="1" xr3:uid="{A36A2B86-0F30-4188-9ECD-AE5BC71A59F4}" name="Module Code" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{D3F20037-EF35-4207-A530-484E1EB45719}" name="Module Title" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{40C22022-10B9-411F-9B76-B89140ABFFB2}" name="Alternative Module Code" dataDxfId="29"/>
+    <tableColumn id="13" xr3:uid="{CB12E405-1802-457C-AF17-F1B9CB3BBF13}" name="Source" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{EA737976-1AA7-49B6-8752-A388621554F4}" name="Semester" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{16DFC84F-5858-467D-B447-49992D721E4B}" name="Level" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{A17BC4BA-A3CB-442D-9BDC-D3B41B98B389}" name="Credits" dataDxfId="25"/>
+    <tableColumn id="19" xr3:uid="{98846C13-E462-4CFF-858E-AF75931B6712}" name="AllUG" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{7E25B4F4-1A7D-48D9-AAA2-AF5C97240797}" name="Physics" dataDxfId="23"/>
     <tableColumn id="17" xr3:uid="{AA3AE96F-2651-49D7-89AD-BA94806438AE}" name="PhysAstro"/>
-    <tableColumn id="4" xr3:uid="{9C7DD469-E550-411F-8467-246A1543FB38}" name="Astro" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{3C5D3AEB-487E-4678-A42F-BE4BA4D0E9AA}" name="MedPhys" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{9C7DD469-E550-411F-8467-246A1543FB38}" name="Astro" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{3C5D3AEB-487E-4678-A42F-BE4BA4D0E9AA}" name="MedPhys" dataDxfId="21"/>
     <tableColumn id="20" xr3:uid="{C3673B06-C0A2-44F6-8978-F392282CECF8}" name="AllPG"/>
-    <tableColumn id="14" xr3:uid="{AE552873-9B31-41A6-B73C-D052477CA74C}" name="MScPhysics" dataDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{8F51CE76-3A29-487A-A13C-FB63C79CF3E6}" name="MScAstro" dataDxfId="18"/>
-    <tableColumn id="21" xr3:uid="{FC74E264-78AB-4682-A1B8-D8964ED1C3F3}" name="MScDataPhys" dataDxfId="17"/>
-    <tableColumn id="22" xr3:uid="{2D5776F7-D7F7-4D20-A7CB-DB57997AD074}" name="MScDataAstro" dataDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{AE552873-9B31-41A6-B73C-D052477CA74C}" name="MScPhysics" dataDxfId="20"/>
+    <tableColumn id="15" xr3:uid="{8F51CE76-3A29-487A-A13C-FB63C79CF3E6}" name="MScAstro" dataDxfId="19"/>
+    <tableColumn id="21" xr3:uid="{FC74E264-78AB-4682-A1B8-D8964ED1C3F3}" name="MScDataPhys" dataDxfId="18"/>
+    <tableColumn id="22" xr3:uid="{2D5776F7-D7F7-4D20-A7CB-DB57997AD074}" name="MScDataAstro" dataDxfId="17"/>
     <tableColumn id="18" xr3:uid="{10668F71-1EDF-482E-86A5-46E1F3C15120}" name="MScCSPhysics"/>
     <tableColumn id="23" xr3:uid="{E837FCBC-49C7-45CE-AFAA-4F01143EF2A8}" name="CDTCSPhysics"/>
     <tableColumn id="16" xr3:uid="{DB790F5F-BEF0-41CE-A68A-1AA9DF83D66B}" name="Contact Time"/>
-    <tableColumn id="10" xr3:uid="{60774AFA-B365-4EB5-AAFF-6235868F8C97}" name="Exam Weight (%)" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{537B7C75-E9C0-42F2-9F3C-6E960AB2D257}" name="CA weight" dataDxfId="14">
+    <tableColumn id="10" xr3:uid="{60774AFA-B365-4EB5-AAFF-6235868F8C97}" name="Exam Weight (%)" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{537B7C75-E9C0-42F2-9F3C-6E960AB2D257}" name="CA weight" dataDxfId="15">
       <calculatedColumnFormula>100-Table2[[#This Row],[Exam Weight (%)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{75DA2527-5A08-4ECE-B4E4-752A8F8BF059}" name="CA Check" dataDxfId="13">
+    <tableColumn id="11" xr3:uid="{75DA2527-5A08-4ECE-B4E4-752A8F8BF059}" name="CA Check" dataDxfId="14">
       <calculatedColumnFormula>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10234,7 +10234,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K2" s="11">
@@ -10313,7 +10313,7 @@
         <v>4</v>
       </c>
       <c r="J3" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K3" s="11"/>
@@ -10386,7 +10386,7 @@
         <v>3</v>
       </c>
       <c r="J4" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K4" s="11"/>
@@ -10459,7 +10459,7 @@
         <v>1</v>
       </c>
       <c r="J5" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>2</v>
       </c>
       <c r="K5" s="11">
@@ -10532,7 +10532,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>1.9999999999999998</v>
       </c>
       <c r="K6" s="11">
@@ -10619,7 +10619,7 @@
         <v>2</v>
       </c>
       <c r="J7" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>1.6</v>
       </c>
       <c r="K7" s="11">
@@ -10700,7 +10700,7 @@
         <v>2</v>
       </c>
       <c r="J8" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>12</v>
       </c>
       <c r="K8" s="11">
@@ -10773,7 +10773,7 @@
         <v>1</v>
       </c>
       <c r="J9" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4.0000000000000009</v>
       </c>
       <c r="K9" s="11">
@@ -10884,7 +10884,7 @@
         <v>2</v>
       </c>
       <c r="J10" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>7.1999999999999984</v>
       </c>
       <c r="K10" s="11">
@@ -10967,7 +10967,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>7.1999999999999993</v>
       </c>
       <c r="K11" s="11">
@@ -11040,7 +11040,7 @@
         <v>3</v>
       </c>
       <c r="J12" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>14.8</v>
       </c>
       <c r="K12" s="11"/>
@@ -11113,7 +11113,7 @@
         <v>2</v>
       </c>
       <c r="J13" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>2.4000000000000004</v>
       </c>
       <c r="K13" s="11">
@@ -11204,7 +11204,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>1.9999999999999998</v>
       </c>
       <c r="K14" s="11">
@@ -11295,8 +11295,8 @@
         <v>3</v>
       </c>
       <c r="J15" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>8</v>
       </c>
       <c r="K15" s="11">
         <v>5</v>
@@ -11370,7 +11370,7 @@
         <v>2</v>
       </c>
       <c r="J16" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>12</v>
       </c>
       <c r="K16" s="11">
@@ -11443,7 +11443,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>0.8</v>
       </c>
       <c r="K17" s="11">
@@ -11524,7 +11524,7 @@
         <v>4</v>
       </c>
       <c r="J18" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K18" s="11"/>
@@ -11595,7 +11595,7 @@
         <v>4</v>
       </c>
       <c r="J19" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K19" s="11"/>
@@ -11666,8 +11666,8 @@
         <v>2</v>
       </c>
       <c r="J20" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>2.4000000000000004</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>4</v>
       </c>
       <c r="K20" s="11">
         <v>4</v>
@@ -11747,7 +11747,7 @@
         <v>6</v>
       </c>
       <c r="J21" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>2</v>
       </c>
       <c r="K21" s="11"/>
@@ -11818,7 +11818,7 @@
         <v>6</v>
       </c>
       <c r="J22" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>6</v>
       </c>
       <c r="K22" s="11"/>
@@ -11889,8 +11889,8 @@
         <v>1</v>
       </c>
       <c r="J23" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>-0.79999999999999982</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>0</v>
       </c>
       <c r="K23" s="11">
         <v>0.5</v>
@@ -11980,8 +11980,8 @@
         <v>3</v>
       </c>
       <c r="J24" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>-12</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>0</v>
       </c>
       <c r="K24" s="11">
         <v>15</v>
@@ -12055,7 +12055,7 @@
         <v>2</v>
       </c>
       <c r="J25" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>6.4</v>
       </c>
       <c r="K25" s="11">
@@ -12136,7 +12136,7 @@
         <v>1</v>
       </c>
       <c r="J26" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>1.142857142857143</v>
       </c>
       <c r="K26" s="11"/>
@@ -12219,7 +12219,7 @@
         <v>3</v>
       </c>
       <c r="J27" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K27" s="11">
@@ -12292,7 +12292,7 @@
         <v>1</v>
       </c>
       <c r="J28" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>0.39999999999999991</v>
       </c>
       <c r="K28" s="11">
@@ -12383,8 +12383,8 @@
         <v>3</v>
       </c>
       <c r="J29" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>2.6666666666666665</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>8</v>
       </c>
       <c r="K29" s="11">
         <v>15</v>
@@ -12460,7 +12460,7 @@
         <v>1</v>
       </c>
       <c r="J30" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>20</v>
       </c>
       <c r="K30" s="11">
@@ -12533,8 +12533,8 @@
         <v>3</v>
       </c>
       <c r="J31" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>2.6666666666666665</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>8</v>
       </c>
       <c r="K31" s="11">
         <v>6</v>
@@ -12610,7 +12610,7 @@
         <v>1</v>
       </c>
       <c r="J32" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>0.4</v>
       </c>
       <c r="K32" s="11"/>
@@ -12697,8 +12697,8 @@
         <v>2</v>
       </c>
       <c r="J33" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>1.1333333333333333</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>3.2</v>
       </c>
       <c r="K33" s="11">
         <v>2</v>
@@ -12774,8 +12774,8 @@
         <v>3</v>
       </c>
       <c r="J34" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>8</v>
       </c>
       <c r="K34" s="11">
         <v>15</v>
@@ -12849,7 +12849,7 @@
         <v>9</v>
       </c>
       <c r="J35" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>22</v>
       </c>
       <c r="K35" s="11">
@@ -12922,7 +12922,7 @@
         <v>1</v>
       </c>
       <c r="J36" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>2</v>
       </c>
       <c r="K36" s="11">
@@ -13003,7 +13003,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>6</v>
       </c>
       <c r="K37" s="11">
@@ -13076,7 +13076,7 @@
         <v>5</v>
       </c>
       <c r="J38" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K38" s="11"/>
@@ -13147,7 +13147,7 @@
         <v>3</v>
       </c>
       <c r="J39" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>7.2000000000000011</v>
       </c>
       <c r="K39" s="11">
@@ -13224,7 +13224,7 @@
         <v>1</v>
       </c>
       <c r="J40" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K40" s="11">
@@ -13297,7 +13297,7 @@
         <v>3</v>
       </c>
       <c r="J41" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>12</v>
       </c>
       <c r="K41" s="11">
@@ -13370,7 +13370,7 @@
         <v>9</v>
       </c>
       <c r="J42" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>2.4</v>
       </c>
       <c r="K42" s="11"/>
@@ -13441,7 +13441,7 @@
         <v>1</v>
       </c>
       <c r="J43" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4.0000000000000018</v>
       </c>
       <c r="K43" s="11">
@@ -13550,7 +13550,7 @@
         <v>1</v>
       </c>
       <c r="J44" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K44" s="11">
@@ -13623,7 +13623,7 @@
         <v>3</v>
       </c>
       <c r="J45" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8.0000000000000018</v>
       </c>
       <c r="K45" s="11">
@@ -13700,7 +13700,7 @@
         <v>3</v>
       </c>
       <c r="J46" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8.0000000000000018</v>
       </c>
       <c r="K46" s="11">
@@ -13777,7 +13777,7 @@
         <v>11</v>
       </c>
       <c r="J47" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K47" s="11">
@@ -13850,7 +13850,7 @@
         <v>4</v>
       </c>
       <c r="J48" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>24</v>
       </c>
       <c r="K48" s="11">
@@ -13923,7 +13923,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4.0000000000000009</v>
       </c>
       <c r="K49" s="11">
@@ -14034,7 +14034,7 @@
         <v>2</v>
       </c>
       <c r="J50" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K50" s="11">
@@ -14113,7 +14113,7 @@
         <v>2</v>
       </c>
       <c r="J51" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K51" s="11"/>
@@ -14184,7 +14184,7 @@
         <v>3</v>
       </c>
       <c r="J52" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>16</v>
       </c>
       <c r="K52" s="11">
@@ -14257,7 +14257,7 @@
         <v>6</v>
       </c>
       <c r="J53" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>24</v>
       </c>
       <c r="K53" s="11"/>
@@ -14328,7 +14328,7 @@
         <v>1</v>
       </c>
       <c r="J54" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>1.6</v>
       </c>
       <c r="K54" s="11">
@@ -14409,7 +14409,7 @@
         <v>3</v>
       </c>
       <c r="J55" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K55" s="11">
@@ -14484,8 +14484,8 @@
         <v>1</v>
       </c>
       <c r="J56" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>2</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>4.0000000000000009</v>
       </c>
       <c r="K56" s="11"/>
       <c r="L56" s="18"/>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="AL56" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>6</v>
+        <v>12.000000000000004</v>
       </c>
     </row>
     <row r="57" spans="1:38" ht="28">
@@ -14561,7 +14561,7 @@
         <v>1</v>
       </c>
       <c r="J57" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>1.2</v>
       </c>
       <c r="K57" s="11"/>
@@ -14640,7 +14640,7 @@
         <v>1</v>
       </c>
       <c r="J58" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>1.2</v>
       </c>
       <c r="K58" s="11"/>
@@ -14719,7 +14719,7 @@
         <v>4</v>
       </c>
       <c r="J59" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K59" s="11"/>
@@ -14790,7 +14790,7 @@
         <v>4</v>
       </c>
       <c r="J60" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K60" s="11"/>
@@ -14861,7 +14861,7 @@
         <v>1</v>
       </c>
       <c r="J61" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>3.5999999999999992</v>
       </c>
       <c r="K61" s="11">
@@ -14948,7 +14948,7 @@
         <v>6</v>
       </c>
       <c r="J62" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>5.2</v>
       </c>
       <c r="K62" s="11"/>
@@ -15019,7 +15019,7 @@
         <v>1</v>
       </c>
       <c r="J63" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>2</v>
       </c>
       <c r="K63" s="11">
@@ -15092,7 +15092,7 @@
         <v>9</v>
       </c>
       <c r="J64" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K64" s="11"/>
@@ -15163,7 +15163,7 @@
         <v>1</v>
       </c>
       <c r="J65" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>3.5999999999999992</v>
       </c>
       <c r="K65" s="11">
@@ -15250,7 +15250,7 @@
         <v>6</v>
       </c>
       <c r="J66" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>5.2</v>
       </c>
       <c r="K66" s="11"/>
@@ -15321,7 +15321,7 @@
         <v>1</v>
       </c>
       <c r="J67" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>2</v>
       </c>
       <c r="K67" s="11">
@@ -15394,7 +15394,7 @@
         <v>1</v>
       </c>
       <c r="J68" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K68" s="11"/>
@@ -15463,7 +15463,7 @@
         <v>1</v>
       </c>
       <c r="J69" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>0.8</v>
       </c>
       <c r="K69" s="11">
@@ -15552,7 +15552,7 @@
         <v>1</v>
       </c>
       <c r="J70" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K70" s="11">
@@ -15625,7 +15625,7 @@
         <v>4</v>
       </c>
       <c r="J71" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K71" s="11"/>
@@ -15696,7 +15696,7 @@
         <v>1</v>
       </c>
       <c r="J72" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>1.3333333333333333</v>
       </c>
       <c r="K72" s="11"/>
@@ -15790,7 +15790,7 @@
         <v>1</v>
       </c>
       <c r="J73" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>2.5</v>
       </c>
       <c r="K73" s="11">
@@ -15877,7 +15877,7 @@
         <v>1</v>
       </c>
       <c r="J74" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K74" s="11">
@@ -15952,7 +15952,7 @@
         <v>4</v>
       </c>
       <c r="J75" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>14</v>
       </c>
       <c r="K75" s="11"/>
@@ -16023,7 +16023,7 @@
         <v>4</v>
       </c>
       <c r="J76" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>18</v>
       </c>
       <c r="K76" s="11"/>
@@ -16094,8 +16094,8 @@
         <v>4</v>
       </c>
       <c r="J77" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>-4</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>0</v>
       </c>
       <c r="K77" s="11"/>
       <c r="L77" s="18"/>
@@ -16167,7 +16167,7 @@
         <v>2</v>
       </c>
       <c r="J78" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>2</v>
       </c>
       <c r="K78" s="11"/>
@@ -16244,7 +16244,7 @@
         <v>1</v>
       </c>
       <c r="J79" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>10</v>
       </c>
       <c r="K79" s="11">
@@ -16321,7 +16321,7 @@
         <v>1</v>
       </c>
       <c r="J80" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K80" s="11">
@@ -16394,7 +16394,7 @@
         <v>5</v>
       </c>
       <c r="J81" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>6</v>
       </c>
       <c r="K81" s="11">
@@ -16467,7 +16467,7 @@
         <v>1</v>
       </c>
       <c r="J82" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>2.125</v>
       </c>
       <c r="K82" s="11">
@@ -16554,7 +16554,7 @@
         <v>1</v>
       </c>
       <c r="J83" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K83" s="11">
@@ -16629,7 +16629,7 @@
         <v>4</v>
       </c>
       <c r="J84" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>14</v>
       </c>
       <c r="K84" s="11"/>
@@ -16700,7 +16700,7 @@
         <v>4</v>
       </c>
       <c r="J85" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>18</v>
       </c>
       <c r="K85" s="11"/>
@@ -16771,7 +16771,7 @@
         <v>1</v>
       </c>
       <c r="J86" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>0.39999999999999991</v>
       </c>
       <c r="K86" s="11">
@@ -16862,8 +16862,8 @@
         <v>4</v>
       </c>
       <c r="J87" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>8</v>
       </c>
       <c r="K87" s="13"/>
       <c r="L87" s="25"/>
@@ -16901,7 +16901,7 @@
       </c>
       <c r="AL87" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:38" ht="28">
@@ -16935,7 +16935,7 @@
         <v>1</v>
       </c>
       <c r="J88" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>1.2</v>
       </c>
       <c r="K88" s="11">
@@ -17016,7 +17016,7 @@
         <v>1</v>
       </c>
       <c r="J89" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>1.2</v>
       </c>
       <c r="K89" s="11">
@@ -17097,7 +17097,7 @@
         <v>3</v>
       </c>
       <c r="J90" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K90" s="11"/>
@@ -17168,7 +17168,7 @@
         <v>2</v>
       </c>
       <c r="J91" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K91" s="11"/>
@@ -17239,7 +17239,7 @@
         <v>4</v>
       </c>
       <c r="J92" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K92" s="11"/>
@@ -17310,7 +17310,7 @@
         <v>11</v>
       </c>
       <c r="J93" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>16</v>
       </c>
       <c r="K93" s="11"/>
@@ -17381,7 +17381,7 @@
         <v>4</v>
       </c>
       <c r="J94" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K94" s="11"/>
@@ -17450,7 +17450,7 @@
         <v>4</v>
       </c>
       <c r="J95" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K95" s="11"/>
@@ -17521,7 +17521,7 @@
         <v>1</v>
       </c>
       <c r="J96" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>0.56000000000000005</v>
       </c>
       <c r="K96" s="11">
@@ -17612,7 +17612,7 @@
         <v>1</v>
       </c>
       <c r="J97" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>5.6000000000000005</v>
       </c>
       <c r="K97" s="11">
@@ -17685,7 +17685,7 @@
         <v>3</v>
       </c>
       <c r="J98" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>6.1333333333333337</v>
       </c>
       <c r="K98" s="11"/>
@@ -17760,7 +17760,7 @@
         <v>6</v>
       </c>
       <c r="J99" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K99" s="11"/>
@@ -17831,7 +17831,7 @@
         <v>3</v>
       </c>
       <c r="J100" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>1.6</v>
       </c>
       <c r="K100" s="11"/>
@@ -17902,7 +17902,7 @@
         <v>6</v>
       </c>
       <c r="J101" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>6.4</v>
       </c>
       <c r="K101" s="11"/>
@@ -17973,7 +17973,7 @@
         <v>6</v>
       </c>
       <c r="J102" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K102" s="11">
@@ -18046,7 +18046,7 @@
         <v>2</v>
       </c>
       <c r="J103" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K103" s="11">
@@ -18119,7 +18119,7 @@
         <v>11</v>
       </c>
       <c r="J104" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>28</v>
       </c>
       <c r="K104" s="11">
@@ -18192,7 +18192,7 @@
         <v>11</v>
       </c>
       <c r="J105" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K105" s="11">
@@ -18265,7 +18265,7 @@
         <v>11</v>
       </c>
       <c r="J106" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K106" s="11">
@@ -18338,7 +18338,7 @@
         <v>6</v>
       </c>
       <c r="J107" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K107" s="11"/>
@@ -18409,7 +18409,7 @@
         <v>2</v>
       </c>
       <c r="J108" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K108" s="11"/>
@@ -18480,7 +18480,7 @@
         <v>4</v>
       </c>
       <c r="J109" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K109" s="11">
@@ -18553,7 +18553,7 @@
         <v>1</v>
       </c>
       <c r="J110" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4.9999999999999982</v>
       </c>
       <c r="K110" s="11">
@@ -18673,7 +18673,7 @@
         <v>1</v>
       </c>
       <c r="J111" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K111" s="11">
@@ -18750,7 +18750,7 @@
         <v>1</v>
       </c>
       <c r="J112" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>48</v>
       </c>
       <c r="K112" s="13">
@@ -18823,7 +18823,7 @@
         <v>11</v>
       </c>
       <c r="J113" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>24</v>
       </c>
       <c r="K113" s="11">
@@ -18896,7 +18896,7 @@
         <v>11</v>
       </c>
       <c r="J114" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>48</v>
       </c>
       <c r="K114" s="11">
@@ -18969,7 +18969,7 @@
         <v>6</v>
       </c>
       <c r="J115" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>24</v>
       </c>
       <c r="K115" s="11">
@@ -19042,8 +19042,8 @@
         <v>4</v>
       </c>
       <c r="J116" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0.29599999999999999</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>0.49999999999999994</v>
       </c>
       <c r="K116" s="11">
         <v>0.5</v>
@@ -19133,8 +19133,8 @@
         <v>4</v>
       </c>
       <c r="J117" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>8</v>
       </c>
       <c r="K117" s="11"/>
       <c r="L117" s="18"/>
@@ -19172,7 +19172,7 @@
       </c>
       <c r="AL117" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:38">
@@ -19206,7 +19206,7 @@
         <v>3</v>
       </c>
       <c r="J118" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>6</v>
       </c>
       <c r="K118" s="11"/>
@@ -19277,7 +19277,7 @@
         <v>3</v>
       </c>
       <c r="J119" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>6</v>
       </c>
       <c r="K119" s="11"/>
@@ -19348,7 +19348,7 @@
         <v>2</v>
       </c>
       <c r="J120" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>10</v>
       </c>
       <c r="K120" s="11">
@@ -19421,7 +19421,7 @@
         <v>1</v>
       </c>
       <c r="J121" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>0.6</v>
       </c>
       <c r="K121" s="11">
@@ -19508,7 +19508,7 @@
         <v>6</v>
       </c>
       <c r="J122" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>3.5999999999999996</v>
       </c>
       <c r="K122" s="11"/>
@@ -19581,7 +19581,7 @@
         <v>1</v>
       </c>
       <c r="J123" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>0.49999999999999994</v>
       </c>
       <c r="K123" s="11">
@@ -19664,7 +19664,7 @@
         <v>1</v>
       </c>
       <c r="J124" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K124" s="11">
@@ -19737,8 +19737,8 @@
         <v>4</v>
       </c>
       <c r="J125" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>14</v>
       </c>
       <c r="K125" s="11"/>
       <c r="L125" s="18"/>
@@ -19776,7 +19776,7 @@
       </c>
       <c r="AL125" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="126" spans="1:38">
@@ -19810,7 +19810,7 @@
         <v>4</v>
       </c>
       <c r="J126" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>22</v>
       </c>
       <c r="K126" s="11"/>
@@ -19881,7 +19881,7 @@
         <v>1</v>
       </c>
       <c r="J127" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>0.39999999999999991</v>
       </c>
       <c r="K127" s="11">
@@ -19972,7 +19972,7 @@
         <v>2</v>
       </c>
       <c r="J128" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K128" s="11"/>
@@ -20049,7 +20049,7 @@
         <v>3</v>
       </c>
       <c r="J129" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K129" s="11"/>
@@ -20120,7 +20120,7 @@
         <v>4</v>
       </c>
       <c r="J130" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>12</v>
       </c>
       <c r="K130" s="11"/>
@@ -20191,7 +20191,7 @@
         <v>1</v>
       </c>
       <c r="J131" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>0.79999999999999982</v>
       </c>
       <c r="K131" s="11">
@@ -20282,7 +20282,7 @@
         <v>3</v>
       </c>
       <c r="J132" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K132" s="11"/>
@@ -20353,7 +20353,7 @@
         <v>2</v>
       </c>
       <c r="J133" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>12</v>
       </c>
       <c r="K133" s="11"/>
@@ -20424,7 +20424,7 @@
         <v>1</v>
       </c>
       <c r="J134" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>0.8</v>
       </c>
       <c r="K134" s="11">
@@ -20505,7 +20505,7 @@
         <v>1</v>
       </c>
       <c r="J135" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>0.8</v>
       </c>
       <c r="K135" s="11">
@@ -20586,7 +20586,7 @@
         <v>3</v>
       </c>
       <c r="J136" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>16</v>
       </c>
       <c r="K136" s="11"/>
@@ -20657,7 +20657,7 @@
         <v>3</v>
       </c>
       <c r="J137" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>22</v>
       </c>
       <c r="K137" s="11"/>
@@ -20728,7 +20728,7 @@
         <v>1</v>
       </c>
       <c r="J138" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>2</v>
       </c>
       <c r="K138" s="11">
@@ -20801,8 +20801,8 @@
         <v>1</v>
       </c>
       <c r="J139" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0.32727272727272722</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>0.39999999999999991</v>
       </c>
       <c r="K139" s="11">
         <v>0.5</v>
@@ -20894,8 +20894,8 @@
         <v>4</v>
       </c>
       <c r="J140" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>2.6666666666666665</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>8</v>
       </c>
       <c r="K140" s="11"/>
       <c r="L140" s="18"/>
@@ -20935,7 +20935,7 @@
       </c>
       <c r="AL140" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>5.333333333333333</v>
+        <v>16</v>
       </c>
     </row>
     <row r="141" spans="1:38" ht="28">
@@ -20969,7 +20969,7 @@
         <v>1</v>
       </c>
       <c r="J141" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>1.2</v>
       </c>
       <c r="K141" s="11"/>
@@ -21048,7 +21048,7 @@
         <v>1</v>
       </c>
       <c r="J142" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>1.2</v>
       </c>
       <c r="K142" s="11"/>
@@ -21127,7 +21127,7 @@
         <v>3</v>
       </c>
       <c r="J143" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>20</v>
       </c>
       <c r="K143" s="11"/>
@@ -21198,7 +21198,7 @@
         <v>3</v>
       </c>
       <c r="J144" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K144" s="11"/>
@@ -21271,8 +21271,8 @@
         <v>3</v>
       </c>
       <c r="J145" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
-        <v>0</v>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>8</v>
       </c>
       <c r="K145" s="11"/>
       <c r="L145" s="18"/>
@@ -21292,12 +21292,10 @@
       <c r="Z145" s="20"/>
       <c r="AA145" s="20"/>
       <c r="AB145" s="20"/>
-      <c r="AC145" s="20">
-        <v>0.2</v>
-      </c>
+      <c r="AC145" s="20"/>
       <c r="AD145" s="20"/>
       <c r="AE145" s="20">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="AF145" s="20"/>
       <c r="AG145" s="20"/>
@@ -21310,7 +21308,7 @@
       </c>
       <c r="AL145" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:38">
@@ -21344,7 +21342,7 @@
         <v>3</v>
       </c>
       <c r="J146" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>12</v>
       </c>
       <c r="K146" s="11"/>
@@ -21415,7 +21413,7 @@
         <v>3</v>
       </c>
       <c r="J147" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K147" s="11"/>
@@ -21486,7 +21484,7 @@
         <v>3</v>
       </c>
       <c r="J148" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>12</v>
       </c>
       <c r="K148" s="11"/>
@@ -21557,7 +21555,7 @@
         <v>3</v>
       </c>
       <c r="J149" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K149" s="11"/>
@@ -21628,7 +21626,7 @@
         <v>1</v>
       </c>
       <c r="J150" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>9.9999999999999964</v>
       </c>
       <c r="K150" s="11">
@@ -21748,7 +21746,7 @@
         <v>1</v>
       </c>
       <c r="J151" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>10</v>
       </c>
       <c r="K151" s="11">
@@ -21825,7 +21823,7 @@
         <v>1</v>
       </c>
       <c r="J152" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>60</v>
       </c>
       <c r="K152" s="11">
@@ -21898,7 +21896,7 @@
         <v>1</v>
       </c>
       <c r="J153" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>24</v>
       </c>
       <c r="K153" s="11">
@@ -21971,7 +21969,7 @@
         <v>11</v>
       </c>
       <c r="J154" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>48</v>
       </c>
       <c r="K154" s="11">
@@ -22044,7 +22042,7 @@
         <v>11</v>
       </c>
       <c r="J155" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>96</v>
       </c>
       <c r="K155" s="11">
@@ -22117,7 +22115,7 @@
         <v>1</v>
       </c>
       <c r="J156" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>36</v>
       </c>
       <c r="K156" s="11">
@@ -22190,7 +22188,7 @@
         <v>1</v>
       </c>
       <c r="J157" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>36</v>
       </c>
       <c r="K157" s="11">
@@ -22263,7 +22261,7 @@
         <v>2</v>
       </c>
       <c r="J158" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>16</v>
       </c>
       <c r="K158" s="11"/>
@@ -22334,7 +22332,7 @@
         <v>4</v>
       </c>
       <c r="J159" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>16</v>
       </c>
       <c r="K159" s="11"/>
@@ -22405,7 +22403,7 @@
         <v>3</v>
       </c>
       <c r="J160" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K160" s="11"/>
@@ -22476,7 +22474,7 @@
         <v>5</v>
       </c>
       <c r="J161" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>20</v>
       </c>
       <c r="K161" s="11"/>
@@ -22549,7 +22547,7 @@
         <v>1</v>
       </c>
       <c r="J162" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>1.9999999999999998</v>
       </c>
       <c r="K162" s="11"/>
@@ -22638,7 +22636,7 @@
         <v>1</v>
       </c>
       <c r="J163" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>0.79999999999999982</v>
       </c>
       <c r="K163" s="11"/>
@@ -22727,7 +22725,7 @@
         <v>11</v>
       </c>
       <c r="J164" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>12</v>
       </c>
       <c r="K164" s="11"/>
@@ -22798,7 +22796,7 @@
         <v>2</v>
       </c>
       <c r="J165" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K165" s="11"/>
@@ -22869,7 +22867,7 @@
         <v>2</v>
       </c>
       <c r="J166" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K166" s="11"/>
@@ -22940,7 +22938,7 @@
         <v>3</v>
       </c>
       <c r="J167" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>24</v>
       </c>
       <c r="K167" s="11"/>
@@ -23011,7 +23009,7 @@
         <v>6</v>
       </c>
       <c r="J168" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K168" s="11">
@@ -23084,7 +23082,7 @@
         <v>6</v>
       </c>
       <c r="J169" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>24</v>
       </c>
       <c r="K169" s="11">
@@ -23157,7 +23155,7 @@
         <v>1</v>
       </c>
       <c r="J170" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>16</v>
       </c>
       <c r="K170" s="11">
@@ -23230,7 +23228,7 @@
         <v>3</v>
       </c>
       <c r="J171" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K171" s="11"/>
@@ -23301,7 +23299,7 @@
         <v>7</v>
       </c>
       <c r="J172" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>16</v>
       </c>
       <c r="K172" s="11">
@@ -23374,7 +23372,7 @@
         <v>6</v>
       </c>
       <c r="J173" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>24</v>
       </c>
       <c r="K173" s="11"/>
@@ -23445,7 +23443,7 @@
         <v>6</v>
       </c>
       <c r="J174" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>36</v>
       </c>
       <c r="K174" s="11"/>
@@ -23516,7 +23514,7 @@
         <v>4</v>
       </c>
       <c r="J175" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>4</v>
       </c>
       <c r="K175" s="11"/>
@@ -23587,7 +23585,7 @@
         <v>6</v>
       </c>
       <c r="J176" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K176" s="11"/>
@@ -23658,7 +23656,7 @@
         <v>3</v>
       </c>
       <c r="J177" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>8</v>
       </c>
       <c r="K177" s="11"/>
@@ -23729,7 +23727,7 @@
         <v>8</v>
       </c>
       <c r="J178" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>20</v>
       </c>
       <c r="K178" s="11"/>
@@ -23800,7 +23798,7 @@
         <v>3</v>
       </c>
       <c r="J179" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>12</v>
       </c>
       <c r="K179" s="11"/>
@@ -23871,7 +23869,7 @@
         <v>4</v>
       </c>
       <c r="J180" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>40</v>
       </c>
       <c r="K180" s="11">
@@ -23944,7 +23942,7 @@
         <v>1</v>
       </c>
       <c r="J181" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>40</v>
       </c>
       <c r="K181" s="11">
@@ -24017,7 +24015,7 @@
         <v>2</v>
       </c>
       <c r="J182" s="11">
-        <f>AVERAGE(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]]</f>
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>40</v>
       </c>
       <c r="K182" s="11">
@@ -35589,24 +35587,24 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E2:E100">
-    <cfRule type="containsText" dxfId="12" priority="12" operator="containsText" text="SEMD">
+    <cfRule type="containsText" dxfId="13" priority="12" operator="containsText" text="SEMD">
       <formula>NOT(ISERROR(SEARCH("SEMD",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="13" operator="containsText" text="SEM2">
+    <cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="SEM2">
       <formula>NOT(ISERROR(SEARCH("SEM2",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="14" operator="containsText" text="SEM1">
+    <cfRule type="containsText" dxfId="11" priority="14" operator="containsText" text="SEM1">
       <formula>NOT(ISERROR(SEARCH("SEM1",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E96:E100">
-    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="SEMD">
+    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="SEMD">
       <formula>NOT(ISERROR(SEARCH("SEMD",E96)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="SEM2">
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="SEM2">
       <formula>NOT(ISERROR(SEARCH("SEM2",E96)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="SEM1">
+    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="SEM1">
       <formula>NOT(ISERROR(SEARCH("SEM1",E96)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35655,23 +35653,23 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:T95 H96:S100">
-    <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="O">
+    <cfRule type="containsText" dxfId="7" priority="16" operator="containsText" text="O">
       <formula>NOT(ISERROR(SEARCH("O",H2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="17" operator="containsText" text="C">
+    <cfRule type="containsText" dxfId="6" priority="17" operator="containsText" text="C">
       <formula>NOT(ISERROR(SEARCH("C",H2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T96:T100">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="O">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="O">
       <formula>NOT(ISERROR(SEARCH("O",T96)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="C">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="C">
       <formula>NOT(ISERROR(SEARCH("C",T96)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W100">
-    <cfRule type="expression" dxfId="0" priority="9">
+    <cfRule type="expression" dxfId="1" priority="9">
       <formula>W2&lt;&gt;V2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36212,7 +36210,7 @@
       </c>
       <c r="C23">
         <f>SUMIF(Table1[Module Code],Sheet2!A23,Table1[Total Hours])</f>
-        <v>6</v>
+        <v>12.000000000000004</v>
       </c>
       <c r="D23">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A23,Table14[Module Code],0))</f>
@@ -36220,11 +36218,11 @@
       </c>
       <c r="E23">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F23">
         <f t="shared" si="1"/>
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -36500,7 +36498,7 @@
       </c>
       <c r="C35">
         <f>SUMIF(Table1[Module Code],Sheet2!A35,Table1[Total Hours])</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D35">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A35,Table14[Module Code],0))</f>
@@ -36508,11 +36506,11 @@
       </c>
       <c r="E35">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="F35">
         <f t="shared" si="1"/>
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -36860,7 +36858,7 @@
       </c>
       <c r="C50">
         <f>SUMIF(Table1[Module Code],Sheet2!A50,Table1[Total Hours])</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D50">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A50,Table14[Module Code],0))</f>
@@ -36868,11 +36866,11 @@
       </c>
       <c r="E50">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F50">
         <f t="shared" si="1"/>
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -36980,7 +36978,7 @@
       </c>
       <c r="C55">
         <f>SUMIF(Table1[Module Code],Sheet2!A55,Table1[Total Hours])</f>
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D55">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A55,Table14[Module Code],0))</f>
@@ -36988,11 +36986,11 @@
       </c>
       <c r="E55">
         <f t="shared" si="0"/>
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F55">
         <f t="shared" si="1"/>
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -37196,7 +37194,7 @@
       </c>
       <c r="C64">
         <f>SUMIF(Table1[Module Code],Sheet2!A64,Table1[Total Hours])</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D64">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A64,Table14[Module Code],0))</f>
@@ -37204,11 +37202,11 @@
       </c>
       <c r="E64">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F64">
         <f t="shared" si="1"/>
-        <v>3.6</v>
+        <v>4.4000000000000004</v>
       </c>
     </row>
     <row r="65" spans="1:6">

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1725" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC466023-8838-48DA-AF14-A3A1A7521268}"/>
+  <xr:revisionPtr revIDLastSave="1728" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C271CFC-A94B-4760-B8F3-68A74A2BE097}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
@@ -12394,11 +12394,9 @@
       <c r="N29" s="18"/>
       <c r="O29" s="19"/>
       <c r="P29" s="18"/>
-      <c r="Q29" s="18">
+      <c r="Q29" s="18"/>
+      <c r="R29" s="18">
         <v>0.2</v>
-      </c>
-      <c r="R29" s="18">
-        <v>-0.2</v>
       </c>
       <c r="S29" s="19"/>
       <c r="T29" s="18"/>

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1728" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C271CFC-A94B-4760-B8F3-68A74A2BE097}"/>
+  <xr:revisionPtr revIDLastSave="1752" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2844FD40-6E74-4300-9BDB-7F13D7C71129}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="26115" windowHeight="15675" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Assessments" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId5"/>
+    <pivotCache cacheId="4" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2907" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2907" uniqueCount="391">
   <si>
     <t>Module Code</t>
   </si>
@@ -1231,6 +1231,9 @@
   </si>
   <si>
     <t>Synoptic Reflection</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
 </sst>
 </file>
@@ -1462,31 +1465,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="113">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3482,6 +3460,31 @@
         <name val="Calibri (Body)"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -9161,7 +9164,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B70" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="34">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -9625,39 +9628,39 @@
     <tableColumn id="36" xr3:uid="{A7BF30F6-C808-4B8F-B3FF-9FAF20E2145A}" name="Summative" dataDxfId="101"/>
     <tableColumn id="37" xr3:uid="{68E504F9-116C-43AB-BCC6-3BB48B0860D2}" name="Day of Week" dataDxfId="100"/>
     <tableColumn id="16" xr3:uid="{E6637FEB-7F23-45F0-99D2-96D20DD2DAEF}" name="Duration" dataDxfId="99"/>
-    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="0">
+    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="98">
       <calculatedColumnFormula>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="98"/>
-    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="97"/>
-    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="96"/>
-    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="95"/>
-    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="94"/>
-    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="93"/>
-    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="92"/>
-    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="90"/>
-    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="89"/>
-    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="88"/>
-    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="87"/>
-    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="86"/>
-    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="85"/>
-    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="84"/>
-    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="83"/>
-    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="82"/>
-    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="81"/>
-    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="80"/>
-    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="79"/>
-    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="78"/>
-    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="77"/>
-    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="76"/>
-    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="75"/>
-    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="74"/>
-    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="73"/>
-    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="72">
+    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="97"/>
+    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="96"/>
+    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="95"/>
+    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="94"/>
+    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="93"/>
+    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="92"/>
+    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="91"/>
+    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="90"/>
+    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="89"/>
+    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="88"/>
+    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="87"/>
+    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="86"/>
+    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="85"/>
+    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="84"/>
+    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="83"/>
+    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="82"/>
+    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="81"/>
+    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="80"/>
+    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="79"/>
+    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="78"/>
+    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="77"/>
+    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="76"/>
+    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="75"/>
+    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="74"/>
+    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="73"/>
+    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="72"/>
+    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="71">
       <calculatedColumnFormula>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="71">
+    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="70">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9666,49 +9669,49 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="70" dataDxfId="68" headerRowBorderDxfId="69" tableBorderDxfId="67" totalsRowBorderDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68" tableBorderDxfId="66" totalsRowBorderDxfId="65">
   <autoFilter ref="A1:AE64" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD64">
     <sortCondition ref="A1:A132"/>
   </sortState>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="65"/>
-    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="64"/>
-    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="63"/>
-    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="62">
+    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="62"/>
+    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="61">
       <calculatedColumnFormula>INDEX(Table2[Credits],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="61">
+    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="60">
       <calculatedColumnFormula>INDEX(Table2[Semester],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="60">
+    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="59">
       <calculatedColumnFormula>INDEX(Table2[Contact Time],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="59"/>
-    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="58"/>
-    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="57"/>
-    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="56"/>
-    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="55"/>
-    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="54"/>
-    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="53"/>
-    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="52"/>
-    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="51"/>
-    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="50"/>
-    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="49"/>
-    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="48"/>
-    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="47"/>
-    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="46"/>
-    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="45"/>
-    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="44"/>
-    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="43"/>
-    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="42"/>
-    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="41"/>
-    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="40"/>
-    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="39"/>
-    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="38"/>
-    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="37"/>
-    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="36"/>
-    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="35">
+    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="55"/>
+    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="54"/>
+    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="53"/>
+    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="52"/>
+    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="51"/>
+    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="50"/>
+    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="49"/>
+    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="48"/>
+    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="47"/>
+    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="46"/>
+    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="45"/>
+    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="44"/>
+    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="43"/>
+    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="42"/>
+    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="41"/>
+    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="40"/>
+    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="39"/>
+    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="38"/>
+    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="37"/>
+    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="36"/>
+    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="35"/>
+    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="34">
       <calculatedColumnFormula>SUM(Table14[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9717,37 +9720,37 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}" name="Table2" displayName="Table2" ref="A1:W100" totalsRowShown="0" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}" name="Table2" displayName="Table2" ref="A1:W100" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32">
   <autoFilter ref="A1:W100" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B62">
     <sortCondition ref="A1:A62"/>
   </sortState>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{A36A2B86-0F30-4188-9ECD-AE5BC71A59F4}" name="Module Code" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{D3F20037-EF35-4207-A530-484E1EB45719}" name="Module Title" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{40C22022-10B9-411F-9B76-B89140ABFFB2}" name="Alternative Module Code" dataDxfId="29"/>
-    <tableColumn id="13" xr3:uid="{CB12E405-1802-457C-AF17-F1B9CB3BBF13}" name="Source" dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{EA737976-1AA7-49B6-8752-A388621554F4}" name="Semester" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{16DFC84F-5858-467D-B447-49992D721E4B}" name="Level" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{A17BC4BA-A3CB-442D-9BDC-D3B41B98B389}" name="Credits" dataDxfId="25"/>
-    <tableColumn id="19" xr3:uid="{98846C13-E462-4CFF-858E-AF75931B6712}" name="AllUG" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{7E25B4F4-1A7D-48D9-AAA2-AF5C97240797}" name="Physics" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{A36A2B86-0F30-4188-9ECD-AE5BC71A59F4}" name="Module Code" dataDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{D3F20037-EF35-4207-A530-484E1EB45719}" name="Module Title" dataDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{40C22022-10B9-411F-9B76-B89140ABFFB2}" name="Alternative Module Code" dataDxfId="28"/>
+    <tableColumn id="13" xr3:uid="{CB12E405-1802-457C-AF17-F1B9CB3BBF13}" name="Source" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{EA737976-1AA7-49B6-8752-A388621554F4}" name="Semester" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{16DFC84F-5858-467D-B447-49992D721E4B}" name="Level" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{A17BC4BA-A3CB-442D-9BDC-D3B41B98B389}" name="Credits" dataDxfId="24"/>
+    <tableColumn id="19" xr3:uid="{98846C13-E462-4CFF-858E-AF75931B6712}" name="AllUG" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{7E25B4F4-1A7D-48D9-AAA2-AF5C97240797}" name="Physics" dataDxfId="22"/>
     <tableColumn id="17" xr3:uid="{AA3AE96F-2651-49D7-89AD-BA94806438AE}" name="PhysAstro"/>
-    <tableColumn id="4" xr3:uid="{9C7DD469-E550-411F-8467-246A1543FB38}" name="Astro" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{3C5D3AEB-487E-4678-A42F-BE4BA4D0E9AA}" name="MedPhys" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{9C7DD469-E550-411F-8467-246A1543FB38}" name="Astro" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{3C5D3AEB-487E-4678-A42F-BE4BA4D0E9AA}" name="MedPhys" dataDxfId="20"/>
     <tableColumn id="20" xr3:uid="{C3673B06-C0A2-44F6-8978-F392282CECF8}" name="AllPG"/>
-    <tableColumn id="14" xr3:uid="{AE552873-9B31-41A6-B73C-D052477CA74C}" name="MScPhysics" dataDxfId="20"/>
-    <tableColumn id="15" xr3:uid="{8F51CE76-3A29-487A-A13C-FB63C79CF3E6}" name="MScAstro" dataDxfId="19"/>
-    <tableColumn id="21" xr3:uid="{FC74E264-78AB-4682-A1B8-D8964ED1C3F3}" name="MScDataPhys" dataDxfId="18"/>
-    <tableColumn id="22" xr3:uid="{2D5776F7-D7F7-4D20-A7CB-DB57997AD074}" name="MScDataAstro" dataDxfId="17"/>
+    <tableColumn id="14" xr3:uid="{AE552873-9B31-41A6-B73C-D052477CA74C}" name="MScPhysics" dataDxfId="19"/>
+    <tableColumn id="15" xr3:uid="{8F51CE76-3A29-487A-A13C-FB63C79CF3E6}" name="MScAstro" dataDxfId="18"/>
+    <tableColumn id="21" xr3:uid="{FC74E264-78AB-4682-A1B8-D8964ED1C3F3}" name="MScDataPhys" dataDxfId="17"/>
+    <tableColumn id="22" xr3:uid="{2D5776F7-D7F7-4D20-A7CB-DB57997AD074}" name="MScDataAstro" dataDxfId="16"/>
     <tableColumn id="18" xr3:uid="{10668F71-1EDF-482E-86A5-46E1F3C15120}" name="MScCSPhysics"/>
     <tableColumn id="23" xr3:uid="{E837FCBC-49C7-45CE-AFAA-4F01143EF2A8}" name="CDTCSPhysics"/>
     <tableColumn id="16" xr3:uid="{DB790F5F-BEF0-41CE-A68A-1AA9DF83D66B}" name="Contact Time"/>
-    <tableColumn id="10" xr3:uid="{60774AFA-B365-4EB5-AAFF-6235868F8C97}" name="Exam Weight (%)" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{537B7C75-E9C0-42F2-9F3C-6E960AB2D257}" name="CA weight" dataDxfId="15">
+    <tableColumn id="10" xr3:uid="{60774AFA-B365-4EB5-AAFF-6235868F8C97}" name="Exam Weight (%)" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{537B7C75-E9C0-42F2-9F3C-6E960AB2D257}" name="CA weight" dataDxfId="14">
       <calculatedColumnFormula>100-Table2[[#This Row],[Exam Weight (%)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{75DA2527-5A08-4ECE-B4E4-752A8F8BF059}" name="CA Check" dataDxfId="14">
+    <tableColumn id="11" xr3:uid="{75DA2527-5A08-4ECE-B4E4-752A8F8BF059}" name="CA Check" dataDxfId="13">
       <calculatedColumnFormula>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -19125,7 +19128,7 @@
         <v>229</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="I117" s="11">
         <v>4</v>
@@ -19438,12 +19441,14 @@
       <c r="P121" s="18">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="Q121" s="18"/>
+      <c r="Q121" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
       <c r="R121" s="18">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="S121" s="18">
-        <v>1.4999999999999999E-2</v>
+        <v>-1.4999999999999999E-2</v>
       </c>
       <c r="T121" s="18">
         <v>1.4999999999999999E-2</v>
@@ -19500,7 +19505,7 @@
         <v>229</v>
       </c>
       <c r="H122" s="11" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="I122" s="11">
         <v>6</v>
@@ -19516,10 +19521,12 @@
       <c r="O122" s="19"/>
       <c r="P122" s="18"/>
       <c r="Q122" s="19">
+        <v>-0.1</v>
+      </c>
+      <c r="R122" s="18"/>
+      <c r="S122" s="19">
         <v>0.1</v>
       </c>
-      <c r="R122" s="18"/>
-      <c r="S122" s="19"/>
       <c r="T122" s="18"/>
       <c r="U122" s="19">
         <v>0.08</v>
@@ -19743,11 +19750,9 @@
       <c r="M125" s="18"/>
       <c r="N125" s="18"/>
       <c r="O125" s="19"/>
-      <c r="P125" s="18">
+      <c r="P125" s="18"/>
+      <c r="Q125" s="18">
         <v>0.35</v>
-      </c>
-      <c r="Q125" s="18">
-        <v>-0.35</v>
       </c>
       <c r="R125" s="18"/>
       <c r="S125" s="19"/>
@@ -22785,7 +22790,7 @@
         <v>303</v>
       </c>
       <c r="G165" s="11" t="s">
-        <v>229</v>
+        <v>390</v>
       </c>
       <c r="H165" s="11" t="s">
         <v>300</v>
@@ -22856,7 +22861,7 @@
         <v>304</v>
       </c>
       <c r="G166" s="11" t="s">
-        <v>229</v>
+        <v>390</v>
       </c>
       <c r="H166" s="11" t="s">
         <v>300</v>
@@ -22943,9 +22948,11 @@
       <c r="L167" s="18"/>
       <c r="M167" s="18"/>
       <c r="N167" s="18"/>
-      <c r="O167" s="19"/>
+      <c r="O167" s="19">
+        <v>0.3</v>
+      </c>
       <c r="P167" s="18">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
       <c r="Q167" s="18"/>
       <c r="R167" s="18"/>
@@ -23081,7 +23088,7 @@
       </c>
       <c r="J169" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K169" s="11">
         <v>0.5</v>
@@ -23097,7 +23104,7 @@
       <c r="T169" s="18"/>
       <c r="U169" s="18"/>
       <c r="V169" s="18">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W169" s="19"/>
       <c r="X169" s="20"/>
@@ -23115,7 +23122,7 @@
       <c r="AJ169" s="20"/>
       <c r="AK169" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AL169" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -23147,14 +23154,14 @@
         <v>229</v>
       </c>
       <c r="H170" s="11" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="I170" s="11">
         <v>1</v>
       </c>
       <c r="J170" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="K170" s="11">
         <v>1</v>
@@ -23170,7 +23177,7 @@
       <c r="T170" s="18"/>
       <c r="U170" s="18"/>
       <c r="V170" s="18">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W170" s="19"/>
       <c r="X170" s="20"/>
@@ -23188,7 +23195,7 @@
       <c r="AJ170" s="20"/>
       <c r="AK170" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AL170" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -23217,7 +23224,7 @@
         <v>311</v>
       </c>
       <c r="G171" s="11" t="s">
-        <v>229</v>
+        <v>390</v>
       </c>
       <c r="H171" s="11" t="s">
         <v>300</v>
@@ -23442,7 +23449,7 @@
       </c>
       <c r="J174" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K174" s="11"/>
       <c r="L174" s="18"/>
@@ -23469,16 +23476,16 @@
       <c r="AG174" s="20"/>
       <c r="AH174" s="20"/>
       <c r="AI174" s="20">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AJ174" s="20"/>
       <c r="AK174" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AL174" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="175" spans="1:38">
@@ -35585,24 +35592,24 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E2:E100">
-    <cfRule type="containsText" dxfId="13" priority="12" operator="containsText" text="SEMD">
+    <cfRule type="containsText" dxfId="12" priority="12" operator="containsText" text="SEMD">
       <formula>NOT(ISERROR(SEARCH("SEMD",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="SEM2">
+    <cfRule type="containsText" dxfId="11" priority="13" operator="containsText" text="SEM2">
       <formula>NOT(ISERROR(SEARCH("SEM2",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="14" operator="containsText" text="SEM1">
+    <cfRule type="containsText" dxfId="10" priority="14" operator="containsText" text="SEM1">
       <formula>NOT(ISERROR(SEARCH("SEM1",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E96:E100">
-    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="SEMD">
+    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="SEMD">
       <formula>NOT(ISERROR(SEARCH("SEMD",E96)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="SEM2">
+    <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="SEM2">
       <formula>NOT(ISERROR(SEARCH("SEM2",E96)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="SEM1">
+    <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="SEM1">
       <formula>NOT(ISERROR(SEARCH("SEM1",E96)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -35651,23 +35658,23 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:T95 H96:S100">
-    <cfRule type="containsText" dxfId="7" priority="16" operator="containsText" text="O">
+    <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="O">
       <formula>NOT(ISERROR(SEARCH("O",H2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="17" operator="containsText" text="C">
+    <cfRule type="containsText" dxfId="5" priority="17" operator="containsText" text="C">
       <formula>NOT(ISERROR(SEARCH("C",H2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T96:T100">
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="O">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="O">
       <formula>NOT(ISERROR(SEARCH("O",T96)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="C">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="C">
       <formula>NOT(ISERROR(SEARCH("C",T96)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W100">
-    <cfRule type="expression" dxfId="1" priority="9">
+    <cfRule type="expression" dxfId="0" priority="9">
       <formula>W2&lt;&gt;V2</formula>
     </cfRule>
   </conditionalFormatting>
@@ -37312,7 +37319,7 @@
       </c>
       <c r="C69">
         <f>SUMIF(Table1[Module Code],Sheet2!A69,Table1[Total Hours])</f>
-        <v>64.5</v>
+        <v>68.5</v>
       </c>
       <c r="D69">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A69,Table14[Module Code],0))</f>
@@ -37320,11 +37327,11 @@
       </c>
       <c r="E69">
         <f t="shared" ref="E69" si="2">SUM(C69:D69)</f>
-        <v>108.5</v>
+        <v>112.5</v>
       </c>
       <c r="F69">
         <f t="shared" ref="F69:F70" si="3">E69/B69</f>
-        <v>5.4249999999999998</v>
+        <v>5.625</v>
       </c>
     </row>
     <row r="70" spans="1:6">

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1752" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2844FD40-6E74-4300-9BDB-7F13D7C71129}"/>
+  <xr:revisionPtr revIDLastSave="1759" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AFACCC6-BA25-4A66-ABBD-4FF1B201EE46}"/>
   <bookViews>
     <workbookView xWindow="28702" yWindow="-98" windowWidth="26115" windowHeight="15675" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2907" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="391">
   <si>
     <t>Module Code</t>
   </si>
@@ -9613,10 +9613,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}" name="Table1" displayName="Table1" ref="A1:AL182" totalsRowShown="0" headerRowDxfId="112" dataDxfId="110" headerRowBorderDxfId="111" tableBorderDxfId="109" totalsRowBorderDxfId="108">
-  <autoFilter ref="A1:AL182" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AI153">
-    <sortCondition ref="A1:A153"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}" name="Table1" displayName="Table1" ref="A1:AL183" totalsRowShown="0" headerRowDxfId="112" dataDxfId="110" headerRowBorderDxfId="111" tableBorderDxfId="109" totalsRowBorderDxfId="108">
+  <autoFilter ref="A1:AL183" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AI154">
+    <sortCondition ref="A1:A154"/>
   </sortState>
   <tableColumns count="38">
     <tableColumn id="1" xr3:uid="{7078548A-F011-4851-AB36-1F04238FA2FE}" name="Module Code" dataDxfId="107"/>
@@ -10075,7 +10075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66039B40-29AD-4D93-B125-EAF72A7B3996}">
-  <dimension ref="A1:AL182"/>
+  <dimension ref="A1:AL183"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
@@ -19122,20 +19122,20 @@
         <v>10</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>206</v>
+        <v>381</v>
       </c>
       <c r="G117" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H117" s="11" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I117" s="11">
         <v>4</v>
       </c>
       <c r="J117" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K117" s="11"/>
       <c r="L117" s="18"/>
@@ -19147,9 +19147,7 @@
       <c r="R117" s="18">
         <v>-0.2</v>
       </c>
-      <c r="S117" s="19">
-        <v>0.2</v>
-      </c>
+      <c r="S117" s="19"/>
       <c r="T117" s="18"/>
       <c r="U117" s="18"/>
       <c r="V117" s="18"/>
@@ -19169,19 +19167,19 @@
       <c r="AJ117" s="20"/>
       <c r="AK117" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AL117" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:38">
       <c r="A118" s="4" t="s">
-        <v>238</v>
+        <v>61</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>237</v>
+        <v>62</v>
       </c>
       <c r="C118" s="11" t="s">
         <v>5</v>
@@ -19201,14 +19199,14 @@
         <v>229</v>
       </c>
       <c r="H118" s="11" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="I118" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J118" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K118" s="11"/>
       <c r="L118" s="18"/>
@@ -19218,10 +19216,10 @@
       <c r="P118" s="18"/>
       <c r="Q118" s="18"/>
       <c r="R118" s="18"/>
-      <c r="S118" s="19"/>
-      <c r="T118" s="18">
-        <v>0.15</v>
-      </c>
+      <c r="S118" s="19">
+        <v>0.2</v>
+      </c>
+      <c r="T118" s="18"/>
       <c r="U118" s="18"/>
       <c r="V118" s="18"/>
       <c r="W118" s="19"/>
@@ -19240,11 +19238,11 @@
       <c r="AJ118" s="20"/>
       <c r="AK118" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="AL118" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:38">
@@ -19255,7 +19253,7 @@
         <v>237</v>
       </c>
       <c r="C119" s="11" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="D119" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -19266,13 +19264,13 @@
         <v>10</v>
       </c>
       <c r="F119" s="11" t="s">
-        <v>370</v>
+        <v>206</v>
       </c>
       <c r="G119" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H119" s="11" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="I119" s="11">
         <v>3</v>
@@ -19288,11 +19286,11 @@
       <c r="O119" s="19"/>
       <c r="P119" s="18"/>
       <c r="Q119" s="18"/>
-      <c r="R119" s="18">
+      <c r="R119" s="18"/>
+      <c r="S119" s="19"/>
+      <c r="T119" s="18">
         <v>0.15</v>
       </c>
-      <c r="S119" s="19"/>
-      <c r="T119" s="18"/>
       <c r="U119" s="18"/>
       <c r="V119" s="18"/>
       <c r="W119" s="19"/>
@@ -19318,54 +19316,52 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:38" ht="28">
+    <row r="120" spans="1:38">
       <c r="A120" s="4" t="s">
-        <v>63</v>
+        <v>238</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>294</v>
+        <v>237</v>
       </c>
       <c r="C120" s="11" t="s">
         <v>121</v>
       </c>
       <c r="D120" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E120" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F120" s="37" t="s">
-        <v>386</v>
+      <c r="F120" s="11" t="s">
+        <v>370</v>
       </c>
       <c r="G120" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H120" s="11" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="I120" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J120" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>10</v>
-      </c>
-      <c r="K120" s="11">
-        <v>15</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K120" s="11"/>
       <c r="L120" s="18"/>
       <c r="M120" s="18"/>
       <c r="N120" s="18"/>
       <c r="O120" s="19"/>
       <c r="P120" s="18"/>
       <c r="Q120" s="18"/>
-      <c r="R120" s="18"/>
+      <c r="R120" s="18">
+        <v>0.15</v>
+      </c>
       <c r="S120" s="19"/>
-      <c r="T120" s="18">
-        <v>0.25</v>
-      </c>
+      <c r="T120" s="18"/>
       <c r="U120" s="18"/>
       <c r="V120" s="18"/>
       <c r="W120" s="19"/>
@@ -19384,79 +19380,63 @@
       <c r="AJ120" s="20"/>
       <c r="AK120" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="AL120" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:38" ht="28">
       <c r="A121" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>67</v>
+        <v>294</v>
       </c>
       <c r="C121" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D121" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E121" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F121" s="37" t="s">
-        <v>286</v>
+        <v>386</v>
       </c>
       <c r="G121" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H121" s="11" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="I121" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J121" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>0.6</v>
+        <v>10</v>
       </c>
       <c r="K121" s="11">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L121" s="18"/>
-      <c r="M121" s="18">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="N121" s="18">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="O121" s="18">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="P121" s="18">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="Q121" s="18">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="R121" s="18">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="S121" s="18">
-        <v>-1.4999999999999999E-2</v>
-      </c>
+      <c r="M121" s="18"/>
+      <c r="N121" s="18"/>
+      <c r="O121" s="19"/>
+      <c r="P121" s="18"/>
+      <c r="Q121" s="18"/>
+      <c r="R121" s="18"/>
+      <c r="S121" s="19"/>
       <c r="T121" s="18">
-        <v>1.4999999999999999E-2</v>
+        <v>0.25</v>
       </c>
       <c r="U121" s="18"/>
-      <c r="V121" s="18">
-        <v>1.4999999999999999E-2</v>
-      </c>
+      <c r="V121" s="18"/>
       <c r="W121" s="19"/>
       <c r="X121" s="20"/>
       <c r="Y121" s="20"/>
@@ -19473,14 +19453,14 @@
       <c r="AJ121" s="20"/>
       <c r="AK121" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="AL121" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="122" spans="1:38">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:38" ht="28">
       <c r="A122" s="4" t="s">
         <v>66</v>
       </c>
@@ -19488,7 +19468,7 @@
         <v>67</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="D122" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -19498,40 +19478,54 @@
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F122" s="11" t="s">
-        <v>206</v>
+      <c r="F122" s="37" t="s">
+        <v>286</v>
       </c>
       <c r="G122" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H122" s="11" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I122" s="11">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J122" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>3.5999999999999996</v>
-      </c>
-      <c r="K122" s="11"/>
+        <v>0.6</v>
+      </c>
+      <c r="K122" s="11">
+        <v>2</v>
+      </c>
       <c r="L122" s="18"/>
-      <c r="M122" s="18"/>
-      <c r="N122" s="18"/>
-      <c r="O122" s="19"/>
-      <c r="P122" s="18"/>
-      <c r="Q122" s="19">
-        <v>-0.1</v>
-      </c>
-      <c r="R122" s="18"/>
-      <c r="S122" s="19">
-        <v>0.1</v>
-      </c>
-      <c r="T122" s="18"/>
-      <c r="U122" s="19">
-        <v>0.08</v>
-      </c>
-      <c r="V122" s="18"/>
+      <c r="M122" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N122" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="O122" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="P122" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="Q122" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="R122" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="S122" s="18">
+        <v>-1.4999999999999999E-2</v>
+      </c>
+      <c r="T122" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="U122" s="18"/>
+      <c r="V122" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
       <c r="W122" s="19"/>
       <c r="X122" s="20"/>
       <c r="Y122" s="20"/>
@@ -19548,74 +19542,64 @@
       <c r="AJ122" s="20"/>
       <c r="AK122" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="AL122" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>7.1999999999999993</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" spans="1:38">
       <c r="A123" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>125</v>
+        <v>5</v>
       </c>
       <c r="D123" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E123" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F123" s="11" t="s">
-        <v>298</v>
+        <v>206</v>
       </c>
       <c r="G123" s="11" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="H123" s="11" t="s">
         <v>300</v>
       </c>
       <c r="I123" s="11">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J123" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>0.49999999999999994</v>
-      </c>
-      <c r="K123" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="L123" s="18">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="M123" s="18">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="N123" s="18">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="O123" s="18">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="P123" s="18">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="Q123" s="18"/>
-      <c r="R123" s="18">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="S123" s="18"/>
-      <c r="T123" s="18">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="U123" s="18"/>
+        <v>3.5999999999999996</v>
+      </c>
+      <c r="K123" s="11"/>
+      <c r="L123" s="18"/>
+      <c r="M123" s="18"/>
+      <c r="N123" s="18"/>
+      <c r="O123" s="19"/>
+      <c r="P123" s="18"/>
+      <c r="Q123" s="19">
+        <v>-0.1</v>
+      </c>
+      <c r="R123" s="18"/>
+      <c r="S123" s="19">
+        <v>0.1</v>
+      </c>
+      <c r="T123" s="18"/>
+      <c r="U123" s="19">
+        <v>0.08</v>
+      </c>
       <c r="V123" s="18"/>
       <c r="W123" s="19"/>
       <c r="X123" s="20"/>
@@ -19633,11 +19617,11 @@
       <c r="AJ123" s="20"/>
       <c r="AK123" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>8.7499999999999994E-2</v>
+        <v>0.18</v>
       </c>
       <c r="AL123" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>3.5</v>
+        <v>7.1999999999999993</v>
       </c>
     </row>
     <row r="124" spans="1:38">
@@ -19647,7 +19631,9 @@
       <c r="B124" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C124" s="11"/>
+      <c r="C124" s="11" t="s">
+        <v>125</v>
+      </c>
       <c r="D124" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
@@ -19657,10 +19643,10 @@
         <v>10</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G124" s="11" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="H124" s="11" t="s">
         <v>300</v>
@@ -19670,24 +19656,36 @@
       </c>
       <c r="J124" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>4</v>
+        <v>0.49999999999999994</v>
       </c>
       <c r="K124" s="11">
         <v>0.5</v>
       </c>
-      <c r="L124" s="18"/>
-      <c r="M124" s="18"/>
-      <c r="N124" s="18"/>
-      <c r="O124" s="19"/>
-      <c r="P124" s="18"/>
+      <c r="L124" s="18">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="M124" s="18">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="N124" s="18">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="O124" s="18">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="P124" s="18">
+        <v>1.2500000000000001E-2</v>
+      </c>
       <c r="Q124" s="18"/>
-      <c r="R124" s="18"/>
-      <c r="S124" s="19"/>
-      <c r="T124" s="18"/>
+      <c r="R124" s="18">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="S124" s="18"/>
+      <c r="T124" s="18">
+        <v>1.2500000000000001E-2</v>
+      </c>
       <c r="U124" s="18"/>
-      <c r="V124" s="18">
-        <v>0.1</v>
-      </c>
+      <c r="V124" s="18"/>
       <c r="W124" s="19"/>
       <c r="X124" s="20"/>
       <c r="Y124" s="20"/>
@@ -19704,11 +19702,11 @@
       <c r="AJ124" s="20"/>
       <c r="AK124" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.1</v>
+        <v>8.7499999999999994E-2</v>
       </c>
       <c r="AL124" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="125" spans="1:38">
@@ -19718,9 +19716,7 @@
       <c r="B125" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C125" s="11" t="s">
-        <v>4</v>
-      </c>
+      <c r="C125" s="11"/>
       <c r="D125" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>100</v>
@@ -19730,35 +19726,37 @@
         <v>10</v>
       </c>
       <c r="F125" s="11" t="s">
-        <v>328</v>
+        <v>297</v>
       </c>
       <c r="G125" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H125" s="11" t="s">
-        <v>346</v>
+        <v>300</v>
       </c>
       <c r="I125" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J125" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>14</v>
-      </c>
-      <c r="K125" s="11"/>
+        <v>4</v>
+      </c>
+      <c r="K125" s="11">
+        <v>0.5</v>
+      </c>
       <c r="L125" s="18"/>
       <c r="M125" s="18"/>
       <c r="N125" s="18"/>
       <c r="O125" s="19"/>
       <c r="P125" s="18"/>
-      <c r="Q125" s="18">
-        <v>0.35</v>
-      </c>
+      <c r="Q125" s="18"/>
       <c r="R125" s="18"/>
       <c r="S125" s="19"/>
       <c r="T125" s="18"/>
       <c r="U125" s="18"/>
-      <c r="V125" s="18"/>
+      <c r="V125" s="18">
+        <v>0.1</v>
+      </c>
       <c r="W125" s="19"/>
       <c r="X125" s="20"/>
       <c r="Y125" s="20"/>
@@ -19775,11 +19773,11 @@
       <c r="AJ125" s="20"/>
       <c r="AK125" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="AL125" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>14</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="126" spans="1:38">
@@ -19790,7 +19788,7 @@
         <v>70</v>
       </c>
       <c r="C126" s="11" t="s">
-        <v>123</v>
+        <v>4</v>
       </c>
       <c r="D126" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -19801,20 +19799,20 @@
         <v>10</v>
       </c>
       <c r="F126" s="11" t="s">
-        <v>201</v>
+        <v>328</v>
       </c>
       <c r="G126" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H126" s="11" t="s">
-        <v>300</v>
+        <v>346</v>
       </c>
       <c r="I126" s="11">
         <v>4</v>
       </c>
       <c r="J126" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K126" s="11"/>
       <c r="L126" s="18"/>
@@ -19822,14 +19820,14 @@
       <c r="N126" s="18"/>
       <c r="O126" s="19"/>
       <c r="P126" s="18"/>
-      <c r="Q126" s="18"/>
+      <c r="Q126" s="18">
+        <v>0.35</v>
+      </c>
       <c r="R126" s="18"/>
       <c r="S126" s="19"/>
       <c r="T126" s="18"/>
       <c r="U126" s="18"/>
-      <c r="V126" s="18">
-        <v>0.55000000000000004</v>
-      </c>
+      <c r="V126" s="18"/>
       <c r="W126" s="19"/>
       <c r="X126" s="20"/>
       <c r="Y126" s="20"/>
@@ -19846,80 +19844,60 @@
       <c r="AJ126" s="20"/>
       <c r="AK126" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.55000000000000004</v>
+        <v>0.35</v>
       </c>
       <c r="AL126" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="127" spans="1:38" ht="28">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="127" spans="1:38">
       <c r="A127" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C127" s="11" t="s">
-        <v>4</v>
+        <v>123</v>
       </c>
       <c r="D127" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E127" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F127" s="37" t="s">
-        <v>362</v>
+      <c r="F127" s="11" t="s">
+        <v>201</v>
       </c>
       <c r="G127" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H127" s="11" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I127" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J127" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>0.39999999999999991</v>
-      </c>
-      <c r="K127" s="11">
-        <v>0.5</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="K127" s="11"/>
       <c r="L127" s="18"/>
-      <c r="M127" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="N127" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="O127" s="19">
-        <v>0.01</v>
-      </c>
-      <c r="P127" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="Q127" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="R127" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="S127" s="19">
-        <v>0.01</v>
-      </c>
-      <c r="T127" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="U127" s="18">
-        <v>0.01</v>
-      </c>
+      <c r="M127" s="18"/>
+      <c r="N127" s="18"/>
+      <c r="O127" s="19"/>
+      <c r="P127" s="18"/>
+      <c r="Q127" s="18"/>
+      <c r="R127" s="18"/>
+      <c r="S127" s="19"/>
+      <c r="T127" s="18"/>
+      <c r="U127" s="18"/>
       <c r="V127" s="18">
-        <v>0.01</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="W127" s="19"/>
       <c r="X127" s="20"/>
@@ -19937,14 +19915,14 @@
       <c r="AJ127" s="20"/>
       <c r="AK127" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>9.9999999999999992E-2</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AL127" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="128" spans="1:38">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="128" spans="1:38" ht="28">
       <c r="A128" s="4" t="s">
         <v>71</v>
       </c>
@@ -19952,7 +19930,7 @@
         <v>72</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D128" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -19962,42 +19940,56 @@
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F128" s="11" t="s">
-        <v>206</v>
+      <c r="F128" s="37" t="s">
+        <v>362</v>
       </c>
       <c r="G128" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H128" s="11" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="I128" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J128" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>4</v>
-      </c>
-      <c r="K128" s="11"/>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="K128" s="11">
+        <v>0.5</v>
+      </c>
       <c r="L128" s="18"/>
-      <c r="M128" s="18"/>
+      <c r="M128" s="18">
+        <v>0.01</v>
+      </c>
       <c r="N128" s="18">
-        <v>0.1</v>
-      </c>
-      <c r="O128" s="19"/>
+        <v>0.01</v>
+      </c>
+      <c r="O128" s="19">
+        <v>0.01</v>
+      </c>
       <c r="P128" s="18">
-        <v>0.1</v>
-      </c>
-      <c r="Q128" s="18"/>
+        <v>0.01</v>
+      </c>
+      <c r="Q128" s="18">
+        <v>0.01</v>
+      </c>
       <c r="R128" s="18">
-        <v>0.1</v>
-      </c>
-      <c r="S128" s="19"/>
-      <c r="T128" s="18"/>
+        <v>0.01</v>
+      </c>
+      <c r="S128" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="T128" s="18">
+        <v>0.01</v>
+      </c>
       <c r="U128" s="18">
-        <v>0.1</v>
-      </c>
-      <c r="V128" s="18"/>
+        <v>0.01</v>
+      </c>
+      <c r="V128" s="18">
+        <v>0.01</v>
+      </c>
       <c r="W128" s="19"/>
       <c r="X128" s="20"/>
       <c r="Y128" s="20"/>
@@ -20014,66 +20006,72 @@
       <c r="AJ128" s="20"/>
       <c r="AK128" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.4</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="AL128" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:38">
-      <c r="A129" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B129" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C129" s="12" t="s">
+      <c r="A129" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C129" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D129" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E129" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F129" s="12" t="s">
+      <c r="F129" s="11" t="s">
         <v>206</v>
       </c>
       <c r="G129" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H129" s="11" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I129" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J129" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K129" s="11"/>
       <c r="L129" s="18"/>
       <c r="M129" s="18"/>
-      <c r="N129" s="18"/>
+      <c r="N129" s="18">
+        <v>0.1</v>
+      </c>
       <c r="O129" s="19"/>
-      <c r="P129" s="18"/>
+      <c r="P129" s="18">
+        <v>0.1</v>
+      </c>
       <c r="Q129" s="18"/>
-      <c r="R129" s="18"/>
+      <c r="R129" s="18">
+        <v>0.1</v>
+      </c>
       <c r="S129" s="19"/>
       <c r="T129" s="18"/>
-      <c r="U129" s="18"/>
+      <c r="U129" s="18">
+        <v>0.1</v>
+      </c>
       <c r="V129" s="18"/>
       <c r="W129" s="19"/>
       <c r="X129" s="20"/>
       <c r="Y129" s="20"/>
       <c r="Z129" s="20"/>
-      <c r="AA129" s="20">
-        <v>0.2</v>
-      </c>
+      <c r="AA129" s="20"/>
       <c r="AB129" s="20"/>
       <c r="AC129" s="20"/>
       <c r="AD129" s="20"/>
@@ -20085,26 +20083,26 @@
       <c r="AJ129" s="20"/>
       <c r="AK129" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AL129" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="130" spans="1:38">
       <c r="A130" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C130" s="12" t="s">
         <v>5</v>
       </c>
       <c r="D130" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E130" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -20117,14 +20115,14 @@
         <v>229</v>
       </c>
       <c r="H130" s="11" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="I130" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J130" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K130" s="11"/>
       <c r="L130" s="18"/>
@@ -20142,64 +20140,62 @@
       <c r="X130" s="20"/>
       <c r="Y130" s="20"/>
       <c r="Z130" s="20"/>
-      <c r="AA130" s="20"/>
+      <c r="AA130" s="20">
+        <v>0.2</v>
+      </c>
       <c r="AB130" s="20"/>
       <c r="AC130" s="20"/>
       <c r="AD130" s="20"/>
       <c r="AE130" s="20"/>
-      <c r="AF130" s="20">
-        <v>0.3</v>
-      </c>
+      <c r="AF130" s="20"/>
       <c r="AG130" s="20"/>
       <c r="AH130" s="20"/>
       <c r="AI130" s="20"/>
       <c r="AJ130" s="20"/>
       <c r="AK130" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AL130" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="131" spans="1:38" ht="28">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:38">
       <c r="A131" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C131" s="11" t="s">
-        <v>125</v>
+        <v>111</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>5</v>
       </c>
       <c r="D131" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E131" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F131" s="37" t="s">
-        <v>287</v>
+      <c r="F131" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="G131" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H131" s="11" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I131" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J131" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>0.79999999999999982</v>
-      </c>
-      <c r="K131" s="11">
-        <v>0.5</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="K131" s="11"/>
       <c r="L131" s="18"/>
       <c r="M131" s="18"/>
       <c r="N131" s="18"/>
@@ -20213,56 +20209,38 @@
       <c r="V131" s="18"/>
       <c r="W131" s="19"/>
       <c r="X131" s="20"/>
-      <c r="Y131" s="20">
-        <v>0.02</v>
-      </c>
-      <c r="Z131" s="20">
-        <v>0.02</v>
-      </c>
-      <c r="AA131" s="20">
-        <v>0.02</v>
-      </c>
-      <c r="AB131" s="20">
-        <v>0.02</v>
-      </c>
-      <c r="AC131" s="20">
-        <v>0.02</v>
-      </c>
-      <c r="AD131" s="20">
-        <v>0.02</v>
-      </c>
-      <c r="AE131" s="20">
-        <v>0.02</v>
-      </c>
+      <c r="Y131" s="20"/>
+      <c r="Z131" s="20"/>
+      <c r="AA131" s="20"/>
+      <c r="AB131" s="20"/>
+      <c r="AC131" s="20"/>
+      <c r="AD131" s="20"/>
+      <c r="AE131" s="20"/>
       <c r="AF131" s="20">
-        <v>0.02</v>
-      </c>
-      <c r="AG131" s="20">
-        <v>0.02</v>
-      </c>
-      <c r="AH131" s="20">
-        <v>0.02</v>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="AG131" s="20"/>
+      <c r="AH131" s="20"/>
       <c r="AI131" s="20"/>
       <c r="AJ131" s="20"/>
       <c r="AK131" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.19999999999999998</v>
+        <v>0.3</v>
       </c>
       <c r="AL131" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="132" spans="1:38">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="132" spans="1:38" ht="28">
       <c r="A132" s="3" t="s">
         <v>192</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C132" s="12" t="s">
-        <v>5</v>
+      <c r="C132" s="11" t="s">
+        <v>125</v>
       </c>
       <c r="D132" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -20272,23 +20250,25 @@
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F132" s="12" t="s">
-        <v>206</v>
+      <c r="F132" s="37" t="s">
+        <v>287</v>
       </c>
       <c r="G132" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H132" s="11" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="I132" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J132" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>4</v>
-      </c>
-      <c r="K132" s="11"/>
+        <v>0.79999999999999982</v>
+      </c>
+      <c r="K132" s="11">
+        <v>0.5</v>
+      </c>
       <c r="L132" s="18"/>
       <c r="M132" s="18"/>
       <c r="N132" s="18"/>
@@ -20302,27 +20282,45 @@
       <c r="V132" s="18"/>
       <c r="W132" s="19"/>
       <c r="X132" s="20"/>
-      <c r="Y132" s="20"/>
-      <c r="Z132" s="20"/>
-      <c r="AA132" s="20"/>
-      <c r="AB132" s="20"/>
-      <c r="AC132" s="20"/>
+      <c r="Y132" s="20">
+        <v>0.02</v>
+      </c>
+      <c r="Z132" s="20">
+        <v>0.02</v>
+      </c>
+      <c r="AA132" s="20">
+        <v>0.02</v>
+      </c>
+      <c r="AB132" s="20">
+        <v>0.02</v>
+      </c>
+      <c r="AC132" s="20">
+        <v>0.02</v>
+      </c>
       <c r="AD132" s="20">
-        <v>0.1</v>
-      </c>
-      <c r="AE132" s="20"/>
-      <c r="AF132" s="20"/>
-      <c r="AG132" s="20"/>
-      <c r="AH132" s="20"/>
+        <v>0.02</v>
+      </c>
+      <c r="AE132" s="20">
+        <v>0.02</v>
+      </c>
+      <c r="AF132" s="20">
+        <v>0.02</v>
+      </c>
+      <c r="AG132" s="20">
+        <v>0.02</v>
+      </c>
+      <c r="AH132" s="20">
+        <v>0.02</v>
+      </c>
       <c r="AI132" s="20"/>
       <c r="AJ132" s="20"/>
       <c r="AK132" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.1</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="AL132" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:38">
@@ -20333,7 +20331,7 @@
         <v>112</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="D133" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -20344,20 +20342,20 @@
         <v>10</v>
       </c>
       <c r="F133" s="12" t="s">
-        <v>337</v>
+        <v>206</v>
       </c>
       <c r="G133" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H133" s="11" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="I133" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J133" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K133" s="11"/>
       <c r="L133" s="18"/>
@@ -20378,61 +20376,59 @@
       <c r="AA133" s="20"/>
       <c r="AB133" s="20"/>
       <c r="AC133" s="20"/>
-      <c r="AD133" s="20"/>
+      <c r="AD133" s="20">
+        <v>0.1</v>
+      </c>
       <c r="AE133" s="20"/>
       <c r="AF133" s="20"/>
       <c r="AG133" s="20"/>
-      <c r="AH133" s="20">
-        <v>0.3</v>
-      </c>
+      <c r="AH133" s="20"/>
       <c r="AI133" s="20"/>
       <c r="AJ133" s="20"/>
       <c r="AK133" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="AL133" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="134" spans="1:38" ht="28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:38">
       <c r="A134" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C134" s="11" t="s">
-        <v>125</v>
+        <v>112</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>121</v>
       </c>
       <c r="D134" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E134" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F134" s="37" t="s">
-        <v>288</v>
+      <c r="F134" s="12" t="s">
+        <v>337</v>
       </c>
       <c r="G134" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H134" s="11" t="s">
-        <v>354</v>
+        <v>310</v>
       </c>
       <c r="I134" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J134" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>0.8</v>
-      </c>
-      <c r="K134" s="11">
-        <v>0.5</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="K134" s="11"/>
       <c r="L134" s="18"/>
       <c r="M134" s="18"/>
       <c r="N134" s="18"/>
@@ -20446,35 +20442,27 @@
       <c r="V134" s="18"/>
       <c r="W134" s="19"/>
       <c r="X134" s="20"/>
-      <c r="Y134" s="20">
-        <v>0.02</v>
-      </c>
-      <c r="Z134" s="20">
-        <v>0.02</v>
-      </c>
-      <c r="AA134" s="20">
-        <v>0.02</v>
-      </c>
-      <c r="AB134" s="20">
-        <v>0.02</v>
-      </c>
-      <c r="AC134" s="20">
-        <v>0.02</v>
-      </c>
+      <c r="Y134" s="20"/>
+      <c r="Z134" s="20"/>
+      <c r="AA134" s="20"/>
+      <c r="AB134" s="20"/>
+      <c r="AC134" s="20"/>
       <c r="AD134" s="20"/>
       <c r="AE134" s="20"/>
       <c r="AF134" s="20"/>
       <c r="AG134" s="20"/>
-      <c r="AH134" s="20"/>
+      <c r="AH134" s="20">
+        <v>0.3</v>
+      </c>
       <c r="AI134" s="20"/>
       <c r="AJ134" s="20"/>
       <c r="AK134" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="AL134" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>2.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135" spans="1:38" ht="28">
@@ -20496,7 +20484,7 @@
         <v>10</v>
       </c>
       <c r="F135" s="37" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G135" s="11" t="s">
         <v>229</v>
@@ -20527,26 +20515,26 @@
       <c r="V135" s="18"/>
       <c r="W135" s="19"/>
       <c r="X135" s="20"/>
-      <c r="Y135" s="20"/>
-      <c r="Z135" s="20"/>
-      <c r="AA135" s="20"/>
-      <c r="AB135" s="20"/>
-      <c r="AC135" s="20"/>
-      <c r="AD135" s="20">
+      <c r="Y135" s="20">
         <v>0.02</v>
       </c>
-      <c r="AE135" s="20">
+      <c r="Z135" s="20">
         <v>0.02</v>
       </c>
-      <c r="AF135" s="20">
+      <c r="AA135" s="20">
         <v>0.02</v>
       </c>
-      <c r="AG135" s="20">
+      <c r="AB135" s="20">
         <v>0.02</v>
       </c>
-      <c r="AH135" s="20">
+      <c r="AC135" s="20">
         <v>0.02</v>
       </c>
+      <c r="AD135" s="20"/>
+      <c r="AE135" s="20"/>
+      <c r="AF135" s="20"/>
+      <c r="AG135" s="20"/>
+      <c r="AH135" s="20"/>
       <c r="AI135" s="20"/>
       <c r="AJ135" s="20"/>
       <c r="AK135" s="27">
@@ -20558,41 +20546,43 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="136" spans="1:38">
+    <row r="136" spans="1:38" ht="28">
       <c r="A136" s="3" t="s">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C136" s="12" t="s">
-        <v>5</v>
+        <v>113</v>
+      </c>
+      <c r="C136" s="11" t="s">
+        <v>125</v>
       </c>
       <c r="D136" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="E136" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F136" s="12" t="s">
-        <v>268</v>
+      <c r="F136" s="37" t="s">
+        <v>289</v>
       </c>
       <c r="G136" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H136" s="11" t="s">
-        <v>300</v>
+        <v>354</v>
       </c>
       <c r="I136" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J136" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>16</v>
-      </c>
-      <c r="K136" s="11"/>
+        <v>0.8</v>
+      </c>
+      <c r="K136" s="11">
+        <v>0.5</v>
+      </c>
       <c r="L136" s="18"/>
       <c r="M136" s="18"/>
       <c r="N136" s="18"/>
@@ -20612,21 +20602,29 @@
       <c r="AB136" s="20"/>
       <c r="AC136" s="20"/>
       <c r="AD136" s="20">
-        <v>0.4</v>
-      </c>
-      <c r="AE136" s="20"/>
-      <c r="AF136" s="20"/>
-      <c r="AG136" s="20"/>
-      <c r="AH136" s="20"/>
+        <v>0.02</v>
+      </c>
+      <c r="AE136" s="20">
+        <v>0.02</v>
+      </c>
+      <c r="AF136" s="20">
+        <v>0.02</v>
+      </c>
+      <c r="AG136" s="20">
+        <v>0.02</v>
+      </c>
+      <c r="AH136" s="20">
+        <v>0.02</v>
+      </c>
       <c r="AI136" s="20"/>
       <c r="AJ136" s="20"/>
       <c r="AK136" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="AL136" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>16</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="137" spans="1:38">
@@ -20637,7 +20635,7 @@
         <v>115</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>123</v>
+        <v>5</v>
       </c>
       <c r="D137" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -20648,7 +20646,7 @@
         <v>10</v>
       </c>
       <c r="F137" s="12" t="s">
-        <v>201</v>
+        <v>268</v>
       </c>
       <c r="G137" s="11" t="s">
         <v>229</v>
@@ -20661,7 +20659,7 @@
       </c>
       <c r="J137" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K137" s="11"/>
       <c r="L137" s="18"/>
@@ -20682,22 +20680,22 @@
       <c r="AA137" s="20"/>
       <c r="AB137" s="20"/>
       <c r="AC137" s="20"/>
-      <c r="AD137" s="20"/>
+      <c r="AD137" s="20">
+        <v>0.4</v>
+      </c>
       <c r="AE137" s="20"/>
       <c r="AF137" s="20"/>
-      <c r="AG137" s="20">
-        <v>0.55000000000000004</v>
-      </c>
+      <c r="AG137" s="20"/>
       <c r="AH137" s="20"/>
       <c r="AI137" s="20"/>
       <c r="AJ137" s="20"/>
       <c r="AK137" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.55000000000000004</v>
+        <v>0.4</v>
       </c>
       <c r="AL137" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138" spans="1:38">
@@ -20708,7 +20706,7 @@
         <v>115</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D138" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -20719,7 +20717,7 @@
         <v>10</v>
       </c>
       <c r="F138" s="12" t="s">
-        <v>259</v>
+        <v>201</v>
       </c>
       <c r="G138" s="11" t="s">
         <v>229</v>
@@ -20728,15 +20726,13 @@
         <v>300</v>
       </c>
       <c r="I138" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J138" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>2</v>
-      </c>
-      <c r="K138" s="11">
-        <v>0.5</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="K138" s="11"/>
       <c r="L138" s="18"/>
       <c r="M138" s="18"/>
       <c r="N138" s="18"/>
@@ -20758,54 +20754,54 @@
       <c r="AD138" s="20"/>
       <c r="AE138" s="20"/>
       <c r="AF138" s="20"/>
-      <c r="AG138" s="20"/>
-      <c r="AH138" s="20">
-        <v>0.05</v>
-      </c>
+      <c r="AG138" s="20">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AH138" s="20"/>
       <c r="AI138" s="20"/>
       <c r="AJ138" s="20"/>
       <c r="AK138" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.05</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AL138" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="139" spans="1:38" ht="28">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="139" spans="1:38">
       <c r="A139" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B139" s="28" t="s">
-        <v>240</v>
+        <v>114</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>4</v>
+        <v>122</v>
       </c>
       <c r="D139" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E139" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F139" s="45" t="s">
-        <v>287</v>
+      <c r="F139" s="12" t="s">
+        <v>259</v>
       </c>
       <c r="G139" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H139" s="11" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I139" s="11">
         <v>1</v>
       </c>
       <c r="J139" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>0.39999999999999991</v>
+        <v>2</v>
       </c>
       <c r="K139" s="11">
         <v>0.5</v>
@@ -20822,51 +20818,31 @@
       <c r="U139" s="18"/>
       <c r="V139" s="18"/>
       <c r="W139" s="19"/>
-      <c r="X139" s="20">
-        <v>-0.01</v>
-      </c>
-      <c r="Y139" s="20">
-        <v>0.01</v>
-      </c>
-      <c r="Z139" s="20">
-        <v>0.01</v>
-      </c>
-      <c r="AA139" s="20">
-        <v>0.01</v>
-      </c>
-      <c r="AB139" s="20">
-        <v>0.01</v>
-      </c>
-      <c r="AC139" s="20">
-        <v>0.01</v>
-      </c>
-      <c r="AD139" s="20">
-        <v>0.01</v>
-      </c>
-      <c r="AE139" s="20">
-        <v>0.01</v>
-      </c>
-      <c r="AF139" s="20">
-        <v>0.01</v>
-      </c>
-      <c r="AG139" s="20">
-        <v>0.01</v>
-      </c>
+      <c r="X139" s="20"/>
+      <c r="Y139" s="20"/>
+      <c r="Z139" s="20"/>
+      <c r="AA139" s="20"/>
+      <c r="AB139" s="20"/>
+      <c r="AC139" s="20"/>
+      <c r="AD139" s="20"/>
+      <c r="AE139" s="20"/>
+      <c r="AF139" s="20"/>
+      <c r="AG139" s="20"/>
       <c r="AH139" s="20">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="AI139" s="20"/>
       <c r="AJ139" s="20"/>
       <c r="AK139" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>9.9999999999999992E-2</v>
+        <v>0.05</v>
       </c>
       <c r="AL139" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="140" spans="1:38">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:38" ht="28">
       <c r="A140" s="3" t="s">
         <v>239</v>
       </c>
@@ -20874,7 +20850,7 @@
         <v>240</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D140" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -20884,23 +20860,25 @@
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F140" s="12" t="s">
-        <v>206</v>
+      <c r="F140" s="45" t="s">
+        <v>287</v>
       </c>
       <c r="G140" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H140" s="11" t="s">
-        <v>346</v>
+        <v>306</v>
       </c>
       <c r="I140" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J140" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>8</v>
-      </c>
-      <c r="K140" s="11"/>
+        <v>0.39999999999999991</v>
+      </c>
+      <c r="K140" s="11">
+        <v>0.5</v>
+      </c>
       <c r="L140" s="18"/>
       <c r="M140" s="18"/>
       <c r="N140" s="18"/>
@@ -20913,67 +20891,83 @@
       <c r="U140" s="18"/>
       <c r="V140" s="18"/>
       <c r="W140" s="19"/>
-      <c r="X140" s="20"/>
-      <c r="Y140" s="20"/>
-      <c r="Z140" s="20"/>
-      <c r="AA140" s="20"/>
-      <c r="AB140" s="20"/>
+      <c r="X140" s="20">
+        <v>-0.01</v>
+      </c>
+      <c r="Y140" s="20">
+        <v>0.01</v>
+      </c>
+      <c r="Z140" s="20">
+        <v>0.01</v>
+      </c>
+      <c r="AA140" s="20">
+        <v>0.01</v>
+      </c>
+      <c r="AB140" s="20">
+        <v>0.01</v>
+      </c>
       <c r="AC140" s="20">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="AD140" s="20">
-        <v>-0.2</v>
-      </c>
-      <c r="AE140" s="20"/>
-      <c r="AF140" s="20"/>
-      <c r="AG140" s="20"/>
+        <v>0.01</v>
+      </c>
+      <c r="AE140" s="20">
+        <v>0.01</v>
+      </c>
+      <c r="AF140" s="20">
+        <v>0.01</v>
+      </c>
+      <c r="AG140" s="20">
+        <v>0.01</v>
+      </c>
       <c r="AH140" s="20">
-        <v>0.2</v>
+        <v>0.01</v>
       </c>
       <c r="AI140" s="20"/>
       <c r="AJ140" s="20"/>
       <c r="AK140" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.4</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="AL140" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="141" spans="1:38" ht="28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:38">
       <c r="A141" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C141" s="11" t="s">
-        <v>125</v>
+        <v>239</v>
+      </c>
+      <c r="B141" s="28" t="s">
+        <v>240</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>5</v>
       </c>
       <c r="D141" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E141" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F141" s="37" t="s">
-        <v>290</v>
+      <c r="F141" s="12" t="s">
+        <v>206</v>
       </c>
       <c r="G141" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H141" s="11" t="s">
-        <v>300</v>
+        <v>346</v>
       </c>
       <c r="I141" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J141" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="K141" s="11"/>
       <c r="L141" s="18"/>
@@ -20989,35 +20983,31 @@
       <c r="V141" s="18"/>
       <c r="W141" s="19"/>
       <c r="X141" s="20"/>
-      <c r="Y141" s="20">
-        <v>0.03</v>
-      </c>
-      <c r="Z141" s="20">
-        <v>0.03</v>
-      </c>
-      <c r="AA141" s="20">
-        <v>0.03</v>
-      </c>
-      <c r="AB141" s="20">
-        <v>0.03</v>
-      </c>
+      <c r="Y141" s="20"/>
+      <c r="Z141" s="20"/>
+      <c r="AA141" s="20"/>
+      <c r="AB141" s="20"/>
       <c r="AC141" s="20">
-        <v>0.03</v>
-      </c>
-      <c r="AD141" s="20"/>
+        <v>0.2</v>
+      </c>
+      <c r="AD141" s="20">
+        <v>-0.2</v>
+      </c>
       <c r="AE141" s="20"/>
       <c r="AF141" s="20"/>
       <c r="AG141" s="20"/>
-      <c r="AH141" s="20"/>
+      <c r="AH141" s="20">
+        <v>0.2</v>
+      </c>
       <c r="AI141" s="20"/>
       <c r="AJ141" s="20"/>
       <c r="AK141" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="AL141" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="142" spans="1:38" ht="28">
@@ -21039,7 +21029,7 @@
         <v>10</v>
       </c>
       <c r="F142" s="37" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G142" s="11" t="s">
         <v>229</v>
@@ -21068,26 +21058,26 @@
       <c r="V142" s="18"/>
       <c r="W142" s="19"/>
       <c r="X142" s="20"/>
-      <c r="Y142" s="20"/>
-      <c r="Z142" s="20"/>
-      <c r="AA142" s="20"/>
-      <c r="AB142" s="20"/>
-      <c r="AC142" s="20"/>
-      <c r="AD142" s="20">
+      <c r="Y142" s="20">
         <v>0.03</v>
       </c>
-      <c r="AE142" s="20">
+      <c r="Z142" s="20">
         <v>0.03</v>
       </c>
-      <c r="AF142" s="20">
+      <c r="AA142" s="20">
         <v>0.03</v>
       </c>
-      <c r="AG142" s="20">
+      <c r="AB142" s="20">
         <v>0.03</v>
       </c>
-      <c r="AH142" s="20">
+      <c r="AC142" s="20">
         <v>0.03</v>
       </c>
+      <c r="AD142" s="20"/>
+      <c r="AE142" s="20"/>
+      <c r="AF142" s="20"/>
+      <c r="AG142" s="20"/>
+      <c r="AH142" s="20"/>
       <c r="AI142" s="20"/>
       <c r="AJ142" s="20"/>
       <c r="AK142" s="27">
@@ -21099,26 +21089,26 @@
         <v>6</v>
       </c>
     </row>
-    <row r="143" spans="1:38">
+    <row r="143" spans="1:38" ht="28">
       <c r="A143" s="3" t="s">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C143" s="12" t="s">
-        <v>5</v>
+        <v>117</v>
+      </c>
+      <c r="C143" s="11" t="s">
+        <v>125</v>
       </c>
       <c r="D143" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E143" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F143" s="12" t="s">
-        <v>385</v>
+      <c r="F143" s="37" t="s">
+        <v>291</v>
       </c>
       <c r="G143" s="11" t="s">
         <v>229</v>
@@ -21127,11 +21117,11 @@
         <v>300</v>
       </c>
       <c r="I143" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J143" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>20</v>
+        <v>1.2</v>
       </c>
       <c r="K143" s="11"/>
       <c r="L143" s="18"/>
@@ -21152,44 +21142,52 @@
       <c r="AA143" s="20"/>
       <c r="AB143" s="20"/>
       <c r="AC143" s="20"/>
-      <c r="AD143" s="20"/>
-      <c r="AE143" s="20"/>
-      <c r="AF143" s="20"/>
-      <c r="AG143" s="20"/>
-      <c r="AH143" s="20"/>
-      <c r="AI143" s="20">
-        <v>0.5</v>
-      </c>
+      <c r="AD143" s="20">
+        <v>0.03</v>
+      </c>
+      <c r="AE143" s="20">
+        <v>0.03</v>
+      </c>
+      <c r="AF143" s="20">
+        <v>0.03</v>
+      </c>
+      <c r="AG143" s="20">
+        <v>0.03</v>
+      </c>
+      <c r="AH143" s="20">
+        <v>0.03</v>
+      </c>
+      <c r="AI143" s="20"/>
       <c r="AJ143" s="20"/>
       <c r="AK143" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AL143" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144" spans="1:38">
       <c r="A144" s="3" t="s">
-        <v>194</v>
+        <v>68</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="C144" s="12" t="s">
         <v>5</v>
       </c>
       <c r="D144" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E144" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F144" s="12" t="s">
-        <v>277</v>
+        <v>385</v>
       </c>
       <c r="G144" s="11" t="s">
         <v>229</v>
@@ -21202,7 +21200,7 @@
       </c>
       <c r="J144" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K144" s="11"/>
       <c r="L144" s="18"/>
@@ -21220,27 +21218,25 @@
       <c r="X144" s="20"/>
       <c r="Y144" s="20"/>
       <c r="Z144" s="20"/>
-      <c r="AA144" s="20">
-        <v>0.1</v>
-      </c>
+      <c r="AA144" s="20"/>
       <c r="AB144" s="20"/>
       <c r="AC144" s="20"/>
       <c r="AD144" s="20"/>
       <c r="AE144" s="20"/>
       <c r="AF144" s="20"/>
       <c r="AG144" s="20"/>
-      <c r="AH144" s="20">
-        <v>0.1</v>
-      </c>
-      <c r="AI144" s="20"/>
+      <c r="AH144" s="20"/>
+      <c r="AI144" s="20">
+        <v>0.5</v>
+      </c>
       <c r="AJ144" s="20"/>
       <c r="AK144" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AL144" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="145" spans="1:38">
@@ -21262,7 +21258,7 @@
         <v>10</v>
       </c>
       <c r="F145" s="12" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="G145" s="11" t="s">
         <v>229</v>
@@ -21275,7 +21271,7 @@
       </c>
       <c r="J145" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K145" s="11"/>
       <c r="L145" s="18"/>
@@ -21293,16 +21289,18 @@
       <c r="X145" s="20"/>
       <c r="Y145" s="20"/>
       <c r="Z145" s="20"/>
-      <c r="AA145" s="20"/>
+      <c r="AA145" s="20">
+        <v>0.1</v>
+      </c>
       <c r="AB145" s="20"/>
       <c r="AC145" s="20"/>
       <c r="AD145" s="20"/>
-      <c r="AE145" s="20">
-        <v>0.2</v>
-      </c>
+      <c r="AE145" s="20"/>
       <c r="AF145" s="20"/>
       <c r="AG145" s="20"/>
-      <c r="AH145" s="20"/>
+      <c r="AH145" s="20">
+        <v>0.1</v>
+      </c>
       <c r="AI145" s="20"/>
       <c r="AJ145" s="20"/>
       <c r="AK145" s="27">
@@ -21316,24 +21314,24 @@
     </row>
     <row r="146" spans="1:38">
       <c r="A146" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C146" s="12" t="s">
         <v>5</v>
       </c>
       <c r="D146" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="E146" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F146" s="12" t="s">
-        <v>345</v>
+        <v>269</v>
       </c>
       <c r="G146" s="11" t="s">
         <v>229</v>
@@ -21346,7 +21344,7 @@
       </c>
       <c r="J146" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K146" s="11"/>
       <c r="L146" s="18"/>
@@ -21364,13 +21362,13 @@
       <c r="X146" s="20"/>
       <c r="Y146" s="20"/>
       <c r="Z146" s="20"/>
-      <c r="AA146" s="20">
-        <v>0.3</v>
-      </c>
+      <c r="AA146" s="20"/>
       <c r="AB146" s="20"/>
       <c r="AC146" s="20"/>
       <c r="AD146" s="20"/>
-      <c r="AE146" s="20"/>
+      <c r="AE146" s="20">
+        <v>0.2</v>
+      </c>
       <c r="AF146" s="20"/>
       <c r="AG146" s="20"/>
       <c r="AH146" s="20"/>
@@ -21378,11 +21376,11 @@
       <c r="AJ146" s="20"/>
       <c r="AK146" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AL146" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:38">
@@ -21404,7 +21402,7 @@
         <v>10</v>
       </c>
       <c r="F147" s="12" t="s">
-        <v>384</v>
+        <v>345</v>
       </c>
       <c r="G147" s="11" t="s">
         <v>229</v>
@@ -21417,7 +21415,7 @@
       </c>
       <c r="J147" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K147" s="11"/>
       <c r="L147" s="18"/>
@@ -21435,11 +21433,11 @@
       <c r="X147" s="20"/>
       <c r="Y147" s="20"/>
       <c r="Z147" s="20"/>
-      <c r="AA147" s="20"/>
+      <c r="AA147" s="20">
+        <v>0.3</v>
+      </c>
       <c r="AB147" s="20"/>
-      <c r="AC147" s="20">
-        <v>0.2</v>
-      </c>
+      <c r="AC147" s="20"/>
       <c r="AD147" s="20"/>
       <c r="AE147" s="20"/>
       <c r="AF147" s="20"/>
@@ -21449,11 +21447,11 @@
       <c r="AJ147" s="20"/>
       <c r="AK147" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AL147" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="148" spans="1:38">
@@ -21475,7 +21473,7 @@
         <v>10</v>
       </c>
       <c r="F148" s="12" t="s">
-        <v>272</v>
+        <v>384</v>
       </c>
       <c r="G148" s="11" t="s">
         <v>229</v>
@@ -21488,7 +21486,7 @@
       </c>
       <c r="J148" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K148" s="11"/>
       <c r="L148" s="18"/>
@@ -21508,23 +21506,23 @@
       <c r="Z148" s="20"/>
       <c r="AA148" s="20"/>
       <c r="AB148" s="20"/>
-      <c r="AC148" s="20"/>
+      <c r="AC148" s="20">
+        <v>0.2</v>
+      </c>
       <c r="AD148" s="20"/>
       <c r="AE148" s="20"/>
-      <c r="AF148" s="20">
-        <v>0.3</v>
-      </c>
+      <c r="AF148" s="20"/>
       <c r="AG148" s="20"/>
       <c r="AH148" s="20"/>
       <c r="AI148" s="20"/>
       <c r="AJ148" s="20"/>
       <c r="AK148" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AL148" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:38">
@@ -21546,7 +21544,7 @@
         <v>10</v>
       </c>
       <c r="F149" s="12" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G149" s="11" t="s">
         <v>229</v>
@@ -21559,7 +21557,7 @@
       </c>
       <c r="J149" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K149" s="11"/>
       <c r="L149" s="18"/>
@@ -21582,151 +21580,102 @@
       <c r="AC149" s="20"/>
       <c r="AD149" s="20"/>
       <c r="AE149" s="20"/>
-      <c r="AF149" s="20"/>
+      <c r="AF149" s="20">
+        <v>0.3</v>
+      </c>
       <c r="AG149" s="20"/>
-      <c r="AH149" s="20">
-        <v>0.2</v>
-      </c>
+      <c r="AH149" s="20"/>
       <c r="AI149" s="20"/>
       <c r="AJ149" s="20"/>
       <c r="AK149" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AL149" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:38">
       <c r="A150" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B150" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="C150" s="11" t="s">
-        <v>123</v>
+        <v>195</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>5</v>
       </c>
       <c r="D150" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E150" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>60</v>
-      </c>
-      <c r="F150" s="11" t="s">
-        <v>231</v>
+        <v>10</v>
+      </c>
+      <c r="F150" s="12" t="s">
+        <v>273</v>
       </c>
       <c r="G150" s="11" t="s">
-        <v>339</v>
+        <v>229</v>
       </c>
       <c r="H150" s="11" t="s">
-        <v>361</v>
+        <v>300</v>
       </c>
       <c r="I150" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J150" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>9.9999999999999964</v>
-      </c>
-      <c r="K150" s="11">
-        <v>20</v>
-      </c>
-      <c r="L150" s="18">
-        <f>1/24</f>
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="M150" s="18">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="N150" s="18">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="O150" s="19">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="P150" s="18">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="Q150" s="18">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="R150" s="18">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="S150" s="19">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="T150" s="18">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="U150" s="18">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="V150" s="18">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="W150" s="19">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="X150" s="20">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="Y150" s="20">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="Z150" s="20">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="AA150" s="20">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="AB150" s="20">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="AC150" s="20">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="AD150" s="20">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="AE150" s="20">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="AF150" s="20">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="AG150" s="20">
-        <v>4.1666666666666664E-2</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="K150" s="11"/>
+      <c r="L150" s="18"/>
+      <c r="M150" s="18"/>
+      <c r="N150" s="18"/>
+      <c r="O150" s="19"/>
+      <c r="P150" s="18"/>
+      <c r="Q150" s="18"/>
+      <c r="R150" s="18"/>
+      <c r="S150" s="19"/>
+      <c r="T150" s="18"/>
+      <c r="U150" s="18"/>
+      <c r="V150" s="18"/>
+      <c r="W150" s="19"/>
+      <c r="X150" s="20"/>
+      <c r="Y150" s="20"/>
+      <c r="Z150" s="20"/>
+      <c r="AA150" s="20"/>
+      <c r="AB150" s="20"/>
+      <c r="AC150" s="20"/>
+      <c r="AD150" s="20"/>
+      <c r="AE150" s="20"/>
+      <c r="AF150" s="20"/>
+      <c r="AG150" s="20"/>
       <c r="AH150" s="20">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="AI150" s="20">
-        <v>4.1666666666666664E-2</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="AI150" s="20"/>
       <c r="AJ150" s="20"/>
       <c r="AK150" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.99999999999999956</v>
+        <v>0.2</v>
       </c>
       <c r="AL150" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>480</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:38">
-      <c r="A151" s="4" t="s">
+      <c r="A151" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="B151" s="28" t="s">
         <v>23</v>
       </c>
       <c r="C151" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D151" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -21737,62 +21686,105 @@
         <v>60</v>
       </c>
       <c r="F151" s="11" t="s">
-        <v>333</v>
+        <v>231</v>
       </c>
       <c r="G151" s="11" t="s">
-        <v>220</v>
+        <v>339</v>
       </c>
       <c r="H151" s="11" t="s">
-        <v>300</v>
+        <v>361</v>
       </c>
       <c r="I151" s="11">
         <v>1</v>
       </c>
       <c r="J151" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>10</v>
+        <v>9.9999999999999964</v>
       </c>
       <c r="K151" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="L151" s="18"/>
-      <c r="M151" s="18"/>
-      <c r="N151" s="18"/>
-      <c r="O151" s="19"/>
-      <c r="P151" s="18"/>
+        <v>20</v>
+      </c>
+      <c r="L151" s="18">
+        <f>1/24</f>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="M151" s="18">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="N151" s="18">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="O151" s="19">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="P151" s="18">
+        <v>4.1666666666666664E-2</v>
+      </c>
       <c r="Q151" s="18">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="R151" s="18"/>
-      <c r="S151" s="19"/>
-      <c r="T151" s="18"/>
-      <c r="U151" s="18"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="R151" s="18">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="S151" s="19">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="T151" s="18">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="U151" s="18">
+        <v>4.1666666666666664E-2</v>
+      </c>
       <c r="V151" s="18">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="W151" s="19"/>
-      <c r="X151" s="20"/>
-      <c r="Y151" s="20"/>
-      <c r="Z151" s="20"/>
-      <c r="AA151" s="20"/>
-      <c r="AB151" s="20"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="W151" s="19">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="X151" s="20">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="Y151" s="20">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="Z151" s="20">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="AA151" s="20">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="AB151" s="20">
+        <v>4.1666666666666664E-2</v>
+      </c>
       <c r="AC151" s="20">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="AD151" s="20"/>
-      <c r="AE151" s="20"/>
-      <c r="AF151" s="20"/>
-      <c r="AG151" s="20"/>
-      <c r="AH151" s="20"/>
-      <c r="AI151" s="20"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="AD151" s="20">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="AE151" s="20">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="AF151" s="20">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="AG151" s="20">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="AH151" s="20">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="AI151" s="20">
+        <v>4.1666666666666664E-2</v>
+      </c>
       <c r="AJ151" s="20"/>
       <c r="AK151" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.125</v>
+        <v>0.99999999999999956</v>
       </c>
       <c r="AL151" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>0.30000000000000004</v>
+        <v>480</v>
       </c>
     </row>
     <row r="152" spans="1:38">
@@ -21814,20 +21806,20 @@
         <v>60</v>
       </c>
       <c r="F152" s="11" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G152" s="11" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="H152" s="11" t="s">
-        <v>346</v>
+        <v>300</v>
       </c>
       <c r="I152" s="11">
         <v>1</v>
       </c>
       <c r="J152" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="K152" s="11">
         <v>0.1</v>
@@ -21835,37 +21827,41 @@
       <c r="L152" s="18"/>
       <c r="M152" s="18"/>
       <c r="N152" s="18"/>
-      <c r="O152" s="18"/>
+      <c r="O152" s="19"/>
       <c r="P152" s="18"/>
-      <c r="Q152" s="18"/>
+      <c r="Q152" s="18">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="R152" s="18"/>
-      <c r="S152" s="18"/>
+      <c r="S152" s="19"/>
       <c r="T152" s="18"/>
       <c r="U152" s="18"/>
-      <c r="V152" s="18"/>
-      <c r="W152" s="18"/>
+      <c r="V152" s="18">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="W152" s="19"/>
       <c r="X152" s="20"/>
       <c r="Y152" s="20"/>
       <c r="Z152" s="20"/>
       <c r="AA152" s="20"/>
       <c r="AB152" s="20"/>
-      <c r="AC152" s="20"/>
+      <c r="AC152" s="20">
+        <v>7.4999999999999997E-2</v>
+      </c>
       <c r="AD152" s="20"/>
       <c r="AE152" s="20"/>
       <c r="AF152" s="20"/>
       <c r="AG152" s="20"/>
       <c r="AH152" s="20"/>
-      <c r="AI152" s="20">
-        <v>0.25</v>
-      </c>
+      <c r="AI152" s="20"/>
       <c r="AJ152" s="20"/>
       <c r="AK152" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="AL152" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
     </row>
     <row r="153" spans="1:38">
@@ -21876,7 +21872,7 @@
         <v>23</v>
       </c>
       <c r="C153" s="11" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D153" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -21887,39 +21883,37 @@
         <v>60</v>
       </c>
       <c r="F153" s="11" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G153" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H153" s="11" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="I153" s="11">
         <v>1</v>
       </c>
       <c r="J153" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="K153" s="11">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="L153" s="18"/>
       <c r="M153" s="18"/>
       <c r="N153" s="18"/>
-      <c r="O153" s="19"/>
+      <c r="O153" s="18"/>
       <c r="P153" s="18"/>
       <c r="Q153" s="18"/>
       <c r="R153" s="18"/>
-      <c r="S153" s="19"/>
+      <c r="S153" s="18"/>
       <c r="T153" s="18"/>
       <c r="U153" s="18"/>
       <c r="V153" s="18"/>
-      <c r="W153" s="19"/>
-      <c r="X153" s="20">
-        <v>0.1</v>
-      </c>
+      <c r="W153" s="18"/>
+      <c r="X153" s="20"/>
       <c r="Y153" s="20"/>
       <c r="Z153" s="20"/>
       <c r="AA153" s="20"/>
@@ -21930,15 +21924,17 @@
       <c r="AF153" s="20"/>
       <c r="AG153" s="20"/>
       <c r="AH153" s="20"/>
-      <c r="AI153" s="20"/>
+      <c r="AI153" s="20">
+        <v>0.25</v>
+      </c>
       <c r="AJ153" s="20"/>
       <c r="AK153" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="AL153" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="154" spans="1:38">
@@ -21949,7 +21945,7 @@
         <v>23</v>
       </c>
       <c r="C154" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D154" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -21960,23 +21956,23 @@
         <v>60</v>
       </c>
       <c r="F154" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G154" s="11" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="H154" s="11" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="I154" s="11">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J154" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="K154" s="11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L154" s="18"/>
       <c r="M154" s="18"/>
@@ -21988,11 +21984,11 @@
       <c r="S154" s="19"/>
       <c r="T154" s="18"/>
       <c r="U154" s="18"/>
-      <c r="V154" s="18">
-        <v>0.2</v>
-      </c>
+      <c r="V154" s="18"/>
       <c r="W154" s="19"/>
-      <c r="X154" s="20"/>
+      <c r="X154" s="20">
+        <v>0.1</v>
+      </c>
       <c r="Y154" s="20"/>
       <c r="Z154" s="20"/>
       <c r="AA154" s="20"/>
@@ -22007,11 +22003,11 @@
       <c r="AJ154" s="20"/>
       <c r="AK154" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AL154" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:38">
@@ -22033,20 +22029,20 @@
         <v>60</v>
       </c>
       <c r="F155" s="11" t="s">
-        <v>232</v>
+        <v>336</v>
       </c>
       <c r="G155" s="11" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="H155" s="11" t="s">
-        <v>346</v>
+        <v>300</v>
       </c>
       <c r="I155" s="11">
         <v>11</v>
       </c>
       <c r="J155" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="K155" s="11">
         <v>10</v>
@@ -22061,7 +22057,9 @@
       <c r="S155" s="19"/>
       <c r="T155" s="18"/>
       <c r="U155" s="18"/>
-      <c r="V155" s="18"/>
+      <c r="V155" s="18">
+        <v>0.2</v>
+      </c>
       <c r="W155" s="19"/>
       <c r="X155" s="20"/>
       <c r="Y155" s="20"/>
@@ -22074,13 +22072,11 @@
       <c r="AF155" s="20"/>
       <c r="AG155" s="20"/>
       <c r="AH155" s="20"/>
-      <c r="AI155" s="20">
-        <v>0.4</v>
-      </c>
+      <c r="AI155" s="20"/>
       <c r="AJ155" s="20"/>
       <c r="AK155" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AL155" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
@@ -22095,7 +22091,7 @@
         <v>23</v>
       </c>
       <c r="C156" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D156" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -22106,23 +22102,23 @@
         <v>60</v>
       </c>
       <c r="F156" s="11" t="s">
-        <v>337</v>
+        <v>232</v>
       </c>
       <c r="G156" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H156" s="11" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="I156" s="11">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J156" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>36</v>
+        <v>96</v>
       </c>
       <c r="K156" s="11">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L156" s="18"/>
       <c r="M156" s="18"/>
@@ -22147,17 +22143,17 @@
       <c r="AF156" s="20"/>
       <c r="AG156" s="20"/>
       <c r="AH156" s="20"/>
-      <c r="AI156" s="20"/>
-      <c r="AJ156" s="20">
-        <v>0.15</v>
-      </c>
+      <c r="AI156" s="20">
+        <v>0.4</v>
+      </c>
+      <c r="AJ156" s="20"/>
       <c r="AK156" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AL156" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:38">
@@ -22168,7 +22164,7 @@
         <v>23</v>
       </c>
       <c r="C157" s="11" t="s">
-        <v>308</v>
+        <v>121</v>
       </c>
       <c r="D157" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -22178,8 +22174,8 @@
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>60</v>
       </c>
-      <c r="F157" s="37" t="s">
-        <v>338</v>
+      <c r="F157" s="11" t="s">
+        <v>337</v>
       </c>
       <c r="G157" s="11" t="s">
         <v>229</v>
@@ -22195,7 +22191,7 @@
         <v>36</v>
       </c>
       <c r="K157" s="11">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="L157" s="18"/>
       <c r="M157" s="18"/>
@@ -22235,45 +22231,45 @@
     </row>
     <row r="158" spans="1:38">
       <c r="A158" s="4" t="s">
-        <v>244</v>
+        <v>74</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>245</v>
+        <v>23</v>
       </c>
       <c r="C158" s="11" t="s">
-        <v>5</v>
+        <v>308</v>
       </c>
       <c r="D158" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="E158" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>10</v>
-      </c>
-      <c r="F158" s="11" t="s">
-        <v>274</v>
+        <v>60</v>
+      </c>
+      <c r="F158" s="37" t="s">
+        <v>338</v>
       </c>
       <c r="G158" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H158" s="11" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="I158" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J158" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>16</v>
-      </c>
-      <c r="K158" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="K158" s="11">
+        <v>2</v>
+      </c>
       <c r="L158" s="18"/>
       <c r="M158" s="18"/>
       <c r="N158" s="18"/>
-      <c r="O158" s="19">
-        <v>0.4</v>
-      </c>
+      <c r="O158" s="19"/>
       <c r="P158" s="18"/>
       <c r="Q158" s="18"/>
       <c r="R158" s="18"/>
@@ -22294,14 +22290,16 @@
       <c r="AG158" s="20"/>
       <c r="AH158" s="20"/>
       <c r="AI158" s="20"/>
-      <c r="AJ158" s="20"/>
+      <c r="AJ158" s="20">
+        <v>0.15</v>
+      </c>
       <c r="AK158" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AL158" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159" spans="1:38">
@@ -22323,7 +22321,7 @@
         <v>10</v>
       </c>
       <c r="F159" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G159" s="11" t="s">
         <v>229</v>
@@ -22332,7 +22330,7 @@
         <v>300</v>
       </c>
       <c r="I159" s="11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J159" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
@@ -22342,13 +22340,13 @@
       <c r="L159" s="18"/>
       <c r="M159" s="18"/>
       <c r="N159" s="18"/>
-      <c r="O159" s="19"/>
+      <c r="O159" s="19">
+        <v>0.4</v>
+      </c>
       <c r="P159" s="18"/>
       <c r="Q159" s="18"/>
       <c r="R159" s="18"/>
-      <c r="S159" s="19">
-        <v>0.4</v>
-      </c>
+      <c r="S159" s="19"/>
       <c r="T159" s="18"/>
       <c r="U159" s="18"/>
       <c r="V159" s="18"/>
@@ -22394,7 +22392,7 @@
         <v>10</v>
       </c>
       <c r="F160" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G160" s="11" t="s">
         <v>229</v>
@@ -22403,11 +22401,11 @@
         <v>300</v>
       </c>
       <c r="I160" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J160" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K160" s="11"/>
       <c r="L160" s="18"/>
@@ -22417,12 +22415,12 @@
       <c r="P160" s="18"/>
       <c r="Q160" s="18"/>
       <c r="R160" s="18"/>
-      <c r="S160" s="19"/>
+      <c r="S160" s="19">
+        <v>0.4</v>
+      </c>
       <c r="T160" s="18"/>
       <c r="U160" s="18"/>
-      <c r="V160" s="18">
-        <v>0.2</v>
-      </c>
+      <c r="V160" s="18"/>
       <c r="W160" s="19"/>
       <c r="X160" s="20"/>
       <c r="Y160" s="20"/>
@@ -22439,19 +22437,19 @@
       <c r="AJ160" s="20"/>
       <c r="AK160" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AL160" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="161" spans="1:38">
       <c r="A161" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C161" s="11" t="s">
         <v>5</v>
@@ -22465,7 +22463,7 @@
         <v>10</v>
       </c>
       <c r="F161" s="11" t="s">
-        <v>205</v>
+        <v>276</v>
       </c>
       <c r="G161" s="11" t="s">
         <v>229</v>
@@ -22474,11 +22472,11 @@
         <v>300</v>
       </c>
       <c r="I161" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J161" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K161" s="11"/>
       <c r="L161" s="18"/>
@@ -22491,40 +22489,38 @@
       <c r="S161" s="19"/>
       <c r="T161" s="18"/>
       <c r="U161" s="18"/>
-      <c r="V161" s="18"/>
+      <c r="V161" s="18">
+        <v>0.2</v>
+      </c>
       <c r="W161" s="19"/>
       <c r="X161" s="20"/>
       <c r="Y161" s="20"/>
       <c r="Z161" s="20"/>
       <c r="AA161" s="20"/>
       <c r="AB161" s="20"/>
-      <c r="AC161" s="20">
-        <v>0.5</v>
-      </c>
+      <c r="AC161" s="20"/>
       <c r="AD161" s="20"/>
       <c r="AE161" s="20"/>
       <c r="AF161" s="20"/>
       <c r="AG161" s="20"/>
-      <c r="AH161" s="20">
-        <v>0.5</v>
-      </c>
+      <c r="AH161" s="20"/>
       <c r="AI161" s="20"/>
       <c r="AJ161" s="20"/>
       <c r="AK161" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="AL161" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:38">
       <c r="A162" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B162" s="28" t="s">
-        <v>243</v>
+        <v>246</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="C162" s="11" t="s">
         <v>5</v>
@@ -22538,7 +22534,7 @@
         <v>10</v>
       </c>
       <c r="F162" s="11" t="s">
-        <v>299</v>
+        <v>205</v>
       </c>
       <c r="G162" s="11" t="s">
         <v>229</v>
@@ -22547,43 +22543,23 @@
         <v>300</v>
       </c>
       <c r="I162" s="11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J162" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>1.9999999999999998</v>
+        <v>20</v>
       </c>
       <c r="K162" s="11"/>
-      <c r="L162" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="M162" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="N162" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="O162" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="P162" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="Q162" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="R162" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="S162" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="T162" s="18">
-        <v>0.05</v>
-      </c>
-      <c r="U162" s="18">
-        <v>0.05</v>
-      </c>
+      <c r="L162" s="18"/>
+      <c r="M162" s="18"/>
+      <c r="N162" s="18"/>
+      <c r="O162" s="19"/>
+      <c r="P162" s="18"/>
+      <c r="Q162" s="18"/>
+      <c r="R162" s="18"/>
+      <c r="S162" s="19"/>
+      <c r="T162" s="18"/>
+      <c r="U162" s="18"/>
       <c r="V162" s="18"/>
       <c r="W162" s="19"/>
       <c r="X162" s="20"/>
@@ -22591,21 +22567,25 @@
       <c r="Z162" s="20"/>
       <c r="AA162" s="20"/>
       <c r="AB162" s="20"/>
-      <c r="AC162" s="20"/>
+      <c r="AC162" s="20">
+        <v>0.5</v>
+      </c>
       <c r="AD162" s="20"/>
       <c r="AE162" s="20"/>
       <c r="AF162" s="20"/>
       <c r="AG162" s="20"/>
-      <c r="AH162" s="20"/>
+      <c r="AH162" s="20">
+        <v>0.5</v>
+      </c>
       <c r="AI162" s="20"/>
       <c r="AJ162" s="20"/>
       <c r="AK162" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.49999999999999994</v>
+        <v>1</v>
       </c>
       <c r="AL162" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>19.999999999999996</v>
+        <v>40</v>
       </c>
     </row>
     <row r="163" spans="1:38">
@@ -22627,7 +22607,7 @@
         <v>10</v>
       </c>
       <c r="F163" s="11" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G163" s="11" t="s">
         <v>229</v>
@@ -22640,38 +22620,38 @@
       </c>
       <c r="J163" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>0.79999999999999982</v>
+        <v>1.9999999999999998</v>
       </c>
       <c r="K163" s="11"/>
       <c r="L163" s="18">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="M163" s="18">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="N163" s="18">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="O163" s="18">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="P163" s="18">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="Q163" s="18">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="R163" s="18">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="S163" s="18">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="T163" s="18">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="U163" s="18">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="V163" s="18"/>
       <c r="W163" s="19"/>
@@ -22690,11 +22670,11 @@
       <c r="AJ163" s="20"/>
       <c r="AK163" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.19999999999999998</v>
+        <v>0.49999999999999994</v>
       </c>
       <c r="AL163" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>7.9999999999999982</v>
+        <v>19.999999999999996</v>
       </c>
     </row>
     <row r="164" spans="1:38">
@@ -22716,7 +22696,7 @@
         <v>10</v>
       </c>
       <c r="F164" s="11" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G164" s="11" t="s">
         <v>229</v>
@@ -22725,26 +22705,44 @@
         <v>300</v>
       </c>
       <c r="I164" s="11">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J164" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>12</v>
+        <v>0.79999999999999982</v>
       </c>
       <c r="K164" s="11"/>
-      <c r="L164" s="18"/>
-      <c r="M164" s="18"/>
-      <c r="N164" s="18"/>
-      <c r="O164" s="19"/>
-      <c r="P164" s="18"/>
-      <c r="Q164" s="18"/>
-      <c r="R164" s="18"/>
-      <c r="S164" s="19"/>
-      <c r="T164" s="18"/>
-      <c r="U164" s="18"/>
-      <c r="V164" s="18">
-        <v>0.3</v>
-      </c>
+      <c r="L164" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="M164" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="N164" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="O164" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="P164" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="Q164" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="R164" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="S164" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="T164" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="U164" s="18">
+        <v>0.02</v>
+      </c>
+      <c r="V164" s="18"/>
       <c r="W164" s="19"/>
       <c r="X164" s="20"/>
       <c r="Y164" s="20"/>
@@ -22761,19 +22759,19 @@
       <c r="AJ164" s="20"/>
       <c r="AK164" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.3</v>
+        <v>0.19999999999999998</v>
       </c>
       <c r="AL164" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>12</v>
+        <v>7.9999999999999982</v>
       </c>
     </row>
     <row r="165" spans="1:38">
       <c r="A165" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>184</v>
+        <v>242</v>
+      </c>
+      <c r="B165" s="28" t="s">
+        <v>243</v>
       </c>
       <c r="C165" s="11" t="s">
         <v>5</v>
@@ -22784,30 +22782,28 @@
       </c>
       <c r="E165" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F165" s="11" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G165" s="11" t="s">
-        <v>390</v>
+        <v>229</v>
       </c>
       <c r="H165" s="11" t="s">
         <v>300</v>
       </c>
       <c r="I165" s="11">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="J165" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K165" s="11"/>
       <c r="L165" s="18"/>
       <c r="M165" s="18"/>
-      <c r="N165" s="18">
-        <v>0.05</v>
-      </c>
+      <c r="N165" s="18"/>
       <c r="O165" s="19"/>
       <c r="P165" s="18"/>
       <c r="Q165" s="18"/>
@@ -22815,7 +22811,9 @@
       <c r="S165" s="19"/>
       <c r="T165" s="18"/>
       <c r="U165" s="18"/>
-      <c r="V165" s="18"/>
+      <c r="V165" s="18">
+        <v>0.3</v>
+      </c>
       <c r="W165" s="19"/>
       <c r="X165" s="20"/>
       <c r="Y165" s="20"/>
@@ -22832,11 +22830,11 @@
       <c r="AJ165" s="20"/>
       <c r="AK165" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="AL165" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="166" spans="1:38">
@@ -22858,7 +22856,7 @@
         <v>20</v>
       </c>
       <c r="F166" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G166" s="11" t="s">
         <v>390</v>
@@ -22929,31 +22927,29 @@
         <v>20</v>
       </c>
       <c r="F167" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G167" s="11" t="s">
-        <v>229</v>
+        <v>390</v>
       </c>
       <c r="H167" s="11" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I167" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J167" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K167" s="11"/>
       <c r="L167" s="18"/>
       <c r="M167" s="18"/>
-      <c r="N167" s="18"/>
-      <c r="O167" s="19">
-        <v>0.3</v>
-      </c>
-      <c r="P167" s="18">
-        <v>-0.3</v>
-      </c>
+      <c r="N167" s="18">
+        <v>0.05</v>
+      </c>
+      <c r="O167" s="19"/>
+      <c r="P167" s="18"/>
       <c r="Q167" s="18"/>
       <c r="R167" s="18"/>
       <c r="S167" s="19"/>
@@ -22976,11 +22972,11 @@
       <c r="AJ167" s="20"/>
       <c r="AK167" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="AL167" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168" spans="1:38">
@@ -22991,7 +22987,7 @@
         <v>184</v>
       </c>
       <c r="C168" s="11" t="s">
-        <v>123</v>
+        <v>5</v>
       </c>
       <c r="D168" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -23002,32 +22998,32 @@
         <v>20</v>
       </c>
       <c r="F168" s="11" t="s">
-        <v>265</v>
+        <v>305</v>
       </c>
       <c r="G168" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H168" s="11" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="I168" s="11">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J168" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>8</v>
-      </c>
-      <c r="K168" s="11">
-        <v>4</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="K168" s="11"/>
       <c r="L168" s="18"/>
       <c r="M168" s="18"/>
       <c r="N168" s="18"/>
-      <c r="O168" s="19"/>
-      <c r="P168" s="18"/>
-      <c r="Q168" s="18">
-        <v>0.1</v>
-      </c>
+      <c r="O168" s="19">
+        <v>0.3</v>
+      </c>
+      <c r="P168" s="18">
+        <v>-0.3</v>
+      </c>
+      <c r="Q168" s="18"/>
       <c r="R168" s="18"/>
       <c r="S168" s="19"/>
       <c r="T168" s="18"/>
@@ -23049,11 +23045,11 @@
       <c r="AJ168" s="20"/>
       <c r="AK168" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="AL168" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="169" spans="1:38">
@@ -23064,7 +23060,7 @@
         <v>184</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D169" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -23075,7 +23071,7 @@
         <v>20</v>
       </c>
       <c r="F169" s="11" t="s">
-        <v>307</v>
+        <v>265</v>
       </c>
       <c r="G169" s="11" t="s">
         <v>229</v>
@@ -23088,24 +23084,24 @@
       </c>
       <c r="J169" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="K169" s="11">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="L169" s="18"/>
       <c r="M169" s="18"/>
       <c r="N169" s="18"/>
       <c r="O169" s="19"/>
       <c r="P169" s="18"/>
-      <c r="Q169" s="18"/>
+      <c r="Q169" s="18">
+        <v>0.1</v>
+      </c>
       <c r="R169" s="18"/>
       <c r="S169" s="19"/>
       <c r="T169" s="18"/>
       <c r="U169" s="18"/>
-      <c r="V169" s="18">
-        <v>0.2</v>
-      </c>
+      <c r="V169" s="18"/>
       <c r="W169" s="19"/>
       <c r="X169" s="20"/>
       <c r="Y169" s="20"/>
@@ -23122,11 +23118,11 @@
       <c r="AJ169" s="20"/>
       <c r="AK169" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AL169" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>0.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170" spans="1:38">
@@ -23137,7 +23133,7 @@
         <v>184</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>308</v>
+        <v>122</v>
       </c>
       <c r="D170" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -23148,23 +23144,23 @@
         <v>20</v>
       </c>
       <c r="F170" s="11" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G170" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H170" s="11" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="I170" s="11">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J170" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K170" s="11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L170" s="18"/>
       <c r="M170" s="18"/>
@@ -23177,7 +23173,7 @@
       <c r="T170" s="18"/>
       <c r="U170" s="18"/>
       <c r="V170" s="18">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W170" s="19"/>
       <c r="X170" s="20"/>
@@ -23195,22 +23191,22 @@
       <c r="AJ170" s="20"/>
       <c r="AK170" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AL170" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="171" spans="1:38">
       <c r="A171" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C171" s="11" t="s">
-        <v>5</v>
+        <v>308</v>
       </c>
       <c r="D171" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -23221,22 +23217,24 @@
         <v>20</v>
       </c>
       <c r="F171" s="11" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G171" s="11" t="s">
-        <v>390</v>
+        <v>229</v>
       </c>
       <c r="H171" s="11" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="I171" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J171" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>4</v>
-      </c>
-      <c r="K171" s="11"/>
+        <v>32</v>
+      </c>
+      <c r="K171" s="11">
+        <v>1</v>
+      </c>
       <c r="L171" s="18"/>
       <c r="M171" s="18"/>
       <c r="N171" s="18"/>
@@ -23247,13 +23245,13 @@
       <c r="S171" s="19"/>
       <c r="T171" s="18"/>
       <c r="U171" s="18"/>
-      <c r="V171" s="18"/>
+      <c r="V171" s="18">
+        <v>0.4</v>
+      </c>
       <c r="W171" s="19"/>
       <c r="X171" s="20"/>
       <c r="Y171" s="20"/>
-      <c r="Z171" s="20">
-        <v>0.05</v>
-      </c>
+      <c r="Z171" s="20"/>
       <c r="AA171" s="20"/>
       <c r="AB171" s="20"/>
       <c r="AC171" s="20"/>
@@ -23266,11 +23264,11 @@
       <c r="AJ171" s="20"/>
       <c r="AK171" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="AL171" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:38">
@@ -23281,7 +23279,7 @@
         <v>185</v>
       </c>
       <c r="C172" s="11" t="s">
-        <v>123</v>
+        <v>5</v>
       </c>
       <c r="D172" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -23292,24 +23290,22 @@
         <v>20</v>
       </c>
       <c r="F172" s="11" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="G172" s="11" t="s">
-        <v>229</v>
+        <v>390</v>
       </c>
       <c r="H172" s="11" t="s">
         <v>300</v>
       </c>
       <c r="I172" s="11">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J172" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>16</v>
-      </c>
-      <c r="K172" s="11">
-        <v>0.5</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="K172" s="11"/>
       <c r="L172" s="18"/>
       <c r="M172" s="18"/>
       <c r="N172" s="18"/>
@@ -23324,13 +23320,13 @@
       <c r="W172" s="19"/>
       <c r="X172" s="20"/>
       <c r="Y172" s="20"/>
-      <c r="Z172" s="20"/>
+      <c r="Z172" s="20">
+        <v>0.05</v>
+      </c>
       <c r="AA172" s="20"/>
       <c r="AB172" s="20"/>
       <c r="AC172" s="20"/>
-      <c r="AD172" s="20">
-        <v>0.2</v>
-      </c>
+      <c r="AD172" s="20"/>
       <c r="AE172" s="20"/>
       <c r="AF172" s="20"/>
       <c r="AG172" s="20"/>
@@ -23339,11 +23335,11 @@
       <c r="AJ172" s="20"/>
       <c r="AK172" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="AL172" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>0.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173" spans="1:38">
@@ -23354,7 +23350,7 @@
         <v>185</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D173" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -23365,7 +23361,7 @@
         <v>20</v>
       </c>
       <c r="F173" s="11" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="G173" s="11" t="s">
         <v>229</v>
@@ -23374,13 +23370,15 @@
         <v>300</v>
       </c>
       <c r="I173" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J173" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>24</v>
-      </c>
-      <c r="K173" s="11"/>
+        <v>16</v>
+      </c>
+      <c r="K173" s="11">
+        <v>0.5</v>
+      </c>
       <c r="L173" s="18"/>
       <c r="M173" s="18"/>
       <c r="N173" s="18"/>
@@ -23398,10 +23396,10 @@
       <c r="Z173" s="20"/>
       <c r="AA173" s="20"/>
       <c r="AB173" s="20"/>
-      <c r="AC173" s="20">
-        <v>0.3</v>
-      </c>
-      <c r="AD173" s="20"/>
+      <c r="AC173" s="20"/>
+      <c r="AD173" s="20">
+        <v>0.2</v>
+      </c>
       <c r="AE173" s="20"/>
       <c r="AF173" s="20"/>
       <c r="AG173" s="20"/>
@@ -23410,11 +23408,11 @@
       <c r="AJ173" s="20"/>
       <c r="AK173" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AL173" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>24</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="174" spans="1:38">
@@ -23425,7 +23423,7 @@
         <v>185</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D174" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -23436,7 +23434,7 @@
         <v>20</v>
       </c>
       <c r="F174" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G174" s="11" t="s">
         <v>229</v>
@@ -23449,7 +23447,7 @@
       </c>
       <c r="J174" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="K174" s="11"/>
       <c r="L174" s="18"/>
@@ -23469,58 +23467,58 @@
       <c r="Z174" s="20"/>
       <c r="AA174" s="20"/>
       <c r="AB174" s="20"/>
-      <c r="AC174" s="20"/>
+      <c r="AC174" s="20">
+        <v>0.3</v>
+      </c>
       <c r="AD174" s="20"/>
       <c r="AE174" s="20"/>
       <c r="AF174" s="20"/>
       <c r="AG174" s="20"/>
       <c r="AH174" s="20"/>
-      <c r="AI174" s="20">
-        <v>0.5</v>
-      </c>
+      <c r="AI174" s="20"/>
       <c r="AJ174" s="20"/>
       <c r="AK174" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="AL174" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>40</v>
+        <v>24</v>
       </c>
     </row>
     <row r="175" spans="1:38">
-      <c r="A175" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="B175" s="28" t="s">
-        <v>315</v>
+      <c r="A175" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="C175" s="11" t="s">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="D175" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E175" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F175" s="11" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="G175" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H175" s="11" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="I175" s="11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J175" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="K175" s="11"/>
       <c r="L175" s="18"/>
@@ -23529,9 +23527,7 @@
       <c r="O175" s="19"/>
       <c r="P175" s="18"/>
       <c r="Q175" s="18"/>
-      <c r="R175" s="18">
-        <v>0.1</v>
-      </c>
+      <c r="R175" s="18"/>
       <c r="S175" s="19"/>
       <c r="T175" s="18"/>
       <c r="U175" s="18"/>
@@ -23548,15 +23544,17 @@
       <c r="AF175" s="20"/>
       <c r="AG175" s="20"/>
       <c r="AH175" s="20"/>
-      <c r="AI175" s="20"/>
+      <c r="AI175" s="20">
+        <v>0.5</v>
+      </c>
       <c r="AJ175" s="20"/>
       <c r="AK175" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="AL175" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="176" spans="1:38">
@@ -23578,7 +23576,7 @@
         <v>10</v>
       </c>
       <c r="F176" s="11" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G176" s="11" t="s">
         <v>229</v>
@@ -23587,11 +23585,11 @@
         <v>317</v>
       </c>
       <c r="I176" s="11">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J176" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K176" s="11"/>
       <c r="L176" s="18"/>
@@ -23600,14 +23598,14 @@
       <c r="O176" s="19"/>
       <c r="P176" s="18"/>
       <c r="Q176" s="18"/>
-      <c r="R176" s="18"/>
+      <c r="R176" s="18">
+        <v>0.1</v>
+      </c>
       <c r="S176" s="19"/>
       <c r="T176" s="18"/>
       <c r="U176" s="18"/>
       <c r="V176" s="18"/>
-      <c r="W176" s="19">
-        <v>0.2</v>
-      </c>
+      <c r="W176" s="19"/>
       <c r="X176" s="20"/>
       <c r="Y176" s="20"/>
       <c r="Z176" s="20"/>
@@ -23623,42 +23621,42 @@
       <c r="AJ176" s="20"/>
       <c r="AK176" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="AL176" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="177" spans="1:38">
       <c r="A177" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B177" s="28" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C177" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D177" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E177" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F177" s="11" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="G177" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H177" s="11" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="I177" s="11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J177" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
@@ -23676,13 +23674,13 @@
       <c r="T177" s="18"/>
       <c r="U177" s="18"/>
       <c r="V177" s="18"/>
-      <c r="W177" s="19"/>
+      <c r="W177" s="19">
+        <v>0.2</v>
+      </c>
       <c r="X177" s="20"/>
       <c r="Y177" s="20"/>
       <c r="Z177" s="20"/>
-      <c r="AA177" s="20">
-        <v>0.2</v>
-      </c>
+      <c r="AA177" s="20"/>
       <c r="AB177" s="20"/>
       <c r="AC177" s="20"/>
       <c r="AD177" s="20"/>
@@ -23720,7 +23718,7 @@
         <v>10</v>
       </c>
       <c r="F178" s="11" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G178" s="11" t="s">
         <v>229</v>
@@ -23729,11 +23727,11 @@
         <v>322</v>
       </c>
       <c r="I178" s="11">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J178" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K178" s="11"/>
       <c r="L178" s="18"/>
@@ -23751,7 +23749,9 @@
       <c r="X178" s="20"/>
       <c r="Y178" s="20"/>
       <c r="Z178" s="20"/>
-      <c r="AA178" s="20"/>
+      <c r="AA178" s="20">
+        <v>0.2</v>
+      </c>
       <c r="AB178" s="20"/>
       <c r="AC178" s="20"/>
       <c r="AD178" s="20"/>
@@ -23759,17 +23759,15 @@
       <c r="AF178" s="20"/>
       <c r="AG178" s="20"/>
       <c r="AH178" s="20"/>
-      <c r="AI178" s="20">
-        <v>0.5</v>
-      </c>
+      <c r="AI178" s="20"/>
       <c r="AJ178" s="20"/>
       <c r="AK178" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AL178" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:38">
@@ -23791,7 +23789,7 @@
         <v>10</v>
       </c>
       <c r="F179" s="11" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G179" s="11" t="s">
         <v>229</v>
@@ -23800,11 +23798,11 @@
         <v>322</v>
       </c>
       <c r="I179" s="11">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J179" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K179" s="11"/>
       <c r="L179" s="18"/>
@@ -23831,24 +23829,24 @@
       <c r="AG179" s="20"/>
       <c r="AH179" s="20"/>
       <c r="AI179" s="20">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AJ179" s="20"/>
       <c r="AK179" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="AL179" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="180" spans="1:38">
       <c r="A180" s="3" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B180" s="28" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="C180" s="11" t="s">
         <v>5</v>
@@ -23859,10 +23857,10 @@
       </c>
       <c r="E180" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F180" s="11" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G180" s="11" t="s">
         <v>229</v>
@@ -23871,15 +23869,13 @@
         <v>322</v>
       </c>
       <c r="I180" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J180" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>40</v>
-      </c>
-      <c r="K180" s="11">
-        <v>20</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="K180" s="11"/>
       <c r="L180" s="18"/>
       <c r="M180" s="18"/>
       <c r="N180" s="18"/>
@@ -23904,16 +23900,16 @@
       <c r="AG180" s="20"/>
       <c r="AH180" s="20"/>
       <c r="AI180" s="20">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="AJ180" s="20"/>
       <c r="AK180" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="AL180" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="181" spans="1:38">
@@ -23924,7 +23920,7 @@
         <v>326</v>
       </c>
       <c r="C181" s="11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D181" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -23935,23 +23931,23 @@
         <v>20</v>
       </c>
       <c r="F181" s="11" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G181" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H181" s="11" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="I181" s="11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J181" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>40</v>
       </c>
       <c r="K181" s="11">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L181" s="18"/>
       <c r="M181" s="18"/>
@@ -23971,14 +23967,14 @@
       <c r="AA181" s="20"/>
       <c r="AB181" s="20"/>
       <c r="AC181" s="20"/>
-      <c r="AD181" s="20">
-        <v>0.5</v>
-      </c>
+      <c r="AD181" s="20"/>
       <c r="AE181" s="20"/>
       <c r="AF181" s="20"/>
       <c r="AG181" s="20"/>
       <c r="AH181" s="20"/>
-      <c r="AI181" s="20"/>
+      <c r="AI181" s="20">
+        <v>0.5</v>
+      </c>
       <c r="AJ181" s="20"/>
       <c r="AK181" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
@@ -23986,45 +23982,45 @@
       </c>
       <c r="AL181" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="182" spans="1:38">
       <c r="A182" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B182" s="28" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C182" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D182" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E182" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>20</v>
       </c>
       <c r="F182" s="11" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="G182" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H182" s="11" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="I182" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J182" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>40</v>
       </c>
       <c r="K182" s="11">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L182" s="18"/>
       <c r="M182" s="18"/>
@@ -24036,9 +24032,7 @@
       <c r="S182" s="19"/>
       <c r="T182" s="18"/>
       <c r="U182" s="18"/>
-      <c r="V182" s="18">
-        <v>0.5</v>
-      </c>
+      <c r="V182" s="18"/>
       <c r="W182" s="19"/>
       <c r="X182" s="20"/>
       <c r="Y182" s="20"/>
@@ -24046,7 +24040,9 @@
       <c r="AA182" s="20"/>
       <c r="AB182" s="20"/>
       <c r="AC182" s="20"/>
-      <c r="AD182" s="20"/>
+      <c r="AD182" s="20">
+        <v>0.5</v>
+      </c>
       <c r="AE182" s="20"/>
       <c r="AF182" s="20"/>
       <c r="AG182" s="20"/>
@@ -24058,6 +24054,79 @@
         <v>0.5</v>
       </c>
       <c r="AL182" s="27">
+        <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:38">
+      <c r="A183" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B183" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="C183" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D183" s="29">
+        <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
+        <v>50</v>
+      </c>
+      <c r="E183" s="29">
+        <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
+        <v>20</v>
+      </c>
+      <c r="F183" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="G183" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="H183" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="I183" s="11">
+        <v>2</v>
+      </c>
+      <c r="J183" s="11">
+        <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
+        <v>40</v>
+      </c>
+      <c r="K183" s="11">
+        <v>8</v>
+      </c>
+      <c r="L183" s="18"/>
+      <c r="M183" s="18"/>
+      <c r="N183" s="18"/>
+      <c r="O183" s="19"/>
+      <c r="P183" s="18"/>
+      <c r="Q183" s="18"/>
+      <c r="R183" s="18"/>
+      <c r="S183" s="19"/>
+      <c r="T183" s="18"/>
+      <c r="U183" s="18"/>
+      <c r="V183" s="18">
+        <v>0.5</v>
+      </c>
+      <c r="W183" s="19"/>
+      <c r="X183" s="20"/>
+      <c r="Y183" s="20"/>
+      <c r="Z183" s="20"/>
+      <c r="AA183" s="20"/>
+      <c r="AB183" s="20"/>
+      <c r="AC183" s="20"/>
+      <c r="AD183" s="20"/>
+      <c r="AE183" s="20"/>
+      <c r="AF183" s="20"/>
+      <c r="AG183" s="20"/>
+      <c r="AH183" s="20"/>
+      <c r="AI183" s="20"/>
+      <c r="AJ183" s="20"/>
+      <c r="AK183" s="27">
+        <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
+        <v>0.5</v>
+      </c>
+      <c r="AL183" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
         <v>8</v>
       </c>

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1759" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AFACCC6-BA25-4A66-ABBD-4FF1B201EE46}"/>
+  <xr:revisionPtr revIDLastSave="1767" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{666049B0-0C3F-49B4-99BF-E7A63C1909BF}"/>
   <bookViews>
     <workbookView xWindow="28702" yWindow="-98" windowWidth="26115" windowHeight="15675" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2913" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="391">
   <si>
     <t>Module Code</t>
   </si>
@@ -1178,9 +1178,6 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>na/</t>
-  </si>
-  <si>
     <t>PXT143</t>
   </si>
   <si>
@@ -1234,6 +1231,9 @@
   </si>
   <si>
     <t>F</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -11880,7 +11880,7 @@
         <v>20</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>229</v>
@@ -11971,7 +11971,7 @@
         <v>20</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>229</v>
@@ -12599,7 +12599,7 @@
         <v>10</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G32" s="11" t="s">
         <v>229</v>
@@ -12686,7 +12686,7 @@
         <v>10</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G33" s="11" t="s">
         <v>229</v>
@@ -12838,7 +12838,7 @@
         <v>10</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G35" s="11" t="s">
         <v>229</v>
@@ -15459,7 +15459,9 @@
       <c r="G69" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H69" s="11"/>
+      <c r="H69" s="11" t="s">
+        <v>390</v>
+      </c>
       <c r="I69" s="11">
         <v>1</v>
       </c>
@@ -15685,7 +15687,7 @@
         <v>10</v>
       </c>
       <c r="F72" s="37" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G72" s="11" t="s">
         <v>229</v>
@@ -15786,7 +15788,9 @@
       <c r="G73" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="H73" s="11"/>
+      <c r="H73" s="11" t="s">
+        <v>390</v>
+      </c>
       <c r="I73" s="11">
         <v>1</v>
       </c>
@@ -16083,7 +16087,7 @@
         <v>10</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G77" s="11" t="s">
         <v>229</v>
@@ -17516,7 +17520,7 @@
         <v>220</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="I96" s="11">
         <v>1</v>
@@ -19122,7 +19126,7 @@
         <v>10</v>
       </c>
       <c r="F117" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G117" s="11" t="s">
         <v>229</v>
@@ -19406,7 +19410,7 @@
         <v>10</v>
       </c>
       <c r="F121" s="37" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G121" s="11" t="s">
         <v>229</v>
@@ -21187,7 +21191,7 @@
         <v>10</v>
       </c>
       <c r="F144" s="12" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G144" s="11" t="s">
         <v>229</v>
@@ -21473,7 +21477,7 @@
         <v>10</v>
       </c>
       <c r="F148" s="12" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G148" s="11" t="s">
         <v>229</v>
@@ -22859,7 +22863,7 @@
         <v>303</v>
       </c>
       <c r="G166" s="11" t="s">
-        <v>390</v>
+        <v>220</v>
       </c>
       <c r="H166" s="11" t="s">
         <v>300</v>
@@ -22930,7 +22934,7 @@
         <v>304</v>
       </c>
       <c r="G167" s="11" t="s">
-        <v>390</v>
+        <v>220</v>
       </c>
       <c r="H167" s="11" t="s">
         <v>300</v>
@@ -23223,7 +23227,7 @@
         <v>229</v>
       </c>
       <c r="H171" s="11" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I171" s="11">
         <v>1</v>
@@ -23293,7 +23297,7 @@
         <v>311</v>
       </c>
       <c r="G172" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H172" s="11" t="s">
         <v>300</v>
@@ -30357,16 +30361,16 @@
         <v>197</v>
       </c>
       <c r="P1" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q1" s="5" t="s">
         <v>379</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>380</v>
       </c>
       <c r="R1" s="5" t="s">
         <v>241</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="T1" s="5" t="s">
         <v>212</v>
@@ -32278,7 +32282,7 @@
         <v>357</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D39" s="28" t="s">
         <v>180</v>
@@ -34132,7 +34136,7 @@
     </row>
     <row r="74" spans="1:23">
       <c r="A74" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>357</v>
@@ -34144,7 +34148,7 @@
         <v>178</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F74" s="4">
         <v>7</v>
@@ -35334,10 +35338,10 @@
     </row>
     <row r="97" spans="1:23">
       <c r="A97" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>376</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>377</v>
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="28" t="s">

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1767" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{666049B0-0C3F-49B4-99BF-E7A63C1909BF}"/>
+  <xr:revisionPtr revIDLastSave="1772" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABE74BD0-B894-4D1A-AC75-15F407EC500F}"/>
   <bookViews>
     <workbookView xWindow="28702" yWindow="-98" windowWidth="26115" windowHeight="15675" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
@@ -1233,7 +1233,7 @@
     <t>F</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>N/A</t>
   </si>
 </sst>
 </file>

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1809" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41F5D988-B2E7-4269-B188-F27C51DF2FED}"/>
+  <xr:revisionPtr revIDLastSave="1824" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFF74950-B363-4DB4-8A6E-EF6E3E4CD00F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
+    <workbookView xWindow="3800" yWindow="3800" windowWidth="28800" windowHeight="15370" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Assessments" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="3" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -9167,7 +9167,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B70" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="34">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -10079,21 +10079,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66039B40-29AD-4D93-B125-EAF72A7B3996}">
   <dimension ref="A1:AL184"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.81640625" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10" style="10" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="21.7109375" style="10" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.7109375" style="10" customWidth="1"/>
-    <col min="12" max="23" width="9.140625" style="14" customWidth="1"/>
-    <col min="24" max="36" width="9.140625" style="16" customWidth="1"/>
+    <col min="6" max="6" width="21.7265625" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="21.7265625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="10.7265625" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.7265625" style="10" customWidth="1"/>
+    <col min="12" max="23" width="9.1796875" style="14" customWidth="1"/>
+    <col min="24" max="36" width="9.1796875" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="44" customFormat="1" ht="30">
+    <row r="1" spans="1:38" s="44" customFormat="1" ht="29">
       <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
@@ -10507,7 +10507,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="28.5">
+    <row r="6" spans="1:38" ht="28">
       <c r="A6" s="4" t="s">
         <v>252</v>
       </c>
@@ -11088,7 +11088,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="28.5">
+    <row r="13" spans="1:38" ht="28">
       <c r="A13" s="3" t="s">
         <v>81</v>
       </c>
@@ -11116,7 +11116,7 @@
         <v>300</v>
       </c>
       <c r="I13" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
@@ -11864,7 +11864,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:38" ht="28.5">
+    <row r="23" spans="1:38" ht="28">
       <c r="A23" s="4" t="s">
         <v>37</v>
       </c>
@@ -12661,7 +12661,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:38" ht="28.5">
+    <row r="33" spans="1:38" ht="28">
       <c r="A33" s="4" t="s">
         <v>44</v>
       </c>
@@ -13198,7 +13198,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:38" ht="28.5">
+    <row r="40" spans="1:38" ht="28">
       <c r="A40" s="4" t="s">
         <v>49</v>
       </c>
@@ -13856,7 +13856,7 @@
         <v>300</v>
       </c>
       <c r="I48" s="11">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J48" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
@@ -14614,7 +14614,7 @@
         <v>12.000000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:38" ht="28.5">
+    <row r="58" spans="1:38" ht="28">
       <c r="A58" s="3" t="s">
         <v>186</v>
       </c>
@@ -14693,7 +14693,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:38" ht="28.5">
+    <row r="59" spans="1:38" ht="28">
       <c r="A59" s="3" t="s">
         <v>186</v>
       </c>
@@ -15029,7 +15029,7 @@
         <v>300</v>
       </c>
       <c r="I63" s="11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J63" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
@@ -15331,7 +15331,7 @@
         <v>300</v>
       </c>
       <c r="I67" s="11">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J67" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
@@ -15475,7 +15475,7 @@
         <v>306</v>
       </c>
       <c r="I69" s="11">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J69" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
@@ -15607,7 +15607,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="71" spans="1:38" ht="28.5">
+    <row r="71" spans="1:38" ht="28">
       <c r="A71" s="4" t="s">
         <v>1</v>
       </c>
@@ -15751,7 +15751,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:38" ht="28.5">
+    <row r="73" spans="1:38" ht="28">
       <c r="A73" s="4" t="s">
         <v>248</v>
       </c>
@@ -16828,7 +16828,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:38" ht="28.5">
+    <row r="87" spans="1:38" ht="28">
       <c r="A87" s="4" t="s">
         <v>16</v>
       </c>
@@ -16992,7 +16992,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:38" ht="28.5">
+    <row r="89" spans="1:38" ht="28">
       <c r="A89" s="4" t="s">
         <v>18</v>
       </c>
@@ -17026,9 +17026,7 @@
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>1.2</v>
       </c>
-      <c r="K89" s="11">
-        <v>0.5</v>
-      </c>
+      <c r="K89" s="11"/>
       <c r="L89" s="18">
         <v>0.03</v>
       </c>
@@ -17070,10 +17068,10 @@
       </c>
       <c r="AL89" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:38" ht="28.5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:38" ht="28">
       <c r="A90" s="4" t="s">
         <v>18</v>
       </c>
@@ -17107,9 +17105,7 @@
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
         <v>1.2</v>
       </c>
-      <c r="K90" s="11">
-        <v>0.5</v>
-      </c>
+      <c r="K90" s="11"/>
       <c r="L90" s="18"/>
       <c r="M90" s="18"/>
       <c r="N90" s="18"/>
@@ -17151,7 +17147,7 @@
       </c>
       <c r="AL90" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>2.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:38">
@@ -17438,7 +17434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="95" spans="1:38" ht="28.5">
+    <row r="95" spans="1:38">
       <c r="A95" s="8" t="s">
         <v>21</v>
       </c>
@@ -17509,7 +17505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:38" ht="28.5">
+    <row r="96" spans="1:38">
       <c r="A96" s="8" t="s">
         <v>21</v>
       </c>
@@ -17669,7 +17665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:38" ht="28.5">
+    <row r="98" spans="1:38" ht="28">
       <c r="A98" s="3" t="s">
         <v>106</v>
       </c>
@@ -17959,7 +17955,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="102" spans="1:38" ht="28.5">
+    <row r="102" spans="1:38" ht="28">
       <c r="A102" s="3" t="s">
         <v>108</v>
       </c>
@@ -19099,7 +19095,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="117" spans="1:38" ht="28.5">
+    <row r="117" spans="1:38" ht="28">
       <c r="A117" s="4" t="s">
         <v>61</v>
       </c>
@@ -19474,7 +19470,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:38" ht="28.5">
+    <row r="122" spans="1:38" ht="28">
       <c r="A122" s="4" t="s">
         <v>63</v>
       </c>
@@ -19547,7 +19543,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" spans="1:38" ht="28.5">
+    <row r="123" spans="1:38" ht="28">
       <c r="A123" s="4" t="s">
         <v>66</v>
       </c>
@@ -20009,7 +20005,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="129" spans="1:38" ht="28.5">
+    <row r="129" spans="1:38" ht="28">
       <c r="A129" s="4" t="s">
         <v>71</v>
       </c>
@@ -20319,7 +20315,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:38" ht="28.5">
+    <row r="133" spans="1:38" ht="28">
       <c r="A133" s="3" t="s">
         <v>192</v>
       </c>
@@ -20552,7 +20548,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="1:38" ht="28.5">
+    <row r="136" spans="1:38" ht="28">
       <c r="A136" s="3" t="s">
         <v>193</v>
       </c>
@@ -20633,7 +20629,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="137" spans="1:38" ht="28.5">
+    <row r="137" spans="1:38" ht="28">
       <c r="A137" s="3" t="s">
         <v>193</v>
       </c>
@@ -20929,7 +20925,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="141" spans="1:38" ht="28.5">
+    <row r="141" spans="1:38" ht="28">
       <c r="A141" s="3" t="s">
         <v>239</v>
       </c>
@@ -21097,7 +21093,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="143" spans="1:38" ht="28.5">
+    <row r="143" spans="1:38" ht="28">
       <c r="A143" s="3" t="s">
         <v>116</v>
       </c>
@@ -21176,7 +21172,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:38" ht="28.5">
+    <row r="144" spans="1:38" ht="28">
       <c r="A144" s="3" t="s">
         <v>116</v>
       </c>
@@ -24231,16 +24227,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0482654D-1732-43E5-85EC-021407B07CE5}">
   <dimension ref="A1:AE141"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.81640625" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10" style="10" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="10" customWidth="1"/>
-    <col min="7" max="15" width="16.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="17.28515625" style="14" bestFit="1" customWidth="1"/>
-    <col min="19" max="30" width="8.7109375" style="16"/>
+    <col min="6" max="6" width="10.7265625" style="10" customWidth="1"/>
+    <col min="7" max="15" width="16.26953125" style="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="17.26953125" style="14" bestFit="1" customWidth="1"/>
+    <col min="19" max="30" width="8.7265625" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -27558,7 +27554,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:31" ht="28.5">
+    <row r="36" spans="1:31">
       <c r="A36" s="8" t="s">
         <v>21</v>
       </c>
@@ -30381,14 +30377,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D548CE7-BEAC-43FA-847F-FDE82E3A5926}">
   <dimension ref="A1:W129"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="66.85546875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.81640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.26953125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.26953125" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="5" customWidth="1"/>
   </cols>
@@ -35875,11 +35871,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4F541C-C22C-46EF-BD21-4F8C93ABA5A9}">
   <dimension ref="A3:F70"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:6">
@@ -36679,7 +36675,7 @@
       </c>
       <c r="C36">
         <f>SUMIF(Table1[Module Code],Sheet2!A36,Table1[Total Hours])</f>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D36">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A36,Table14[Module Code],0))</f>
@@ -36687,11 +36683,11 @@
       </c>
       <c r="E36">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F36">
         <f t="shared" si="1"/>
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="37" spans="1:6">

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1824" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFF74950-B363-4DB4-8A6E-EF6E3E4CD00F}"/>
+  <xr:revisionPtr revIDLastSave="1945" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4C1820A-80D9-40AB-88F9-12CD5884B830}"/>
   <bookViews>
-    <workbookView xWindow="3800" yWindow="3800" windowWidth="28800" windowHeight="15370" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="26115" windowHeight="15675" activeTab="2" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Assessments" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2951" uniqueCount="416">
   <si>
     <t>Module Code</t>
   </si>
@@ -1237,6 +1237,78 @@
   </si>
   <si>
     <t>CA (Old)</t>
+  </si>
+  <si>
+    <t>O [1]</t>
+  </si>
+  <si>
+    <t>O [2]</t>
+  </si>
+  <si>
+    <t>Astrophysics Project</t>
+  </si>
+  <si>
+    <t>PX3360</t>
+  </si>
+  <si>
+    <t>PX3370</t>
+  </si>
+  <si>
+    <t>Medical Physics Project</t>
+  </si>
+  <si>
+    <t>[1]</t>
+  </si>
+  <si>
+    <t>[2]</t>
+  </si>
+  <si>
+    <t>[3]</t>
+  </si>
+  <si>
+    <t>A different module code exists for students on Astrophyscs (PX3360) and Medical Physics (PX3370) programmes</t>
+  </si>
+  <si>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>PX4320</t>
+  </si>
+  <si>
+    <t>[4]</t>
+  </si>
+  <si>
+    <t>Astrophysics students take PX4320</t>
+  </si>
+  <si>
+    <t>O [3]</t>
+  </si>
+  <si>
+    <t>O [4]</t>
+  </si>
+  <si>
+    <t>C [5]</t>
+  </si>
+  <si>
+    <t>C [6]</t>
+  </si>
+  <si>
+    <t>[5]</t>
+  </si>
+  <si>
+    <t>[6]</t>
+  </si>
+  <si>
+    <t>Physics with Astronomy students should select exactly one of PX2241 and PX2242</t>
+  </si>
+  <si>
+    <t>PX2141 is strongly encouraged for students on placement degrees</t>
+  </si>
+  <si>
+    <t>Physics students should select **AT MOST** one astrophysics module per semester</t>
+  </si>
+  <si>
+    <t>Astrophysics students should select **AT LEAST** one astrophysics module per semester</t>
   </si>
 </sst>
 </file>
@@ -1331,7 +1403,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1463,11 +1535,23 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="113">
+  <dxfs count="134">
     <dxf>
       <fill>
         <patternFill>
@@ -1556,6 +1640,216 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -9167,7 +9461,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B70" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="34">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -9616,54 +9910,54 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}" name="Table1" displayName="Table1" ref="A1:AL184" totalsRowShown="0" headerRowDxfId="112" dataDxfId="110" headerRowBorderDxfId="111" tableBorderDxfId="109" totalsRowBorderDxfId="108">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}" name="Table1" displayName="Table1" ref="A1:AL184" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129">
   <autoFilter ref="A1:AL184" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AI155">
     <sortCondition ref="A1:A155"/>
   </sortState>
   <tableColumns count="38">
-    <tableColumn id="1" xr3:uid="{7078548A-F011-4851-AB36-1F04238FA2FE}" name="Module Code" dataDxfId="107"/>
-    <tableColumn id="2" xr3:uid="{D2290F36-B8B3-427A-AEFE-45FD22901411}" name="Module Title" dataDxfId="106"/>
-    <tableColumn id="3" xr3:uid="{31165455-2AA3-4532-A0A0-C942837C0F79}" name="CA type" dataDxfId="105"/>
-    <tableColumn id="33" xr3:uid="{B83E0E3E-2B28-42F1-BC64-5D7177EC4229}" name="CA Weight" dataDxfId="104"/>
-    <tableColumn id="34" xr3:uid="{AEA2048C-138D-450A-BE52-3FCBDE03C67D}" name="Credits" dataDxfId="103"/>
-    <tableColumn id="30" xr3:uid="{82DD5B5B-C808-4E6E-849C-7A03DC6D0B69}" name="Description" dataDxfId="102"/>
-    <tableColumn id="36" xr3:uid="{A7BF30F6-C808-4B8F-B3FF-9FAF20E2145A}" name="Summative" dataDxfId="101"/>
-    <tableColumn id="37" xr3:uid="{68E504F9-116C-43AB-BCC6-3BB48B0860D2}" name="Day of Week" dataDxfId="100"/>
-    <tableColumn id="16" xr3:uid="{E6637FEB-7F23-45F0-99D2-96D20DD2DAEF}" name="Duration" dataDxfId="99"/>
-    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="98">
+    <tableColumn id="1" xr3:uid="{7078548A-F011-4851-AB36-1F04238FA2FE}" name="Module Code" dataDxfId="128"/>
+    <tableColumn id="2" xr3:uid="{D2290F36-B8B3-427A-AEFE-45FD22901411}" name="Module Title" dataDxfId="127"/>
+    <tableColumn id="3" xr3:uid="{31165455-2AA3-4532-A0A0-C942837C0F79}" name="CA type" dataDxfId="126"/>
+    <tableColumn id="33" xr3:uid="{B83E0E3E-2B28-42F1-BC64-5D7177EC4229}" name="CA Weight" dataDxfId="125"/>
+    <tableColumn id="34" xr3:uid="{AEA2048C-138D-450A-BE52-3FCBDE03C67D}" name="Credits" dataDxfId="124"/>
+    <tableColumn id="30" xr3:uid="{82DD5B5B-C808-4E6E-849C-7A03DC6D0B69}" name="Description" dataDxfId="123"/>
+    <tableColumn id="36" xr3:uid="{A7BF30F6-C808-4B8F-B3FF-9FAF20E2145A}" name="Summative" dataDxfId="122"/>
+    <tableColumn id="37" xr3:uid="{68E504F9-116C-43AB-BCC6-3BB48B0860D2}" name="Day of Week" dataDxfId="121"/>
+    <tableColumn id="16" xr3:uid="{E6637FEB-7F23-45F0-99D2-96D20DD2DAEF}" name="Duration" dataDxfId="120"/>
+    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="119">
       <calculatedColumnFormula>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="97"/>
-    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="96"/>
-    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="95"/>
-    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="94"/>
-    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="93"/>
-    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="92"/>
-    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="91"/>
-    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="90"/>
-    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="89"/>
-    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="88"/>
-    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="87"/>
-    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="86"/>
-    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="85"/>
-    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="84"/>
-    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="83"/>
-    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="82"/>
-    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="81"/>
-    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="80"/>
-    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="79"/>
-    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="78"/>
-    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="77"/>
-    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="76"/>
-    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="75"/>
-    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="74"/>
-    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="73"/>
-    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="72"/>
-    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="71">
+    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="118"/>
+    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="117"/>
+    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="116"/>
+    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="115"/>
+    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="114"/>
+    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="113"/>
+    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="112"/>
+    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="111"/>
+    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="110"/>
+    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="109"/>
+    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="108"/>
+    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="107"/>
+    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="106"/>
+    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="105"/>
+    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="104"/>
+    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="103"/>
+    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="102"/>
+    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="101"/>
+    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="100"/>
+    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="99"/>
+    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="98"/>
+    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="97"/>
+    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="96"/>
+    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="95"/>
+    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="94"/>
+    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="93"/>
+    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="92">
       <calculatedColumnFormula>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="70">
+    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="91">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9672,49 +9966,49 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="69" dataDxfId="67" headerRowBorderDxfId="68" tableBorderDxfId="66" totalsRowBorderDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="90" dataDxfId="88" headerRowBorderDxfId="89" tableBorderDxfId="87" totalsRowBorderDxfId="86">
   <autoFilter ref="A1:AE64" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD64">
     <sortCondition ref="A1:A132"/>
   </sortState>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="62"/>
-    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="61">
+    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="85"/>
+    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="84"/>
+    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="83"/>
+    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="82">
       <calculatedColumnFormula>INDEX(Table2[Credits],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="60">
+    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="81">
       <calculatedColumnFormula>INDEX(Table2[Semester],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="59">
+    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="80">
       <calculatedColumnFormula>INDEX(Table2[Contact Time],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="58"/>
-    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="56"/>
-    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="55"/>
-    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="54"/>
-    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="53"/>
-    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="52"/>
-    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="51"/>
-    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="50"/>
-    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="49"/>
-    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="48"/>
-    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="47"/>
-    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="46"/>
-    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="45"/>
-    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="44"/>
-    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="43"/>
-    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="42"/>
-    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="41"/>
-    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="40"/>
-    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="39"/>
-    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="38"/>
-    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="37"/>
-    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="36"/>
-    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="35"/>
-    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="34">
+    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="79"/>
+    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="78"/>
+    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="77"/>
+    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="76"/>
+    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="75"/>
+    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="74"/>
+    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="73"/>
+    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="72"/>
+    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="71"/>
+    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="70"/>
+    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="69"/>
+    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="68"/>
+    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="67"/>
+    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="66"/>
+    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="65"/>
+    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="64"/>
+    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="63"/>
+    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="62"/>
+    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="61"/>
+    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="60"/>
+    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="59"/>
+    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="58"/>
+    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="57"/>
+    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="56"/>
+    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="55">
       <calculatedColumnFormula>SUM(Table14[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9723,37 +10017,38 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}" name="Table2" displayName="Table2" ref="A1:W100" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32">
-  <autoFilter ref="A1:W100" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B62">
-    <sortCondition ref="A1:A62"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}" name="Table2" displayName="Table2" ref="A1:X109" totalsRowShown="0" headerRowDxfId="54" dataDxfId="52" headerRowBorderDxfId="53">
+  <autoFilter ref="A1:X109" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B64">
+    <sortCondition ref="A1:A64"/>
   </sortState>
-  <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{A36A2B86-0F30-4188-9ECD-AE5BC71A59F4}" name="Module Code" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{D3F20037-EF35-4207-A530-484E1EB45719}" name="Module Title" dataDxfId="29"/>
-    <tableColumn id="9" xr3:uid="{40C22022-10B9-411F-9B76-B89140ABFFB2}" name="Alternative Module Code" dataDxfId="28"/>
-    <tableColumn id="13" xr3:uid="{CB12E405-1802-457C-AF17-F1B9CB3BBF13}" name="Source" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{EA737976-1AA7-49B6-8752-A388621554F4}" name="Semester" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{16DFC84F-5858-467D-B447-49992D721E4B}" name="Level" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{A17BC4BA-A3CB-442D-9BDC-D3B41B98B389}" name="Credits" dataDxfId="24"/>
-    <tableColumn id="19" xr3:uid="{98846C13-E462-4CFF-858E-AF75931B6712}" name="AllUG" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{7E25B4F4-1A7D-48D9-AAA2-AF5C97240797}" name="Physics" dataDxfId="22"/>
+  <tableColumns count="24">
+    <tableColumn id="1" xr3:uid="{A36A2B86-0F30-4188-9ECD-AE5BC71A59F4}" name="Module Code" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{D3F20037-EF35-4207-A530-484E1EB45719}" name="Module Title" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{40C22022-10B9-411F-9B76-B89140ABFFB2}" name="Alternative Module Code" dataDxfId="49"/>
+    <tableColumn id="13" xr3:uid="{CB12E405-1802-457C-AF17-F1B9CB3BBF13}" name="Source" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{EA737976-1AA7-49B6-8752-A388621554F4}" name="Semester" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{16DFC84F-5858-467D-B447-49992D721E4B}" name="Level" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{A17BC4BA-A3CB-442D-9BDC-D3B41B98B389}" name="Credits" dataDxfId="45"/>
+    <tableColumn id="24" xr3:uid="{597B34DA-41F4-4D1D-AA24-07FF8D78D4D2}" name="Parent" dataDxfId="13"/>
+    <tableColumn id="19" xr3:uid="{98846C13-E462-4CFF-858E-AF75931B6712}" name="AllUG" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{7E25B4F4-1A7D-48D9-AAA2-AF5C97240797}" name="Physics" dataDxfId="43"/>
     <tableColumn id="17" xr3:uid="{AA3AE96F-2651-49D7-89AD-BA94806438AE}" name="PhysAstro"/>
-    <tableColumn id="4" xr3:uid="{9C7DD469-E550-411F-8467-246A1543FB38}" name="Astro" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{3C5D3AEB-487E-4678-A42F-BE4BA4D0E9AA}" name="MedPhys" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{9C7DD469-E550-411F-8467-246A1543FB38}" name="Astro" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{3C5D3AEB-487E-4678-A42F-BE4BA4D0E9AA}" name="MedPhys" dataDxfId="41"/>
     <tableColumn id="20" xr3:uid="{C3673B06-C0A2-44F6-8978-F392282CECF8}" name="AllPG"/>
-    <tableColumn id="14" xr3:uid="{AE552873-9B31-41A6-B73C-D052477CA74C}" name="MScPhysics" dataDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{8F51CE76-3A29-487A-A13C-FB63C79CF3E6}" name="MScAstro" dataDxfId="18"/>
-    <tableColumn id="21" xr3:uid="{FC74E264-78AB-4682-A1B8-D8964ED1C3F3}" name="MScDataPhys" dataDxfId="17"/>
-    <tableColumn id="22" xr3:uid="{2D5776F7-D7F7-4D20-A7CB-DB57997AD074}" name="MScDataAstro" dataDxfId="16"/>
+    <tableColumn id="14" xr3:uid="{AE552873-9B31-41A6-B73C-D052477CA74C}" name="MScPhysics" dataDxfId="40"/>
+    <tableColumn id="15" xr3:uid="{8F51CE76-3A29-487A-A13C-FB63C79CF3E6}" name="MScAstro" dataDxfId="39"/>
+    <tableColumn id="21" xr3:uid="{FC74E264-78AB-4682-A1B8-D8964ED1C3F3}" name="MScDataPhys" dataDxfId="38"/>
+    <tableColumn id="22" xr3:uid="{2D5776F7-D7F7-4D20-A7CB-DB57997AD074}" name="MScDataAstro" dataDxfId="37"/>
     <tableColumn id="18" xr3:uid="{10668F71-1EDF-482E-86A5-46E1F3C15120}" name="MScCSPhysics"/>
     <tableColumn id="23" xr3:uid="{E837FCBC-49C7-45CE-AFAA-4F01143EF2A8}" name="CDTCSPhysics"/>
     <tableColumn id="16" xr3:uid="{DB790F5F-BEF0-41CE-A68A-1AA9DF83D66B}" name="Contact Time"/>
-    <tableColumn id="10" xr3:uid="{60774AFA-B365-4EB5-AAFF-6235868F8C97}" name="Exam Weight (%)" dataDxfId="15"/>
-    <tableColumn id="12" xr3:uid="{537B7C75-E9C0-42F2-9F3C-6E960AB2D257}" name="CA weight" dataDxfId="14">
+    <tableColumn id="10" xr3:uid="{60774AFA-B365-4EB5-AAFF-6235868F8C97}" name="Exam Weight (%)" dataDxfId="36"/>
+    <tableColumn id="12" xr3:uid="{537B7C75-E9C0-42F2-9F3C-6E960AB2D257}" name="CA weight" dataDxfId="35">
       <calculatedColumnFormula>100-Table2[[#This Row],[Exam Weight (%)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{75DA2527-5A08-4ECE-B4E4-752A8F8BF059}" name="CA Check" dataDxfId="13">
+    <tableColumn id="11" xr3:uid="{75DA2527-5A08-4ECE-B4E4-752A8F8BF059}" name="CA Check" dataDxfId="34">
       <calculatedColumnFormula>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -30376,7 +30671,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D548CE7-BEAC-43FA-847F-FDE82E3A5926}">
-  <dimension ref="A1:W129"/>
+  <dimension ref="A1:X133"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
@@ -30386,10 +30681,10 @@
     <col min="5" max="5" width="10.7265625" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.26953125" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="5" customWidth="1"/>
+    <col min="8" max="9" width="9" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -30412,55 +30707,58 @@
         <v>140</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" s="5" t="s">
         <v>377</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="U1" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2" s="4" t="s">
         <v>55</v>
       </c>
@@ -30480,10 +30778,8 @@
       <c r="G2" s="2">
         <v>20</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J2" t="s">
@@ -30495,22 +30791,25 @@
       <c r="L2" t="s">
         <v>143</v>
       </c>
-      <c r="T2">
+      <c r="M2" t="s">
+        <v>143</v>
+      </c>
+      <c r="U2">
         <v>4</v>
       </c>
-      <c r="U2">
+      <c r="V2">
         <v>60</v>
       </c>
-      <c r="V2">
+      <c r="W2">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="W2">
+      <c r="X2">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:24">
       <c r="A3" s="4" t="s">
         <v>252</v>
       </c>
@@ -30530,10 +30829,8 @@
       <c r="G3" s="2">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J3" t="s">
@@ -30545,22 +30842,25 @@
       <c r="L3" t="s">
         <v>143</v>
       </c>
-      <c r="T3">
+      <c r="M3" t="s">
+        <v>143</v>
+      </c>
+      <c r="U3">
         <v>4</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>60</v>
       </c>
-      <c r="V3">
+      <c r="W3">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="W3">
+      <c r="X3">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:24">
       <c r="A4" s="4" t="s">
         <v>255</v>
       </c>
@@ -30580,10 +30880,8 @@
       <c r="G4" s="2">
         <v>10</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J4" t="s">
@@ -30595,22 +30893,25 @@
       <c r="L4" t="s">
         <v>143</v>
       </c>
-      <c r="T4">
-        <v>2</v>
+      <c r="M4" t="s">
+        <v>143</v>
       </c>
       <c r="U4">
+        <v>2</v>
+      </c>
+      <c r="V4">
         <v>50</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>50</v>
       </c>
-      <c r="W4">
+      <c r="X4">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:24">
       <c r="A5" s="4" t="s">
         <v>59</v>
       </c>
@@ -30630,10 +30931,8 @@
       <c r="G5" s="2">
         <v>20</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J5" t="s">
@@ -30645,22 +30944,25 @@
       <c r="L5" t="s">
         <v>143</v>
       </c>
-      <c r="T5">
+      <c r="M5" t="s">
+        <v>143</v>
+      </c>
+      <c r="U5">
         <v>4</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>0</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W5">
+      <c r="X5">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:24">
       <c r="A6" s="3" t="s">
         <v>81</v>
       </c>
@@ -30680,10 +30982,8 @@
       <c r="G6" s="2">
         <v>20</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J6" t="s">
@@ -30695,22 +30995,25 @@
       <c r="L6" t="s">
         <v>143</v>
       </c>
-      <c r="T6">
+      <c r="M6" t="s">
+        <v>143</v>
+      </c>
+      <c r="U6">
         <v>4</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>70</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W6">
+      <c r="X6">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30.000000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:24">
       <c r="A7" s="3" t="s">
         <v>187</v>
       </c>
@@ -30730,10 +31033,8 @@
       <c r="G7" s="2">
         <v>10</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="H7" s="2"/>
+      <c r="I7" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J7" t="s">
@@ -30745,22 +31046,25 @@
       <c r="L7" t="s">
         <v>143</v>
       </c>
-      <c r="T7">
+      <c r="M7" t="s">
+        <v>143</v>
+      </c>
+      <c r="U7">
         <v>3</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>0</v>
       </c>
-      <c r="V7">
+      <c r="W7">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W7">
+      <c r="X7">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:24">
       <c r="A8" s="3" t="s">
         <v>83</v>
       </c>
@@ -30780,19 +31084,19 @@
       <c r="G8" s="2">
         <v>10</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>144</v>
-      </c>
-      <c r="J8" t="s">
-        <v>143</v>
       </c>
       <c r="K8" t="s">
         <v>143</v>
       </c>
-      <c r="L8" s="6"/>
+      <c r="L8" t="s">
+        <v>143</v>
+      </c>
       <c r="M8" s="6"/>
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
@@ -30800,22 +31104,23 @@
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
-      <c r="T8" s="6">
-        <v>2</v>
-      </c>
-      <c r="U8">
+      <c r="T8" s="6"/>
+      <c r="U8" s="6">
+        <v>2</v>
+      </c>
+      <c r="V8">
         <v>70</v>
       </c>
-      <c r="V8">
+      <c r="W8">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30.000000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:24">
       <c r="A9" s="3" t="s">
         <v>84</v>
       </c>
@@ -30835,10 +31140,8 @@
       <c r="G9" s="2">
         <v>10</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="H9" s="2"/>
+      <c r="I9" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J9" t="s">
@@ -30850,22 +31153,25 @@
       <c r="L9" t="s">
         <v>143</v>
       </c>
-      <c r="T9">
-        <v>2</v>
+      <c r="M9" t="s">
+        <v>143</v>
       </c>
       <c r="U9">
+        <v>2</v>
+      </c>
+      <c r="V9">
         <v>60</v>
       </c>
-      <c r="V9">
+      <c r="W9">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="W9">
+      <c r="X9">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:24">
       <c r="A10" s="7" t="s">
         <v>82</v>
       </c>
@@ -30885,33 +31191,34 @@
       <c r="G10" s="2">
         <v>10</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="2"/>
+      <c r="I10" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>144</v>
       </c>
-      <c r="J10" s="6"/>
       <c r="K10" s="6"/>
-      <c r="L10" t="s">
+      <c r="L10" s="6"/>
+      <c r="M10" t="s">
         <v>143</v>
       </c>
-      <c r="T10">
-        <v>2</v>
-      </c>
       <c r="U10">
+        <v>2</v>
+      </c>
+      <c r="V10">
         <v>80</v>
       </c>
-      <c r="V10">
+      <c r="W10">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W10">
+      <c r="X10">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:24">
       <c r="A11" s="3" t="s">
         <v>215</v>
       </c>
@@ -30931,37 +31238,38 @@
       <c r="G11" s="2">
         <v>0</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="2"/>
+      <c r="I11" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="I11" t="s">
-        <v>143</v>
-      </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" t="s">
         <v>143</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="T11">
+      <c r="M11" t="s">
+        <v>143</v>
+      </c>
+      <c r="U11">
         <v>1</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <v>0</v>
       </c>
-      <c r="V11">
+      <c r="W11">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W11">
+      <c r="X11">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:24">
       <c r="A12" s="4" t="s">
         <v>37</v>
       </c>
@@ -30981,10 +31289,8 @@
       <c r="G12" s="2">
         <v>20</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="H12" s="2"/>
+      <c r="I12" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J12" t="s">
@@ -30996,22 +31302,25 @@
       <c r="L12" t="s">
         <v>143</v>
       </c>
-      <c r="T12">
+      <c r="M12" t="s">
+        <v>143</v>
+      </c>
+      <c r="U12">
         <v>4</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>60</v>
       </c>
-      <c r="V12">
+      <c r="W12">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="W12">
+      <c r="X12">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:24">
       <c r="A13" s="4" t="s">
         <v>258</v>
       </c>
@@ -31031,10 +31340,8 @@
       <c r="G13" s="2">
         <v>10</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="H13" s="2"/>
+      <c r="I13" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J13" t="s">
@@ -31046,22 +31353,25 @@
       <c r="L13" t="s">
         <v>143</v>
       </c>
-      <c r="T13">
+      <c r="M13" t="s">
+        <v>143</v>
+      </c>
+      <c r="U13">
         <v>3</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>60</v>
       </c>
-      <c r="V13">
+      <c r="W13">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="W13">
+      <c r="X13">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:24">
       <c r="A14" s="4" t="s">
         <v>49</v>
       </c>
@@ -31082,28 +31392,29 @@
         <v>10</v>
       </c>
       <c r="H14" s="2"/>
-      <c r="I14" s="6"/>
+      <c r="I14" s="2"/>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
-      <c r="L14" t="s">
+      <c r="L14" s="6"/>
+      <c r="M14" t="s">
         <v>143</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <v>4</v>
       </c>
-      <c r="U14">
+      <c r="V14">
         <v>0</v>
       </c>
-      <c r="V14">
+      <c r="W14">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W14">
+      <c r="X14">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:24">
       <c r="A15" s="4" t="s">
         <v>234</v>
       </c>
@@ -31123,10 +31434,8 @@
       <c r="G15" s="2">
         <v>10</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="H15" s="2"/>
+      <c r="I15" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J15" t="s">
@@ -31138,22 +31447,25 @@
       <c r="L15" t="s">
         <v>143</v>
       </c>
-      <c r="T15">
+      <c r="M15" t="s">
+        <v>143</v>
+      </c>
+      <c r="U15">
         <v>3</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>0</v>
       </c>
-      <c r="V15">
+      <c r="W15">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W15">
+      <c r="X15">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:24">
       <c r="A16" s="4" t="s">
         <v>40</v>
       </c>
@@ -31173,19 +31485,19 @@
       <c r="G16" s="2">
         <v>10</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="H16" s="2"/>
+      <c r="I16" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J16" t="s">
         <v>144</v>
       </c>
       <c r="K16" t="s">
+        <v>144</v>
+      </c>
+      <c r="L16" t="s">
         <v>143</v>
       </c>
-      <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
@@ -31193,22 +31505,23 @@
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
       <c r="S16" s="6"/>
-      <c r="T16" s="6">
-        <v>2</v>
-      </c>
-      <c r="U16">
+      <c r="T16" s="6"/>
+      <c r="U16" s="6">
+        <v>2</v>
+      </c>
+      <c r="V16">
         <v>60</v>
       </c>
-      <c r="V16">
+      <c r="W16">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="W16">
+      <c r="X16">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:24">
       <c r="A17" s="4" t="s">
         <v>44</v>
       </c>
@@ -31228,16 +31541,16 @@
       <c r="G17" s="2">
         <v>10</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="2"/>
+      <c r="I17" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I17" t="s">
-        <v>144</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="K17" s="6"/>
+      <c r="J17" t="s">
+        <v>392</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>392</v>
+      </c>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
@@ -31246,22 +31559,23 @@
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
-      <c r="T17" s="6">
-        <v>2</v>
-      </c>
-      <c r="U17">
+      <c r="T17" s="6"/>
+      <c r="U17" s="6">
+        <v>2</v>
+      </c>
+      <c r="V17">
         <v>0</v>
       </c>
-      <c r="V17">
+      <c r="W17">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W17">
+      <c r="X17">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:24">
       <c r="A18" s="4" t="s">
         <v>45</v>
       </c>
@@ -31281,35 +31595,36 @@
       <c r="G18" s="2">
         <v>10</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="2"/>
+      <c r="I18" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>144</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="K18" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K18" s="6"/>
-      <c r="L18" t="s">
+      <c r="L18" s="6"/>
+      <c r="M18" t="s">
         <v>143</v>
       </c>
-      <c r="T18">
-        <v>2</v>
-      </c>
       <c r="U18">
+        <v>2</v>
+      </c>
+      <c r="V18">
         <v>65</v>
       </c>
-      <c r="V18">
+      <c r="W18">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>35</v>
       </c>
-      <c r="W18">
+      <c r="X18">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:24">
       <c r="A19" s="4" t="s">
         <v>51</v>
       </c>
@@ -31329,13 +31644,13 @@
       <c r="G19" s="2">
         <v>20</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="2"/>
+      <c r="I19" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>143</v>
       </c>
-      <c r="J19" s="6"/>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
@@ -31345,22 +31660,23 @@
       <c r="Q19" s="6"/>
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
-      <c r="T19" s="6">
+      <c r="T19" s="6"/>
+      <c r="U19" s="6">
         <v>4</v>
       </c>
-      <c r="U19">
+      <c r="V19">
         <v>0</v>
       </c>
-      <c r="V19">
+      <c r="W19">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W19">
+      <c r="X19">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100.00000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:24">
       <c r="A20" s="4" t="s">
         <v>53</v>
       </c>
@@ -31380,17 +31696,17 @@
       <c r="G20" s="2">
         <v>20</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="H20" s="2"/>
+      <c r="I20" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I20" s="6"/>
-      <c r="J20" t="s">
-        <v>143</v>
-      </c>
+      <c r="J20" s="6"/>
       <c r="K20" t="s">
         <v>143</v>
       </c>
-      <c r="L20" s="6"/>
+      <c r="L20" t="s">
+        <v>143</v>
+      </c>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
@@ -31398,22 +31714,23 @@
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
-      <c r="T20" s="6">
+      <c r="T20" s="6"/>
+      <c r="U20" s="6">
         <v>3</v>
       </c>
-      <c r="U20">
+      <c r="V20">
         <v>0</v>
       </c>
-      <c r="V20">
+      <c r="W20">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W20">
+      <c r="X20">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:24">
       <c r="A21" s="3" t="s">
         <v>93</v>
       </c>
@@ -31433,10 +31750,8 @@
       <c r="G21" s="2">
         <v>20</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="H21" s="2"/>
+      <c r="I21" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J21" t="s">
@@ -31448,22 +31763,25 @@
       <c r="L21" t="s">
         <v>143</v>
       </c>
-      <c r="T21">
+      <c r="M21" t="s">
+        <v>143</v>
+      </c>
+      <c r="U21">
         <v>4</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <v>70</v>
       </c>
-      <c r="V21">
+      <c r="W21">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W21">
+      <c r="X21">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30.000000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:24">
       <c r="A22" s="3" t="s">
         <v>94</v>
       </c>
@@ -31483,10 +31801,8 @@
       <c r="G22" s="2">
         <v>10</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="H22" s="2"/>
+      <c r="I22" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J22" t="s">
@@ -31498,22 +31814,25 @@
       <c r="L22" t="s">
         <v>143</v>
       </c>
-      <c r="T22">
-        <v>2</v>
+      <c r="M22" t="s">
+        <v>143</v>
       </c>
       <c r="U22">
+        <v>2</v>
+      </c>
+      <c r="V22">
         <v>70</v>
       </c>
-      <c r="V22">
+      <c r="W22">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W22">
+      <c r="X22">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30.000000000000004</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:24">
       <c r="A23" s="3" t="s">
         <v>186</v>
       </c>
@@ -31533,10 +31852,8 @@
       <c r="G23" s="2">
         <v>10</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="H23" s="2"/>
+      <c r="I23" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J23" t="s">
@@ -31548,22 +31865,25 @@
       <c r="L23" t="s">
         <v>143</v>
       </c>
-      <c r="T23">
+      <c r="M23" t="s">
+        <v>143</v>
+      </c>
+      <c r="U23">
         <v>3</v>
       </c>
-      <c r="U23">
+      <c r="V23">
         <v>70</v>
       </c>
-      <c r="V23">
+      <c r="W23">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W23">
+      <c r="X23">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:24">
       <c r="A24" s="3" t="s">
         <v>89</v>
       </c>
@@ -31583,31 +31903,32 @@
       <c r="G24" s="2">
         <v>10</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H24" s="2"/>
+      <c r="I24" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I24" s="6"/>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
-      <c r="L24" t="s">
+      <c r="L24" s="6"/>
+      <c r="M24" t="s">
         <v>143</v>
       </c>
-      <c r="T24">
-        <v>2</v>
-      </c>
       <c r="U24">
+        <v>2</v>
+      </c>
+      <c r="V24">
         <v>80</v>
       </c>
-      <c r="V24">
+      <c r="W24">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W24">
+      <c r="X24">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:24">
       <c r="A25" s="3" t="s">
         <v>91</v>
       </c>
@@ -31627,35 +31948,36 @@
       <c r="G25" s="2">
         <v>10</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="2"/>
+      <c r="I25" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>143</v>
       </c>
-      <c r="J25" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="K25" s="6"/>
-      <c r="L25" t="s">
+      <c r="K25" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="L25" s="6"/>
+      <c r="M25" t="s">
         <v>143</v>
       </c>
-      <c r="T25">
+      <c r="U25">
         <v>3</v>
       </c>
-      <c r="U25">
+      <c r="V25">
         <v>0</v>
       </c>
-      <c r="V25">
+      <c r="W25">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W25">
+      <c r="X25">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:24">
       <c r="A26" s="3" t="s">
         <v>95</v>
       </c>
@@ -31675,17 +31997,17 @@
       <c r="G26" s="2">
         <v>10</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="2"/>
+      <c r="I26" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I26" s="6"/>
-      <c r="J26" t="s">
-        <v>144</v>
-      </c>
+      <c r="J26" s="6"/>
       <c r="K26" t="s">
+        <v>393</v>
+      </c>
+      <c r="L26" t="s">
         <v>143</v>
       </c>
-      <c r="L26" s="6"/>
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
@@ -31693,22 +32015,23 @@
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="6"/>
-      <c r="T26" s="6">
+      <c r="T26" s="6"/>
+      <c r="U26" s="6">
         <v>3</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <v>0</v>
       </c>
-      <c r="V26">
+      <c r="W26">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W26">
+      <c r="X26">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:24">
       <c r="A27" s="4" t="s">
         <v>1</v>
       </c>
@@ -31728,10 +32051,8 @@
       <c r="G27" s="2">
         <v>20</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I27" t="s">
+      <c r="H27" s="2"/>
+      <c r="I27" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J27" t="s">
@@ -31743,22 +32064,25 @@
       <c r="L27" t="s">
         <v>143</v>
       </c>
-      <c r="T27">
+      <c r="M27" t="s">
+        <v>143</v>
+      </c>
+      <c r="U27">
         <v>4</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>80</v>
       </c>
-      <c r="V27">
+      <c r="W27">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W27">
+      <c r="X27">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:24">
       <c r="A28" s="4" t="s">
         <v>248</v>
       </c>
@@ -31780,14 +32104,12 @@
       <c r="G28" s="2">
         <v>10</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="H28" s="2"/>
+      <c r="I28" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
         <v>143</v>
-      </c>
-      <c r="J28" t="s">
-        <v>144</v>
       </c>
       <c r="K28" t="s">
         <v>144</v>
@@ -31795,22 +32117,25 @@
       <c r="L28" t="s">
         <v>144</v>
       </c>
-      <c r="T28">
+      <c r="M28" t="s">
+        <v>144</v>
+      </c>
+      <c r="U28">
         <v>3</v>
       </c>
-      <c r="U28">
+      <c r="V28">
         <v>70</v>
       </c>
-      <c r="V28">
+      <c r="W28">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W28">
+      <c r="X28">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:24">
       <c r="A29" s="4" t="s">
         <v>8</v>
       </c>
@@ -31832,10 +32157,8 @@
       <c r="G29" s="2">
         <v>10</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I29" t="s">
+      <c r="H29" s="2"/>
+      <c r="I29" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J29" t="s">
@@ -31847,22 +32170,25 @@
       <c r="L29" t="s">
         <v>144</v>
       </c>
-      <c r="T29">
-        <v>2</v>
+      <c r="M29" t="s">
+        <v>144</v>
       </c>
       <c r="U29">
+        <v>2</v>
+      </c>
+      <c r="V29">
         <v>0</v>
       </c>
-      <c r="V29">
+      <c r="W29">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W29">
+      <c r="X29">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:24">
       <c r="A30" s="4" t="s">
         <v>10</v>
       </c>
@@ -31884,37 +32210,38 @@
       <c r="G30" s="2">
         <v>10</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="H30" s="2"/>
+      <c r="I30" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I30" t="s">
+      <c r="J30" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="K30" t="s">
         <v>144</v>
       </c>
-      <c r="J30" t="s">
+      <c r="L30" t="s">
+        <v>407</v>
+      </c>
+      <c r="M30" t="s">
         <v>144</v>
       </c>
-      <c r="K30" t="s">
-        <v>143</v>
-      </c>
-      <c r="L30" t="s">
-        <v>144</v>
-      </c>
-      <c r="T30">
-        <v>2</v>
-      </c>
       <c r="U30">
+        <v>2</v>
+      </c>
+      <c r="V30">
         <v>80</v>
       </c>
-      <c r="V30">
+      <c r="W30">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W30">
+      <c r="X30">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:24">
       <c r="A31" s="4" t="s">
         <v>14</v>
       </c>
@@ -31936,10 +32263,8 @@
       <c r="G31" s="2">
         <v>10</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I31" t="s">
+      <c r="H31" s="2"/>
+      <c r="I31" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J31" t="s">
@@ -31951,22 +32276,25 @@
       <c r="L31" t="s">
         <v>144</v>
       </c>
-      <c r="T31">
-        <v>2</v>
+      <c r="M31" t="s">
+        <v>144</v>
       </c>
       <c r="U31">
+        <v>2</v>
+      </c>
+      <c r="V31">
         <v>0</v>
       </c>
-      <c r="V31">
+      <c r="W31">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W31">
+      <c r="X31">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:24">
       <c r="A32" s="4" t="s">
         <v>15</v>
       </c>
@@ -31988,42 +32316,43 @@
       <c r="G32" s="2">
         <v>10</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" s="2"/>
+      <c r="I32" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>144</v>
       </c>
-      <c r="J32" s="6" t="s">
+      <c r="K32" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6" t="s">
+      <c r="L32" s="6"/>
+      <c r="M32" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="M32" s="6"/>
       <c r="N32" s="6"/>
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="6"/>
-      <c r="T32" s="6">
-        <v>2</v>
-      </c>
-      <c r="U32">
+      <c r="T32" s="6"/>
+      <c r="U32" s="6">
+        <v>2</v>
+      </c>
+      <c r="V32">
         <v>0</v>
       </c>
-      <c r="V32">
+      <c r="W32">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W32">
+      <c r="X32">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:24">
       <c r="A33" s="4" t="s">
         <v>16</v>
       </c>
@@ -32045,17 +32374,19 @@
       <c r="G33" s="2">
         <v>10</v>
       </c>
-      <c r="H33" s="2" t="s">
+      <c r="H33" s="2"/>
+      <c r="I33" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I33" s="6"/>
-      <c r="J33" t="s">
+      <c r="J33" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="K33" t="s">
         <v>144</v>
       </c>
-      <c r="K33" t="s">
-        <v>143</v>
-      </c>
-      <c r="L33" s="6"/>
+      <c r="L33" t="s">
+        <v>407</v>
+      </c>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
@@ -32063,22 +32394,23 @@
       <c r="Q33" s="6"/>
       <c r="R33" s="6"/>
       <c r="S33" s="6"/>
-      <c r="T33" s="6">
-        <v>2</v>
-      </c>
-      <c r="U33">
+      <c r="T33" s="6"/>
+      <c r="U33" s="6">
+        <v>2</v>
+      </c>
+      <c r="V33">
         <v>70</v>
       </c>
-      <c r="V33">
+      <c r="W33">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W33">
+      <c r="X33">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:24">
       <c r="A34" s="4" t="s">
         <v>18</v>
       </c>
@@ -32100,13 +32432,11 @@
       <c r="G34" s="2">
         <v>10</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H34" s="2"/>
+      <c r="I34" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I34" t="s">
-        <v>144</v>
-      </c>
-      <c r="J34" s="6" t="s">
+      <c r="J34" t="s">
         <v>144</v>
       </c>
       <c r="K34" s="6" t="s">
@@ -32115,29 +32445,32 @@
       <c r="L34" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="M34" s="6"/>
+      <c r="M34" s="6" t="s">
+        <v>144</v>
+      </c>
       <c r="N34" s="6"/>
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
       <c r="S34" s="6"/>
-      <c r="T34" s="6">
-        <v>2</v>
-      </c>
-      <c r="U34">
+      <c r="T34" s="6"/>
+      <c r="U34" s="6">
+        <v>2</v>
+      </c>
+      <c r="V34">
         <v>70</v>
       </c>
-      <c r="V34">
+      <c r="W34">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W34">
+      <c r="X34">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:24">
       <c r="A35" s="4" t="s">
         <v>24</v>
       </c>
@@ -32159,13 +32492,11 @@
       <c r="G35" s="2">
         <v>10</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H35" s="2"/>
+      <c r="I35" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I35" t="s">
-        <v>144</v>
-      </c>
-      <c r="J35" s="6" t="s">
+      <c r="J35" t="s">
         <v>144</v>
       </c>
       <c r="K35" s="6" t="s">
@@ -32174,29 +32505,32 @@
       <c r="L35" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="M35" s="6"/>
+      <c r="M35" s="6" t="s">
+        <v>144</v>
+      </c>
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
       <c r="P35" s="6"/>
       <c r="Q35" s="6"/>
       <c r="R35" s="6"/>
       <c r="S35" s="6"/>
-      <c r="T35" s="6">
+      <c r="T35" s="6"/>
+      <c r="U35" s="6">
         <v>3</v>
       </c>
-      <c r="U35">
+      <c r="V35">
         <v>0</v>
       </c>
-      <c r="V35">
+      <c r="W35">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W35">
+      <c r="X35">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:24">
       <c r="A36" s="8" t="s">
         <v>21</v>
       </c>
@@ -32216,40 +32550,41 @@
       <c r="G36" s="2">
         <v>10</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H36" s="2"/>
+      <c r="I36" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I36" t="s">
+      <c r="J36" t="s">
         <v>144</v>
       </c>
-      <c r="J36" s="6"/>
       <c r="K36" s="6"/>
-      <c r="L36" s="6" t="s">
+      <c r="L36" s="6"/>
+      <c r="M36" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="M36" s="6"/>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
       <c r="P36" s="6"/>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="6"/>
-      <c r="T36" s="6">
-        <v>2</v>
-      </c>
-      <c r="U36">
+      <c r="T36" s="6"/>
+      <c r="U36" s="6">
+        <v>2</v>
+      </c>
+      <c r="V36">
         <v>80</v>
       </c>
-      <c r="V36">
+      <c r="W36">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W36">
+      <c r="X36">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:24">
       <c r="A37" s="3" t="s">
         <v>106</v>
       </c>
@@ -32269,10 +32604,8 @@
       <c r="G37" s="2">
         <v>20</v>
       </c>
-      <c r="H37" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I37" t="s">
+      <c r="H37" s="2"/>
+      <c r="I37" s="2" t="s">
         <v>143</v>
       </c>
       <c r="J37" t="s">
@@ -32284,22 +32617,25 @@
       <c r="L37" t="s">
         <v>143</v>
       </c>
-      <c r="T37">
+      <c r="M37" t="s">
+        <v>144</v>
+      </c>
+      <c r="U37">
         <v>4</v>
       </c>
-      <c r="U37">
+      <c r="V37">
         <v>70</v>
       </c>
-      <c r="V37">
+      <c r="W37">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W37">
+      <c r="X37">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30.000000000000004</v>
       </c>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:24">
       <c r="A38" s="3" t="s">
         <v>188</v>
       </c>
@@ -32319,10 +32655,8 @@
       <c r="G38" s="2">
         <v>10</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I38" t="s">
+      <c r="H38" s="2"/>
+      <c r="I38" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J38" t="s">
@@ -32334,22 +32668,25 @@
       <c r="L38" t="s">
         <v>144</v>
       </c>
-      <c r="T38">
-        <v>2</v>
+      <c r="M38" t="s">
+        <v>144</v>
       </c>
       <c r="U38">
+        <v>2</v>
+      </c>
+      <c r="V38">
         <v>80</v>
       </c>
-      <c r="V38">
+      <c r="W38">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W38">
+      <c r="X38">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:23">
+    <row r="39" spans="1:24">
       <c r="A39" s="3" t="s">
         <v>108</v>
       </c>
@@ -32371,10 +32708,8 @@
       <c r="G39" s="46">
         <v>10</v>
       </c>
-      <c r="H39" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="I39" t="s">
+      <c r="H39" s="46"/>
+      <c r="I39" s="28" t="s">
         <v>144</v>
       </c>
       <c r="J39" t="s">
@@ -32386,22 +32721,25 @@
       <c r="L39" t="s">
         <v>144</v>
       </c>
-      <c r="T39">
-        <v>2</v>
+      <c r="M39" t="s">
+        <v>144</v>
       </c>
       <c r="U39">
+        <v>2</v>
+      </c>
+      <c r="V39">
         <v>80</v>
       </c>
-      <c r="V39">
+      <c r="W39">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W39">
+      <c r="X39">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:23">
+    <row r="40" spans="1:24">
       <c r="A40" s="3" t="s">
         <v>189</v>
       </c>
@@ -32423,17 +32761,19 @@
       <c r="G40" s="2">
         <v>10</v>
       </c>
-      <c r="H40" s="2" t="s">
+      <c r="H40" s="2"/>
+      <c r="I40" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6" t="s">
+      <c r="J40" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="K40" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K40" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="L40" s="6"/>
+      <c r="L40" t="s">
+        <v>407</v>
+      </c>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
       <c r="O40" s="6"/>
@@ -32441,22 +32781,23 @@
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
       <c r="S40" s="6"/>
-      <c r="T40" s="6">
-        <v>2</v>
-      </c>
-      <c r="U40">
+      <c r="T40" s="6"/>
+      <c r="U40" s="6">
+        <v>2</v>
+      </c>
+      <c r="V40">
         <v>60</v>
       </c>
-      <c r="V40">
+      <c r="W40">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="W40">
+      <c r="X40">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:24">
       <c r="A41" s="3" t="s">
         <v>109</v>
       </c>
@@ -32478,10 +32819,8 @@
       <c r="G41" s="2">
         <v>10</v>
       </c>
-      <c r="H41" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I41" t="s">
+      <c r="H41" s="2"/>
+      <c r="I41" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J41" t="s">
@@ -32493,22 +32832,25 @@
       <c r="L41" t="s">
         <v>144</v>
       </c>
-      <c r="T41">
-        <v>2</v>
+      <c r="M41" t="s">
+        <v>144</v>
       </c>
       <c r="U41">
+        <v>2</v>
+      </c>
+      <c r="V41">
         <v>0</v>
       </c>
-      <c r="V41">
+      <c r="W41">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W41">
+      <c r="X41">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="42" spans="1:23">
+    <row r="42" spans="1:24">
       <c r="A42" s="3" t="s">
         <v>100</v>
       </c>
@@ -32530,19 +32872,19 @@
       <c r="G42" s="2">
         <v>10</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="H42" s="2"/>
+      <c r="I42" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I42" t="s">
+      <c r="J42" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="K42" t="s">
         <v>144</v>
       </c>
-      <c r="J42" t="s">
-        <v>144</v>
-      </c>
-      <c r="K42" t="s">
-        <v>143</v>
-      </c>
-      <c r="L42" s="6"/>
+      <c r="L42" t="s">
+        <v>407</v>
+      </c>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
       <c r="O42" s="6"/>
@@ -32550,22 +32892,23 @@
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
       <c r="S42" s="6"/>
-      <c r="T42" s="6">
-        <v>2</v>
-      </c>
-      <c r="U42">
+      <c r="T42" s="6"/>
+      <c r="U42" s="6">
+        <v>2</v>
+      </c>
+      <c r="V42">
         <v>80</v>
       </c>
-      <c r="V42">
+      <c r="W42">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W42">
+      <c r="X42">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="43" spans="1:23">
+    <row r="43" spans="1:24">
       <c r="A43" s="3" t="s">
         <v>102</v>
       </c>
@@ -32585,42 +32928,43 @@
       <c r="G43" s="2">
         <v>10</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="H43" s="2"/>
+      <c r="I43" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I43" t="s">
+      <c r="J43" t="s">
         <v>144</v>
       </c>
-      <c r="J43" s="6" t="s">
+      <c r="K43" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6" t="s">
+      <c r="L43" s="6"/>
+      <c r="M43" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="M43" s="6"/>
       <c r="N43" s="6"/>
       <c r="O43" s="6"/>
       <c r="P43" s="6"/>
       <c r="Q43" s="6"/>
       <c r="R43" s="6"/>
       <c r="S43" s="6"/>
-      <c r="T43" s="6">
-        <v>2</v>
-      </c>
-      <c r="U43">
+      <c r="T43" s="6"/>
+      <c r="U43" s="6">
+        <v>2</v>
+      </c>
+      <c r="V43">
         <v>80</v>
       </c>
-      <c r="V43">
+      <c r="W43">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W43">
+      <c r="X43">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:24">
       <c r="A44" s="3" t="s">
         <v>104</v>
       </c>
@@ -32640,42 +32984,43 @@
       <c r="G44" s="2">
         <v>10</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="H44" s="2"/>
+      <c r="I44" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I44" t="s">
+      <c r="J44" t="s">
         <v>144</v>
       </c>
-      <c r="J44" s="6" t="s">
+      <c r="K44" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6" t="s">
+      <c r="L44" s="6"/>
+      <c r="M44" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
       <c r="P44" s="6"/>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
       <c r="S44" s="6"/>
-      <c r="T44" s="6">
-        <v>2</v>
-      </c>
-      <c r="U44">
+      <c r="T44" s="6"/>
+      <c r="U44" s="6">
+        <v>2</v>
+      </c>
+      <c r="V44">
         <v>80</v>
       </c>
-      <c r="V44">
+      <c r="W44">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W44">
+      <c r="X44">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:24">
       <c r="A45" s="9" t="s">
         <v>47</v>
       </c>
@@ -32695,11 +33040,9 @@
       <c r="G45" s="2">
         <v>30</v>
       </c>
-      <c r="H45" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I45" t="s">
-        <v>143</v>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2" t="s">
+        <v>408</v>
       </c>
       <c r="J45" t="s">
         <v>143</v>
@@ -32707,147 +33050,126 @@
       <c r="K45" t="s">
         <v>143</v>
       </c>
-      <c r="L45" t="s">
-        <v>143</v>
-      </c>
-      <c r="T45">
+      <c r="U45">
         <v>0.5</v>
       </c>
-      <c r="U45">
+      <c r="V45">
         <v>0</v>
       </c>
-      <c r="V45">
+      <c r="W45">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W45">
+      <c r="X45">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:23">
-      <c r="A46" s="4" t="s">
+    <row r="46" spans="1:24">
+      <c r="A46" s="47" t="s">
+        <v>395</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C46" s="47"/>
+      <c r="D46" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F46" s="2">
+        <v>6</v>
+      </c>
+      <c r="G46" s="2">
+        <v>30</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I46" s="28"/>
+      <c r="J46" s="50"/>
+      <c r="L46" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="M46" s="50"/>
+      <c r="O46" s="50"/>
+      <c r="P46" s="50"/>
+      <c r="Q46" s="50"/>
+      <c r="R46" s="50"/>
+      <c r="U46">
+        <v>0.5</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46" s="51">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X46" s="51">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24">
+      <c r="A47" s="47" t="s">
+        <v>396</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C47" s="47"/>
+      <c r="D47" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F47" s="2">
+        <v>6</v>
+      </c>
+      <c r="G47" s="2">
+        <v>30</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I47" s="28"/>
+      <c r="J47" s="50"/>
+      <c r="L47" s="50"/>
+      <c r="M47" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="O47" s="50"/>
+      <c r="P47" s="50"/>
+      <c r="Q47" s="50"/>
+      <c r="R47" s="50"/>
+      <c r="U47">
+        <v>0.5</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47" s="51">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X47" s="51">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24">
+      <c r="A48" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B48" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F46" s="2">
-        <v>7</v>
-      </c>
-      <c r="G46" s="2">
-        <v>10</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I46" t="s">
-        <v>144</v>
-      </c>
-      <c r="J46" t="s">
-        <v>144</v>
-      </c>
-      <c r="K46" t="s">
-        <v>143</v>
-      </c>
-      <c r="L46" s="6"/>
-      <c r="M46" s="6"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="6"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6">
-        <v>2</v>
-      </c>
-      <c r="U46">
-        <v>70</v>
-      </c>
-      <c r="V46">
-        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="W46">
-        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23">
-      <c r="A47" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F47" s="2">
-        <v>7</v>
-      </c>
-      <c r="G47" s="2">
-        <v>10</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I47" t="s">
-        <v>144</v>
-      </c>
-      <c r="J47" t="s">
-        <v>144</v>
-      </c>
-      <c r="K47" t="s">
-        <v>144</v>
-      </c>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6"/>
-      <c r="N47" s="6"/>
-      <c r="O47" s="6"/>
-      <c r="P47" s="6"/>
-      <c r="Q47" s="6"/>
-      <c r="R47" s="6"/>
-      <c r="S47" s="6"/>
-      <c r="T47" s="6">
-        <v>2</v>
-      </c>
-      <c r="U47">
-        <v>70</v>
-      </c>
-      <c r="V47">
-        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="W47">
-        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23">
-      <c r="A48" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>180</v>
@@ -32861,15 +33183,19 @@
       <c r="G48" s="2">
         <v>10</v>
       </c>
-      <c r="H48" s="2" t="s">
+      <c r="H48" s="2"/>
+      <c r="I48" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I48" t="s">
+      <c r="J48" t="s">
         <v>144</v>
       </c>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
+      <c r="K48" t="s">
+        <v>144</v>
+      </c>
+      <c r="L48" t="s">
+        <v>143</v>
+      </c>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
       <c r="O48" s="6"/>
@@ -32877,30 +33203,31 @@
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
       <c r="S48" s="6"/>
-      <c r="T48" s="6">
-        <v>2</v>
-      </c>
-      <c r="U48">
-        <v>75</v>
+      <c r="T48" s="6"/>
+      <c r="U48" s="6">
+        <v>2</v>
       </c>
       <c r="V48">
+        <v>70</v>
+      </c>
+      <c r="W48">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>25</v>
-      </c>
-      <c r="W48">
+        <v>30</v>
+      </c>
+      <c r="X48">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24">
       <c r="A49" s="4" t="s">
-        <v>66</v>
+        <v>238</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>67</v>
+        <v>237</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>135</v>
+        <v>251</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>180</v>
@@ -32914,10 +33241,8 @@
       <c r="G49" s="2">
         <v>10</v>
       </c>
-      <c r="H49" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I49" t="s">
+      <c r="H49" s="2"/>
+      <c r="I49" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J49" t="s">
@@ -32926,7 +33251,9 @@
       <c r="K49" t="s">
         <v>144</v>
       </c>
-      <c r="L49" s="6"/>
+      <c r="L49" t="s">
+        <v>144</v>
+      </c>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
       <c r="O49" s="6"/>
@@ -32934,30 +33261,31 @@
       <c r="Q49" s="6"/>
       <c r="R49" s="6"/>
       <c r="S49" s="6"/>
-      <c r="T49" s="6">
-        <v>3</v>
-      </c>
-      <c r="U49">
+      <c r="T49" s="6"/>
+      <c r="U49" s="6">
+        <v>2</v>
+      </c>
+      <c r="V49">
         <v>70</v>
       </c>
-      <c r="V49">
+      <c r="W49">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W49">
+      <c r="X49">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:23">
+    <row r="50" spans="1:24">
       <c r="A50" s="4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>70</v>
+        <v>294</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>180</v>
@@ -32971,18 +33299,14 @@
       <c r="G50" s="2">
         <v>10</v>
       </c>
-      <c r="H50" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I50" t="s">
+      <c r="H50" s="2"/>
+      <c r="I50" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J50" t="s">
         <v>144</v>
       </c>
-      <c r="K50" t="s">
-        <v>144</v>
-      </c>
+      <c r="K50" s="6"/>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
@@ -32991,30 +33315,31 @@
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
       <c r="S50" s="6"/>
-      <c r="T50" s="6">
-        <v>2</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
+      <c r="T50" s="6"/>
+      <c r="U50" s="6">
+        <v>2</v>
       </c>
       <c r="V50">
+        <v>75</v>
+      </c>
+      <c r="W50">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="W50">
+        <v>25</v>
+      </c>
+      <c r="X50">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:23">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24">
       <c r="A51" s="4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>180</v>
@@ -33028,10 +33353,8 @@
       <c r="G51" s="2">
         <v>10</v>
       </c>
-      <c r="H51" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I51" t="s">
+      <c r="H51" s="2"/>
+      <c r="I51" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J51" t="s">
@@ -33040,7 +33363,9 @@
       <c r="K51" t="s">
         <v>144</v>
       </c>
-      <c r="L51" s="6"/>
+      <c r="L51" t="s">
+        <v>144</v>
+      </c>
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
       <c r="O51" s="6"/>
@@ -33048,36 +33373,37 @@
       <c r="Q51" s="6"/>
       <c r="R51" s="6"/>
       <c r="S51" s="6"/>
-      <c r="T51" s="6">
-        <v>2</v>
-      </c>
-      <c r="U51">
-        <v>50</v>
+      <c r="T51" s="6"/>
+      <c r="U51" s="6">
+        <v>3</v>
       </c>
       <c r="V51">
+        <v>70</v>
+      </c>
+      <c r="W51">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>50</v>
-      </c>
-      <c r="W51">
+        <v>30</v>
+      </c>
+      <c r="X51">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:23">
-      <c r="A52" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>154</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24">
+      <c r="A52" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>148</v>
+      <c r="E52" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F52" s="2">
         <v>7</v>
@@ -33085,15 +33411,19 @@
       <c r="G52" s="2">
         <v>10</v>
       </c>
-      <c r="H52" s="2" t="s">
+      <c r="H52" s="2"/>
+      <c r="I52" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I52" t="s">
+      <c r="J52" t="s">
         <v>144</v>
       </c>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
+      <c r="K52" t="s">
+        <v>144</v>
+      </c>
+      <c r="L52" t="s">
+        <v>144</v>
+      </c>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
@@ -33101,36 +33431,37 @@
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
       <c r="S52" s="6"/>
-      <c r="T52" s="6">
-        <v>2</v>
-      </c>
-      <c r="U52">
-        <v>80</v>
+      <c r="T52" s="6"/>
+      <c r="U52" s="6">
+        <v>2</v>
       </c>
       <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>20</v>
-      </c>
-      <c r="W52">
+        <v>100</v>
+      </c>
+      <c r="X52">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" spans="1:23">
-      <c r="A53" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>153</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24">
+      <c r="A53" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>148</v>
+      <c r="E53" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="F53" s="2">
         <v>7</v>
@@ -33138,10 +33469,8 @@
       <c r="G53" s="2">
         <v>10</v>
       </c>
-      <c r="H53" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I53" t="s">
+      <c r="H53" s="2"/>
+      <c r="I53" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J53" t="s">
@@ -33150,7 +33479,9 @@
       <c r="K53" t="s">
         <v>144</v>
       </c>
-      <c r="L53" s="6"/>
+      <c r="L53" t="s">
+        <v>144</v>
+      </c>
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
       <c r="O53" s="6"/>
@@ -33158,30 +33489,31 @@
       <c r="Q53" s="6"/>
       <c r="R53" s="6"/>
       <c r="S53" s="6"/>
-      <c r="T53" s="6">
-        <v>2</v>
-      </c>
-      <c r="U53">
-        <v>70</v>
+      <c r="T53" s="6"/>
+      <c r="U53" s="6">
+        <v>2</v>
       </c>
       <c r="V53">
+        <v>50</v>
+      </c>
+      <c r="W53">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="W53">
+        <v>50</v>
+      </c>
+      <c r="X53">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="54" spans="1:23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24">
       <c r="A54" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>180</v>
@@ -33195,18 +33527,14 @@
       <c r="G54" s="2">
         <v>10</v>
       </c>
-      <c r="H54" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I54" t="s">
+      <c r="H54" s="2"/>
+      <c r="I54" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J54" t="s">
         <v>144</v>
       </c>
-      <c r="K54" t="s">
-        <v>144</v>
-      </c>
+      <c r="K54" s="6"/>
       <c r="L54" s="6"/>
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
@@ -33215,30 +33543,31 @@
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
       <c r="S54" s="6"/>
-      <c r="T54" s="6">
-        <v>2</v>
-      </c>
-      <c r="U54">
-        <v>40</v>
+      <c r="T54" s="6"/>
+      <c r="U54" s="6">
+        <v>2</v>
       </c>
       <c r="V54">
+        <v>80</v>
+      </c>
+      <c r="W54">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>60</v>
-      </c>
-      <c r="W54">
+        <v>20</v>
+      </c>
+      <c r="X54">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="55" spans="1:23">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24">
       <c r="A55" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>180</v>
@@ -33252,17 +33581,19 @@
       <c r="G55" s="2">
         <v>10</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="H55" s="2"/>
+      <c r="I55" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I55" s="6"/>
       <c r="J55" t="s">
         <v>144</v>
       </c>
       <c r="K55" t="s">
-        <v>143</v>
-      </c>
-      <c r="L55" s="6"/>
+        <v>144</v>
+      </c>
+      <c r="L55" t="s">
+        <v>144</v>
+      </c>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
       <c r="O55" s="6"/>
@@ -33270,30 +33601,31 @@
       <c r="Q55" s="6"/>
       <c r="R55" s="6"/>
       <c r="S55" s="6"/>
-      <c r="T55" s="6">
-        <v>2</v>
-      </c>
-      <c r="U55">
-        <v>80</v>
+      <c r="T55" s="6"/>
+      <c r="U55" s="6">
+        <v>2</v>
       </c>
       <c r="V55">
+        <v>70</v>
+      </c>
+      <c r="W55">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>20</v>
-      </c>
-      <c r="W55">
+        <v>30</v>
+      </c>
+      <c r="X55">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" spans="1:23">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24">
       <c r="A56" s="3" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>180</v>
@@ -33307,10 +33639,8 @@
       <c r="G56" s="2">
         <v>10</v>
       </c>
-      <c r="H56" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I56" t="s">
+      <c r="H56" s="2"/>
+      <c r="I56" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J56" t="s">
@@ -33319,7 +33649,9 @@
       <c r="K56" t="s">
         <v>144</v>
       </c>
-      <c r="L56" s="6"/>
+      <c r="L56" t="s">
+        <v>144</v>
+      </c>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
       <c r="O56" s="6"/>
@@ -33327,30 +33659,31 @@
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
       <c r="S56" s="6"/>
-      <c r="T56" s="6">
-        <v>3</v>
-      </c>
-      <c r="U56">
-        <v>0</v>
+      <c r="T56" s="6"/>
+      <c r="U56" s="6">
+        <v>2</v>
       </c>
       <c r="V56">
+        <v>40</v>
+      </c>
+      <c r="W56">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="W56">
+        <v>60</v>
+      </c>
+      <c r="X56">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" spans="1:23">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24">
       <c r="A57" s="3" t="s">
-        <v>116</v>
+        <v>193</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>180</v>
@@ -33364,19 +33697,17 @@
       <c r="G57" s="2">
         <v>10</v>
       </c>
-      <c r="H57" s="2" t="s">
+      <c r="H57" s="2"/>
+      <c r="I57" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I57" t="s">
-        <v>144</v>
-      </c>
-      <c r="J57" t="s">
-        <v>144</v>
-      </c>
+      <c r="J57" s="6"/>
       <c r="K57" t="s">
         <v>144</v>
       </c>
-      <c r="L57" s="6"/>
+      <c r="L57" t="s">
+        <v>143</v>
+      </c>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
       <c r="O57" s="6"/>
@@ -33384,30 +33715,31 @@
       <c r="Q57" s="6"/>
       <c r="R57" s="6"/>
       <c r="S57" s="6"/>
-      <c r="T57" s="6">
-        <v>2</v>
-      </c>
-      <c r="U57">
-        <v>70</v>
+      <c r="T57" s="6"/>
+      <c r="U57" s="6">
+        <v>2</v>
       </c>
       <c r="V57">
+        <v>80</v>
+      </c>
+      <c r="W57">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="W57">
+        <v>20</v>
+      </c>
+      <c r="X57">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="58" spans="1:23">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24">
       <c r="A58" s="3" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>180</v>
@@ -33421,15 +33753,19 @@
       <c r="G58" s="2">
         <v>10</v>
       </c>
-      <c r="H58" s="2" t="s">
+      <c r="H58" s="2"/>
+      <c r="I58" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="I58" t="s">
+      <c r="J58" t="s">
         <v>144</v>
       </c>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
+      <c r="K58" t="s">
+        <v>144</v>
+      </c>
+      <c r="L58" t="s">
+        <v>144</v>
+      </c>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
       <c r="O58" s="6"/>
@@ -33437,30 +33773,31 @@
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
       <c r="S58" s="6"/>
-      <c r="T58" s="6">
-        <v>2</v>
-      </c>
-      <c r="U58">
-        <v>50</v>
+      <c r="T58" s="6"/>
+      <c r="U58" s="6">
+        <v>3</v>
       </c>
       <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>50</v>
-      </c>
-      <c r="W58">
+        <v>100</v>
+      </c>
+      <c r="X58">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="59" spans="1:23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24">
       <c r="A59" s="3" t="s">
-        <v>194</v>
+        <v>116</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>180</v>
@@ -33474,10 +33811,8 @@
       <c r="G59" s="2">
         <v>10</v>
       </c>
-      <c r="H59" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I59" t="s">
+      <c r="H59" s="2"/>
+      <c r="I59" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J59" t="s">
@@ -33486,7 +33821,9 @@
       <c r="K59" t="s">
         <v>144</v>
       </c>
-      <c r="L59" s="6"/>
+      <c r="L59" t="s">
+        <v>144</v>
+      </c>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
       <c r="O59" s="6"/>
@@ -33494,30 +33831,31 @@
       <c r="Q59" s="6"/>
       <c r="R59" s="6"/>
       <c r="S59" s="6"/>
-      <c r="T59" s="6">
-        <v>3</v>
-      </c>
-      <c r="U59">
-        <v>60</v>
+      <c r="T59" s="6"/>
+      <c r="U59" s="6">
+        <v>2</v>
       </c>
       <c r="V59">
+        <v>70</v>
+      </c>
+      <c r="W59">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>40</v>
-      </c>
-      <c r="W59">
+        <v>30</v>
+      </c>
+      <c r="X59">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="60" spans="1:23">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24">
       <c r="A60" s="3" t="s">
-        <v>195</v>
+        <v>68</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>180</v>
@@ -33531,18 +33869,14 @@
       <c r="G60" s="2">
         <v>10</v>
       </c>
-      <c r="H60" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I60" t="s">
+      <c r="H60" s="2"/>
+      <c r="I60" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J60" t="s">
         <v>144</v>
       </c>
-      <c r="K60" t="s">
-        <v>144</v>
-      </c>
+      <c r="K60" s="6"/>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
@@ -33551,47 +33885,46 @@
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
       <c r="S60" s="6"/>
-      <c r="T60" s="6">
-        <v>2</v>
-      </c>
-      <c r="U60">
-        <v>0</v>
+      <c r="T60" s="6"/>
+      <c r="U60" s="6">
+        <v>2</v>
       </c>
       <c r="V60">
+        <v>50</v>
+      </c>
+      <c r="W60">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="W60">
+        <v>50</v>
+      </c>
+      <c r="X60">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="1:23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24">
       <c r="A61" s="3" t="s">
-        <v>239</v>
+        <v>194</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>240</v>
+        <v>118</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D61" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>180</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F61" s="4">
+      <c r="F61" s="2">
         <v>7</v>
       </c>
-      <c r="G61" s="28">
+      <c r="G61" s="2">
         <v>10</v>
       </c>
-      <c r="H61" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="I61" t="s">
+      <c r="H61" s="2"/>
+      <c r="I61" s="2" t="s">
         <v>144</v>
       </c>
       <c r="J61" t="s">
@@ -33600,7 +33933,9 @@
       <c r="K61" t="s">
         <v>144</v>
       </c>
-      <c r="L61" s="6"/>
+      <c r="L61" t="s">
+        <v>144</v>
+      </c>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
       <c r="O61" s="6"/>
@@ -33608,54 +33943,57 @@
       <c r="Q61" s="6"/>
       <c r="R61" s="6"/>
       <c r="S61" s="6"/>
-      <c r="T61" s="6">
-        <v>2</v>
-      </c>
-      <c r="U61">
-        <v>50</v>
+      <c r="T61" s="6"/>
+      <c r="U61" s="6">
+        <v>3</v>
       </c>
       <c r="V61">
+        <v>60</v>
+      </c>
+      <c r="W61">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>50</v>
-      </c>
-      <c r="W61">
+        <v>40</v>
+      </c>
+      <c r="X61">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="62" spans="1:23">
-      <c r="A62" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24">
+      <c r="A62" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>162</v>
+      </c>
       <c r="D62" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>149</v>
+      <c r="E62" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="F62" s="2">
         <v>7</v>
       </c>
       <c r="G62" s="2">
-        <v>60</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I62" t="s">
-        <v>143</v>
+        <v>10</v>
+      </c>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="J62" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K62" t="s">
-        <v>143</v>
-      </c>
-      <c r="L62" s="6"/>
+        <v>144</v>
+      </c>
+      <c r="L62" t="s">
+        <v>144</v>
+      </c>
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
       <c r="O62" s="6"/>
@@ -33663,1601 +34001,1654 @@
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
       <c r="S62" s="6"/>
-      <c r="T62" s="6">
+      <c r="T62" s="6"/>
+      <c r="U62" s="6">
+        <v>2</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X62">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24">
+      <c r="A63" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D63" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F63" s="4">
+        <v>7</v>
+      </c>
+      <c r="G63" s="28">
+        <v>10</v>
+      </c>
+      <c r="H63" s="28"/>
+      <c r="I63" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="J63" t="s">
+        <v>144</v>
+      </c>
+      <c r="K63" t="s">
+        <v>144</v>
+      </c>
+      <c r="L63" t="s">
+        <v>144</v>
+      </c>
+      <c r="M63" s="6"/>
+      <c r="N63" s="6"/>
+      <c r="O63" s="6"/>
+      <c r="P63" s="6"/>
+      <c r="Q63" s="6"/>
+      <c r="R63" s="6"/>
+      <c r="S63" s="6"/>
+      <c r="T63" s="6"/>
+      <c r="U63" s="6">
+        <v>2</v>
+      </c>
+      <c r="V63">
+        <v>50</v>
+      </c>
+      <c r="W63">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>50</v>
+      </c>
+      <c r="X63">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24">
+      <c r="A64" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F64" s="2">
+        <v>7</v>
+      </c>
+      <c r="G64" s="2">
+        <v>60</v>
+      </c>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="J64" t="s">
+        <v>143</v>
+      </c>
+      <c r="K64" t="s">
+        <v>143</v>
+      </c>
+      <c r="M64" s="6"/>
+      <c r="N64" s="6"/>
+      <c r="O64" s="6"/>
+      <c r="P64" s="6"/>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6"/>
+      <c r="T64" s="6"/>
+      <c r="U64" s="6">
         <v>0.5</v>
       </c>
-      <c r="U62">
+      <c r="V64">
         <v>25</v>
       </c>
-      <c r="V62">
+      <c r="W64">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>75</v>
       </c>
-      <c r="W62">
+      <c r="X64">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>75</v>
       </c>
     </row>
-    <row r="63" spans="1:23">
-      <c r="A63" s="3" t="s">
+    <row r="65" spans="1:24">
+      <c r="A65" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F65" s="2">
+        <v>7</v>
+      </c>
+      <c r="G65" s="2">
+        <v>60</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I65" s="28"/>
+      <c r="J65" s="50"/>
+      <c r="L65" t="s">
+        <v>143</v>
+      </c>
+      <c r="M65" s="52"/>
+      <c r="N65" s="6"/>
+      <c r="O65" s="52"/>
+      <c r="P65" s="52"/>
+      <c r="Q65" s="52"/>
+      <c r="R65" s="52"/>
+      <c r="S65" s="6"/>
+      <c r="T65" s="6"/>
+      <c r="U65" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="V65">
+        <v>25</v>
+      </c>
+      <c r="W65" s="51">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>75</v>
+      </c>
+      <c r="X65" s="51">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24">
+      <c r="A66" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B66" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D63" s="28" t="s">
+      <c r="D66" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E66" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F66" s="4">
         <v>7</v>
       </c>
-      <c r="G63" s="2">
+      <c r="G66" s="2">
         <v>10</v>
       </c>
-      <c r="H63" s="2"/>
-      <c r="M63" t="s">
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="N66" t="s">
         <v>144</v>
       </c>
-      <c r="N63" t="s">
+      <c r="O66" t="s">
         <v>144</v>
       </c>
-      <c r="T63">
-        <f>INDEX(T2:T62,MATCH(Table2[[#This Row],[Alternative Module Code]],A2:A62,0))</f>
+      <c r="U66">
+        <f>INDEX(U2:U64,MATCH(Table2[[#This Row],[Alternative Module Code]],A2:A64,0))</f>
         <v>3</v>
       </c>
-      <c r="U63">
+      <c r="V66">
         <v>70</v>
       </c>
-      <c r="V63">
+      <c r="W66">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W63">
+      <c r="X66">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="1:23">
-      <c r="A64" s="3" t="s">
+    <row r="67" spans="1:24">
+      <c r="A67" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B67" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D64" s="28" t="s">
+      <c r="D67" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E67" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F64" s="4">
+      <c r="F67" s="4">
         <v>7</v>
       </c>
-      <c r="G64" s="2">
+      <c r="G67" s="2">
         <v>10</v>
       </c>
-      <c r="H64" s="2"/>
-      <c r="M64" t="s">
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="N67" t="s">
         <v>144</v>
       </c>
-      <c r="N64" t="s">
+      <c r="O67" t="s">
         <v>144</v>
       </c>
-      <c r="O64" t="s">
+      <c r="P67" t="s">
         <v>144</v>
       </c>
-      <c r="R64" t="s">
+      <c r="S67" t="s">
         <v>144</v>
       </c>
-      <c r="T64">
-        <f>INDEX(T3:T63,MATCH(Table2[[#This Row],[Alternative Module Code]],A3:A63,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U64">
+      <c r="U67">
+        <f>INDEX(U3:U66,MATCH(Table2[[#This Row],[Alternative Module Code]],A3:A66,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V67">
         <v>0</v>
       </c>
-      <c r="V64">
+      <c r="W67">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W64">
+      <c r="X67">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:23">
-      <c r="A65" s="3" t="s">
+    <row r="68" spans="1:24">
+      <c r="A68" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B68" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D65" s="28" t="s">
+      <c r="D68" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F65" s="4">
+      <c r="F68" s="4">
         <v>7</v>
       </c>
-      <c r="G65" s="2">
+      <c r="G68" s="2">
         <v>10</v>
       </c>
-      <c r="H65" s="2"/>
-      <c r="M65" t="s">
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="N68" t="s">
         <v>144</v>
       </c>
-      <c r="O65" t="s">
+      <c r="P68" t="s">
         <v>144</v>
       </c>
-      <c r="Q65" t="s">
+      <c r="R68" t="s">
         <v>144</v>
       </c>
-      <c r="T65">
-        <f>INDEX(T4:T64,MATCH(Table2[[#This Row],[Alternative Module Code]],A4:A64,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U65">
+      <c r="U68">
+        <f>INDEX(U4:U67,MATCH(Table2[[#This Row],[Alternative Module Code]],A4:A67,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V68">
         <v>80</v>
       </c>
-      <c r="V65">
+      <c r="W68">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W65">
+      <c r="X68">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:23">
-      <c r="A66" s="3" t="s">
+    <row r="69" spans="1:24">
+      <c r="A69" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B69" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D66" s="28" t="s">
+      <c r="D69" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="E69" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F66" s="4">
+      <c r="F69" s="4">
         <v>7</v>
       </c>
-      <c r="G66" s="2">
+      <c r="G69" s="2">
         <v>10</v>
       </c>
-      <c r="H66" s="2"/>
-      <c r="M66" t="s">
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="N69" t="s">
         <v>144</v>
       </c>
-      <c r="N66" t="s">
+      <c r="O69" t="s">
         <v>144</v>
       </c>
-      <c r="T66">
-        <f>INDEX(T5:T65,MATCH(Table2[[#This Row],[Alternative Module Code]],A5:A65,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U66">
+      <c r="U69">
+        <f>INDEX(U5:U68,MATCH(Table2[[#This Row],[Alternative Module Code]],A5:A68,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V69">
         <v>0</v>
       </c>
-      <c r="V66">
+      <c r="W69">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W66">
+      <c r="X69">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:23">
-      <c r="A67" s="3" t="s">
+    <row r="70" spans="1:24">
+      <c r="A70" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B70" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D67" s="28" t="s">
+      <c r="D70" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F70" s="4">
         <v>7</v>
       </c>
-      <c r="G67" s="2">
+      <c r="G70" s="2">
         <v>10</v>
       </c>
-      <c r="H67" s="2"/>
-      <c r="M67" t="s">
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="N70" t="s">
         <v>144</v>
       </c>
-      <c r="N67" t="s">
+      <c r="O70" t="s">
         <v>144</v>
       </c>
-      <c r="T67">
-        <f>INDEX(T6:T66,MATCH(Table2[[#This Row],[Alternative Module Code]],A6:A66,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U67">
+      <c r="U70">
+        <f>INDEX(U6:U69,MATCH(Table2[[#This Row],[Alternative Module Code]],A6:A69,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V70">
         <v>0</v>
       </c>
-      <c r="V67">
+      <c r="W70">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W67">
+      <c r="X70">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:23">
-      <c r="A68" s="3" t="s">
+    <row r="71" spans="1:24">
+      <c r="A71" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B71" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D68" s="28" t="s">
+      <c r="D71" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E71" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F68" s="4">
+      <c r="F71" s="4">
         <v>7</v>
       </c>
-      <c r="G68" s="2">
+      <c r="G71" s="2">
         <v>10</v>
       </c>
-      <c r="H68" s="2"/>
-      <c r="M68" t="s">
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="N71" t="s">
         <v>144</v>
       </c>
-      <c r="O68" t="s">
+      <c r="P71" t="s">
         <v>144</v>
       </c>
-      <c r="Q68" t="s">
+      <c r="R71" t="s">
         <v>144</v>
       </c>
-      <c r="T68">
-        <f>INDEX(T7:T67,MATCH(Table2[[#This Row],[Alternative Module Code]],A7:A67,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U68">
+      <c r="U71">
+        <f>INDEX(U7:U70,MATCH(Table2[[#This Row],[Alternative Module Code]],A7:A70,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V71">
         <v>70</v>
       </c>
-      <c r="V68">
+      <c r="W71">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W68">
+      <c r="X71">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:23">
-      <c r="A69" s="3" t="s">
+    <row r="72" spans="1:24">
+      <c r="A72" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B72" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D69" s="28" t="s">
+      <c r="D72" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F69" s="4">
+      <c r="F72" s="4">
         <v>7</v>
       </c>
-      <c r="G69" s="2">
+      <c r="G72" s="2">
         <v>10</v>
       </c>
-      <c r="H69" s="2"/>
-      <c r="M69" t="s">
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="N72" t="s">
         <v>144</v>
       </c>
-      <c r="N69" t="s">
+      <c r="O72" t="s">
         <v>144</v>
       </c>
-      <c r="O69" t="s">
+      <c r="P72" t="s">
         <v>144</v>
       </c>
-      <c r="P69" t="s">
+      <c r="Q72" t="s">
         <v>144</v>
       </c>
-      <c r="T69">
-        <f>INDEX(T8:T68,MATCH(Table2[[#This Row],[Alternative Module Code]],A8:A68,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U69">
+      <c r="U72">
+        <f>INDEX(U8:U71,MATCH(Table2[[#This Row],[Alternative Module Code]],A8:A71,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V72">
         <v>70</v>
       </c>
-      <c r="V69">
+      <c r="W72">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W69">
+      <c r="X72">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="70" spans="1:23">
-      <c r="A70" s="3" t="s">
+    <row r="73" spans="1:24">
+      <c r="A73" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B73" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D70" s="28" t="s">
+      <c r="D73" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E73" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F70" s="4">
+      <c r="F73" s="4">
         <v>7</v>
       </c>
-      <c r="G70" s="2">
+      <c r="G73" s="2">
         <v>10</v>
       </c>
-      <c r="H70" s="2"/>
-      <c r="M70" t="s">
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="N73" t="s">
         <v>144</v>
       </c>
-      <c r="N70" t="s">
+      <c r="O73" t="s">
         <v>144</v>
       </c>
-      <c r="O70" t="s">
+      <c r="P73" t="s">
         <v>144</v>
       </c>
-      <c r="R70" t="s">
+      <c r="S73" t="s">
         <v>144</v>
       </c>
-      <c r="T70">
-        <f>INDEX(T9:T69,MATCH(Table2[[#This Row],[Alternative Module Code]],A9:A69,0))</f>
+      <c r="U73">
+        <f>INDEX(U9:U72,MATCH(Table2[[#This Row],[Alternative Module Code]],A9:A72,0))</f>
         <v>3</v>
       </c>
-      <c r="U70">
+      <c r="V73">
         <v>0</v>
       </c>
-      <c r="V70">
+      <c r="W73">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W70">
+      <c r="X73">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:23">
-      <c r="A71" s="3" t="s">
+    <row r="74" spans="1:24">
+      <c r="A74" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B74" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D71" s="28" t="s">
+      <c r="D74" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E74" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F71" s="4">
+      <c r="F74" s="4">
         <v>7</v>
       </c>
-      <c r="G71" s="2">
+      <c r="G74" s="2">
         <v>10</v>
       </c>
-      <c r="H71" s="2"/>
-      <c r="M71" t="s">
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="N74" t="s">
         <v>144</v>
       </c>
-      <c r="O71" t="s">
+      <c r="P74" t="s">
         <v>144</v>
       </c>
-      <c r="Q71" t="s">
+      <c r="R74" t="s">
         <v>144</v>
       </c>
-      <c r="T71">
-        <f>INDEX(T10:T70,MATCH(Table2[[#This Row],[Alternative Module Code]],A10:A70,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U71">
+      <c r="U74">
+        <f>INDEX(U10:U73,MATCH(Table2[[#This Row],[Alternative Module Code]],A10:A73,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V74">
         <v>60</v>
       </c>
-      <c r="V71">
+      <c r="W74">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="W71">
+      <c r="X74">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:23">
-      <c r="A72" s="3" t="s">
+    <row r="75" spans="1:24">
+      <c r="A75" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B75" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D72" s="28" t="s">
+      <c r="D75" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E75" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F72" s="4">
+      <c r="F75" s="4">
         <v>7</v>
       </c>
-      <c r="G72" s="2">
+      <c r="G75" s="2">
         <v>10</v>
       </c>
-      <c r="H72" s="2"/>
-      <c r="M72" t="s">
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="N75" t="s">
         <v>144</v>
       </c>
-      <c r="N72" t="s">
+      <c r="O75" t="s">
         <v>144</v>
       </c>
-      <c r="R72" t="s">
+      <c r="S75" t="s">
         <v>144</v>
       </c>
-      <c r="S72" t="s">
+      <c r="T75" t="s">
         <v>144</v>
       </c>
-      <c r="T72">
-        <f>INDEX(T13:T71,MATCH(Table2[[#This Row],[Alternative Module Code]],A13:A71,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U72">
+      <c r="U75">
+        <f>INDEX(U13:U74,MATCH(Table2[[#This Row],[Alternative Module Code]],A13:A74,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V75">
         <v>0</v>
       </c>
-      <c r="V72">
+      <c r="W75">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W72">
+      <c r="X75">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="73" spans="1:23">
-      <c r="A73" s="3" t="s">
+    <row r="76" spans="1:24">
+      <c r="A76" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B76" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D73" s="28" t="s">
+      <c r="D76" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="E76" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F73" s="4">
+      <c r="F76" s="4">
         <v>7</v>
       </c>
-      <c r="G73" s="2">
+      <c r="G76" s="2">
         <v>10</v>
       </c>
-      <c r="H73" s="2"/>
-      <c r="M73" t="s">
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="N76" t="s">
         <v>144</v>
       </c>
-      <c r="O73" t="s">
+      <c r="P76" t="s">
         <v>144</v>
       </c>
-      <c r="Q73" t="s">
+      <c r="R76" t="s">
         <v>144</v>
       </c>
-      <c r="T73">
-        <f>INDEX(T14:T72,MATCH(Table2[[#This Row],[Alternative Module Code]],A14:A72,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U73">
+      <c r="U76">
+        <f>INDEX(U14:U75,MATCH(Table2[[#This Row],[Alternative Module Code]],A14:A75,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V76">
         <v>80</v>
       </c>
-      <c r="V73">
+      <c r="W76">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W73">
+      <c r="X76">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:23">
-      <c r="A74" s="3" t="s">
+    <row r="77" spans="1:24">
+      <c r="A77" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B77" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D74" s="28" t="s">
+      <c r="D77" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E74" s="3" t="s">
+      <c r="E77" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="F74" s="4">
+      <c r="F77" s="4">
         <v>7</v>
       </c>
-      <c r="G74" s="28">
+      <c r="G77" s="28">
         <v>10</v>
       </c>
-      <c r="H74" s="28"/>
-      <c r="M74" t="s">
+      <c r="H77" s="28"/>
+      <c r="I77" s="28"/>
+      <c r="N77" t="s">
         <v>144</v>
       </c>
-      <c r="N74" t="s">
+      <c r="O77" t="s">
         <v>144</v>
       </c>
-      <c r="O74" t="s">
+      <c r="P77" t="s">
         <v>144</v>
       </c>
-      <c r="P74" t="s">
+      <c r="Q77" t="s">
         <v>144</v>
       </c>
-      <c r="Q74" t="s">
+      <c r="R77" t="s">
         <v>144</v>
       </c>
-      <c r="R74" t="s">
+      <c r="S77" t="s">
         <v>144</v>
       </c>
-      <c r="S74" t="s">
+      <c r="T77" t="s">
         <v>144</v>
       </c>
-      <c r="T74">
-        <v>2</v>
-      </c>
-      <c r="U74">
+      <c r="U77">
+        <v>2</v>
+      </c>
+      <c r="V77">
         <v>80</v>
       </c>
-      <c r="V74">
+      <c r="W77">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W74">
+      <c r="X77">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="75" spans="1:23">
-      <c r="A75" s="3" t="s">
+    <row r="78" spans="1:24">
+      <c r="A78" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B78" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D75" s="28" t="s">
+      <c r="D78" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="E78" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F75" s="4">
+      <c r="F78" s="4">
         <v>7</v>
       </c>
-      <c r="G75" s="2">
+      <c r="G78" s="2">
         <v>10</v>
       </c>
-      <c r="H75" s="2"/>
-      <c r="M75" t="s">
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="N78" t="s">
         <v>144</v>
       </c>
-      <c r="N75" t="s">
+      <c r="O78" t="s">
         <v>144</v>
       </c>
-      <c r="O75" t="s">
+      <c r="P78" t="s">
         <v>144</v>
       </c>
-      <c r="Q75" t="s">
+      <c r="R78" t="s">
         <v>144</v>
       </c>
-      <c r="T75">
-        <f>INDEX(T16:T73,MATCH(Table2[[#This Row],[Alternative Module Code]],A16:A73,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U75">
+      <c r="U78">
+        <f>INDEX(U16:U76,MATCH(Table2[[#This Row],[Alternative Module Code]],A16:A76,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V78">
         <v>70</v>
       </c>
-      <c r="V75">
+      <c r="W78">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W75">
+      <c r="X78">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="76" spans="1:23">
-      <c r="A76" s="3" t="s">
+    <row r="79" spans="1:24">
+      <c r="A79" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B79" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D76" s="28" t="s">
+      <c r="D79" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="E79" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F76" s="4">
+      <c r="F79" s="4">
         <v>7</v>
       </c>
-      <c r="G76" s="2">
+      <c r="G79" s="2">
         <v>10</v>
       </c>
-      <c r="H76" s="2"/>
-      <c r="M76" t="s">
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="N79" t="s">
         <v>144</v>
       </c>
-      <c r="N76" t="s">
+      <c r="O79" t="s">
         <v>144</v>
       </c>
-      <c r="O76" t="s">
+      <c r="P79" t="s">
         <v>144</v>
       </c>
-      <c r="R76" t="s">
+      <c r="S79" t="s">
         <v>144</v>
       </c>
-      <c r="S76" t="s">
+      <c r="T79" t="s">
         <v>144</v>
       </c>
-      <c r="T76">
-        <f>INDEX(T17:T75,MATCH(Table2[[#This Row],[Alternative Module Code]],A17:A75,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U76">
+      <c r="U79">
+        <f>INDEX(U17:U78,MATCH(Table2[[#This Row],[Alternative Module Code]],A17:A78,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V79">
         <v>70</v>
       </c>
-      <c r="V76">
+      <c r="W79">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W76">
+      <c r="X79">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="77" spans="1:23">
-      <c r="A77" s="3" t="s">
+    <row r="80" spans="1:24">
+      <c r="A80" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B80" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D77" s="28" t="s">
+      <c r="D80" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E80" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F77" s="4">
+      <c r="F80" s="4">
         <v>7</v>
       </c>
-      <c r="G77" s="2">
+      <c r="G80" s="2">
         <v>10</v>
       </c>
-      <c r="H77" s="2"/>
-      <c r="M77" t="s">
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="N80" t="s">
         <v>144</v>
       </c>
-      <c r="N77" t="s">
+      <c r="O80" t="s">
         <v>144</v>
       </c>
-      <c r="R77" t="s">
+      <c r="S80" t="s">
         <v>143</v>
       </c>
-      <c r="S77" t="s">
+      <c r="T80" t="s">
         <v>143</v>
       </c>
-      <c r="T77">
-        <f>INDEX(T18:T76,MATCH(Table2[[#This Row],[Alternative Module Code]],A18:A76,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U77">
+      <c r="U80">
+        <f>INDEX(U18:U79,MATCH(Table2[[#This Row],[Alternative Module Code]],A18:A79,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V80">
         <v>75</v>
       </c>
-      <c r="V77">
+      <c r="W80">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>25</v>
       </c>
-      <c r="W77">
+      <c r="X80">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>25</v>
       </c>
     </row>
-    <row r="78" spans="1:23">
-      <c r="A78" s="3" t="s">
+    <row r="81" spans="1:24">
+      <c r="A81" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B81" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C81" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D78" s="28" t="s">
+      <c r="D81" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="E81" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F78" s="4">
+      <c r="F81" s="4">
         <v>7</v>
       </c>
-      <c r="G78" s="2">
+      <c r="G81" s="2">
         <v>10</v>
       </c>
-      <c r="H78" s="2"/>
-      <c r="M78" t="s">
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="N81" t="s">
         <v>144</v>
       </c>
-      <c r="N78" t="s">
+      <c r="O81" t="s">
         <v>144</v>
       </c>
-      <c r="P78" t="s">
+      <c r="Q81" t="s">
         <v>144</v>
       </c>
-      <c r="R78" t="s">
+      <c r="S81" t="s">
         <v>144</v>
       </c>
-      <c r="S78" t="s">
+      <c r="T81" t="s">
         <v>144</v>
       </c>
-      <c r="T78">
-        <f>INDEX(T20:T77,MATCH(Table2[[#This Row],[Alternative Module Code]],A20:A77,0))</f>
+      <c r="U81">
+        <f>INDEX(U20:U80,MATCH(Table2[[#This Row],[Alternative Module Code]],A20:A80,0))</f>
         <v>3</v>
       </c>
-      <c r="U78">
+      <c r="V81">
         <v>70</v>
       </c>
-      <c r="V78">
+      <c r="W81">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W78">
+      <c r="X81">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="79" spans="1:23">
-      <c r="A79" s="3" t="s">
+    <row r="82" spans="1:24">
+      <c r="A82" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B82" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C82" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D79" s="28" t="s">
+      <c r="D82" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E82" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F79" s="4">
+      <c r="F82" s="4">
         <v>7</v>
       </c>
-      <c r="G79" s="2">
+      <c r="G82" s="2">
         <v>10</v>
       </c>
-      <c r="H79" s="2"/>
-      <c r="M79" t="s">
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="N82" t="s">
         <v>144</v>
       </c>
-      <c r="N79" t="s">
+      <c r="O82" t="s">
         <v>144</v>
       </c>
-      <c r="O79" t="s">
+      <c r="P82" t="s">
         <v>144</v>
       </c>
-      <c r="P79" t="s">
+      <c r="Q82" t="s">
         <v>143</v>
       </c>
-      <c r="Q79" t="s">
+      <c r="R82" t="s">
         <v>143</v>
       </c>
-      <c r="R79" t="s">
+      <c r="S82" t="s">
         <v>144</v>
       </c>
-      <c r="S79" t="s">
+      <c r="T82" t="s">
         <v>144</v>
       </c>
-      <c r="T79">
-        <f>INDEX(T21:T78,MATCH(Table2[[#This Row],[Alternative Module Code]],A21:A78,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U79">
+      <c r="U82">
+        <f>INDEX(U21:U81,MATCH(Table2[[#This Row],[Alternative Module Code]],A21:A81,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V82">
         <v>0</v>
       </c>
-      <c r="V79">
+      <c r="W82">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W79">
+      <c r="X82">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="80" spans="1:23">
-      <c r="A80" s="3" t="s">
+    <row r="83" spans="1:24">
+      <c r="A83" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B83" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D80" s="28" t="s">
+      <c r="D83" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="E83" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="F80" s="4">
+      <c r="F83" s="4">
         <v>7</v>
       </c>
-      <c r="G80" s="2">
+      <c r="G83" s="2">
         <v>10</v>
       </c>
-      <c r="H80" s="2"/>
-      <c r="M80" t="s">
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="N83" t="s">
         <v>144</v>
       </c>
-      <c r="N80" t="s">
+      <c r="O83" t="s">
         <v>144</v>
       </c>
-      <c r="O80" t="s">
+      <c r="P83" t="s">
         <v>144</v>
       </c>
-      <c r="R80" t="s">
+      <c r="S83" t="s">
         <v>144</v>
       </c>
-      <c r="S80" t="s">
+      <c r="T83" t="s">
         <v>144</v>
       </c>
-      <c r="T80">
-        <f>INDEX(T22:T79,MATCH(Table2[[#This Row],[Alternative Module Code]],A22:A79,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U80">
+      <c r="U83">
+        <f>INDEX(U22:U82,MATCH(Table2[[#This Row],[Alternative Module Code]],A22:A82,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V83">
         <v>50</v>
       </c>
-      <c r="V80">
+      <c r="W83">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>50</v>
       </c>
-      <c r="W80">
+      <c r="X83">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="81" spans="1:23">
-      <c r="A81" s="3" t="s">
+    <row r="84" spans="1:24">
+      <c r="A84" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B84" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D81" s="28" t="s">
+      <c r="D84" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E84" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F81" s="4">
+      <c r="F84" s="4">
         <v>7</v>
       </c>
-      <c r="G81" s="2">
+      <c r="G84" s="2">
         <v>10</v>
       </c>
-      <c r="H81" s="2"/>
-      <c r="M81" t="s">
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="N84" t="s">
         <v>144</v>
       </c>
-      <c r="N81" t="s">
+      <c r="O84" t="s">
         <v>144</v>
       </c>
-      <c r="P81" t="s">
+      <c r="Q84" t="s">
         <v>144</v>
       </c>
-      <c r="R81" t="s">
+      <c r="S84" t="s">
         <v>144</v>
       </c>
-      <c r="S81" t="s">
+      <c r="T84" t="s">
         <v>144</v>
       </c>
-      <c r="T81">
-        <f>INDEX(T23:T80,MATCH(Table2[[#This Row],[Alternative Module Code]],A23:A80,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U81">
+      <c r="U84">
+        <f>INDEX(U23:U83,MATCH(Table2[[#This Row],[Alternative Module Code]],A23:A83,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V84">
         <v>80</v>
       </c>
-      <c r="V81">
+      <c r="W84">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W81">
+      <c r="X84">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:23">
-      <c r="A82" s="3" t="s">
+    <row r="85" spans="1:24">
+      <c r="A85" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B85" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D82" s="28" t="s">
+      <c r="D85" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="E85" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F82" s="4">
+      <c r="F85" s="4">
         <v>7</v>
       </c>
-      <c r="G82" s="2">
+      <c r="G85" s="2">
         <v>10</v>
       </c>
-      <c r="H82" s="2"/>
-      <c r="M82" t="s">
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="N85" t="s">
         <v>144</v>
       </c>
-      <c r="N82" t="s">
+      <c r="O85" t="s">
         <v>144</v>
       </c>
-      <c r="O82" t="s">
+      <c r="P85" t="s">
         <v>144</v>
       </c>
-      <c r="P82" t="s">
+      <c r="Q85" t="s">
         <v>144</v>
       </c>
-      <c r="Q82" t="s">
+      <c r="R85" t="s">
         <v>144</v>
       </c>
-      <c r="T82">
-        <f>INDEX(T24:T81,MATCH(Table2[[#This Row],[Alternative Module Code]],A24:A81,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U82">
+      <c r="U85">
+        <f>INDEX(U24:U84,MATCH(Table2[[#This Row],[Alternative Module Code]],A24:A84,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V85">
         <v>70</v>
       </c>
-      <c r="V82">
+      <c r="W85">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W82">
+      <c r="X85">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="83" spans="1:23">
-      <c r="A83" s="3" t="s">
+    <row r="86" spans="1:24">
+      <c r="A86" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B86" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D83" s="28" t="s">
+      <c r="D86" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="E86" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F83" s="4">
+      <c r="F86" s="4">
         <v>7</v>
       </c>
-      <c r="G83" s="2">
+      <c r="G86" s="2">
         <v>10</v>
       </c>
-      <c r="H83" s="2"/>
-      <c r="M83" t="s">
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="N86" t="s">
         <v>144</v>
       </c>
-      <c r="N83" t="s">
+      <c r="O86" t="s">
         <v>144</v>
       </c>
-      <c r="O83" t="s">
+      <c r="P86" t="s">
         <v>144</v>
       </c>
-      <c r="P83" t="s">
+      <c r="Q86" t="s">
         <v>144</v>
       </c>
-      <c r="Q83" t="s">
+      <c r="R86" t="s">
         <v>144</v>
       </c>
-      <c r="R83" t="s">
+      <c r="S86" t="s">
         <v>144</v>
       </c>
-      <c r="T83">
-        <f>INDEX(T25:T82,MATCH(Table2[[#This Row],[Alternative Module Code]],A25:A82,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U83">
+      <c r="U86">
+        <f>INDEX(U25:U85,MATCH(Table2[[#This Row],[Alternative Module Code]],A25:A85,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V86">
         <v>40</v>
       </c>
-      <c r="V83">
+      <c r="W86">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>60</v>
       </c>
-      <c r="W83">
+      <c r="X86">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>60</v>
       </c>
     </row>
-    <row r="84" spans="1:23">
-      <c r="A84" s="3" t="s">
+    <row r="87" spans="1:24">
+      <c r="A87" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B87" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C87" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="D84" s="28" t="s">
+      <c r="D87" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="E87" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F84" s="4">
+      <c r="F87" s="4">
         <v>7</v>
       </c>
-      <c r="G84" s="2">
+      <c r="G87" s="2">
         <v>10</v>
       </c>
-      <c r="H84" s="2"/>
-      <c r="M84" t="s">
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="N87" t="s">
         <v>144</v>
       </c>
-      <c r="O84" t="s">
+      <c r="P87" t="s">
         <v>144</v>
       </c>
-      <c r="Q84" t="s">
+      <c r="R87" t="s">
         <v>144</v>
       </c>
-      <c r="T84">
-        <f>INDEX(T26:T83,MATCH(Table2[[#This Row],[Alternative Module Code]],A26:A83,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U84">
+      <c r="U87">
+        <f>INDEX(U26:U86,MATCH(Table2[[#This Row],[Alternative Module Code]],A26:A86,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V87">
         <v>80</v>
       </c>
-      <c r="V84">
+      <c r="W87">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>20</v>
       </c>
-      <c r="W84">
+      <c r="X87">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>20</v>
       </c>
     </row>
-    <row r="85" spans="1:23">
-      <c r="A85" s="3" t="s">
+    <row r="88" spans="1:24">
+      <c r="A88" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B88" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D85" s="28" t="s">
+      <c r="D88" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="E88" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F85" s="4">
+      <c r="F88" s="4">
         <v>7</v>
       </c>
-      <c r="G85" s="2">
+      <c r="G88" s="2">
         <v>10</v>
       </c>
-      <c r="H85" s="2"/>
-      <c r="M85" t="s">
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="N88" t="s">
         <v>144</v>
       </c>
-      <c r="N85" t="s">
+      <c r="O88" t="s">
         <v>144</v>
       </c>
-      <c r="O85" t="s">
+      <c r="P88" t="s">
         <v>144</v>
       </c>
-      <c r="P85" t="s">
+      <c r="Q88" t="s">
         <v>144</v>
       </c>
-      <c r="Q85" t="s">
+      <c r="R88" t="s">
         <v>144</v>
       </c>
-      <c r="T85">
-        <f>INDEX(T27:T84,MATCH(Table2[[#This Row],[Alternative Module Code]],A27:A84,0))</f>
+      <c r="U88">
+        <f>INDEX(U27:U87,MATCH(Table2[[#This Row],[Alternative Module Code]],A27:A87,0))</f>
         <v>3</v>
       </c>
-      <c r="U85">
+      <c r="V88">
         <v>0</v>
       </c>
-      <c r="V85">
+      <c r="W88">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W85">
+      <c r="X88">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="86" spans="1:23">
-      <c r="A86" s="3" t="s">
+    <row r="89" spans="1:24">
+      <c r="A89" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B89" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D86" s="28" t="s">
+      <c r="D89" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="E89" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F86" s="4">
+      <c r="F89" s="4">
         <v>7</v>
       </c>
-      <c r="G86" s="2">
+      <c r="G89" s="2">
         <v>10</v>
       </c>
-      <c r="H86" s="2"/>
-      <c r="M86" t="s">
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="N89" t="s">
         <v>144</v>
       </c>
-      <c r="N86" t="s">
+      <c r="O89" t="s">
         <v>144</v>
       </c>
-      <c r="O86" t="s">
+      <c r="P89" t="s">
         <v>144</v>
       </c>
-      <c r="P86" t="s">
+      <c r="Q89" t="s">
         <v>144</v>
       </c>
-      <c r="T86">
-        <f>INDEX(T28:T85,MATCH(Table2[[#This Row],[Alternative Module Code]],A28:A85,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U86">
+      <c r="U89">
+        <f>INDEX(U28:U88,MATCH(Table2[[#This Row],[Alternative Module Code]],A28:A88,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V89">
         <v>70</v>
       </c>
-      <c r="V86">
+      <c r="W89">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>30</v>
       </c>
-      <c r="W86">
+      <c r="X89">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:23">
-      <c r="A87" s="3" t="s">
+    <row r="90" spans="1:24">
+      <c r="A90" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B90" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C90" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D87" s="28" t="s">
+      <c r="D90" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="E90" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F87" s="4">
+      <c r="F90" s="4">
         <v>7</v>
       </c>
-      <c r="G87" s="2">
+      <c r="G90" s="2">
         <v>10</v>
       </c>
-      <c r="H87" s="2"/>
-      <c r="M87" t="s">
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="N90" t="s">
         <v>144</v>
       </c>
-      <c r="R87" t="s">
+      <c r="S90" t="s">
         <v>143</v>
       </c>
-      <c r="S87" t="s">
+      <c r="T90" t="s">
         <v>143</v>
       </c>
-      <c r="T87">
-        <f>INDEX(T29:T86,MATCH(Table2[[#This Row],[Alternative Module Code]],A29:A86,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U87">
+      <c r="U90">
+        <f>INDEX(U29:U89,MATCH(Table2[[#This Row],[Alternative Module Code]],A29:A89,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V90">
         <v>50</v>
       </c>
-      <c r="V87">
+      <c r="W90">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>50</v>
       </c>
-      <c r="W87">
+      <c r="X90">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:23">
-      <c r="A88" s="3" t="s">
+    <row r="91" spans="1:24">
+      <c r="A91" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B91" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C91" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D88" s="28" t="s">
+      <c r="D91" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="E91" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F88" s="4">
+      <c r="F91" s="4">
         <v>7</v>
       </c>
-      <c r="G88" s="2">
+      <c r="G91" s="2">
         <v>10</v>
       </c>
-      <c r="H88" s="2"/>
-      <c r="M88" t="s">
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="N91" t="s">
         <v>144</v>
       </c>
-      <c r="O88" t="s">
+      <c r="P91" t="s">
         <v>144</v>
       </c>
-      <c r="Q88" t="s">
+      <c r="R91" t="s">
         <v>144</v>
       </c>
-      <c r="T88">
-        <f>INDEX(T30:T87,MATCH(Table2[[#This Row],[Alternative Module Code]],A30:A87,0))</f>
+      <c r="U91">
+        <f>INDEX(U30:U90,MATCH(Table2[[#This Row],[Alternative Module Code]],A30:A90,0))</f>
         <v>3</v>
       </c>
-      <c r="U88">
+      <c r="V91">
         <v>60</v>
       </c>
-      <c r="V88">
+      <c r="W91">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>40</v>
       </c>
-      <c r="W88">
+      <c r="X91">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>40</v>
       </c>
     </row>
-    <row r="89" spans="1:23">
-      <c r="A89" s="3" t="s">
+    <row r="92" spans="1:24">
+      <c r="A92" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B92" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C92" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D89" s="28" t="s">
+      <c r="D92" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="E92" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F89" s="4">
+      <c r="F92" s="4">
         <v>7</v>
       </c>
-      <c r="G89" s="2">
+      <c r="G92" s="2">
         <v>10</v>
       </c>
-      <c r="H89" s="2"/>
-      <c r="M89" t="s">
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="N92" t="s">
         <v>144</v>
       </c>
-      <c r="N89" t="s">
+      <c r="O92" t="s">
         <v>144</v>
       </c>
-      <c r="O89" t="s">
+      <c r="P92" t="s">
         <v>144</v>
       </c>
-      <c r="P89" t="s">
+      <c r="Q92" t="s">
         <v>144</v>
       </c>
-      <c r="Q89" t="s">
+      <c r="R92" t="s">
         <v>144</v>
       </c>
-      <c r="T89">
-        <f>INDEX(T31:T88,MATCH(Table2[[#This Row],[Alternative Module Code]],A31:A88,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U89">
+      <c r="U92">
+        <f>INDEX(U31:U91,MATCH(Table2[[#This Row],[Alternative Module Code]],A31:A91,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V92">
         <v>0</v>
       </c>
-      <c r="V89">
+      <c r="W92">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W89">
+      <c r="X92">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="1:23">
-      <c r="A90" s="3" t="s">
+    <row r="93" spans="1:24">
+      <c r="A93" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B93" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C93" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D90" s="28" t="s">
+      <c r="D93" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="E93" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F90" s="4">
+      <c r="F93" s="4">
         <v>7</v>
       </c>
-      <c r="G90" s="28">
+      <c r="G93" s="28">
         <v>10</v>
       </c>
-      <c r="H90" s="28"/>
-      <c r="M90" t="s">
+      <c r="H93" s="28"/>
+      <c r="I93" s="28"/>
+      <c r="N93" t="s">
         <v>144</v>
       </c>
-      <c r="N90" t="s">
+      <c r="O93" t="s">
         <v>144</v>
       </c>
-      <c r="O90" t="s">
+      <c r="P93" t="s">
         <v>144</v>
       </c>
-      <c r="P90" t="s">
+      <c r="Q93" t="s">
         <v>144</v>
       </c>
-      <c r="Q90" t="s">
+      <c r="R93" t="s">
         <v>144</v>
       </c>
-      <c r="T90">
-        <f>INDEX(T32:T89,MATCH(Table2[[#This Row],[Alternative Module Code]],A32:A89,0))</f>
-        <v>2</v>
-      </c>
-      <c r="U90">
+      <c r="U93">
+        <f>INDEX(U32:U92,MATCH(Table2[[#This Row],[Alternative Module Code]],A32:A92,0))</f>
+        <v>2</v>
+      </c>
+      <c r="V93">
         <v>50</v>
       </c>
-      <c r="V90">
+      <c r="W93">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>50</v>
       </c>
-      <c r="W90">
+      <c r="X93">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="91" spans="1:23">
-      <c r="A91" s="3" t="s">
+    <row r="94" spans="1:24">
+      <c r="A94" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B94" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="C91" s="3"/>
-      <c r="D91" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F91" s="4">
-        <v>7</v>
-      </c>
-      <c r="G91" s="28">
-        <v>10</v>
-      </c>
-      <c r="H91" s="28"/>
-      <c r="M91" t="s">
-        <v>144</v>
-      </c>
-      <c r="R91" t="s">
-        <v>144</v>
-      </c>
-      <c r="S91" t="s">
-        <v>144</v>
-      </c>
-      <c r="T91">
-        <v>2</v>
-      </c>
-      <c r="U91">
-        <v>0</v>
-      </c>
-      <c r="V91">
-        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="W91">
-        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="92" spans="1:23">
-      <c r="A92" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="C92" s="3"/>
-      <c r="D92" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F92" s="4">
-        <v>7</v>
-      </c>
-      <c r="G92" s="28">
-        <v>10</v>
-      </c>
-      <c r="H92" s="28"/>
-      <c r="M92" t="s">
-        <v>144</v>
-      </c>
-      <c r="N92" t="s">
-        <v>144</v>
-      </c>
-      <c r="R92" t="s">
-        <v>144</v>
-      </c>
-      <c r="S92" t="s">
-        <v>144</v>
-      </c>
-      <c r="T92">
-        <v>2</v>
-      </c>
-      <c r="U92">
-        <v>0</v>
-      </c>
-      <c r="V92">
-        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="W92">
-        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="93" spans="1:23">
-      <c r="A93" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C93" s="3"/>
-      <c r="D93" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F93" s="4">
-        <v>7</v>
-      </c>
-      <c r="G93" s="28">
-        <v>10</v>
-      </c>
-      <c r="H93" s="28"/>
-      <c r="M93" t="s">
-        <v>144</v>
-      </c>
-      <c r="R93" t="s">
-        <v>144</v>
-      </c>
-      <c r="S93" t="s">
-        <v>144</v>
-      </c>
-      <c r="T93">
-        <v>2</v>
-      </c>
-      <c r="U93">
-        <v>0</v>
-      </c>
-      <c r="V93">
-        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="W93">
-        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="94" spans="1:23">
-      <c r="A94" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="C94" s="3"/>
       <c r="D94" s="28" t="s">
@@ -35269,116 +35660,97 @@
       <c r="F94" s="4">
         <v>7</v>
       </c>
-      <c r="G94" s="2">
-        <v>20</v>
-      </c>
-      <c r="H94" s="2"/>
-      <c r="M94" t="s">
-        <v>143</v>
-      </c>
+      <c r="G94" s="28">
+        <v>10</v>
+      </c>
+      <c r="H94" s="28"/>
+      <c r="I94" s="28"/>
       <c r="N94" t="s">
-        <v>143</v>
-      </c>
-      <c r="O94" t="s">
-        <v>143</v>
-      </c>
-      <c r="P94" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q94" t="s">
-        <v>143</v>
-      </c>
-      <c r="R94" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S94" t="s">
-        <v>143</v>
-      </c>
-      <c r="T94">
-        <v>3</v>
+        <v>144</v>
+      </c>
+      <c r="T94" t="s">
+        <v>144</v>
       </c>
       <c r="U94">
+        <v>2</v>
+      </c>
+      <c r="V94">
         <v>0</v>
       </c>
-      <c r="V94">
+      <c r="W94">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W94">
+      <c r="X94">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:23">
+    <row r="95" spans="1:24">
       <c r="A95" s="3" t="s">
-        <v>182</v>
+        <v>244</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="C95" s="3"/>
       <c r="D95" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F95" s="4">
         <v>7</v>
       </c>
-      <c r="G95" s="2">
-        <v>20</v>
-      </c>
-      <c r="H95" s="2"/>
-      <c r="M95" t="s">
-        <v>143</v>
-      </c>
+      <c r="G95" s="28">
+        <v>10</v>
+      </c>
+      <c r="H95" s="28"/>
+      <c r="I95" s="28"/>
       <c r="N95" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O95" t="s">
-        <v>143</v>
-      </c>
-      <c r="P95" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q95" t="s">
-        <v>143</v>
-      </c>
-      <c r="R95" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S95" t="s">
-        <v>143</v>
-      </c>
-      <c r="T95">
-        <v>4</v>
+        <v>144</v>
+      </c>
+      <c r="T95" t="s">
+        <v>144</v>
       </c>
       <c r="U95">
+        <v>2</v>
+      </c>
+      <c r="V95">
         <v>0</v>
       </c>
-      <c r="V95">
+      <c r="W95">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W95">
+      <c r="X95">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="1:23">
+    <row r="96" spans="1:24">
       <c r="A96" s="3" t="s">
-        <v>314</v>
+        <v>246</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>315</v>
+        <v>247</v>
       </c>
       <c r="C96" s="3"/>
       <c r="D96" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F96" s="4">
         <v>7</v>
@@ -35387,81 +35759,95 @@
         <v>10</v>
       </c>
       <c r="H96" s="28"/>
-      <c r="M96" t="s">
-        <v>144</v>
-      </c>
-      <c r="R96" t="s">
+      <c r="I96" s="28"/>
+      <c r="N96" t="s">
         <v>144</v>
       </c>
       <c r="S96" t="s">
         <v>144</v>
       </c>
-      <c r="T96">
-        <v>2</v>
+      <c r="T96" t="s">
+        <v>144</v>
       </c>
       <c r="U96">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="W96">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>30</v>
-      </c>
-      <c r="W96">
+        <v>100</v>
+      </c>
+      <c r="X96">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>30.000000000000004</v>
-      </c>
-    </row>
-    <row r="97" spans="1:23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24">
       <c r="A97" s="3" t="s">
-        <v>375</v>
+        <v>181</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>376</v>
+        <v>184</v>
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F97" s="4">
         <v>7</v>
       </c>
-      <c r="G97" s="28">
-        <v>10</v>
-      </c>
-      <c r="H97" s="28"/>
-      <c r="M97" t="s">
-        <v>144</v>
+      <c r="G97" s="2">
+        <v>20</v>
+      </c>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="N97" t="s">
+        <v>143</v>
+      </c>
+      <c r="O97" t="s">
+        <v>143</v>
+      </c>
+      <c r="P97" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>143</v>
       </c>
       <c r="R97" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S97" t="s">
-        <v>144</v>
-      </c>
-      <c r="T97">
-        <v>2</v>
+        <v>143</v>
+      </c>
+      <c r="T97" t="s">
+        <v>143</v>
       </c>
       <c r="U97">
+        <v>3</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="V97">
-        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>0</v>
-      </c>
-      <c r="W97">
+      <c r="X97">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24">
       <c r="A98" s="3" t="s">
-        <v>319</v>
+        <v>182</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>320</v>
+        <v>185</v>
       </c>
       <c r="C98" s="3"/>
       <c r="D98" s="28" t="s">
@@ -35473,215 +35859,464 @@
       <c r="F98" s="4">
         <v>7</v>
       </c>
-      <c r="G98" s="28">
-        <v>10</v>
-      </c>
-      <c r="H98" s="28"/>
-      <c r="M98" t="s">
-        <v>144</v>
+      <c r="G98" s="2">
+        <v>20</v>
+      </c>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="N98" t="s">
+        <v>143</v>
+      </c>
+      <c r="O98" t="s">
+        <v>143</v>
+      </c>
+      <c r="P98" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>143</v>
       </c>
       <c r="R98" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="S98" t="s">
-        <v>144</v>
-      </c>
-      <c r="T98">
-        <v>2</v>
+        <v>143</v>
+      </c>
+      <c r="T98" t="s">
+        <v>143</v>
       </c>
       <c r="U98">
+        <v>4</v>
+      </c>
+      <c r="V98">
         <v>0</v>
       </c>
-      <c r="V98">
+      <c r="W98">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="W98">
+      <c r="X98">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="99" spans="1:23">
+    <row r="99" spans="1:24">
       <c r="A99" s="3" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="C99" s="3"/>
       <c r="D99" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F99" s="4">
         <v>7</v>
       </c>
       <c r="G99" s="28">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H99" s="28"/>
-      <c r="M99" t="s">
+      <c r="I99" s="28"/>
+      <c r="N99" t="s">
         <v>144</v>
       </c>
-      <c r="P99" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q99" t="s">
-        <v>143</v>
-      </c>
-      <c r="T99">
-        <v>4</v>
+      <c r="S99" t="s">
+        <v>144</v>
+      </c>
+      <c r="T99" t="s">
+        <v>144</v>
       </c>
       <c r="U99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V99">
+        <v>70</v>
+      </c>
+      <c r="W99">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
-      </c>
-      <c r="W99">
+        <v>30</v>
+      </c>
+      <c r="X99">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="100" spans="1:23">
+        <v>30.000000000000004</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24">
       <c r="A100" s="3" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>330</v>
+        <v>376</v>
       </c>
       <c r="C100" s="3"/>
       <c r="D100" s="28" t="s">
         <v>178</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F100" s="4">
         <v>7</v>
       </c>
       <c r="G100" s="28">
+        <v>10</v>
+      </c>
+      <c r="H100" s="28"/>
+      <c r="I100" s="28"/>
+      <c r="N100" t="s">
+        <v>144</v>
+      </c>
+      <c r="S100" t="s">
+        <v>144</v>
+      </c>
+      <c r="T100" t="s">
+        <v>144</v>
+      </c>
+      <c r="U100">
+        <v>2</v>
+      </c>
+      <c r="V100">
+        <v>100</v>
+      </c>
+      <c r="W100">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>0</v>
+      </c>
+      <c r="X100">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24">
+      <c r="A101" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="C101" s="3"/>
+      <c r="D101" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F101" s="4">
+        <v>7</v>
+      </c>
+      <c r="G101" s="28">
+        <v>10</v>
+      </c>
+      <c r="H101" s="28"/>
+      <c r="I101" s="28"/>
+      <c r="N101" t="s">
+        <v>144</v>
+      </c>
+      <c r="S101" t="s">
+        <v>144</v>
+      </c>
+      <c r="T101" t="s">
+        <v>144</v>
+      </c>
+      <c r="U101">
+        <v>2</v>
+      </c>
+      <c r="V101">
+        <v>0</v>
+      </c>
+      <c r="W101">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X101">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24">
+      <c r="A102" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C102" s="3"/>
+      <c r="D102" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F102" s="4">
+        <v>7</v>
+      </c>
+      <c r="G102" s="28">
         <v>20</v>
       </c>
-      <c r="H100" s="28"/>
-      <c r="M100" t="s">
+      <c r="H102" s="28"/>
+      <c r="I102" s="28"/>
+      <c r="N102" t="s">
         <v>144</v>
       </c>
-      <c r="P100" t="s">
+      <c r="Q102" t="s">
         <v>143</v>
       </c>
-      <c r="Q100" t="s">
+      <c r="R102" t="s">
         <v>143</v>
       </c>
-      <c r="T100">
+      <c r="U102">
         <v>4</v>
       </c>
-      <c r="U100">
+      <c r="V102">
+        <v>0</v>
+      </c>
+      <c r="W102">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X102">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24">
+      <c r="A103" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C103" s="3"/>
+      <c r="D103" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F103" s="4">
+        <v>7</v>
+      </c>
+      <c r="G103" s="28">
+        <v>20</v>
+      </c>
+      <c r="H103" s="28"/>
+      <c r="I103" s="28"/>
+      <c r="N103" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>143</v>
+      </c>
+      <c r="R103" t="s">
+        <v>143</v>
+      </c>
+      <c r="U103">
+        <v>4</v>
+      </c>
+      <c r="V103">
         <v>50</v>
       </c>
-      <c r="V100">
+      <c r="W103">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>50</v>
       </c>
-      <c r="W100">
+      <c r="X103">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="101" spans="1:23">
-      <c r="A101"/>
-      <c r="B101"/>
-      <c r="C101"/>
-      <c r="D101"/>
-      <c r="E101"/>
-      <c r="F101"/>
-      <c r="G101"/>
-      <c r="H101"/>
-    </row>
-    <row r="102" spans="1:23">
-      <c r="A102"/>
-      <c r="B102"/>
-      <c r="C102"/>
-      <c r="D102"/>
-      <c r="E102"/>
-      <c r="F102"/>
-      <c r="G102"/>
-      <c r="H102"/>
-    </row>
-    <row r="103" spans="1:23">
-      <c r="A103"/>
-      <c r="B103"/>
-      <c r="C103"/>
-      <c r="D103"/>
-      <c r="E103"/>
-      <c r="F103"/>
-      <c r="G103"/>
-      <c r="H103"/>
-    </row>
-    <row r="104" spans="1:23">
-      <c r="A104"/>
-      <c r="B104"/>
-      <c r="C104"/>
-      <c r="D104"/>
-      <c r="E104"/>
-      <c r="F104"/>
-      <c r="G104"/>
-      <c r="H104"/>
-    </row>
-    <row r="105" spans="1:23">
-      <c r="A105"/>
-      <c r="B105"/>
-      <c r="C105"/>
-      <c r="D105"/>
-      <c r="E105"/>
-      <c r="F105"/>
-      <c r="G105"/>
-      <c r="H105"/>
-    </row>
-    <row r="106" spans="1:23">
-      <c r="A106"/>
-      <c r="B106"/>
-      <c r="C106"/>
-      <c r="D106"/>
-      <c r="E106"/>
-      <c r="F106"/>
-      <c r="G106"/>
-      <c r="H106"/>
-    </row>
-    <row r="107" spans="1:23">
-      <c r="A107"/>
-      <c r="B107"/>
-      <c r="C107"/>
-      <c r="D107"/>
-      <c r="E107"/>
-      <c r="F107"/>
-      <c r="G107"/>
-      <c r="H107"/>
-    </row>
-    <row r="108" spans="1:23">
-      <c r="A108"/>
-      <c r="B108"/>
-      <c r="C108"/>
-      <c r="D108"/>
-      <c r="E108"/>
-      <c r="F108"/>
-      <c r="G108"/>
-      <c r="H108"/>
-    </row>
-    <row r="109" spans="1:23">
-      <c r="A109"/>
-      <c r="B109"/>
-      <c r="C109"/>
-      <c r="D109"/>
-      <c r="E109"/>
-      <c r="F109"/>
-      <c r="G109"/>
-      <c r="H109"/>
-    </row>
-    <row r="110" spans="1:23">
+    <row r="104" spans="1:24">
+      <c r="A104" s="47" t="s">
+        <v>398</v>
+      </c>
+      <c r="B104" s="47" t="s">
+        <v>413</v>
+      </c>
+      <c r="C104" s="47"/>
+      <c r="D104" s="28"/>
+      <c r="E104" s="47"/>
+      <c r="F104" s="48"/>
+      <c r="G104" s="49"/>
+      <c r="H104" s="49"/>
+      <c r="I104" s="28"/>
+      <c r="J104" s="50"/>
+      <c r="L104" s="50"/>
+      <c r="M104" s="50"/>
+      <c r="O104" s="50"/>
+      <c r="P104" s="50"/>
+      <c r="Q104" s="50"/>
+      <c r="R104" s="50"/>
+      <c r="V104" s="50"/>
+      <c r="W104" s="51">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X104" s="51">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24">
+      <c r="A105" s="47" t="s">
+        <v>399</v>
+      </c>
+      <c r="B105" s="47" t="s">
+        <v>412</v>
+      </c>
+      <c r="C105" s="47"/>
+      <c r="D105" s="28"/>
+      <c r="E105" s="47"/>
+      <c r="F105" s="48"/>
+      <c r="G105" s="49"/>
+      <c r="H105" s="49"/>
+      <c r="I105" s="28"/>
+      <c r="J105" s="50"/>
+      <c r="L105" s="50"/>
+      <c r="M105" s="50"/>
+      <c r="O105" s="50"/>
+      <c r="P105" s="50"/>
+      <c r="Q105" s="50"/>
+      <c r="R105" s="50"/>
+      <c r="V105" s="50"/>
+      <c r="W105" s="51">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X105" s="51">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24">
+      <c r="A106" s="47" t="s">
+        <v>400</v>
+      </c>
+      <c r="B106" s="47" t="s">
+        <v>414</v>
+      </c>
+      <c r="C106" s="47"/>
+      <c r="D106" s="28"/>
+      <c r="E106" s="47"/>
+      <c r="F106" s="48"/>
+      <c r="G106" s="49"/>
+      <c r="H106" s="49"/>
+      <c r="I106" s="28"/>
+      <c r="J106" s="50"/>
+      <c r="L106" s="50"/>
+      <c r="M106" s="50"/>
+      <c r="O106" s="50"/>
+      <c r="P106" s="50"/>
+      <c r="Q106" s="50"/>
+      <c r="R106" s="50"/>
+      <c r="V106" s="50"/>
+      <c r="W106" s="51">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X106" s="51">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24">
+      <c r="A107" s="47" t="s">
+        <v>404</v>
+      </c>
+      <c r="B107" s="47" t="s">
+        <v>415</v>
+      </c>
+      <c r="C107" s="47"/>
+      <c r="D107" s="28"/>
+      <c r="E107" s="47"/>
+      <c r="F107" s="48"/>
+      <c r="G107" s="49"/>
+      <c r="H107" s="49"/>
+      <c r="I107" s="28"/>
+      <c r="J107" s="50"/>
+      <c r="L107" s="50"/>
+      <c r="M107" s="50"/>
+      <c r="O107" s="50"/>
+      <c r="P107" s="50"/>
+      <c r="Q107" s="50"/>
+      <c r="R107" s="50"/>
+      <c r="V107" s="50"/>
+      <c r="W107" s="51">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X107" s="51">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24">
+      <c r="A108" s="47" t="s">
+        <v>410</v>
+      </c>
+      <c r="B108" s="47" t="s">
+        <v>401</v>
+      </c>
+      <c r="C108" s="47"/>
+      <c r="D108" s="28"/>
+      <c r="E108" s="47"/>
+      <c r="F108" s="48"/>
+      <c r="G108" s="49"/>
+      <c r="H108" s="49"/>
+      <c r="I108" s="28"/>
+      <c r="J108" s="50"/>
+      <c r="L108" s="50"/>
+      <c r="M108" s="50"/>
+      <c r="O108" s="50"/>
+      <c r="P108" s="50"/>
+      <c r="Q108" s="50"/>
+      <c r="R108" s="50"/>
+      <c r="V108" s="50"/>
+      <c r="W108" s="51">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X108" s="51">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24">
+      <c r="A109" s="47" t="s">
+        <v>411</v>
+      </c>
+      <c r="B109" s="47" t="s">
+        <v>405</v>
+      </c>
+      <c r="C109" s="47"/>
+      <c r="D109" s="28"/>
+      <c r="E109" s="47"/>
+      <c r="F109" s="48"/>
+      <c r="G109" s="49"/>
+      <c r="H109" s="49"/>
+      <c r="I109" s="28"/>
+      <c r="J109" s="50"/>
+      <c r="L109" s="50"/>
+      <c r="M109" s="50"/>
+      <c r="O109" s="50"/>
+      <c r="P109" s="50"/>
+      <c r="Q109" s="50"/>
+      <c r="R109" s="50"/>
+      <c r="V109" s="50"/>
+      <c r="W109" s="51">
+        <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
+        <v>100</v>
+      </c>
+      <c r="X109" s="51">
+        <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24">
       <c r="A110"/>
       <c r="B110"/>
       <c r="C110"/>
@@ -35690,8 +36325,9 @@
       <c r="F110"/>
       <c r="G110"/>
       <c r="H110"/>
-    </row>
-    <row r="111" spans="1:23">
+      <c r="I110"/>
+    </row>
+    <row r="111" spans="1:24">
       <c r="A111"/>
       <c r="B111"/>
       <c r="C111"/>
@@ -35700,8 +36336,9 @@
       <c r="F111"/>
       <c r="G111"/>
       <c r="H111"/>
-    </row>
-    <row r="112" spans="1:23">
+      <c r="I111"/>
+    </row>
+    <row r="112" spans="1:24">
       <c r="A112"/>
       <c r="B112"/>
       <c r="C112"/>
@@ -35710,6 +36347,7 @@
       <c r="F112"/>
       <c r="G112"/>
       <c r="H112"/>
+      <c r="I112"/>
     </row>
     <row r="113" customFormat="1"/>
     <row r="114" customFormat="1"/>
@@ -35727,19 +36365,64 @@
     <row r="126" customFormat="1"/>
     <row r="127" customFormat="1"/>
     <row r="128" customFormat="1"/>
-    <row r="129" spans="1:8">
-      <c r="A129" s="3"/>
-      <c r="B129" s="3"/>
-      <c r="C129" s="3"/>
-      <c r="D129" s="3"/>
-      <c r="E129" s="3"/>
-      <c r="F129" s="3"/>
-      <c r="G129" s="3"/>
-      <c r="H129" s="3"/>
+    <row r="129" spans="1:9">
+      <c r="A129"/>
+      <c r="B129"/>
+      <c r="C129"/>
+      <c r="D129"/>
+      <c r="E129"/>
+      <c r="F129"/>
+      <c r="G129"/>
+      <c r="H129"/>
+      <c r="I129"/>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130"/>
+      <c r="B130"/>
+      <c r="C130"/>
+      <c r="D130"/>
+      <c r="E130"/>
+      <c r="F130"/>
+      <c r="G130"/>
+      <c r="H130"/>
+      <c r="I130"/>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131"/>
+      <c r="B131"/>
+      <c r="C131"/>
+      <c r="D131"/>
+      <c r="E131"/>
+      <c r="F131"/>
+      <c r="G131"/>
+      <c r="H131"/>
+      <c r="I131"/>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132"/>
+      <c r="B132"/>
+      <c r="C132"/>
+      <c r="D132"/>
+      <c r="E132"/>
+      <c r="F132"/>
+      <c r="G132"/>
+      <c r="H132"/>
+      <c r="I132"/>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
+      <c r="H133" s="3"/>
+      <c r="I133" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="E2:E100">
+  <conditionalFormatting sqref="E2:E109">
     <cfRule type="containsText" dxfId="12" priority="12" operator="containsText" text="SEMD">
       <formula>NOT(ISERROR(SEARCH("SEMD",E2)))</formula>
     </cfRule>
@@ -35750,28 +36433,18 @@
       <formula>NOT(ISERROR(SEARCH("SEM1",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E96:E100">
+  <conditionalFormatting sqref="E99:E104">
     <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="SEMD">
-      <formula>NOT(ISERROR(SEARCH("SEMD",E96)))</formula>
+      <formula>NOT(ISERROR(SEARCH("SEMD",E99)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="SEM2">
-      <formula>NOT(ISERROR(SEARCH("SEM2",E96)))</formula>
+      <formula>NOT(ISERROR(SEARCH("SEM2",E99)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="SEM1">
-      <formula>NOT(ISERROR(SEARCH("SEM1",E96)))</formula>
+      <formula>NOT(ISERROR(SEARCH("SEM1",E99)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F100">
-    <cfRule type="colorScale" priority="161">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F96:F100">
+  <conditionalFormatting sqref="F99:F104">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -35781,19 +36454,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G100">
-    <cfRule type="colorScale" priority="163">
-      <colorScale>
-        <cfvo type="num" val="10"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G96:G100">
+  <conditionalFormatting sqref="G99:H104">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="num" val="10"/>
@@ -35805,25 +36466,47 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:T95 H96:S100">
+  <conditionalFormatting sqref="I99:T104 I2:U98">
     <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="O">
-      <formula>NOT(ISERROR(SEARCH("O",H2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("O",I2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="5" priority="17" operator="containsText" text="C">
-      <formula>NOT(ISERROR(SEARCH("C",H2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("C",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T96:T100">
+  <conditionalFormatting sqref="U99:U104">
     <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="O">
-      <formula>NOT(ISERROR(SEARCH("O",T96)))</formula>
+      <formula>NOT(ISERROR(SEARCH("O",U99)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="C">
-      <formula>NOT(ISERROR(SEARCH("C",T96)))</formula>
+      <formula>NOT(ISERROR(SEARCH("C",U99)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W100">
+  <conditionalFormatting sqref="X2:X109">
     <cfRule type="expression" dxfId="0" priority="9">
-      <formula>W2&lt;&gt;V2</formula>
+      <formula>X2&lt;&gt;W2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F109">
+    <cfRule type="colorScale" priority="170">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:H109">
+    <cfRule type="colorScale" priority="172">
+      <colorScale>
+        <cfvo type="num" val="10"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -35836,7 +36519,7 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="10" operator="containsText" id="{AB48118A-1CFE-488B-B12E-453EA0CADD16}">
-            <xm:f>NOT(ISERROR(SEARCH("-",I2)))</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH("-",J2)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
               <fill>
@@ -35846,11 +36529,11 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>I2:T95 I96:S100</xm:sqref>
+          <xm:sqref>J99:T104 J2:U98</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="1" operator="containsText" id="{631B2A6D-16EC-488F-9A76-B8FF0576AF03}">
-            <xm:f>NOT(ISERROR(SEARCH("-",T96)))</xm:f>
+            <xm:f>NOT(ISERROR(SEARCH("-",U99)))</xm:f>
             <xm:f>"-"</xm:f>
             <x14:dxf>
               <fill>
@@ -35860,7 +36543,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>T96:T100</xm:sqref>
+          <xm:sqref>U99:U104</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/AssessmentSchedule_2627.xlsx
+++ b/AssessmentSchedule_2627.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1945" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4C1820A-80D9-40AB-88F9-12CD5884B830}"/>
+  <xr:revisionPtr revIDLastSave="1948" documentId="8_{F30C7968-F540-46E6-A81C-665FBDA0D3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14AF9E4B-1F3E-4DC1-A2BD-AABE582ADC75}"/>
   <bookViews>
     <workbookView xWindow="28702" yWindow="-98" windowWidth="26115" windowHeight="15675" activeTab="2" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="2" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2951" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2947" uniqueCount="416">
   <si>
     <t>Module Code</t>
   </si>
@@ -1403,7 +1403,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1535,23 +1535,11 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="134">
+  <dxfs count="114">
     <dxf>
       <fill>
         <patternFill>
@@ -1672,520 +1660,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -4061,6 +3535,335 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -9461,7 +9264,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B70" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="34">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -9910,54 +9713,54 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}" name="Table1" displayName="Table1" ref="A1:AL184" totalsRowShown="0" headerRowDxfId="133" dataDxfId="131" headerRowBorderDxfId="132" tableBorderDxfId="130" totalsRowBorderDxfId="129">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}" name="Table1" displayName="Table1" ref="A1:AL184" totalsRowShown="0" headerRowDxfId="91" dataDxfId="89" headerRowBorderDxfId="90" tableBorderDxfId="88" totalsRowBorderDxfId="87">
   <autoFilter ref="A1:AL184" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AI155">
     <sortCondition ref="A1:A155"/>
   </sortState>
   <tableColumns count="38">
-    <tableColumn id="1" xr3:uid="{7078548A-F011-4851-AB36-1F04238FA2FE}" name="Module Code" dataDxfId="128"/>
-    <tableColumn id="2" xr3:uid="{D2290F36-B8B3-427A-AEFE-45FD22901411}" name="Module Title" dataDxfId="127"/>
-    <tableColumn id="3" xr3:uid="{31165455-2AA3-4532-A0A0-C942837C0F79}" name="CA type" dataDxfId="126"/>
-    <tableColumn id="33" xr3:uid="{B83E0E3E-2B28-42F1-BC64-5D7177EC4229}" name="CA Weight" dataDxfId="125"/>
-    <tableColumn id="34" xr3:uid="{AEA2048C-138D-450A-BE52-3FCBDE03C67D}" name="Credits" dataDxfId="124"/>
-    <tableColumn id="30" xr3:uid="{82DD5B5B-C808-4E6E-849C-7A03DC6D0B69}" name="Description" dataDxfId="123"/>
-    <tableColumn id="36" xr3:uid="{A7BF30F6-C808-4B8F-B3FF-9FAF20E2145A}" name="Summative" dataDxfId="122"/>
-    <tableColumn id="37" xr3:uid="{68E504F9-116C-43AB-BCC6-3BB48B0860D2}" name="Day of Week" dataDxfId="121"/>
-    <tableColumn id="16" xr3:uid="{E6637FEB-7F23-45F0-99D2-96D20DD2DAEF}" name="Duration" dataDxfId="120"/>
-    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="119">
+    <tableColumn id="1" xr3:uid="{7078548A-F011-4851-AB36-1F04238FA2FE}" name="Module Code" dataDxfId="86"/>
+    <tableColumn id="2" xr3:uid="{D2290F36-B8B3-427A-AEFE-45FD22901411}" name="Module Title" dataDxfId="85"/>
+    <tableColumn id="3" xr3:uid="{31165455-2AA3-4532-A0A0-C942837C0F79}" name="CA type" dataDxfId="84"/>
+    <tableColumn id="33" xr3:uid="{B83E0E3E-2B28-42F1-BC64-5D7177EC4229}" name="CA Weight" dataDxfId="83"/>
+    <tableColumn id="34" xr3:uid="{AEA2048C-138D-450A-BE52-3FCBDE03C67D}" name="Credits" dataDxfId="82"/>
+    <tableColumn id="30" xr3:uid="{82DD5B5B-C808-4E6E-849C-7A03DC6D0B69}" name="Description" dataDxfId="81"/>
+    <tableColumn id="36" xr3:uid="{A7BF30F6-C808-4B8F-B3FF-9FAF20E2145A}" name="Summative" dataDxfId="80"/>
+    <tableColumn id="37" xr3:uid="{68E504F9-116C-43AB-BCC6-3BB48B0860D2}" name="Day of Week" dataDxfId="79"/>
+    <tableColumn id="16" xr3:uid="{E6637FEB-7F23-45F0-99D2-96D20DD2DAEF}" name="Duration" dataDxfId="78"/>
+    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="77">
       <calculatedColumnFormula>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="118"/>
-    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="117"/>
-    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="116"/>
-    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="115"/>
-    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="114"/>
-    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="113"/>
-    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="112"/>
-    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="111"/>
-    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="110"/>
-    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="109"/>
-    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="108"/>
-    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="107"/>
-    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="106"/>
-    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="105"/>
-    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="104"/>
-    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="103"/>
-    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="102"/>
-    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="101"/>
-    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="100"/>
-    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="99"/>
-    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="98"/>
-    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="97"/>
-    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="96"/>
-    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="95"/>
-    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="94"/>
-    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="93"/>
-    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="92">
+    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="76"/>
+    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="75"/>
+    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="74"/>
+    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="73"/>
+    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="72"/>
+    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="71"/>
+    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="70"/>
+    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="69"/>
+    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="68"/>
+    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="67"/>
+    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="66"/>
+    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="65"/>
+    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="64"/>
+    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="63"/>
+    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="62"/>
+    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="61"/>
+    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="60"/>
+    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="59"/>
+    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="58"/>
+    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="57"/>
+    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="56"/>
+    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="55"/>
+    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="54"/>
+    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="53"/>
+    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="52"/>
+    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="51"/>
+    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="50">
       <calculatedColumnFormula>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="91">
+    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="49">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9966,49 +9769,49 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="90" dataDxfId="88" headerRowBorderDxfId="89" tableBorderDxfId="87" totalsRowBorderDxfId="86">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47" tableBorderDxfId="45" totalsRowBorderDxfId="44">
   <autoFilter ref="A1:AE64" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD64">
     <sortCondition ref="A1:A132"/>
   </sortState>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="84"/>
-    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="83"/>
-    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="82">
+    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="41"/>
+    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="40">
       <calculatedColumnFormula>INDEX(Table2[Credits],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="81">
+    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="39">
       <calculatedColumnFormula>INDEX(Table2[Semester],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="80">
+    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="38">
       <calculatedColumnFormula>INDEX(Table2[Contact Time],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="79"/>
-    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="78"/>
-    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="77"/>
-    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="76"/>
-    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="75"/>
-    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="74"/>
-    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="73"/>
-    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="72"/>
-    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="71"/>
-    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="70"/>
-    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="69"/>
-    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="68"/>
-    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="67"/>
-    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="66"/>
-    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="65"/>
-    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="64"/>
-    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="63"/>
-    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="62"/>
-    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="61"/>
-    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="60"/>
-    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="59"/>
-    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="58"/>
-    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="57"/>
-    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="56"/>
-    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="55">
+    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="30"/>
+    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="29"/>
+    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="28"/>
+    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="27"/>
+    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="26"/>
+    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="25"/>
+    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="24"/>
+    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="23"/>
+    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="22"/>
+    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="21"/>
+    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="20"/>
+    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="19"/>
+    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="18"/>
+    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="17"/>
+    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="16"/>
+    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="15"/>
+    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="14"/>
+    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="13">
       <calculatedColumnFormula>SUM(Table14[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10017,38 +9820,38 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}" name="Table2" displayName="Table2" ref="A1:X109" totalsRowShown="0" headerRowDxfId="54" dataDxfId="52" headerRowBorderDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}" name="Table2" displayName="Table2" ref="A1:X109" totalsRowShown="0" headerRowDxfId="113" dataDxfId="111" headerRowBorderDxfId="112">
   <autoFilter ref="A1:X109" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B64">
     <sortCondition ref="A1:A64"/>
   </sortState>
   <tableColumns count="24">
-    <tableColumn id="1" xr3:uid="{A36A2B86-0F30-4188-9ECD-AE5BC71A59F4}" name="Module Code" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{D3F20037-EF35-4207-A530-484E1EB45719}" name="Module Title" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{40C22022-10B9-411F-9B76-B89140ABFFB2}" name="Alternative Module Code" dataDxfId="49"/>
-    <tableColumn id="13" xr3:uid="{CB12E405-1802-457C-AF17-F1B9CB3BBF13}" name="Source" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{EA737976-1AA7-49B6-8752-A388621554F4}" name="Semester" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{16DFC84F-5858-467D-B447-49992D721E4B}" name="Level" dataDxfId="46"/>
-    <tableColumn id="5" xr3:uid="{A17BC4BA-A3CB-442D-9BDC-D3B41B98B389}" name="Credits" dataDxfId="45"/>
-    <tableColumn id="24" xr3:uid="{597B34DA-41F4-4D1D-AA24-07FF8D78D4D2}" name="Parent" dataDxfId="13"/>
-    <tableColumn id="19" xr3:uid="{98846C13-E462-4CFF-858E-AF75931B6712}" name="AllUG" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{7E25B4F4-1A7D-48D9-AAA2-AF5C97240797}" name="Physics" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{A36A2B86-0F30-4188-9ECD-AE5BC71A59F4}" name="Module Code" dataDxfId="110"/>
+    <tableColumn id="2" xr3:uid="{D3F20037-EF35-4207-A530-484E1EB45719}" name="Module Title" dataDxfId="109"/>
+    <tableColumn id="9" xr3:uid="{40C22022-10B9-411F-9B76-B89140ABFFB2}" name="Alternative Module Code" dataDxfId="108"/>
+    <tableColumn id="13" xr3:uid="{CB12E405-1802-457C-AF17-F1B9CB3BBF13}" name="Source" dataDxfId="107"/>
+    <tableColumn id="8" xr3:uid="{EA737976-1AA7-49B6-8752-A388621554F4}" name="Semester" dataDxfId="106"/>
+    <tableColumn id="6" xr3:uid="{16DFC84F-5858-467D-B447-49992D721E4B}" name="Level" dataDxfId="105"/>
+    <tableColumn id="5" xr3:uid="{A17BC4BA-A3CB-442D-9BDC-D3B41B98B389}" name="Credits" dataDxfId="104"/>
+    <tableColumn id="24" xr3:uid="{597B34DA-41F4-4D1D-AA24-07FF8D78D4D2}" name="Parent" dataDxfId="103"/>
+    <tableColumn id="19" xr3:uid="{98846C13-E462-4CFF-858E-AF75931B6712}" name="AllUG" dataDxfId="102"/>
+    <tableColumn id="3" xr3:uid="{7E25B4F4-1A7D-48D9-AAA2-AF5C97240797}" name="Physics" dataDxfId="101"/>
     <tableColumn id="17" xr3:uid="{AA3AE96F-2651-49D7-89AD-BA94806438AE}" name="PhysAstro"/>
-    <tableColumn id="4" xr3:uid="{9C7DD469-E550-411F-8467-246A1543FB38}" name="Astro" dataDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{3C5D3AEB-487E-4678-A42F-BE4BA4D0E9AA}" name="MedPhys" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{9C7DD469-E550-411F-8467-246A1543FB38}" name="Astro" dataDxfId="100"/>
+    <tableColumn id="7" xr3:uid="{3C5D3AEB-487E-4678-A42F-BE4BA4D0E9AA}" name="MedPhys" dataDxfId="99"/>
     <tableColumn id="20" xr3:uid="{C3673B06-C0A2-44F6-8978-F392282CECF8}" name="AllPG"/>
-    <tableColumn id="14" xr3:uid="{AE552873-9B31-41A6-B73C-D052477CA74C}" name="MScPhysics" dataDxfId="40"/>
-    <tableColumn id="15" xr3:uid="{8F51CE76-3A29-487A-A13C-FB63C79CF3E6}" name="MScAstro" dataDxfId="39"/>
-    <tableColumn id="21" xr3:uid="{FC74E264-78AB-4682-A1B8-D8964ED1C3F3}" name="MScDataPhys" dataDxfId="38"/>
-    <tableColumn id="22" xr3:uid="{2D5776F7-D7F7-4D20-A7CB-DB57997AD074}" name="MScDataAstro" dataDxfId="37"/>
+    <tableColumn id="14" xr3:uid="{AE552873-9B31-41A6-B73C-D052477CA74C}" name="MScPhysics" dataDxfId="98"/>
+    <tableColumn id="15" xr3:uid="{8F51CE76-3A29-487A-A13C-FB63C79CF3E6}" name="MScAstro" dataDxfId="97"/>
+    <tableColumn id="21" xr3:uid="{FC74E264-78AB-4682-A1B8-D8964ED1C3F3}" name="MScDataPhys" dataDxfId="96"/>
+    <tableColumn id="22" xr3:uid="{2D5776F7-D7F7-4D20-A7CB-DB57997AD074}" name="MScDataAstro" dataDxfId="95"/>
     <tableColumn id="18" xr3:uid="{10668F71-1EDF-482E-86A5-46E1F3C15120}" name="MScCSPhysics"/>
     <tableColumn id="23" xr3:uid="{E837FCBC-49C7-45CE-AFAA-4F01143EF2A8}" name="CDTCSPhysics"/>
     <tableColumn id="16" xr3:uid="{DB790F5F-BEF0-41CE-A68A-1AA9DF83D66B}" name="Contact Time"/>
-    <tableColumn id="10" xr3:uid="{60774AFA-B365-4EB5-AAFF-6235868F8C97}" name="Exam Weight (%)" dataDxfId="36"/>
-    <tableColumn id="12" xr3:uid="{537B7C75-E9C0-42F2-9F3C-6E960AB2D257}" name="CA weight" dataDxfId="35">
+    <tableColumn id="10" xr3:uid="{60774AFA-B365-4EB5-AAFF-6235868F8C97}" name="Exam Weight (%)" dataDxfId="94"/>
+    <tableColumn id="12" xr3:uid="{537B7C75-E9C0-42F2-9F3C-6E960AB2D257}" name="CA weight" dataDxfId="93">
       <calculatedColumnFormula>100-Table2[[#This Row],[Exam Weight (%)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{75DA2527-5A08-4ECE-B4E4-752A8F8BF059}" name="CA Check" dataDxfId="34">
+    <tableColumn id="11" xr3:uid="{75DA2527-5A08-4ECE-B4E4-752A8F8BF059}" name="CA Check" dataDxfId="92">
       <calculatedColumnFormula>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -10374,21 +10177,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66039B40-29AD-4D93-B125-EAF72A7B3996}">
   <dimension ref="A1:AL184"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.796875" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10" style="10" customWidth="1"/>
-    <col min="6" max="6" width="21.7265625" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="21.7265625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="10.7265625" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.7265625" style="10" customWidth="1"/>
-    <col min="12" max="23" width="9.1796875" style="14" customWidth="1"/>
-    <col min="24" max="36" width="9.1796875" style="16" customWidth="1"/>
+    <col min="6" max="6" width="21.73046875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="21.73046875" style="10" customWidth="1"/>
+    <col min="9" max="9" width="10.73046875" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.73046875" style="10" customWidth="1"/>
+    <col min="12" max="23" width="9.19921875" style="14" customWidth="1"/>
+    <col min="24" max="36" width="9.19921875" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="44" customFormat="1" ht="29">
+    <row r="1" spans="1:38" s="44" customFormat="1" ht="28.5">
       <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
@@ -10802,7 +10605,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="28">
+    <row r="6" spans="1:38" ht="27">
       <c r="A6" s="4" t="s">
         <v>252</v>
       </c>
@@ -11383,7 +11186,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="28">
+    <row r="13" spans="1:38" ht="27">
       <c r="A13" s="3" t="s">
         <v>81</v>
       </c>
@@ -12159,7 +11962,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:38" ht="28">
+    <row r="23" spans="1:38" ht="27">
       <c r="A23" s="4" t="s">
         <v>37</v>
       </c>
@@ -12956,7 +12759,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:38" ht="28">
+    <row r="33" spans="1:38" ht="27">
       <c r="A33" s="4" t="s">
         <v>44</v>
       </c>
@@ -13493,7 +13296,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:38" ht="28">
+    <row r="40" spans="1:38" ht="27">
       <c r="A40" s="4" t="s">
         <v>49</v>
       </c>
@@ -14909,7 +14712,7 @@
         <v>12.000000000000004</v>
       </c>
     </row>
-    <row r="58" spans="1:38" ht="28">
+    <row r="58" spans="1:38" ht="27">
       <c r="A58" s="3" t="s">
         <v>186</v>
       </c>
@@ -14988,7 +14791,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:38" ht="28">
+    <row r="59" spans="1:38" ht="27">
       <c r="A59" s="3" t="s">
         <v>186</v>
       </c>
@@ -15902,7 +15705,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="71" spans="1:38" ht="28">
+    <row r="71" spans="1:38" ht="27">
       <c r="A71" s="4" t="s">
         <v>1</v>
       </c>
@@ -16046,7 +15849,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="1:38" ht="28">
+    <row r="73" spans="1:38" ht="27">
       <c r="A73" s="4" t="s">
         <v>248</v>
       </c>
@@ -17123,7 +16926,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:38" ht="28">
+    <row r="87" spans="1:38" ht="27">
       <c r="A87" s="4" t="s">
         <v>16</v>
       </c>
@@ -17287,7 +17090,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:38" ht="28">
+    <row r="89" spans="1:38" ht="27">
       <c r="A89" s="4" t="s">
         <v>18</v>
       </c>
@@ -17366,7 +17169,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:38" ht="28">
+    <row r="90" spans="1:38" ht="27">
       <c r="A90" s="4" t="s">
         <v>18</v>
       </c>
@@ -17960,7 +17763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:38" ht="28">
+    <row r="98" spans="1:38" ht="27">
       <c r="A98" s="3" t="s">
         <v>106</v>
       </c>
@@ -18250,7 +18053,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="102" spans="1:38" ht="28">
+    <row r="102" spans="1:38" ht="27">
       <c r="A102" s="3" t="s">
         <v>108</v>
       </c>
@@ -19390,7 +19193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="117" spans="1:38" ht="28">
+    <row r="117" spans="1:38" ht="27">
       <c r="A117" s="4" t="s">
         <v>61</v>
       </c>
@@ -19765,7 +19568,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:38" ht="28">
+    <row r="122" spans="1:38" ht="27">
       <c r="A122" s="4" t="s">
         <v>63</v>
       </c>
@@ -19838,7 +19641,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="123" spans="1:38" ht="28">
+    <row r="123" spans="1:38" ht="27">
       <c r="A123" s="4" t="s">
         <v>66</v>
       </c>
@@ -20300,7 +20103,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="129" spans="1:38" ht="28">
+    <row r="129" spans="1:38" ht="27">
       <c r="A129" s="4" t="s">
         <v>71</v>
       </c>
@@ -20610,7 +20413,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="133" spans="1:38" ht="28">
+    <row r="133" spans="1:38" ht="27">
       <c r="A133" s="3" t="s">
         <v>192</v>
       </c>
@@ -20843,7 +20646,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="1:38" ht="28">
+    <row r="136" spans="1:38" ht="27">
       <c r="A136" s="3" t="s">
         <v>193</v>
       </c>
@@ -20924,7 +20727,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="137" spans="1:38" ht="28">
+    <row r="137" spans="1:38" ht="27">
       <c r="A137" s="3" t="s">
         <v>193</v>
       </c>
@@ -21220,7 +21023,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="141" spans="1:38" ht="28">
+    <row r="141" spans="1:38" ht="27">
       <c r="A141" s="3" t="s">
         <v>239</v>
       </c>
@@ -21388,7 +21191,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="143" spans="1:38" ht="28">
+    <row r="143" spans="1:38" ht="27">
       <c r="A143" s="3" t="s">
         <v>116</v>
       </c>
@@ -21467,7 +21270,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="144" spans="1:38" ht="28">
+    <row r="144" spans="1:38" ht="27">
       <c r="A144" s="3" t="s">
         <v>116</v>
       </c>
@@ -24522,16 +24325,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0482654D-1732-43E5-85EC-021407B07CE5}">
   <dimension ref="A1:AE141"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.796875" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10" style="10" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" style="10" customWidth="1"/>
-    <col min="7" max="15" width="16.26953125" style="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="17.26953125" style="14" bestFit="1" customWidth="1"/>
-    <col min="19" max="30" width="8.7265625" style="16"/>
+    <col min="6" max="6" width="10.73046875" style="10" customWidth="1"/>
+    <col min="7" max="15" width="16.265625" style="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="17.265625" style="14" bestFit="1" customWidth="1"/>
+    <col min="19" max="30" width="8.73046875" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -30672,14 +30475,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D548CE7-BEAC-43FA-847F-FDE82E3A5926}">
   <dimension ref="A1:X133"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="66.81640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.26953125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="7.81640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="10.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.796875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.265625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="7.796875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="10.73046875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.265625" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="9" style="5" customWidth="1"/>
   </cols>
@@ -32223,9 +32026,6 @@
       <c r="L30" t="s">
         <v>407</v>
       </c>
-      <c r="M30" t="s">
-        <v>144</v>
-      </c>
       <c r="U30">
         <v>2</v>
       </c>
@@ -32665,9 +32465,6 @@
       <c r="K38" t="s">
         <v>144</v>
       </c>
-      <c r="L38" t="s">
-        <v>144</v>
-      </c>
       <c r="M38" t="s">
         <v>144</v>
       </c>
@@ -32716,12 +32513,6 @@
         <v>144</v>
       </c>
       <c r="K39" t="s">
-        <v>144</v>
-      </c>
-      <c r="L39" t="s">
-        <v>144</v>
-      </c>
-      <c r="M39" t="s">
         <v>144</v>
       </c>
       <c r="U39">
@@ -33066,13 +32857,13 @@
       </c>
     </row>
     <row r="46" spans="1:24">
-      <c r="A46" s="47" t="s">
+      <c r="A46" s="3" t="s">
         <v>395</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="C46" s="47"/>
+      <c r="C46" s="3"/>
       <c r="D46" s="28" t="s">
         <v>180</v>
       </c>
@@ -33089,38 +32880,32 @@
         <v>47</v>
       </c>
       <c r="I46" s="28"/>
-      <c r="J46" s="50"/>
-      <c r="L46" s="50" t="s">
+      <c r="L46" t="s">
         <v>143</v>
       </c>
-      <c r="M46" s="50"/>
-      <c r="O46" s="50"/>
-      <c r="P46" s="50"/>
-      <c r="Q46" s="50"/>
-      <c r="R46" s="50"/>
       <c r="U46">
         <v>0.5</v>
       </c>
       <c r="V46">
         <v>0</v>
       </c>
-      <c r="W46" s="51">
+      <c r="W46">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X46" s="51">
+      <c r="X46">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:24">
-      <c r="A47" s="47" t="s">
+      <c r="A47" s="3" t="s">
         <v>396</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="C47" s="47"/>
+      <c r="C47" s="3"/>
       <c r="D47" s="28" t="s">
         <v>180</v>
       </c>
@@ -33137,26 +32922,20 @@
         <v>47</v>
       </c>
       <c r="I47" s="28"/>
-      <c r="J47" s="50"/>
-      <c r="L47" s="50"/>
-      <c r="M47" s="50" t="s">
+      <c r="M47" t="s">
         <v>143</v>
       </c>
-      <c r="O47" s="50"/>
-      <c r="P47" s="50"/>
-      <c r="Q47" s="50"/>
-      <c r="R47" s="50"/>
       <c r="U47">
         <v>0.5</v>
       </c>
       <c r="V47">
         <v>0</v>
       </c>
-      <c r="W47" s="51">
+      <c r="W47">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X47" s="51">
+      <c r="X47">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
@@ -34152,16 +33931,15 @@
         <v>74</v>
       </c>
       <c r="I65" s="28"/>
-      <c r="J65" s="50"/>
       <c r="L65" t="s">
         <v>143</v>
       </c>
-      <c r="M65" s="52"/>
+      <c r="M65" s="6"/>
       <c r="N65" s="6"/>
-      <c r="O65" s="52"/>
-      <c r="P65" s="52"/>
-      <c r="Q65" s="52"/>
-      <c r="R65" s="52"/>
+      <c r="O65" s="6"/>
+      <c r="P65" s="6"/>
+      <c r="Q65" s="6"/>
+      <c r="R65" s="6"/>
       <c r="S65" s="6"/>
       <c r="T65" s="6"/>
       <c r="U65" s="6">
@@ -34170,11 +33948,11 @@
       <c r="V65">
         <v>25</v>
       </c>
-      <c r="W65" s="51">
+      <c r="W65">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>75</v>
       </c>
-      <c r="X65" s="51">
+      <c r="X65">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
@@ -36131,187 +35909,139 @@
       </c>
     </row>
     <row r="104" spans="1:24">
-      <c r="A104" s="47" t="s">
+      <c r="A104" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="B104" s="47" t="s">
+      <c r="B104" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C104" s="47"/>
+      <c r="C104" s="3"/>
       <c r="D104" s="28"/>
-      <c r="E104" s="47"/>
-      <c r="F104" s="48"/>
-      <c r="G104" s="49"/>
-      <c r="H104" s="49"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="28"/>
+      <c r="H104" s="28"/>
       <c r="I104" s="28"/>
-      <c r="J104" s="50"/>
-      <c r="L104" s="50"/>
-      <c r="M104" s="50"/>
-      <c r="O104" s="50"/>
-      <c r="P104" s="50"/>
-      <c r="Q104" s="50"/>
-      <c r="R104" s="50"/>
-      <c r="V104" s="50"/>
-      <c r="W104" s="51">
+      <c r="W104">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X104" s="51">
+      <c r="X104">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:24">
-      <c r="A105" s="47" t="s">
+      <c r="A105" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="B105" s="47" t="s">
+      <c r="B105" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="C105" s="47"/>
+      <c r="C105" s="3"/>
       <c r="D105" s="28"/>
-      <c r="E105" s="47"/>
-      <c r="F105" s="48"/>
-      <c r="G105" s="49"/>
-      <c r="H105" s="49"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="28"/>
+      <c r="H105" s="28"/>
       <c r="I105" s="28"/>
-      <c r="J105" s="50"/>
-      <c r="L105" s="50"/>
-      <c r="M105" s="50"/>
-      <c r="O105" s="50"/>
-      <c r="P105" s="50"/>
-      <c r="Q105" s="50"/>
-      <c r="R105" s="50"/>
-      <c r="V105" s="50"/>
-      <c r="W105" s="51">
+      <c r="W105">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X105" s="51">
+      <c r="X105">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:24">
-      <c r="A106" s="47" t="s">
+      <c r="A106" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="B106" s="47" t="s">
+      <c r="B106" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="C106" s="47"/>
+      <c r="C106" s="3"/>
       <c r="D106" s="28"/>
-      <c r="E106" s="47"/>
-      <c r="F106" s="48"/>
-      <c r="G106" s="49"/>
-      <c r="H106" s="49"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="28"/>
+      <c r="H106" s="28"/>
       <c r="I106" s="28"/>
-      <c r="J106" s="50"/>
-      <c r="L106" s="50"/>
-      <c r="M106" s="50"/>
-      <c r="O106" s="50"/>
-      <c r="P106" s="50"/>
-      <c r="Q106" s="50"/>
-      <c r="R106" s="50"/>
-      <c r="V106" s="50"/>
-      <c r="W106" s="51">
+      <c r="W106">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X106" s="51">
+      <c r="X106">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:24">
-      <c r="A107" s="47" t="s">
+      <c r="A107" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="B107" s="47" t="s">
+      <c r="B107" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C107" s="47"/>
+      <c r="C107" s="3"/>
       <c r="D107" s="28"/>
-      <c r="E107" s="47"/>
-      <c r="F107" s="48"/>
-      <c r="G107" s="49"/>
-      <c r="H107" s="49"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="28"/>
+      <c r="H107" s="28"/>
       <c r="I107" s="28"/>
-      <c r="J107" s="50"/>
-      <c r="L107" s="50"/>
-      <c r="M107" s="50"/>
-      <c r="O107" s="50"/>
-      <c r="P107" s="50"/>
-      <c r="Q107" s="50"/>
-      <c r="R107" s="50"/>
-      <c r="V107" s="50"/>
-      <c r="W107" s="51">
+      <c r="W107">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X107" s="51">
+      <c r="X107">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:24">
-      <c r="A108" s="47" t="s">
+      <c r="A108" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="B108" s="47" t="s">
+      <c r="B108" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="C108" s="47"/>
+      <c r="C108" s="3"/>
       <c r="D108" s="28"/>
-      <c r="E108" s="47"/>
-      <c r="F108" s="48"/>
-      <c r="G108" s="49"/>
-      <c r="H108" s="49"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="28"/>
+      <c r="H108" s="28"/>
       <c r="I108" s="28"/>
-      <c r="J108" s="50"/>
-      <c r="L108" s="50"/>
-      <c r="M108" s="50"/>
-      <c r="O108" s="50"/>
-      <c r="P108" s="50"/>
-      <c r="Q108" s="50"/>
-      <c r="R108" s="50"/>
-      <c r="V108" s="50"/>
-      <c r="W108" s="51">
+      <c r="W108">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X108" s="51">
+      <c r="X108">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:24">
-      <c r="A109" s="47" t="s">
+      <c r="A109" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="B109" s="47" t="s">
+      <c r="B109" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="C109" s="47"/>
+      <c r="C109" s="3"/>
       <c r="D109" s="28"/>
-      <c r="E109" s="47"/>
-      <c r="F109" s="48"/>
-      <c r="G109" s="49"/>
-      <c r="H109" s="49"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="28"/>
+      <c r="H109" s="28"/>
       <c r="I109" s="28"/>
-      <c r="J109" s="50"/>
-      <c r="L109" s="50"/>
-      <c r="M109" s="50"/>
-      <c r="O109" s="50"/>
-      <c r="P109" s="50"/>
-      <c r="Q109" s="50"/>
-      <c r="R109" s="50"/>
-      <c r="V109" s="50"/>
-      <c r="W109" s="51">
+      <c r="W109">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X109" s="51">
+      <c r="X109">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
@@ -36444,6 +36174,16 @@
       <formula>NOT(ISERROR(SEARCH("SEM1",E99)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F109">
+    <cfRule type="colorScale" priority="170">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFEF9C"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F99:F104">
     <cfRule type="colorScale" priority="7">
       <colorScale>
@@ -36451,6 +36191,18 @@
         <cfvo type="max"/>
         <color rgb="FFFFEF9C"/>
         <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:H109">
+    <cfRule type="colorScale" priority="172">
+      <colorScale>
+        <cfvo type="num" val="10"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -36466,7 +36218,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I99:T104 I2:U98">
+  <conditionalFormatting sqref="I2:U98 I99:T104">
     <cfRule type="containsText" dxfId="6" priority="16" operator="containsText" text="O">
       <formula>NOT(ISERROR(SEARCH("O",I2)))</formula>
     </cfRule>
@@ -36485,28 +36237,6 @@
   <conditionalFormatting sqref="X2:X109">
     <cfRule type="expression" dxfId="0" priority="9">
       <formula>X2&lt;&gt;W2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F109">
-    <cfRule type="colorScale" priority="170">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFFEF9C"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:H109">
-    <cfRule type="colorScale" priority="172">
-      <colorScale>
-        <cfvo type="num" val="10"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36529,7 +36259,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>J99:T104 J2:U98</xm:sqref>
+          <xm:sqref>J2:U98 J99:T104</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="1" operator="containsText" id="{631B2A6D-16EC-488F-9A76-B8FF0576AF03}">
@@ -36554,11 +36284,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4F541C-C22C-46EF-BD21-4F8C93ABA5A9}">
   <dimension ref="A3:F70"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.54296875" customWidth="1"/>
+    <col min="1" max="1" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.53125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:6">
